--- a/Result/checksun_type/玻_碳纖.xlsx
+++ b/Result/checksun_type/玻_碳纖.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-6.4</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2237.086</t>
+          <t>1998.479</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>15.49</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>6.83</t>
+          <t>6.10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,72 +1009,72 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2237</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>40.74</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>80.25</t>
+          <t>50.62</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>121.3</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>119.4</t>
+          <t>119.62</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>119.79</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>121.73</t>
+          <t>121.95</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>506.78</t>
+          <t>20.33</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-99.11</t>
+          <t>-99.06</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>407343962.3748191</t>
+          <t>407263703.2695087</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>274537160.0</t>
+          <t>234536441.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>468607130.0</t>
+          <t>453352594.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>405744996.9</t>
+          <t>414675114.7</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>496122034.34</t>
+          <t>478603045.96</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>62862133</t>
+          <t>38677479</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-7654354.113187951</t>
+          <t>-4899574.583967528</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>28846938.09</v>
+        <v>10251712.83</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>21.21</t>
+          <t>17.17</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1182,37 +1182,37 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>3.304677259170958</t>
+          <t>-4.012262137013166</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-13.63624517069042</t>
+          <t>-1.72716244973935</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>3.993839757333741</t>
+          <t>4.777195903551031</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>94.49</t>
+          <t>91.34</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>48.79</t>
+          <t>46.96</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>12873</t>
+          <t>12444</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>118.5</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>115.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>-6.4</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4742.281</t>
+          <t>2237.086</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-6.67</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>39.36</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>11.30</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14.48</t>
+          <t>6.83</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2237</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>40.74</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>70.67</t>
+          <t>80.25</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>6.49</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>120.2</t>
+          <t>121.3</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>119.4</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>120.2</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>121.48</t>
+          <t>121.73</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>3038.57</t>
+          <t>506.78</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-100.24</t>
+          <t>-99.11</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>407343962.3748191</t>
+          <t>407263703.2695087</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>602848357.0</t>
+          <t>274537160.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>558871972.6</t>
+          <t>468607130.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>401037331.1</t>
+          <t>405744996.9</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>530097463.36</t>
+          <t>496122034.34</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>157834641</t>
+          <t>62862133</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-14290952.69601668</t>
+          <t>-7654354.113187951</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>50095506.5</v>
+        <v>28846938.09</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>29.29</t>
+          <t>21.21</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1613,37 +1613,37 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>3.304677259170958</t>
+          <t>-4.012262137013166</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-13.63624517069042</t>
+          <t>-1.72716244973935</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>3.993839757333741</t>
+          <t>4.777195903551031</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>94.49</t>
+          <t>91.34</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>48.79</t>
+          <t>46.96</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>12873</t>
+          <t>12444</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>8162.419</t>
+          <t>4742.281</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-6.25</t>
+          <t>-10.34</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>39.69</t>
+          <t>39.36</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>10.87</t>
+          <t>11.30</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>24.92</t>
+          <t>14.48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1871,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2237</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1886,62 +1886,62 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>38.67</t>
+          <t>70.67</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>6.49</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>120.2</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>118.2</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>120.52</t>
+          <t>120.2</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>121.12</t>
+          <t>121.48</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>164.26</t>
+          <t>3038.57</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-102.05</t>
+          <t>-100.24</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>407343962.3748191</t>
+          <t>407263703.2695087</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1025439175.0</t>
+          <t>602848357.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>504875555.4</t>
+          <t>558871972.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>361436106.5</t>
+          <t>401037331.1</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>536684043.66</t>
+          <t>530097463.36</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>143439448</t>
+          <t>157834641</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-25997581.64151972</t>
+          <t>-14290952.69601668</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>43485279.32</v>
+        <v>50095506.5</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>29.29</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2044,27 +2044,27 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>3.304677259170958</t>
+          <t>-4.012262137013166</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-13.63624517069042</t>
+          <t>-1.72716244973935</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>3.993839757333741</t>
+          <t>4.777195903551031</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>94.49</t>
+          <t>91.34</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>48.79</t>
+          <t>46.96</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>12873</t>
+          <t>12444</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>124.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1122.329</t>
+          <t>8162.419</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,84 +2186,84 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>127.5</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-9.91</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-0.18</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>39.69</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-09-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>124.5</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>131.5</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
           <t>116.0</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>3.33</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>-1.69</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>22.56</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-09-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>124.5</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>115.0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>131.5</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>116.0</t>
-        </is>
-      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>0</t>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>10.87</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>24.92</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2237</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>38.67</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>118.7</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>117.48</t>
+          <t>118.2</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>120.59</t>
+          <t>120.52</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>120.77</t>
+          <t>121.12</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-89.81</t>
+          <t>164.26</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-102.89</t>
+          <t>-102.05</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>407343962.3748191</t>
+          <t>407263703.2695087</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>129401839.0</t>
+          <t>1025439175.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>335984992.8</t>
+          <t>504875555.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>274141955.5</t>
+          <t>361436106.5</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>533459215.28</t>
+          <t>536684043.66</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>61843037</t>
+          <t>143439448</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-38630829.0899126</t>
+          <t>-25997581.64151972</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-12788535.69</v>
+        <v>43485279.32</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>17.17</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2475,37 +2475,37 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>3.304677259170958</t>
+          <t>-4.012262137013166</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-13.63624517069042</t>
+          <t>-1.72716244973935</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>3.993839757333741</t>
+          <t>4.777195903551031</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>94.49</t>
+          <t>91.34</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>48.79</t>
+          <t>46.96</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>12873</t>
+          <t>12444</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>115.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2764.556</t>
+          <t>1122.329</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,72 +2617,72 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>116.0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-0.18</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>22.56</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-09-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>124.5</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
           <t>115.0</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>4.17</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>-1.69</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>33.12</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-09-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>124.5</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>115.0</t>
-        </is>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -2697,12 +2697,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>-7.63</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>8.44</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>6.61</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,47 +2733,47 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2237</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>34.67</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>118.7</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -2783,27 +2783,27 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>120.88</t>
+          <t>120.59</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>120.53</t>
+          <t>120.77</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-40.51</t>
+          <t>-89.81</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-102.24</t>
+          <t>-102.89</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,45 +2823,45 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>407343962.3748191</t>
+          <t>407263703.2695087</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>310809119.0</t>
+          <t>129401839.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>375997635.0</t>
+          <t>335984992.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>282457551.4</t>
+          <t>274141955.5</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>556111164.18</t>
+          <t>533459215.28</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>93540083</t>
+          <t>61843037</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-43329427.88925355</t>
+          <t>-38630829.0899126</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>3281033.7</v>
+        <v>-12788535.69</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>16.16</t>
+          <t>17.17</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2906,37 +2906,37 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>3.304677259170958</t>
+          <t>-4.012262137013166</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-13.63624517069042</t>
+          <t>-1.72716244973935</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>3.993839757333741</t>
+          <t>4.777195903551031</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>94.49</t>
+          <t>91.34</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>48.79</t>
+          <t>46.96</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>12873</t>
+          <t>12444</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>115.0</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
+          <t>116.5</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>114.0</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
           <t>116.0</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>107.0</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>115.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-10.12</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6206.994</t>
+          <t>2764.556</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>114.5</t>
+          <t>115.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>20.66</t>
+          <t>33.12</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-8.03</t>
+          <t>-7.63</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>8.44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-8.30</t>
+          <t>6.61</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2237</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>34.67</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-5.61</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>121.3</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>118.02</t>
+          <t>117.48</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>121.33</t>
+          <t>120.88</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>120.34</t>
+          <t>120.53</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>141.22</t>
+          <t>-40.51</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-102.02</t>
+          <t>-102.24</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>407343962.3748191</t>
+          <t>407263703.2695087</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>725861373.0</t>
+          <t>310809119.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>342882863.8</t>
+          <t>375997635.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>284169034.6</t>
+          <t>282457551.4</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>580170679.38</t>
+          <t>556111164.18</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>58713829</t>
+          <t>93540083</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-51804057.26877595</t>
+          <t>-43329427.88925355</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>6683887.34</v>
+        <v>3281033.7</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>15.66</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3337,37 +3337,37 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>3.304677259170958</t>
+          <t>-4.012262137013166</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-13.63624517069042</t>
+          <t>-1.72716244973935</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>3.993839757333741</t>
+          <t>4.777195903551031</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>94.49</t>
+          <t>91.34</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>48.79</t>
+          <t>46.96</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>12873</t>
+          <t>12444</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>114.5</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>114.5</t>
+          <t>115.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>-10.12</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2671.658</t>
+          <t>6206.994</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>114.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>20.66</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>-8.03</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>-8.30</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2237</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>79.63</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>-5.61</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>123.3</t>
+          <t>121.3</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>118.8</t>
+          <t>118.02</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>121.87</t>
+          <t>121.33</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>120.15</t>
+          <t>120.34</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>333.84</t>
+          <t>141.22</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-102.73</t>
+          <t>-102.02</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>407343962.3748191</t>
+          <t>407263703.2695087</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>332866271.0</t>
+          <t>725861373.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>243202689.6</t>
+          <t>342882863.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>228452558.7</t>
+          <t>284169034.6</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>663144032.96</t>
+          <t>580170679.38</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>14750130</t>
+          <t>58713829</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-62438229.01579697</t>
+          <t>-51804057.26877595</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-33163487.79</v>
+        <v>6683887.34</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>28.28</t>
+          <t>15.66</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3768,37 +3768,37 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>3.304677259170958</t>
+          <t>-4.012262137013166</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-13.63624517069042</t>
+          <t>-1.72716244973935</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>3.993839757333741</t>
+          <t>4.777195903551031</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>94.49</t>
+          <t>91.34</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>48.79</t>
+          <t>46.96</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>12873</t>
+          <t>12444</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>114.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>114.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1518.372</t>
+          <t>2671.658</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-9.48</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3990,12 +3990,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>5.22</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2237</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>61.11</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>70.54</t>
+          <t>79.63</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>122.2</t>
+          <t>123.3</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>118.98</t>
+          <t>118.8</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>122.3</t>
+          <t>121.87</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>119.69</t>
+          <t>120.15</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>129.29</t>
+          <t>333.84</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-105.00</t>
+          <t>-102.73</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>407343962.3748191</t>
+          <t>407263703.2695087</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>180986362.0</t>
+          <t>332866271.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>217996657.6</t>
+          <t>243202689.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>218528992.0</t>
+          <t>228452558.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>721943048.64</t>
+          <t>663144032.96</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-532334</t>
+          <t>14750130</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-67760909.23843847</t>
+          <t>-62438229.01579697</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-46797281.06</v>
+        <v>-33163487.79</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>28.28</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4199,37 +4199,37 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>3.304677259170958</t>
+          <t>-4.012262137013166</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-13.63624517069042</t>
+          <t>-1.72716244973935</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>3.993839757333741</t>
+          <t>4.777195903551031</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>94.49</t>
+          <t>91.34</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>48.79</t>
+          <t>46.96</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>12873</t>
+          <t>12444</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2659.342</t>
+          <t>1518.372</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4421,12 +4421,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>5.22</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2237</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>61.11</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>70.54</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>121.7</t>
+          <t>122.2</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>119.3</t>
+          <t>118.98</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>122.58</t>
+          <t>122.3</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>119.25</t>
+          <t>119.69</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>113.38</t>
+          <t>129.29</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-106.62</t>
+          <t>-105.00</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>407343962.3748191</t>
+          <t>407263703.2695087</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>329465050.0</t>
+          <t>180986362.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>212298918.2</t>
+          <t>217996657.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>218106553.5</t>
+          <t>218528992.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>737772671.58</t>
+          <t>721943048.64</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-5807635</t>
+          <t>-532334</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-71572477.99861823</t>
+          <t>-67760909.23843847</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-48329949.72</v>
+        <v>-46797281.06</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>23.74</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4630,22 +4630,22 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>3.304677259170958</t>
+          <t>-4.012262137013166</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-13.63624517069042</t>
+          <t>-1.72716244973935</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>3.993839757333741</t>
+          <t>4.777195903551031</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>94.49</t>
+          <t>91.34</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>48.79</t>
+          <t>46.96</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>12873</t>
+          <t>12444</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>119.5</t>
+          <t>116.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1192.575</t>
+          <t>2659.342</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>-5.6</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4852,12 +4852,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>5.65</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>8.12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2237</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>72.73</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>121.7</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>119.45</t>
+          <t>119.3</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>122.59</t>
+          <t>122.58</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>118.7</t>
+          <t>119.25</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>84.77</t>
+          <t>113.38</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-108.49</t>
+          <t>-106.62</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>407343962.3748191</t>
+          <t>407263703.2695087</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>145235263.0</t>
+          <t>329465050.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>188917467.8</t>
+          <t>212298918.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>195309352.7</t>
+          <t>218106553.5</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>743700361.3</t>
+          <t>737772671.58</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-6391884</t>
+          <t>-5807635</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-75798392.23084499</t>
+          <t>-71572477.99861823</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-64701837.61</v>
+        <v>-48329949.72</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>23.74</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5061,22 +5061,22 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>3.304677259170958</t>
+          <t>-4.012262137013166</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-13.63624517069042</t>
+          <t>-1.72716244973935</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>3.993839757333741</t>
+          <t>4.777195903551031</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>94.49</t>
+          <t>91.34</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>48.79</t>
+          <t>46.96</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>12873</t>
+          <t>12444</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>119.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1846.547</t>
+          <t>1192.575</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,74 +5203,74 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>121.5</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-4.74</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-0.18</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-3.27</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-09-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>124.5</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-3.75</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-1.69</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>13.60</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-09-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
         <is>
           <t>124.5</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>115.0</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>124.5</t>
-        </is>
-      </c>
       <c r="T12" t="inlineStr">
         <is>
           <t>131.5</t>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>5.65</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2237</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>72.73</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>121.1</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>119.78</t>
+          <t>119.45</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>122.66</t>
+          <t>122.59</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>118.08</t>
+          <t>118.7</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>69.84</t>
+          <t>84.77</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-110.29</t>
+          <t>-108.49</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>407343962.3748191</t>
+          <t>407263703.2695087</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>227460502.0</t>
+          <t>145235263.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>225455205.4</t>
+          <t>188917467.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>198460457.1</t>
+          <t>195309352.7</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>750430937.44</t>
+          <t>743700361.3</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>26994748</t>
+          <t>-6391884</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-77815947.61675274</t>
+          <t>-75798392.23084499</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-66040563.21</v>
+        <v>-64701837.61</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5492,22 +5492,22 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>3.304677259170958</t>
+          <t>-4.012262137013166</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-13.63624517069042</t>
+          <t>-1.72716244973935</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>3.993839757333741</t>
+          <t>4.777195903551031</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>94.49</t>
+          <t>91.34</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>48.79</t>
+          <t>46.96</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>12873</t>
+          <t>12444</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
+          <t>123.5</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>120.0</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
           <t>121.5</t>
-        </is>
-      </c>
-      <c r="CD12" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>121.0</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>124.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/玻_碳纖.xlsx
+++ b/Result/checksun_type/玻_碳纖.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-5.63</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1998.479</t>
+          <t>2649.921</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,84 +893,84 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>109.5</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>-2.76</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>18.24</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-09-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>124.5</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>131.5</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
           <t>116.0</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-0.18</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>9.33</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-09-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>124.5</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>115.0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>131.5</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>116.0</t>
-        </is>
-      </c>
       <c r="V2" t="inlineStr">
         <is>
           <t>0</t>
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>6.10</t>
+          <t>8.09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2650</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>50.62</t>
+          <t>17.28</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>-8.90</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>120.2</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>119.62</t>
+          <t>119.5</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>119.79</t>
+          <t>119.54</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>121.95</t>
+          <t>121.97</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>20.33</t>
+          <t>-966.59</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-99.06</t>
+          <t>-100.66</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>407263703.2695087</t>
+          <t>407308352.9220779</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>234536441.0</t>
+          <t>292137275.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>453352594.4</t>
+          <t>485899681.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>414675114.7</t>
+          <t>410942337.2</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>478603045.96</t>
+          <t>472868764.64</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>38677479</t>
+          <t>74957344</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-4899574.583967528</t>
+          <t>-3945974.667951212</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>10251712.83</v>
+        <v>1298824.87</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>17.17</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>91.34</t>
+          <t>86.22</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>46.96</t>
+          <t>44.29</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>12444</t>
+          <t>11747</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1257,27 +1257,27 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>綠能環保右上上市</t>
+          <t>綠能環保平上市</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>118.5</t>
+          <t>115.5</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>117.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>115.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>109.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-6.4</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2237.086</t>
+          <t>1998.479</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>15.49</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>6.83</t>
+          <t>6.10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,72 +1440,72 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2650</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>40.74</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>80.25</t>
+          <t>50.62</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>121.3</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>119.4</t>
+          <t>119.62</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>119.79</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>121.73</t>
+          <t>121.95</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>506.78</t>
+          <t>20.33</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-99.11</t>
+          <t>-99.06</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>407263703.2695087</t>
+          <t>407308352.9220779</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>274537160.0</t>
+          <t>234536441.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>468607130.0</t>
+          <t>453352594.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>405744996.9</t>
+          <t>414675114.7</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>496122034.34</t>
+          <t>478603045.96</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>62862133</t>
+          <t>38677479</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-7654354.113187951</t>
+          <t>-4899574.583967528</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>28846938.09</v>
+        <v>10251712.83</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>21.21</t>
+          <t>17.17</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>91.34</t>
+          <t>86.22</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>46.96</t>
+          <t>44.29</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>12444</t>
+          <t>11747</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1688,27 +1688,27 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>綠能環保右上上市</t>
+          <t>綠能環保平上市</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>118.5</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>115.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>-6.4</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4742.281</t>
+          <t>2237.086</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-10.34</t>
+          <t>-9.59</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>39.36</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>11.30</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14.48</t>
+          <t>6.83</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2650</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>40.74</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>70.67</t>
+          <t>80.25</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>6.49</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>120.2</t>
+          <t>121.3</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>119.4</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>120.2</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>121.48</t>
+          <t>121.73</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>3038.57</t>
+          <t>506.78</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-100.24</t>
+          <t>-99.11</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>407263703.2695087</t>
+          <t>407308352.9220779</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>602848357.0</t>
+          <t>274537160.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>558871972.6</t>
+          <t>468607130.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>401037331.1</t>
+          <t>405744996.9</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>530097463.36</t>
+          <t>496122034.34</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>157834641</t>
+          <t>62862133</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-14290952.69601668</t>
+          <t>-7654354.113187951</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>50095506.5</v>
+        <v>28846938.09</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>29.29</t>
+          <t>21.21</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>91.34</t>
+          <t>86.22</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>46.96</t>
+          <t>44.29</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>12444</t>
+          <t>11747</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2119,27 +2119,27 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>綠能環保右上上市</t>
+          <t>綠能環保平上市</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8162.419</t>
+          <t>4742.281</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-9.91</t>
+          <t>-16.89</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>39.69</t>
+          <t>39.36</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>10.87</t>
+          <t>11.30</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>24.92</t>
+          <t>14.48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,12 +2302,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2650</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2317,62 +2317,62 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>38.67</t>
+          <t>70.67</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>6.49</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>120.2</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>118.2</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>120.52</t>
+          <t>120.2</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>121.12</t>
+          <t>121.48</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>164.26</t>
+          <t>3038.57</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-102.05</t>
+          <t>-100.24</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>407263703.2695087</t>
+          <t>407308352.9220779</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1025439175.0</t>
+          <t>602848357.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>504875555.4</t>
+          <t>558871972.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>361436106.5</t>
+          <t>401037331.1</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>536684043.66</t>
+          <t>530097463.36</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>143439448</t>
+          <t>157834641</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-25997581.64151972</t>
+          <t>-14290952.69601668</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>43485279.32</v>
+        <v>50095506.5</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>29.29</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>91.34</t>
+          <t>86.22</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>46.96</t>
+          <t>44.29</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>12444</t>
+          <t>11747</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2550,27 +2550,27 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>綠能環保右上上市</t>
+          <t>綠能環保平上市</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>124.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1122.329</t>
+          <t>8162.419</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,84 +2617,84 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>127.5</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-16.44</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-2.76</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>39.69</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-09-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>124.5</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>131.5</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
           <t>116.0</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>-0.18</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>22.56</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-09-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>124.5</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>115.0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>131.5</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>116.0</t>
-        </is>
-      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>0</t>
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>10.87</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>24.92</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2650</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>38.67</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>118.7</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>117.48</t>
+          <t>118.2</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>120.59</t>
+          <t>120.52</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>120.77</t>
+          <t>121.12</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-89.81</t>
+          <t>164.26</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-102.89</t>
+          <t>-102.05</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>407263703.2695087</t>
+          <t>407308352.9220779</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>129401839.0</t>
+          <t>1025439175.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>335984992.8</t>
+          <t>504875555.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>274141955.5</t>
+          <t>361436106.5</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>533459215.28</t>
+          <t>536684043.66</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>61843037</t>
+          <t>143439448</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-38630829.0899126</t>
+          <t>-25997581.64151972</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-12788535.69</v>
+        <v>43485279.32</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>17.17</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>91.34</t>
+          <t>86.22</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>46.96</t>
+          <t>44.29</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>12444</t>
+          <t>11747</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2981,27 +2981,27 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>綠能環保右上上市</t>
+          <t>綠能環保平上市</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>115.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2764.556</t>
+          <t>1122.329</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,72 +3048,72 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>116.0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-5.94</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-2.76</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>22.56</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-09-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>124.5</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
           <t>115.0</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0.86</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>-0.18</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>33.12</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-09-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>124.5</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>115.0</t>
-        </is>
-      </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-7.63</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>8.44</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>6.61</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,47 +3164,47 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2650</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>34.67</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>118.7</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -3214,27 +3214,27 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>120.88</t>
+          <t>120.59</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>120.53</t>
+          <t>120.77</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-40.51</t>
+          <t>-89.81</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-102.24</t>
+          <t>-102.89</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,45 +3254,45 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>407263703.2695087</t>
+          <t>407308352.9220779</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>310809119.0</t>
+          <t>129401839.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>375997635.0</t>
+          <t>335984992.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>282457551.4</t>
+          <t>274141955.5</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>556111164.18</t>
+          <t>533459215.28</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>93540083</t>
+          <t>61843037</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-43329427.88925355</t>
+          <t>-38630829.0899126</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>3281033.7</v>
+        <v>-12788535.69</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>16.16</t>
+          <t>17.17</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>91.34</t>
+          <t>86.22</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>46.96</t>
+          <t>44.29</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>12444</t>
+          <t>11747</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3412,27 +3412,27 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>綠能環保右上上市</t>
+          <t>綠能環保平上市</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>115.0</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
+          <t>116.5</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>114.0</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
           <t>116.0</t>
-        </is>
-      </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>107.0</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>115.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-10.12</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6206.994</t>
+          <t>2764.556</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>114.5</t>
+          <t>115.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>-5.02</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>20.66</t>
+          <t>33.12</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>-8.03</t>
+          <t>-7.63</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>8.44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-8.30</t>
+          <t>6.61</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2650</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>34.67</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-5.61</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>121.3</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>118.02</t>
+          <t>117.48</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>121.33</t>
+          <t>120.88</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>120.34</t>
+          <t>120.53</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>141.22</t>
+          <t>-40.51</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-102.02</t>
+          <t>-102.24</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>407263703.2695087</t>
+          <t>407308352.9220779</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>725861373.0</t>
+          <t>310809119.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>342882863.8</t>
+          <t>375997635.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>284169034.6</t>
+          <t>282457551.4</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>580170679.38</t>
+          <t>556111164.18</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>58713829</t>
+          <t>93540083</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-51804057.26877595</t>
+          <t>-43329427.88925355</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>6683887.34</v>
+        <v>3281033.7</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>15.66</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,22 +3783,22 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>91.34</t>
+          <t>86.22</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>46.96</t>
+          <t>44.29</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>12444</t>
+          <t>11747</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3843,27 +3843,27 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>綠能環保右上上市</t>
+          <t>綠能環保平上市</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>114.5</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>114.5</t>
+          <t>115.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>-10.12</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2671.658</t>
+          <t>6206.994</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>114.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-9.48</t>
+          <t>-4.57</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>20.66</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3990,12 +3990,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>-8.03</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>-8.30</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2650</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>79.63</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>-5.61</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>123.3</t>
+          <t>121.3</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>118.8</t>
+          <t>118.02</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>121.87</t>
+          <t>121.33</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>120.15</t>
+          <t>120.34</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>333.84</t>
+          <t>141.22</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-102.73</t>
+          <t>-102.02</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>407263703.2695087</t>
+          <t>407308352.9220779</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>332866271.0</t>
+          <t>725861373.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>243202689.6</t>
+          <t>342882863.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>228452558.7</t>
+          <t>284169034.6</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>663144032.96</t>
+          <t>580170679.38</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>14750130</t>
+          <t>58713829</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-62438229.01579697</t>
+          <t>-51804057.26877595</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-33163487.79</v>
+        <v>6683887.34</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>28.28</t>
+          <t>15.66</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,22 +4214,22 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>91.34</t>
+          <t>86.22</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>46.96</t>
+          <t>44.29</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>12444</t>
+          <t>11747</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4274,27 +4274,27 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>綠能環保右上上市</t>
+          <t>綠能環保平上市</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>114.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>114.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1518.372</t>
+          <t>2671.658</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-15.98</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4421,12 +4421,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>5.22</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2650</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>61.11</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>70.54</t>
+          <t>79.63</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>122.2</t>
+          <t>123.3</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>118.98</t>
+          <t>118.8</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>122.3</t>
+          <t>121.87</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>119.69</t>
+          <t>120.15</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>129.29</t>
+          <t>333.84</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-105.00</t>
+          <t>-102.73</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>407263703.2695087</t>
+          <t>407308352.9220779</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>180986362.0</t>
+          <t>332866271.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>217996657.6</t>
+          <t>243202689.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>218528992.0</t>
+          <t>228452558.7</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>721943048.64</t>
+          <t>663144032.96</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-532334</t>
+          <t>14750130</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-67760909.23843847</t>
+          <t>-62438229.01579697</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-46797281.06</v>
+        <v>-33163487.79</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>28.28</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,22 +4645,22 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>91.34</t>
+          <t>86.22</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>46.96</t>
+          <t>44.29</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>12444</t>
+          <t>11747</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4705,27 +4705,27 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>綠能環保右上上市</t>
+          <t>綠能環保平上市</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2659.342</t>
+          <t>1518.372</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-5.6</t>
+          <t>-10.5</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4852,12 +4852,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>5.22</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2650</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>61.11</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>70.54</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>121.7</t>
+          <t>122.2</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>119.3</t>
+          <t>118.98</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>122.58</t>
+          <t>122.3</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>119.25</t>
+          <t>119.69</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>113.38</t>
+          <t>129.29</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-106.62</t>
+          <t>-105.00</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>407263703.2695087</t>
+          <t>407308352.9220779</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>329465050.0</t>
+          <t>180986362.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>212298918.2</t>
+          <t>217996657.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>218106553.5</t>
+          <t>218528992.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>737772671.58</t>
+          <t>721943048.64</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-5807635</t>
+          <t>-532334</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-71572477.99861823</t>
+          <t>-67760909.23843847</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-48329949.72</v>
+        <v>-46797281.06</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>23.74</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>91.34</t>
+          <t>86.22</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>46.96</t>
+          <t>44.29</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>12444</t>
+          <t>11747</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5136,27 +5136,27 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>綠能環保右上上市</t>
+          <t>綠能環保平上市</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>119.5</t>
+          <t>116.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1192.575</t>
+          <t>2659.342</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-4.74</t>
+          <t>-11.87</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>5.65</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>8.12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2650</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>72.73</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>121.7</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>119.45</t>
+          <t>119.3</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>122.59</t>
+          <t>122.58</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>118.7</t>
+          <t>119.25</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>84.77</t>
+          <t>113.38</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-108.49</t>
+          <t>-106.62</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>407263703.2695087</t>
+          <t>407308352.9220779</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>145235263.0</t>
+          <t>329465050.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>188917467.8</t>
+          <t>212298918.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>195309352.7</t>
+          <t>218106553.5</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>743700361.3</t>
+          <t>737772671.58</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-6391884</t>
+          <t>-5807635</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-75798392.23084499</t>
+          <t>-71572477.99861823</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-64701837.61</v>
+        <v>-48329949.72</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>23.74</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>91.34</t>
+          <t>86.22</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>46.96</t>
+          <t>44.29</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>12444</t>
+          <t>11747</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5567,27 +5567,27 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>綠能環保右上上市</t>
+          <t>綠能環保平上市</t>
         </is>
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>119.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/玻_碳纖.xlsx
+++ b/Result/checksun_type/玻_碳纖.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-5.63</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2649.921</t>
+          <t>1722.133</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>18.24</t>
+          <t>-22.70</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2650</t>
+          <t>1722</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>17.28</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-8.90</t>
+          <t>-5.74</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>120.2</t>
+          <t>116.7</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>119.5</t>
+          <t>119.32</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>119.54</t>
+          <t>119.42</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>121.97</t>
+          <t>121.94</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-966.59</t>
+          <t>-315.52</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-100.66</t>
+          <t>-103.15</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>407308352.9220779</t>
+          <t>407124017.5850145</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>292137275.0</t>
+          <t>186253086.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>485899681.6</t>
+          <t>318062463.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>410942337.2</t>
+          <t>411469009.6</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>472868764.64</t>
+          <t>462766906.5</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>74957344</t>
+          <t>-93406545</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-3945974.667951212</t>
+          <t>-5329975.718457082</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>1298824.87</v>
+        <v>-12941981.5</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>86.22</t>
+          <t>86.61</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>44.29</t>
+          <t>43.92</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>11747</t>
+          <t>11800</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>115.5</t>
+          <t>108.5</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>117.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-5.63</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1998.479</t>
+          <t>2649.921</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,84 +1324,84 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>109.5</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-1.27</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>18.24</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-09-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>124.5</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>131.5</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
           <t>116.0</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-5.94</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-2.76</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>9.33</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-09-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>124.5</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>115.0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>131.5</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>116.0</t>
-        </is>
-      </c>
       <c r="V3" t="inlineStr">
         <is>
           <t>0</t>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>6.10</t>
+          <t>8.09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2650</t>
+          <t>1722</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>50.62</t>
+          <t>17.28</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>-8.90</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>120.2</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>119.62</t>
+          <t>119.5</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>119.79</t>
+          <t>119.54</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>121.95</t>
+          <t>121.97</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>20.33</t>
+          <t>-966.59</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-99.06</t>
+          <t>-100.66</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>407308352.9220779</t>
+          <t>407124017.5850145</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>234536441.0</t>
+          <t>292137275.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>453352594.4</t>
+          <t>485899681.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>414675114.7</t>
+          <t>410942337.2</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>478603045.96</t>
+          <t>472868764.64</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>38677479</t>
+          <t>74957344</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-4899574.583967528</t>
+          <t>-3945974.667951212</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>10251712.83</v>
+        <v>1298824.87</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>17.17</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>86.22</t>
+          <t>86.61</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>44.29</t>
+          <t>43.92</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>11747</t>
+          <t>11800</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>118.5</t>
+          <t>115.5</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>117.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>115.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>109.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-6.4</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2237.086</t>
+          <t>1998.479</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-9.59</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>15.49</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>6.83</t>
+          <t>6.10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,72 +1871,72 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2650</t>
+          <t>1722</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>40.74</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>80.25</t>
+          <t>50.62</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>121.3</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>119.4</t>
+          <t>119.62</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>119.79</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>121.73</t>
+          <t>121.95</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>506.78</t>
+          <t>20.33</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-99.11</t>
+          <t>-99.06</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>407308352.9220779</t>
+          <t>407124017.5850145</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>274537160.0</t>
+          <t>234536441.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>468607130.0</t>
+          <t>453352594.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>405744996.9</t>
+          <t>414675114.7</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>496122034.34</t>
+          <t>478603045.96</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>62862133</t>
+          <t>38677479</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-7654354.113187951</t>
+          <t>-4899574.583967528</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>28846938.09</v>
+        <v>10251712.83</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>21.21</t>
+          <t>17.17</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>86.22</t>
+          <t>86.61</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>44.29</t>
+          <t>43.92</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>11747</t>
+          <t>11800</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>118.5</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>115.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>-6.4</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4742.281</t>
+          <t>2237.086</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-16.89</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>39.36</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>11.30</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.48</t>
+          <t>6.83</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2650</t>
+          <t>1722</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>40.74</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>70.67</t>
+          <t>80.25</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>6.49</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>120.2</t>
+          <t>121.3</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>119.4</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>120.2</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>121.48</t>
+          <t>121.73</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>3038.57</t>
+          <t>506.78</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-100.24</t>
+          <t>-99.11</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>407308352.9220779</t>
+          <t>407124017.5850145</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>602848357.0</t>
+          <t>274537160.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>558871972.6</t>
+          <t>468607130.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>401037331.1</t>
+          <t>405744996.9</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>530097463.36</t>
+          <t>496122034.34</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>157834641</t>
+          <t>62862133</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-14290952.69601668</t>
+          <t>-7654354.113187951</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>50095506.5</v>
+        <v>28846938.09</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>29.29</t>
+          <t>21.21</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>86.22</t>
+          <t>86.61</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>44.29</t>
+          <t>43.92</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>11747</t>
+          <t>11800</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8162.419</t>
+          <t>4742.281</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-16.44</t>
+          <t>-16.36</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>39.69</t>
+          <t>39.36</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>10.87</t>
+          <t>11.30</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>24.92</t>
+          <t>14.48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,12 +2733,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2650</t>
+          <t>1722</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2748,62 +2748,62 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>38.67</t>
+          <t>70.67</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>6.49</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>120.2</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>118.2</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>120.52</t>
+          <t>120.2</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>121.12</t>
+          <t>121.48</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>164.26</t>
+          <t>3038.57</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-102.05</t>
+          <t>-100.24</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>407308352.9220779</t>
+          <t>407124017.5850145</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1025439175.0</t>
+          <t>602848357.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>504875555.4</t>
+          <t>558871972.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>361436106.5</t>
+          <t>401037331.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>536684043.66</t>
+          <t>530097463.36</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>143439448</t>
+          <t>157834641</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-25997581.64151972</t>
+          <t>-14290952.69601668</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>43485279.32</v>
+        <v>50095506.5</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>29.29</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>86.22</t>
+          <t>86.61</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>44.29</t>
+          <t>43.92</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>11747</t>
+          <t>11800</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>124.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1122.329</t>
+          <t>8162.419</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,84 +3048,84 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>127.5</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-15.91</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-1.27</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>39.69</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-09-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>124.5</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>131.5</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
           <t>116.0</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-5.94</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>-2.76</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>22.56</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-09-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>124.5</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>115.0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>131.5</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>116.0</t>
-        </is>
-      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>0</t>
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>10.87</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>24.92</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2650</t>
+          <t>1722</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>38.67</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>118.7</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>117.48</t>
+          <t>118.2</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>120.59</t>
+          <t>120.52</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>120.77</t>
+          <t>121.12</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-89.81</t>
+          <t>164.26</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-102.89</t>
+          <t>-102.05</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>407308352.9220779</t>
+          <t>407124017.5850145</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>129401839.0</t>
+          <t>1025439175.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>335984992.8</t>
+          <t>504875555.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>274141955.5</t>
+          <t>361436106.5</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>533459215.28</t>
+          <t>536684043.66</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>61843037</t>
+          <t>143439448</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-38630829.0899126</t>
+          <t>-25997581.64151972</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-12788535.69</v>
+        <v>43485279.32</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>17.17</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>86.22</t>
+          <t>86.61</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>44.29</t>
+          <t>43.92</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>11747</t>
+          <t>11800</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>115.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2764.556</t>
+          <t>1122.329</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,72 +3479,72 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>116.0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-5.45</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-1.27</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>22.56</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-09-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>124.5</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
           <t>115.0</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-5.02</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>-2.76</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>33.12</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-09-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>124.5</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>115.0</t>
-        </is>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>-7.63</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>8.44</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>6.61</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,47 +3595,47 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2650</t>
+          <t>1722</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>34.67</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>118.7</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -3645,27 +3645,27 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>120.88</t>
+          <t>120.59</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>120.53</t>
+          <t>120.77</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-40.51</t>
+          <t>-89.81</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-102.24</t>
+          <t>-102.89</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,45 +3685,45 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>407308352.9220779</t>
+          <t>407124017.5850145</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>310809119.0</t>
+          <t>129401839.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>375997635.0</t>
+          <t>335984992.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>282457551.4</t>
+          <t>274141955.5</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>556111164.18</t>
+          <t>533459215.28</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>93540083</t>
+          <t>61843037</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-43329427.88925355</t>
+          <t>-38630829.0899126</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>3281033.7</v>
+        <v>-12788535.69</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>16.16</t>
+          <t>17.17</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,22 +3783,22 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>86.22</t>
+          <t>86.61</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>44.29</t>
+          <t>43.92</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>11747</t>
+          <t>11800</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>115.0</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
+          <t>116.5</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>114.0</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
           <t>116.0</t>
-        </is>
-      </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>107.0</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>115.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-10.12</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6206.994</t>
+          <t>2764.556</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>114.5</t>
+          <t>115.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-4.57</t>
+          <t>-4.55</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>20.66</t>
+          <t>33.12</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3990,12 +3990,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-8.03</t>
+          <t>-7.63</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>8.44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-8.30</t>
+          <t>6.61</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2650</t>
+          <t>1722</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>34.67</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-5.61</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>121.3</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>118.02</t>
+          <t>117.48</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>121.33</t>
+          <t>120.88</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>120.34</t>
+          <t>120.53</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>141.22</t>
+          <t>-40.51</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-102.02</t>
+          <t>-102.24</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>407308352.9220779</t>
+          <t>407124017.5850145</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>725861373.0</t>
+          <t>310809119.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>342882863.8</t>
+          <t>375997635.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>284169034.6</t>
+          <t>282457551.4</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>580170679.38</t>
+          <t>556111164.18</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>58713829</t>
+          <t>93540083</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-51804057.26877595</t>
+          <t>-43329427.88925355</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>6683887.34</v>
+        <v>3281033.7</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>15.66</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,22 +4214,22 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>86.22</t>
+          <t>86.61</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>44.29</t>
+          <t>43.92</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>11747</t>
+          <t>11800</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>114.5</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>114.5</t>
+          <t>115.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>-10.12</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2671.658</t>
+          <t>6206.994</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>114.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-15.98</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>20.66</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4421,12 +4421,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>-8.03</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>-8.30</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2650</t>
+          <t>1722</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>79.63</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>-5.61</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>123.3</t>
+          <t>121.3</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>118.8</t>
+          <t>118.02</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>121.87</t>
+          <t>121.33</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>120.15</t>
+          <t>120.34</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>333.84</t>
+          <t>141.22</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-102.73</t>
+          <t>-102.02</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>407308352.9220779</t>
+          <t>407124017.5850145</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>332866271.0</t>
+          <t>725861373.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>243202689.6</t>
+          <t>342882863.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>228452558.7</t>
+          <t>284169034.6</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>663144032.96</t>
+          <t>580170679.38</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>14750130</t>
+          <t>58713829</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-62438229.01579697</t>
+          <t>-51804057.26877595</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-33163487.79</v>
+        <v>6683887.34</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>28.28</t>
+          <t>15.66</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,22 +4645,22 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>86.22</t>
+          <t>86.61</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>44.29</t>
+          <t>43.92</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>11747</t>
+          <t>11800</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>114.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>114.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1518.372</t>
+          <t>2671.658</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-10.5</t>
+          <t>-15.45</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4852,12 +4852,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>5.22</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2650</t>
+          <t>1722</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>61.11</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>70.54</t>
+          <t>79.63</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>122.2</t>
+          <t>123.3</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>118.98</t>
+          <t>118.8</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>122.3</t>
+          <t>121.87</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>119.69</t>
+          <t>120.15</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>129.29</t>
+          <t>333.84</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-105.00</t>
+          <t>-102.73</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>407308352.9220779</t>
+          <t>407124017.5850145</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>180986362.0</t>
+          <t>332866271.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>217996657.6</t>
+          <t>243202689.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>218528992.0</t>
+          <t>228452558.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>721943048.64</t>
+          <t>663144032.96</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-532334</t>
+          <t>14750130</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-67760909.23843847</t>
+          <t>-62438229.01579697</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-46797281.06</v>
+        <v>-33163487.79</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>28.28</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>86.22</t>
+          <t>86.61</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>44.29</t>
+          <t>43.92</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>11747</t>
+          <t>11800</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2659.342</t>
+          <t>1518.372</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-11.87</t>
+          <t>-10.0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>5.22</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2650</t>
+          <t>1722</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>61.11</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>70.54</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>121.7</t>
+          <t>122.2</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>119.3</t>
+          <t>118.98</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>122.58</t>
+          <t>122.3</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>119.25</t>
+          <t>119.69</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>113.38</t>
+          <t>129.29</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-106.62</t>
+          <t>-105.00</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>407308352.9220779</t>
+          <t>407124017.5850145</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>329465050.0</t>
+          <t>180986362.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>212298918.2</t>
+          <t>217996657.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>218106553.5</t>
+          <t>218528992.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>737772671.58</t>
+          <t>721943048.64</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-5807635</t>
+          <t>-532334</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-71572477.99861823</t>
+          <t>-67760909.23843847</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-48329949.72</v>
+        <v>-46797281.06</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>23.74</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>86.22</t>
+          <t>86.61</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>44.29</t>
+          <t>43.92</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>11747</t>
+          <t>11800</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>119.5</t>
+          <t>116.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/玻_碳纖.xlsx
+++ b/Result/checksun_type/玻_碳纖.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1722.133</t>
+          <t>987.925</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-22.70</t>
+          <t>-43.50</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1722</t>
+          <t>988</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-5.74</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>116.7</t>
+          <t>113.9</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>119.32</t>
+          <t>119.18</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>119.42</t>
+          <t>119.4</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>121.94</t>
+          <t>121.95</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-315.52</t>
+          <t>-168.80</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-103.15</t>
+          <t>-105.44</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>407124017.5850145</t>
+          <t>406781400.7640288</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>186253086.0</t>
+          <t>112670218.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>318062463.8</t>
+          <t>220026836.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>411469009.6</t>
+          <t>389449404.3</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>462766906.5</t>
+          <t>458112049.14</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-93406545</t>
+          <t>-169422568</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-5329975.718457082</t>
+          <t>-8833935.071817197</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-12941981.5</v>
+        <v>-28105711.52</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>15.15</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>86.61</t>
+          <t>89.76</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>43.92</t>
+          <t>44.26</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>11800</t>
+          <t>12229</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1257,27 +1257,27 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>綠能環保平上市</t>
+          <t>綠能環保右上上市</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>113.5</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>112.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-5.63</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2649.921</t>
+          <t>1722.133</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>18.24</t>
+          <t>-22.70</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1722</t>
+          <t>988</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>17.28</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-8.90</t>
+          <t>-5.74</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>120.2</t>
+          <t>116.7</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>119.5</t>
+          <t>119.32</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>119.54</t>
+          <t>119.42</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>121.97</t>
+          <t>121.94</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-966.59</t>
+          <t>-315.52</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-100.66</t>
+          <t>-103.15</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>407124017.5850145</t>
+          <t>406781400.7640288</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>292137275.0</t>
+          <t>186253086.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>485899681.6</t>
+          <t>318062463.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>410942337.2</t>
+          <t>411469009.6</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>472868764.64</t>
+          <t>462766906.5</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>74957344</t>
+          <t>-93406545</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-3945974.667951212</t>
+          <t>-5329975.718457082</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>1298824.87</v>
+        <v>-12941981.5</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,12 +1628,12 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>86.61</t>
+          <t>89.76</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>43.92</t>
+          <t>44.26</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>11800</t>
+          <t>12229</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1688,27 +1688,27 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>綠能環保平上市</t>
+          <t>綠能環保右上上市</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>115.5</t>
+          <t>108.5</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>117.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-5.63</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1998.479</t>
+          <t>2649.921</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,84 +1755,84 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>109.5</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>3.95</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-1.89</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>18.24</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-09-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>124.5</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>131.5</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
           <t>116.0</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-5.45</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-1.27</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>9.33</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-09-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>124.5</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>115.0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>131.5</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>116.0</t>
-        </is>
-      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>0</t>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>6.10</t>
+          <t>8.09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1722</t>
+          <t>988</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>50.62</t>
+          <t>17.28</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>-8.90</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>120.2</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>119.62</t>
+          <t>119.5</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>119.79</t>
+          <t>119.54</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>121.95</t>
+          <t>121.97</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>20.33</t>
+          <t>-966.59</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-99.06</t>
+          <t>-100.66</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>407124017.5850145</t>
+          <t>406781400.7640288</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>234536441.0</t>
+          <t>292137275.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>453352594.4</t>
+          <t>485899681.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>414675114.7</t>
+          <t>410942337.2</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>478603045.96</t>
+          <t>472868764.64</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>38677479</t>
+          <t>74957344</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-4899574.583967528</t>
+          <t>-3945974.667951212</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>10251712.83</v>
+        <v>1298824.87</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>17.17</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>86.61</t>
+          <t>89.76</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>43.92</t>
+          <t>44.26</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>11800</t>
+          <t>12229</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2119,27 +2119,27 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>綠能環保平上市</t>
+          <t>綠能環保右上上市</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>118.5</t>
+          <t>115.5</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>117.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>115.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>109.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-6.4</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2237.086</t>
+          <t>1998.479</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>15.49</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.83</t>
+          <t>6.10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,72 +2302,72 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1722</t>
+          <t>988</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>40.74</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>80.25</t>
+          <t>50.62</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>121.3</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>119.4</t>
+          <t>119.62</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>119.79</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>121.73</t>
+          <t>121.95</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>506.78</t>
+          <t>20.33</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-99.11</t>
+          <t>-99.06</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>407124017.5850145</t>
+          <t>406781400.7640288</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>274537160.0</t>
+          <t>234536441.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>468607130.0</t>
+          <t>453352594.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>405744996.9</t>
+          <t>414675114.7</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>496122034.34</t>
+          <t>478603045.96</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>62862133</t>
+          <t>38677479</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-7654354.113187951</t>
+          <t>-4899574.583967528</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>28846938.09</v>
+        <v>10251712.83</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>21.21</t>
+          <t>17.17</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>86.61</t>
+          <t>89.76</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>43.92</t>
+          <t>44.26</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>11800</t>
+          <t>12229</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2550,27 +2550,27 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>綠能環保平上市</t>
+          <t>綠能環保右上上市</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>118.5</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>115.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>-6.4</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4742.281</t>
+          <t>2237.086</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-16.36</t>
+          <t>-5.26</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>39.36</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>11.30</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14.48</t>
+          <t>6.83</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1722</t>
+          <t>988</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>40.74</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>70.67</t>
+          <t>80.25</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>6.49</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>120.2</t>
+          <t>121.3</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>119.4</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>120.2</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>121.48</t>
+          <t>121.73</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>3038.57</t>
+          <t>506.78</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-100.24</t>
+          <t>-99.11</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>407124017.5850145</t>
+          <t>406781400.7640288</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>602848357.0</t>
+          <t>274537160.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>558871972.6</t>
+          <t>468607130.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>401037331.1</t>
+          <t>405744996.9</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>530097463.36</t>
+          <t>496122034.34</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>157834641</t>
+          <t>62862133</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-14290952.69601668</t>
+          <t>-7654354.113187951</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>50095506.5</v>
+        <v>28846938.09</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>29.29</t>
+          <t>21.21</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>86.61</t>
+          <t>89.76</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>43.92</t>
+          <t>44.26</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>11800</t>
+          <t>12229</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2981,27 +2981,27 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>綠能環保平上市</t>
+          <t>綠能環保右上上市</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8162.419</t>
+          <t>4742.281</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-15.91</t>
+          <t>-12.28</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>39.69</t>
+          <t>39.36</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>10.87</t>
+          <t>11.30</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>24.92</t>
+          <t>14.48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1722</t>
+          <t>988</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,62 +3179,62 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>38.67</t>
+          <t>70.67</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>6.49</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>120.2</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>118.2</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>120.52</t>
+          <t>120.2</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>121.12</t>
+          <t>121.48</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>164.26</t>
+          <t>3038.57</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-102.05</t>
+          <t>-100.24</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>407124017.5850145</t>
+          <t>406781400.7640288</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1025439175.0</t>
+          <t>602848357.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>504875555.4</t>
+          <t>558871972.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>361436106.5</t>
+          <t>401037331.1</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>536684043.66</t>
+          <t>530097463.36</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>143439448</t>
+          <t>157834641</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-25997581.64151972</t>
+          <t>-14290952.69601668</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>43485279.32</v>
+        <v>50095506.5</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>29.29</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>86.61</t>
+          <t>89.76</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>43.92</t>
+          <t>44.26</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>11800</t>
+          <t>12229</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3412,27 +3412,27 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>綠能環保平上市</t>
+          <t>綠能環保右上上市</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>124.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1122.329</t>
+          <t>8162.419</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,84 +3479,84 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>127.5</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-11.84</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-1.89</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>39.69</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-09-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>124.5</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>131.5</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
           <t>116.0</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-5.45</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>-1.27</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>22.56</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-09-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>124.5</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>115.0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>131.5</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>116.0</t>
-        </is>
-      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>0</t>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>10.87</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>24.92</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1722</t>
+          <t>988</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>38.67</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>118.7</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>117.48</t>
+          <t>118.2</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>120.59</t>
+          <t>120.52</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>120.77</t>
+          <t>121.12</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-89.81</t>
+          <t>164.26</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-102.89</t>
+          <t>-102.05</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>407124017.5850145</t>
+          <t>406781400.7640288</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>129401839.0</t>
+          <t>1025439175.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>335984992.8</t>
+          <t>504875555.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>274141955.5</t>
+          <t>361436106.5</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>533459215.28</t>
+          <t>536684043.66</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>61843037</t>
+          <t>143439448</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-38630829.0899126</t>
+          <t>-25997581.64151972</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-12788535.69</v>
+        <v>43485279.32</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>17.17</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,22 +3783,22 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>86.61</t>
+          <t>89.76</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>43.92</t>
+          <t>44.26</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>11800</t>
+          <t>12229</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3843,27 +3843,27 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>綠能環保平上市</t>
+          <t>綠能環保右上上市</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>115.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2764.556</t>
+          <t>1122.329</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,72 +3910,72 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>116.0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-1.75</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-1.89</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>22.56</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-09-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>124.5</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
           <t>115.0</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-4.55</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>-1.27</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>33.12</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-09-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>124.5</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>115.0</t>
-        </is>
-      </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -3990,12 +3990,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-7.63</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>8.44</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>6.61</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,47 +4026,47 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1722</t>
+          <t>988</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>34.67</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>118.7</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -4076,27 +4076,27 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>120.88</t>
+          <t>120.59</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>120.53</t>
+          <t>120.77</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-40.51</t>
+          <t>-89.81</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-102.24</t>
+          <t>-102.89</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,45 +4116,45 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>407124017.5850145</t>
+          <t>406781400.7640288</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>310809119.0</t>
+          <t>129401839.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>375997635.0</t>
+          <t>335984992.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>282457551.4</t>
+          <t>274141955.5</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>556111164.18</t>
+          <t>533459215.28</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>93540083</t>
+          <t>61843037</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-43329427.88925355</t>
+          <t>-38630829.0899126</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>3281033.7</v>
+        <v>-12788535.69</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>16.16</t>
+          <t>17.17</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,22 +4214,22 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>86.61</t>
+          <t>89.76</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>43.92</t>
+          <t>44.26</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>11800</t>
+          <t>12229</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4274,27 +4274,27 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>綠能環保平上市</t>
+          <t>綠能環保右上上市</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>115.0</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
+          <t>116.5</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>114.0</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
           <t>116.0</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>107.0</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>115.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-10.12</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6206.994</t>
+          <t>2764.556</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>114.5</t>
+          <t>115.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>20.66</t>
+          <t>33.12</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4421,12 +4421,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-8.03</t>
+          <t>-7.63</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>8.44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-8.30</t>
+          <t>6.61</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1722</t>
+          <t>988</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>34.67</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-5.61</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>121.3</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>118.02</t>
+          <t>117.48</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>121.33</t>
+          <t>120.88</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>120.34</t>
+          <t>120.53</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>141.22</t>
+          <t>-40.51</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-102.02</t>
+          <t>-102.24</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>407124017.5850145</t>
+          <t>406781400.7640288</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>725861373.0</t>
+          <t>310809119.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>342882863.8</t>
+          <t>375997635.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>284169034.6</t>
+          <t>282457551.4</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>580170679.38</t>
+          <t>556111164.18</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>58713829</t>
+          <t>93540083</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-51804057.26877595</t>
+          <t>-43329427.88925355</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>6683887.34</v>
+        <v>3281033.7</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>15.66</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>86.61</t>
+          <t>89.76</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>43.92</t>
+          <t>44.26</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>11800</t>
+          <t>12229</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4705,27 +4705,27 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>綠能環保平上市</t>
+          <t>綠能環保右上上市</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>114.5</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>114.5</t>
+          <t>115.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>-10.12</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2671.658</t>
+          <t>6206.994</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>114.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-15.45</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>20.66</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4852,12 +4852,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>-8.03</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>-8.30</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1722</t>
+          <t>988</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>79.63</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>-5.61</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>123.3</t>
+          <t>121.3</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>118.8</t>
+          <t>118.02</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>121.87</t>
+          <t>121.33</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>120.15</t>
+          <t>120.34</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>333.84</t>
+          <t>141.22</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-102.73</t>
+          <t>-102.02</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>407124017.5850145</t>
+          <t>406781400.7640288</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>332866271.0</t>
+          <t>725861373.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>243202689.6</t>
+          <t>342882863.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>228452558.7</t>
+          <t>284169034.6</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>663144032.96</t>
+          <t>580170679.38</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>14750130</t>
+          <t>58713829</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-62438229.01579697</t>
+          <t>-51804057.26877595</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-33163487.79</v>
+        <v>6683887.34</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>28.28</t>
+          <t>15.66</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>86.61</t>
+          <t>89.76</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>43.92</t>
+          <t>44.26</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>11800</t>
+          <t>12229</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5136,27 +5136,27 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>綠能環保平上市</t>
+          <t>綠能環保右上上市</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>114.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>114.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1518.372</t>
+          <t>2671.658</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-10.0</t>
+          <t>-11.4</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>5.22</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1722</t>
+          <t>988</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>61.11</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>70.54</t>
+          <t>79.63</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>122.2</t>
+          <t>123.3</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>118.98</t>
+          <t>118.8</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>122.3</t>
+          <t>121.87</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>119.69</t>
+          <t>120.15</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>129.29</t>
+          <t>333.84</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-105.00</t>
+          <t>-102.73</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>407124017.5850145</t>
+          <t>406781400.7640288</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>180986362.0</t>
+          <t>332866271.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>217996657.6</t>
+          <t>243202689.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>218528992.0</t>
+          <t>228452558.7</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>721943048.64</t>
+          <t>663144032.96</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-532334</t>
+          <t>14750130</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-67760909.23843847</t>
+          <t>-62438229.01579697</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-46797281.06</v>
+        <v>-33163487.79</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>28.28</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>86.61</t>
+          <t>89.76</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>43.92</t>
+          <t>44.26</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>11800</t>
+          <t>12229</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5567,27 +5567,27 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>綠能環保平上市</t>
+          <t>綠能環保右上上市</t>
         </is>
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/玻_碳纖.xlsx
+++ b/Result/checksun_type/玻_碳纖.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI12"/>
+  <dimension ref="A1:CJ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -701,165 +701,170 @@
       </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
-          <t>Volume_Price_Change_sum</t>
+          <t>VPC_MACD</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
         <is>
+          <t>Volume_Price_Change</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -878,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>-6.88</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>987.925</t>
+          <t>1507.376</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-43.50</t>
+          <t>-40.67</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -978,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-7.39</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,17 +1014,17 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>1507</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -1029,57 +1034,57 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>113.9</t>
+          <t>111.2</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>119.18</t>
+          <t>118.72</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>119.4</t>
+          <t>119.21</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>121.95</t>
+          <t>121.84</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-168.80</t>
+          <t>-147.13</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-105.44</t>
+          <t>-108.61</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,135 +1104,135 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>406781400.7640288</t>
+          <t>406547619.4030173</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>112670218.0</t>
+          <t>162713049.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>220026836.0</t>
+          <t>197662013.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>389449404.3</t>
+          <t>333134571.9</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>458112049.14</t>
+          <t>455062786.1</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-169422568</t>
+          <t>-135472558</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-8833935.071817197</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>-28105711.52</v>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-12746324.66319245</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>-34264467.41575634</t>
+        </is>
+      </c>
+      <c r="BD2" t="n">
+        <v>162713049</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
           <t>99.0</t>
         </is>
       </c>
-      <c r="BF2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>2025/07/18</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>15.15</t>
-        </is>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
+          <t>7.58</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
           <t>上緯投控</t>
         </is>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BJ2" t="inlineStr">
         <is>
           <t>上緯投控</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>綠能環保</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BL2" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>1.07</t>
-        </is>
-      </c>
       <c r="BM2" t="inlineStr">
         <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
           <t>-4.012262137013166</t>
         </is>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>-1.72716244973935</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>4.777195903551031</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
           <t>-29.60</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>89.76</t>
-        </is>
-      </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>83.86</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1237,60 +1242,65 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>44.26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>12229</t>
+          <t>43.59</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
+          <t>11425</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
           <t>環保耐蝕材料39.58%、環保綠能材料33.76%、其他25.01%、循環經濟材料1.65% (2024年)</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>上緯投控-綠能環保-上市</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>綠能環保右上上市</t>
-        </is>
-      </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>113.5</t>
+          <t>綠能環保平上市</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
+          <t>106.5</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
           <t>89.23</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>** 風力發電 - 玻/碳纖、樹酯</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1309,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1722.133</t>
+          <t>987.925</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>-7.04</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-22.70</t>
+          <t>-43.50</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,7 +1364,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1409,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>1507</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-5.74</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>116.7</t>
+          <t>113.9</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>119.32</t>
+          <t>119.18</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>119.42</t>
+          <t>119.4</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>121.94</t>
+          <t>121.95</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-315.52</t>
+          <t>-168.80</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-103.15</t>
+          <t>-105.44</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,135 +1540,135 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>406781400.7640288</t>
+          <t>406547619.4030173</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>186253086.0</t>
+          <t>112670218.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>318062463.8</t>
+          <t>220026836.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>411469009.6</t>
+          <t>389449404.3</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>462766906.5</t>
+          <t>458112049.14</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-93406545</t>
+          <t>-169422568</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-5329975.718457082</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
-        <v>-12941981.5</v>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-8833935.071817197</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>-28105711.51529783</t>
+        </is>
+      </c>
+      <c r="BD3" t="n">
+        <v>112670218</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
           <t>99.0</t>
         </is>
       </c>
-      <c r="BF3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2025/07/18</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>11.11</t>
-        </is>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
+          <t>15.15</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
           <t>上緯投控</t>
         </is>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BJ3" t="inlineStr">
         <is>
           <t>上緯投控</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>綠能環保</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BL3" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>1.07</t>
-        </is>
-      </c>
       <c r="BM3" t="inlineStr">
         <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
           <t>-4.012262137013166</t>
         </is>
       </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>-1.72716244973935</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>4.777195903551031</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ3" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
           <t>價漲量-</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>1.23</t>
-        </is>
-      </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
           <t>-29.60</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>89.76</t>
-        </is>
-      </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>83.86</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1668,60 +1678,65 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>44.26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>12229</t>
+          <t>43.59</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
+          <t>11425</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
           <t>環保耐蝕材料39.58%、環保綠能材料33.76%、其他25.01%、循環經濟材料1.65% (2024年)</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>上緯投控-綠能環保-上市</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>綠能環保右上上市</t>
-        </is>
-      </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>綠能環保平上市</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>113.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>112.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
+          <t>114.0</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
           <t>89.23</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>** 風力發電 - 玻/碳纖、樹酯</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1740,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-5.63</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2649.921</t>
+          <t>1722.133</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>18.24</t>
+          <t>-22.70</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1785,7 +1800,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1840,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>1507</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>17.28</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-8.90</t>
+          <t>-5.74</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>120.2</t>
+          <t>116.7</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>119.5</t>
+          <t>119.32</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>119.54</t>
+          <t>119.42</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>121.97</t>
+          <t>121.94</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-966.59</t>
+          <t>-315.52</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-100.66</t>
+          <t>-103.15</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,135 +1976,135 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>406781400.7640288</t>
+          <t>406547619.4030173</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>292137275.0</t>
+          <t>186253086.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>485899681.6</t>
+          <t>318062463.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>410942337.2</t>
+          <t>411469009.6</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>472868764.64</t>
+          <t>462766906.5</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>74957344</t>
+          <t>-93406545</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-3945974.667951212</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
-        <v>1298824.87</v>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-5329975.718457082</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>-12941981.49623936</t>
+        </is>
+      </c>
+      <c r="BD4" t="n">
+        <v>186253086</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
           <t>99.0</t>
         </is>
       </c>
-      <c r="BF4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>2025/07/18</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>10.61</t>
-        </is>
-      </c>
       <c r="BH4" t="inlineStr">
         <is>
+          <t>11.11</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
           <t>上緯投控</t>
         </is>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BJ4" t="inlineStr">
         <is>
           <t>上緯投控</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>綠能環保</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BL4" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>1.07</t>
-        </is>
-      </c>
       <c r="BM4" t="inlineStr">
         <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
           <t>-4.012262137013166</t>
         </is>
       </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>-1.72716244973935</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>4.777195903551031</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
+          <t>價漲量-</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
           <t>1.23</t>
         </is>
       </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>2.06</t>
-        </is>
-      </c>
       <c r="BT4" t="inlineStr">
         <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
           <t>-29.60</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>89.76</t>
-        </is>
-      </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>83.86</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2099,60 +2114,65 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>44.26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>12229</t>
+          <t>43.59</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
+          <t>11425</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
           <t>環保耐蝕材料39.58%、環保綠能材料33.76%、其他25.01%、循環經濟材料1.65% (2024年)</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>上緯投控-綠能環保-上市</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>綠能環保右上上市</t>
-        </is>
-      </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>115.5</t>
+          <t>綠能環保平上市</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>117.0</t>
+          <t>108.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
           <t>89.23</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>** 風力發電 - 玻/碳纖、樹酯</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2171,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-5.63</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1998.479</t>
+          <t>2649.921</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,84 +2206,84 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>109.5</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-2.82</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-3.78</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>18.24</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-09-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>124.5</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>131.5</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
           <t>116.0</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-1.75</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>-1.89</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>9.33</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-09-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>124.5</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>115.0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>131.5</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>116.0</t>
-        </is>
-      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>0</t>
@@ -2271,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.10</t>
+          <t>8.09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>1507</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>50.62</t>
+          <t>17.28</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>-8.90</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>120.2</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>119.62</t>
+          <t>119.5</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>119.79</t>
+          <t>119.54</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>121.95</t>
+          <t>121.97</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>20.33</t>
+          <t>-966.59</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-99.06</t>
+          <t>-100.66</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,135 +2412,135 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>406781400.7640288</t>
+          <t>406547619.4030173</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>234536441.0</t>
+          <t>292137275.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>453352594.4</t>
+          <t>485899681.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>414675114.7</t>
+          <t>410942337.2</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>478603045.96</t>
+          <t>472868764.64</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>38677479</t>
+          <t>74957344</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-4899574.583967528</t>
-        </is>
-      </c>
-      <c r="BC5" t="n">
-        <v>10251712.83</v>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-3945974.667951212</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>1298824.870138526</t>
+        </is>
+      </c>
+      <c r="BD5" t="n">
+        <v>292137275</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
           <t>99.0</t>
         </is>
       </c>
-      <c r="BF5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>2025/07/18</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>17.17</t>
-        </is>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
+          <t>10.61</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
           <t>上緯投控</t>
         </is>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BJ5" t="inlineStr">
         <is>
           <t>上緯投控</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>綠能環保</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BL5" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>1.07</t>
-        </is>
-      </c>
       <c r="BM5" t="inlineStr">
         <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
           <t>-4.012262137013166</t>
         </is>
       </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>-1.72716244973935</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>4.777195903551031</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
           <t>-29.60</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>89.76</t>
-        </is>
-      </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>83.86</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2530,60 +2550,65 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>44.26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>12229</t>
+          <t>43.59</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
+          <t>11425</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
           <t>環保耐蝕材料39.58%、環保綠能材料33.76%、其他25.01%、循環經濟材料1.65% (2024年)</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>上緯投控-綠能環保-上市</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
-        <is>
-          <t>綠能環保右上上市</t>
-        </is>
-      </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>118.5</t>
+          <t>綠能環保平上市</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>115.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>115.5</t>
+          <t>117.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
+          <t>109.5</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
           <t>89.23</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>** 風力發電 - 玻/碳纖、樹酯</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2602,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-6.4</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2237.086</t>
+          <t>1998.479</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-5.26</t>
+          <t>-8.92</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>15.49</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2647,7 +2672,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2702,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>6.83</t>
+          <t>6.10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,72 +2758,72 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>1507</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>40.74</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>80.25</t>
+          <t>50.62</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>121.3</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>119.4</t>
+          <t>119.62</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>119.79</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>121.73</t>
+          <t>121.95</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>506.78</t>
+          <t>20.33</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -2813,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-99.11</t>
+          <t>-99.06</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,135 +2848,135 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>406781400.7640288</t>
+          <t>406547619.4030173</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>274537160.0</t>
+          <t>234536441.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>468607130.0</t>
+          <t>453352594.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>405744996.9</t>
+          <t>414675114.7</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>496122034.34</t>
+          <t>478603045.96</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>62862133</t>
+          <t>38677479</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-7654354.113187951</t>
-        </is>
-      </c>
-      <c r="BC6" t="n">
-        <v>28846938.09</v>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-4899574.583967528</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>10251712.82674479</t>
+        </is>
+      </c>
+      <c r="BD6" t="n">
+        <v>234536441</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
           <t>99.0</t>
         </is>
       </c>
-      <c r="BF6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>2025/07/18</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>21.21</t>
-        </is>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
+          <t>17.17</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
           <t>上緯投控</t>
         </is>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BJ6" t="inlineStr">
         <is>
           <t>上緯投控</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BK6" t="inlineStr">
         <is>
           <t>綠能環保</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr">
+      <c r="BL6" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>1.07</t>
-        </is>
-      </c>
       <c r="BM6" t="inlineStr">
         <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
           <t>-4.012262137013166</t>
         </is>
       </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>-1.72716244973935</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>4.777195903551031</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
           <t>-29.60</t>
         </is>
       </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>89.76</t>
-        </is>
-      </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>83.86</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,60 +2986,65 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>44.26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>12229</t>
+          <t>43.59</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
+          <t>11425</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
           <t>環保耐蝕材料39.58%、環保綠能材料33.76%、其他25.01%、循環經濟材料1.65% (2024年)</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>上緯投控-綠能環保-上市</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>綠能環保右上上市</t>
-        </is>
-      </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>綠能環保平上市</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>118.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>115.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
+          <t>116.0</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
           <t>89.23</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>** 風力發電 - 玻/碳纖、樹酯</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3033,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>-6.4</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4742.281</t>
+          <t>2237.086</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-12.28</t>
+          <t>-12.68</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>39.36</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3108,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>11.30</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14.48</t>
+          <t>6.83</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>1507</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>40.74</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>70.67</t>
+          <t>80.25</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>6.49</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>120.2</t>
+          <t>121.3</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>119.4</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>120.2</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>121.48</t>
+          <t>121.73</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>3038.57</t>
+          <t>506.78</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-100.24</t>
+          <t>-99.11</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,135 +3284,135 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>406781400.7640288</t>
+          <t>406547619.4030173</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>602848357.0</t>
+          <t>274537160.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>558871972.6</t>
+          <t>468607130.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>401037331.1</t>
+          <t>405744996.9</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>530097463.36</t>
+          <t>496122034.34</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>157834641</t>
+          <t>62862133</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-14290952.69601668</t>
-        </is>
-      </c>
-      <c r="BC7" t="n">
-        <v>50095506.5</v>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-7654354.113187951</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>28846938.09237003</t>
+        </is>
+      </c>
+      <c r="BD7" t="n">
+        <v>274537160</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
           <t>99.0</t>
         </is>
       </c>
-      <c r="BF7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>2025/07/18</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>29.29</t>
-        </is>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
+          <t>21.21</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
           <t>上緯投控</t>
         </is>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BJ7" t="inlineStr">
         <is>
           <t>上緯投控</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>綠能環保</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BL7" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>1.07</t>
-        </is>
-      </c>
       <c r="BM7" t="inlineStr">
         <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
           <t>-4.012262137013166</t>
         </is>
       </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>-1.72716244973935</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>4.777195903551031</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
-        </is>
-      </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
           <t>-29.60</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>89.76</t>
-        </is>
-      </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>83.86</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3392,60 +3422,65 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>44.26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>12229</t>
+          <t>43.59</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
+          <t>11425</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
           <t>環保耐蝕材料39.58%、環保綠能材料33.76%、其他25.01%、循環經濟材料1.65% (2024年)</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>上緯投控-綠能環保-上市</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>綠能環保右上上市</t>
-        </is>
-      </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>綠能環保平上市</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
+          <t>120.0</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
           <t>89.23</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
         <is>
           <t>** 風力發電 - 玻/碳纖、樹酯</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3464,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8162.419</t>
+          <t>4742.281</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-11.84</t>
+          <t>-20.19</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>39.69</t>
+          <t>39.36</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3509,7 +3544,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3564,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>10.87</t>
+          <t>11.30</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>24.92</t>
+          <t>14.48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,12 +3630,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>1507</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3610,62 +3645,62 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>38.67</t>
+          <t>70.67</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>6.49</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>120.2</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>118.2</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>120.52</t>
+          <t>120.2</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>121.12</t>
+          <t>121.48</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>164.26</t>
+          <t>3038.57</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-102.05</t>
+          <t>-100.24</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,135 +3720,135 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>406781400.7640288</t>
+          <t>406547619.4030173</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1025439175.0</t>
+          <t>602848357.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>504875555.4</t>
+          <t>558871972.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>361436106.5</t>
+          <t>401037331.1</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>536684043.66</t>
+          <t>530097463.36</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>143439448</t>
+          <t>157834641</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-25997581.64151972</t>
-        </is>
-      </c>
-      <c r="BC8" t="n">
-        <v>43485279.32</v>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-14290952.69601668</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>50095506.50425005</t>
+        </is>
+      </c>
+      <c r="BD8" t="n">
+        <v>602848357</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
           <t>99.0</t>
         </is>
       </c>
-      <c r="BF8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>2025/07/18</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>28.79</t>
-        </is>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
+          <t>29.29</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
           <t>上緯投控</t>
         </is>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BJ8" t="inlineStr">
         <is>
           <t>上緯投控</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BK8" t="inlineStr">
         <is>
           <t>綠能環保</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BL8" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>1.07</t>
-        </is>
-      </c>
       <c r="BM8" t="inlineStr">
         <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
           <t>-4.012262137013166</t>
         </is>
       </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>-1.72716244973935</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>4.777195903551031</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
-        </is>
-      </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
           <t>1.43</t>
         </is>
       </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>2.06</t>
-        </is>
-      </c>
       <c r="BT8" t="inlineStr">
         <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
           <t>-29.60</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>89.76</t>
-        </is>
-      </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>83.86</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3823,60 +3858,65 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>44.26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>12229</t>
+          <t>43.59</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
+          <t>11425</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
           <t>環保耐蝕材料39.58%、環保綠能材料33.76%、其他25.01%、循環經濟材料1.65% (2024年)</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>上緯投控-綠能環保-上市</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>綠能環保右上上市</t>
-        </is>
-      </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>綠能環保平上市</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>124.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
           <t>89.23</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
         <is>
           <t>** 風力發電 - 玻/碳纖、樹酯</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3895,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1122.329</t>
+          <t>8162.419</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,84 +3950,84 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>127.5</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-19.72</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-3.78</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>39.69</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-09-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>124.5</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>131.5</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
           <t>116.0</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-1.75</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>-1.89</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>22.56</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-09-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>124.5</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>115.0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>131.5</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>116.0</t>
-        </is>
-      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>0</t>
@@ -3995,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>10.87</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>24.92</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4066,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>1507</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>38.67</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>118.7</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>117.48</t>
+          <t>118.2</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>120.59</t>
+          <t>120.52</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>120.77</t>
+          <t>121.12</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-89.81</t>
+          <t>164.26</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-102.89</t>
+          <t>-102.05</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,135 +4156,135 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>406781400.7640288</t>
+          <t>406547619.4030173</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>129401839.0</t>
+          <t>1025439175.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>335984992.8</t>
+          <t>504875555.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>274141955.5</t>
+          <t>361436106.5</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>533459215.28</t>
+          <t>536684043.66</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>61843037</t>
+          <t>143439448</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-38630829.0899126</t>
-        </is>
-      </c>
-      <c r="BC9" t="n">
-        <v>-12788535.69</v>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>-25997581.64151972</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>43485279.32464111</t>
+        </is>
+      </c>
+      <c r="BD9" t="n">
+        <v>1025439175</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
           <t>99.0</t>
         </is>
       </c>
-      <c r="BF9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>2025/07/18</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>17.17</t>
-        </is>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
+          <t>28.79</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
           <t>上緯投控</t>
         </is>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BJ9" t="inlineStr">
         <is>
           <t>上緯投控</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BK9" t="inlineStr">
         <is>
           <t>綠能環保</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BL9" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>1.07</t>
-        </is>
-      </c>
       <c r="BM9" t="inlineStr">
         <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
           <t>-4.012262137013166</t>
         </is>
       </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>-1.72716244973935</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>4.777195903551031</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
           <t>-29.60</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>89.76</t>
-        </is>
-      </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>83.86</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4254,60 +4294,65 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>44.26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>12229</t>
+          <t>43.59</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
+          <t>11425</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
           <t>環保耐蝕材料39.58%、環保綠能材料33.76%、其他25.01%、循環經濟材料1.65% (2024年)</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>上緯投控-綠能環保-上市</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>綠能環保右上上市</t>
-        </is>
-      </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>115.0</t>
+          <t>綠能環保平上市</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
+          <t>127.5</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
           <t>89.23</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>** 風力發電 - 玻/碳纖、樹酯</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4326,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2764.556</t>
+          <t>1122.329</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,72 +4386,72 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>116.0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-8.92</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-3.78</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>22.56</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-09-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>124.5</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
           <t>115.0</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-0.88</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>-1.89</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>33.12</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-09-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>124.5</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>115.0</t>
-        </is>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -4421,12 +4466,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-7.63</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>8.44</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>6.61</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,47 +4502,47 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>1507</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>34.67</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>118.7</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -4507,27 +4552,27 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>120.88</t>
+          <t>120.59</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>120.53</t>
+          <t>120.77</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-40.51</t>
+          <t>-89.81</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-102.24</t>
+          <t>-102.89</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,135 +4592,135 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>406781400.7640288</t>
+          <t>406547619.4030173</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>310809119.0</t>
+          <t>129401839.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>375997635.0</t>
+          <t>335984992.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>282457551.4</t>
+          <t>274141955.5</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>556111164.18</t>
+          <t>533459215.28</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>93540083</t>
+          <t>61843037</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-43329427.88925355</t>
-        </is>
-      </c>
-      <c r="BC10" t="n">
-        <v>3281033.7</v>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>2025-11-10</t>
-        </is>
+          <t>-38630829.0899126</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>-12788535.69353741</t>
+        </is>
+      </c>
+      <c r="BD10" t="n">
+        <v>129401839</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
           <t>99.0</t>
         </is>
       </c>
-      <c r="BF10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>2025/07/18</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>16.16</t>
-        </is>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
+          <t>17.17</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
           <t>上緯投控</t>
         </is>
       </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BJ10" t="inlineStr">
         <is>
           <t>上緯投控</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BK10" t="inlineStr">
         <is>
           <t>綠能環保</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BL10" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>1.07</t>
-        </is>
-      </c>
       <c r="BM10" t="inlineStr">
         <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
           <t>-4.012262137013166</t>
         </is>
       </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>-1.72716244973935</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
         <is>
           <t>4.777195903551031</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ10" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
           <t>價跌量增</t>
         </is>
       </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>1.29</t>
-        </is>
-      </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
           <t>-29.60</t>
         </is>
       </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>89.76</t>
-        </is>
-      </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>83.86</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4685,60 +4730,65 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>44.26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>12229</t>
+          <t>43.59</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
+          <t>11425</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
           <t>環保耐蝕材料39.58%、環保綠能材料33.76%、其他25.01%、循環經濟材料1.65% (2024年)</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>上緯投控-綠能環保-上市</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>綠能環保右上上市</t>
-        </is>
-      </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>綠能環保平上市</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
+          <t>115.0</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>116.5</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
+          <t>114.0</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
+        <is>
           <t>116.0</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>107.0</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>115.0</t>
-        </is>
-      </c>
-      <c r="CG10" t="inlineStr">
+      <c r="CH10" t="inlineStr">
         <is>
           <t>89.23</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>** 風力發電 - 玻/碳纖、樹酯</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4757,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-10.12</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6206.994</t>
+          <t>2764.556</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>114.5</t>
+          <t>115.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-7.98</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>20.66</t>
+          <t>33.12</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4802,7 +4852,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4852,12 +4902,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>-8.03</t>
+          <t>-7.63</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>8.44</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-8.30</t>
+          <t>6.61</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>1507</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>34.67</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-5.61</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>121.3</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>118.02</t>
+          <t>117.48</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>121.33</t>
+          <t>120.88</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>120.34</t>
+          <t>120.53</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>141.22</t>
+          <t>-40.51</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-102.02</t>
+          <t>-102.24</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,135 +5028,135 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>406781400.7640288</t>
+          <t>406547619.4030173</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>725861373.0</t>
+          <t>310809119.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>342882863.8</t>
+          <t>375997635.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>284169034.6</t>
+          <t>282457551.4</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>580170679.38</t>
+          <t>556111164.18</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>58713829</t>
+          <t>93540083</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-51804057.26877595</t>
-        </is>
-      </c>
-      <c r="BC11" t="n">
-        <v>6683887.34</v>
-      </c>
-      <c r="BD11" t="inlineStr">
+          <t>-43329427.88925355</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>3281033.69811964</t>
+        </is>
+      </c>
+      <c r="BD11" t="n">
+        <v>310809119</v>
+      </c>
+      <c r="BE11" t="inlineStr">
         <is>
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="BE11" t="inlineStr">
+      <c r="BF11" t="inlineStr">
         <is>
           <t>99.0</t>
         </is>
       </c>
-      <c r="BF11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>2025/07/18</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>15.66</t>
-        </is>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
+          <t>16.16</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
           <t>上緯投控</t>
         </is>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BJ11" t="inlineStr">
         <is>
           <t>上緯投控</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>綠能環保</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BL11" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>1.07</t>
-        </is>
-      </c>
       <c r="BM11" t="inlineStr">
         <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
           <t>-4.012262137013166</t>
         </is>
       </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>-1.72716244973935</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>4.777195903551031</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ11" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>1.28</t>
-        </is>
-      </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
           <t>-29.60</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>89.76</t>
-        </is>
-      </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>83.86</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5116,60 +5166,65 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>44.26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>12229</t>
+          <t>43.59</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
+          <t>11425</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
           <t>環保耐蝕材料39.58%、環保綠能材料33.76%、其他25.01%、循環經濟材料1.65% (2024年)</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>上緯投控-綠能環保-上市</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
-        <is>
-          <t>綠能環保右上上市</t>
-        </is>
-      </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>綠能環保平上市</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>114.5</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>114.5</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
+          <t>115.0</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
+        <is>
           <t>89.23</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CI11" t="inlineStr">
         <is>
           <t>** 風力發電 - 玻/碳纖、樹酯</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5188,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>-10.12</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2671.658</t>
+          <t>6206.994</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>114.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-11.4</t>
+          <t>-7.51</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>20.66</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5233,7 +5288,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5283,12 +5338,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>-8.03</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>-8.30</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>1507</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>79.63</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>-5.61</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>123.3</t>
+          <t>121.3</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>118.8</t>
+          <t>118.02</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>121.87</t>
+          <t>121.33</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>120.15</t>
+          <t>120.34</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>333.84</t>
+          <t>141.22</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-102.73</t>
+          <t>-102.02</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,135 +5464,135 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>406781400.7640288</t>
+          <t>406547619.4030173</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>332866271.0</t>
+          <t>725861373.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>243202689.6</t>
+          <t>342882863.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>228452558.7</t>
+          <t>284169034.6</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>663144032.96</t>
+          <t>580170679.38</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>14750130</t>
+          <t>58713829</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-62438229.01579697</t>
-        </is>
-      </c>
-      <c r="BC12" t="n">
-        <v>-33163487.79</v>
-      </c>
-      <c r="BD12" t="inlineStr">
+          <t>-51804057.26877595</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>6683887.339839697</t>
+        </is>
+      </c>
+      <c r="BD12" t="n">
+        <v>725861373</v>
+      </c>
+      <c r="BE12" t="inlineStr">
         <is>
           <t>2025-11-10</t>
         </is>
       </c>
-      <c r="BE12" t="inlineStr">
+      <c r="BF12" t="inlineStr">
         <is>
           <t>99.0</t>
         </is>
       </c>
-      <c r="BF12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>2025/07/18</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>28.28</t>
-        </is>
-      </c>
       <c r="BH12" t="inlineStr">
         <is>
+          <t>15.66</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
           <t>上緯投控</t>
         </is>
       </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BJ12" t="inlineStr">
         <is>
           <t>上緯投控</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
+      <c r="BK12" t="inlineStr">
         <is>
           <t>綠能環保</t>
         </is>
       </c>
-      <c r="BK12" t="inlineStr">
+      <c r="BL12" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL12" t="inlineStr">
-        <is>
-          <t>1.07</t>
-        </is>
-      </c>
       <c r="BM12" t="inlineStr">
         <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
           <t>-4.012262137013166</t>
         </is>
       </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>-1.72716244973935</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
+      <c r="BP12" t="inlineStr">
         <is>
           <t>4.777195903551031</t>
         </is>
       </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ12" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
           <t>-29.60</t>
         </is>
       </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>89.76</t>
-        </is>
-      </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>83.86</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5547,60 +5602,65 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>44.26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>12229</t>
+          <t>43.59</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
+          <t>11425</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
           <t>環保耐蝕材料39.58%、環保綠能材料33.76%、其他25.01%、循環經濟材料1.65% (2024年)</t>
         </is>
       </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CB12" t="inlineStr">
         <is>
           <t>上緯投控-綠能環保-上市</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
-        <is>
-          <t>綠能環保右上上市</t>
-        </is>
-      </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>綠能環保平上市</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>114.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
+          <t>114.5</t>
+        </is>
+      </c>
+      <c r="CH12" t="inlineStr">
+        <is>
           <t>89.23</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>** 風力發電 - 玻/碳纖、樹酯</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/玻_碳纖.xlsx
+++ b/Result/checksun_type/玻_碳纖.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-6.88</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1507.376</t>
+          <t>1335.506</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-40.67</t>
+          <t>-43.46</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-7.39</t>
+          <t>-9.13</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1507</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,62 +1029,62 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>8.11</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>111.2</t>
+          <t>108.9</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>118.72</t>
+          <t>117.85</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>119.21</t>
+          <t>119.05</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>121.84</t>
+          <t>121.66</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-147.13</t>
+          <t>-123.04</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-108.61</t>
+          <t>-112.43</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>406547619.4030173</t>
+          <t>406264871.9246773</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>162713049.0</t>
+          <t>139648418.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>197662013.8</t>
+          <t>178684409.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>333134571.9</t>
+          <t>316018501.8</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>455062786.1</t>
+          <t>449139949.34</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-135472558</t>
+          <t>-137334092</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-12746324.66319245</t>
+          <t>-16854402.74357567</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-34264467.41575634</t>
+          <t>-39448832.1856834</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>162713049</v>
+        <v>139648418</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>7.58</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>83.86</t>
+          <t>82.28</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>43.59</t>
+          <t>43.53</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>11425</t>
+          <t>11210</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>-6.88</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>987.925</t>
+          <t>1507.376</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-7.04</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-43.50</t>
+          <t>-40.67</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-7.39</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,17 +1450,17 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1507</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1470,57 +1470,57 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>113.9</t>
+          <t>111.2</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>119.18</t>
+          <t>118.72</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>119.4</t>
+          <t>119.21</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>121.95</t>
+          <t>121.84</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-168.80</t>
+          <t>-147.13</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-105.44</t>
+          <t>-108.61</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>406547619.4030173</t>
+          <t>406264871.9246773</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>112670218.0</t>
+          <t>162713049.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>220026836.0</t>
+          <t>197662013.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>389449404.3</t>
+          <t>333134571.9</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>458112049.14</t>
+          <t>455062786.1</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-169422568</t>
+          <t>-135472558</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-8833935.071817197</t>
+          <t>-12746324.66319245</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-28105711.51529783</t>
+          <t>-34264467.41575634</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>112670218</v>
+        <v>162713049</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>15.15</t>
+          <t>7.58</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1643,22 +1643,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>83.86</t>
+          <t>82.28</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>43.59</t>
+          <t>43.53</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>11425</t>
+          <t>11210</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>113.5</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1722.133</t>
+          <t>987.925</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-22.70</t>
+          <t>-43.50</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1507</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-5.74</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>116.7</t>
+          <t>113.9</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>119.32</t>
+          <t>119.18</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>119.42</t>
+          <t>119.4</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>121.94</t>
+          <t>121.95</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-315.52</t>
+          <t>-168.80</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-103.15</t>
+          <t>-105.44</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>406547619.4030173</t>
+          <t>406264871.9246773</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>186253086.0</t>
+          <t>112670218.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>318062463.8</t>
+          <t>220026836.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>411469009.6</t>
+          <t>389449404.3</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>462766906.5</t>
+          <t>458112049.14</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-93406545</t>
+          <t>-169422568</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-5329975.718457082</t>
+          <t>-8833935.071817197</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-12941981.49623936</t>
+          <t>-28105711.51529783</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>186253086</v>
+        <v>112670218</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>15.15</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>83.86</t>
+          <t>82.28</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>43.59</t>
+          <t>43.53</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>11425</t>
+          <t>11210</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>113.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>112.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-5.63</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2649.921</t>
+          <t>1722.133</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-5.26</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>18.24</t>
+          <t>-22.70</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1507</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>17.28</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-8.90</t>
+          <t>-5.74</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>120.2</t>
+          <t>116.7</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>119.5</t>
+          <t>119.32</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>119.54</t>
+          <t>119.42</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>121.97</t>
+          <t>121.94</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-966.59</t>
+          <t>-315.52</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-100.66</t>
+          <t>-103.15</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>406547619.4030173</t>
+          <t>406264871.9246773</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>292137275.0</t>
+          <t>186253086.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>485899681.6</t>
+          <t>318062463.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>410942337.2</t>
+          <t>411469009.6</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>472868764.64</t>
+          <t>462766906.5</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>74957344</t>
+          <t>-93406545</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-3945974.667951212</t>
+          <t>-5329975.718457082</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>1298824.870138526</t>
+          <t>-12941981.49623936</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>292137275</v>
+        <v>186253086</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>83.86</t>
+          <t>82.28</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>43.59</t>
+          <t>43.53</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>11425</t>
+          <t>11210</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>115.5</t>
+          <t>108.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>117.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-5.63</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1998.479</t>
+          <t>2649.921</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,84 +2642,84 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>109.5</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-4.78</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-0.26</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>18.24</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-09-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>124.5</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>131.5</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
           <t>116.0</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-8.92</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>-3.78</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>9.33</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-09-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>124.5</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>115.0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>131.5</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>116.0</t>
-        </is>
-      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>0</t>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>6.10</t>
+          <t>8.09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1507</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>50.62</t>
+          <t>17.28</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>-8.90</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>120.2</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>119.62</t>
+          <t>119.5</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>119.79</t>
+          <t>119.54</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>121.95</t>
+          <t>121.97</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>20.33</t>
+          <t>-966.59</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-99.06</t>
+          <t>-100.66</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>406547619.4030173</t>
+          <t>406264871.9246773</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>234536441.0</t>
+          <t>292137275.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>453352594.4</t>
+          <t>485899681.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>414675114.7</t>
+          <t>410942337.2</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>478603045.96</t>
+          <t>472868764.64</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>38677479</t>
+          <t>74957344</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-4899574.583967528</t>
+          <t>-3945974.667951212</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>10251712.82674479</t>
+          <t>1298824.870138526</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>234536441</v>
+        <v>292137275</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>17.17</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>83.86</t>
+          <t>82.28</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>43.59</t>
+          <t>43.53</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>11425</t>
+          <t>11210</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>118.5</t>
+          <t>115.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>117.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>115.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>109.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-6.4</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2237.086</t>
+          <t>1998.479</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-12.68</t>
+          <t>-11.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>15.49</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>6.83</t>
+          <t>6.10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,72 +3194,72 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1507</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>40.74</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>80.25</t>
+          <t>50.62</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>121.3</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>119.4</t>
+          <t>119.62</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>119.79</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>121.73</t>
+          <t>121.95</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>506.78</t>
+          <t>20.33</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-99.11</t>
+          <t>-99.06</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>406547619.4030173</t>
+          <t>406264871.9246773</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>274537160.0</t>
+          <t>234536441.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>468607130.0</t>
+          <t>453352594.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>405744996.9</t>
+          <t>414675114.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>496122034.34</t>
+          <t>478603045.96</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>62862133</t>
+          <t>38677479</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-7654354.113187951</t>
+          <t>-4899574.583967528</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>28846938.09237003</t>
+          <t>10251712.82674479</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>274537160</v>
+        <v>234536441</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>21.21</t>
+          <t>17.17</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>83.86</t>
+          <t>82.28</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>43.59</t>
+          <t>43.53</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>11425</t>
+          <t>11210</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>118.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>115.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>-6.4</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4742.281</t>
+          <t>2237.086</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-20.19</t>
+          <t>-14.83</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>39.36</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>11.30</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14.48</t>
+          <t>6.83</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,77 +3630,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1507</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>40.74</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>70.67</t>
+          <t>80.25</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>6.49</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>120.2</t>
+          <t>121.3</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>119.4</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>120.2</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>121.48</t>
+          <t>121.73</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>3038.57</t>
+          <t>506.78</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-100.24</t>
+          <t>-99.11</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>406547619.4030173</t>
+          <t>406264871.9246773</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>602848357.0</t>
+          <t>274537160.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>558871972.6</t>
+          <t>468607130.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>401037331.1</t>
+          <t>405744996.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>530097463.36</t>
+          <t>496122034.34</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>157834641</t>
+          <t>62862133</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-14290952.69601668</t>
+          <t>-7654354.113187951</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>50095506.50425005</t>
+          <t>28846938.09237003</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>602848357</v>
+        <v>274537160</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>29.29</t>
+          <t>21.21</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>83.86</t>
+          <t>82.28</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>43.59</t>
+          <t>43.53</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>11425</t>
+          <t>11210</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8162.419</t>
+          <t>4742.281</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-19.72</t>
+          <t>-22.49</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>39.69</t>
+          <t>39.36</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>10.87</t>
+          <t>11.30</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>24.92</t>
+          <t>14.48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,12 +4066,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1507</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4081,62 +4081,62 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>38.67</t>
+          <t>70.67</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>6.49</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>120.2</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>118.2</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>120.52</t>
+          <t>120.2</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>121.12</t>
+          <t>121.48</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>164.26</t>
+          <t>3038.57</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-102.05</t>
+          <t>-100.24</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>406547619.4030173</t>
+          <t>406264871.9246773</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1025439175.0</t>
+          <t>602848357.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>504875555.4</t>
+          <t>558871972.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>361436106.5</t>
+          <t>401037331.1</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>536684043.66</t>
+          <t>530097463.36</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>143439448</t>
+          <t>157834641</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-25997581.64151972</t>
+          <t>-14290952.69601668</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>43485279.32464111</t>
+          <t>50095506.50425005</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>1025439175</v>
+        <v>602848357</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>29.29</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>83.86</t>
+          <t>82.28</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>43.59</t>
+          <t>43.53</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>11425</t>
+          <t>11210</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>124.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1122.329</t>
+          <t>8162.419</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,84 +4386,84 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>127.5</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-22.01</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-0.26</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>39.69</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-09-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>124.5</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>131.5</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
           <t>116.0</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-8.92</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>-3.78</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>22.56</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-09-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>124.5</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>115.0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>131.5</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>116.0</t>
-        </is>
-      </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>0</t>
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>10.87</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>24.92</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,77 +4502,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1507</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>38.67</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>118.7</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>117.48</t>
+          <t>118.2</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>120.59</t>
+          <t>120.52</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>120.77</t>
+          <t>121.12</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-89.81</t>
+          <t>164.26</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-102.89</t>
+          <t>-102.05</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>406547619.4030173</t>
+          <t>406264871.9246773</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>129401839.0</t>
+          <t>1025439175.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>335984992.8</t>
+          <t>504875555.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>274141955.5</t>
+          <t>361436106.5</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>533459215.28</t>
+          <t>536684043.66</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>61843037</t>
+          <t>143439448</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-38630829.0899126</t>
+          <t>-25997581.64151972</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-12788535.69353741</t>
+          <t>43485279.32464111</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>129401839</v>
+        <v>1025439175</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>17.17</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4695,22 +4695,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>83.86</t>
+          <t>82.28</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>43.59</t>
+          <t>43.53</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>11425</t>
+          <t>11210</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>115.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2764.556</t>
+          <t>1122.329</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,72 +4822,72 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>116.0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-11.0</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-0.26</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>22.56</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-09-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>124.5</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
           <t>115.0</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-7.98</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-3.78</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>33.12</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-09-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>124.5</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>115.0</t>
-        </is>
-      </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>-7.63</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>8.44</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>6.61</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,47 +4938,47 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1507</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>34.67</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>118.7</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -4988,27 +4988,27 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>120.88</t>
+          <t>120.59</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>120.53</t>
+          <t>120.77</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-40.51</t>
+          <t>-89.81</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-102.24</t>
+          <t>-102.89</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,50 +5028,50 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>406547619.4030173</t>
+          <t>406264871.9246773</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>310809119.0</t>
+          <t>129401839.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>375997635.0</t>
+          <t>335984992.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>282457551.4</t>
+          <t>274141955.5</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>556111164.18</t>
+          <t>533459215.28</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>93540083</t>
+          <t>61843037</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-43329427.88925355</t>
+          <t>-38630829.0899126</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>3281033.69811964</t>
+          <t>-12788535.69353741</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>310809119</v>
+        <v>129401839</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>16.16</t>
+          <t>17.17</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>83.86</t>
+          <t>82.28</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>43.59</t>
+          <t>43.53</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>11425</t>
+          <t>11210</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>115.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
+          <t>116.5</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
+          <t>114.0</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
+        <is>
           <t>116.0</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>107.0</t>
-        </is>
-      </c>
-      <c r="CG11" t="inlineStr">
-        <is>
-          <t>115.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-10.12</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>6206.994</t>
+          <t>2764.556</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>114.5</t>
+          <t>115.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-7.51</t>
+          <t>-10.05</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>20.66</t>
+          <t>33.12</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5338,12 +5338,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>-8.03</t>
+          <t>-7.63</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>8.44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-8.30</t>
+          <t>6.61</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1507</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>34.67</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-5.61</t>
+          <t>-4.17</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>121.3</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>118.02</t>
+          <t>117.48</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>121.33</t>
+          <t>120.88</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>120.34</t>
+          <t>120.53</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>141.22</t>
+          <t>-40.51</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-102.02</t>
+          <t>-102.24</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>406547619.4030173</t>
+          <t>406264871.9246773</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>725861373.0</t>
+          <t>310809119.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>342882863.8</t>
+          <t>375997635.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>284169034.6</t>
+          <t>282457551.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>580170679.38</t>
+          <t>556111164.18</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>58713829</t>
+          <t>93540083</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-51804057.26877595</t>
+          <t>-43329427.88925355</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>6683887.339839697</t>
+          <t>3281033.69811964</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>725861373</v>
+        <v>310809119</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>15.66</t>
+          <t>16.16</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>83.86</t>
+          <t>82.28</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>43.59</t>
+          <t>43.53</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>11425</t>
+          <t>11210</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>114.5</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>114.5</t>
+          <t>115.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/玻_碳纖.xlsx
+++ b/Result/checksun_type/玻_碳纖.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1335.506</t>
+          <t>823.014</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-43.46</t>
+          <t>-55.86</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-9.13</t>
+          <t>-7.83</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1336</t>
+          <t>823</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.38</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>8.11</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-7.68</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>108.9</t>
+          <t>108.2</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>117.85</t>
+          <t>117.2</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>119.05</t>
+          <t>118.83</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>121.66</t>
+          <t>121.47</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-123.04</t>
+          <t>-93.34</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-112.43</t>
+          <t>-116.22</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>406264871.9246773</t>
+          <t>405869227.0702006</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>139648418.0</t>
+          <t>86736509.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>178684409.2</t>
+          <t>137604256.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>316018501.8</t>
+          <t>311751968.8</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>449139949.34</t>
+          <t>442360683.54</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-137334092</t>
+          <t>-174147712</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-16854402.74357567</t>
+          <t>-21347580.76687022</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-39448832.1856834</t>
+          <t>-46060059.89499024</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>139648418</v>
+        <v>86736509</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>82.28</t>
+          <t>83.46</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>43.53</t>
+          <t>43.67</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>11210</t>
+          <t>11371</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-6.88</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1507.376</t>
+          <t>1335.506</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-40.67</t>
+          <t>-43.46</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-7.39</t>
+          <t>-9.13</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,12 +1450,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1336</t>
+          <t>823</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1465,62 +1465,62 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>8.11</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>111.2</t>
+          <t>108.9</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>118.72</t>
+          <t>117.85</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>119.21</t>
+          <t>119.05</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>121.84</t>
+          <t>121.66</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-147.13</t>
+          <t>-123.04</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-108.61</t>
+          <t>-112.43</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>406264871.9246773</t>
+          <t>405869227.0702006</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>162713049.0</t>
+          <t>139648418.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>197662013.8</t>
+          <t>178684409.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>333134571.9</t>
+          <t>316018501.8</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>455062786.1</t>
+          <t>449139949.34</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-135472558</t>
+          <t>-137334092</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-12746324.66319245</t>
+          <t>-16854402.74357567</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-34264467.41575634</t>
+          <t>-39448832.1856834</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>162713049</v>
+        <v>139648418</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>7.58</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>82.28</t>
+          <t>83.46</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>43.53</t>
+          <t>43.67</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>11210</t>
+          <t>11371</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>-6.88</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>987.925</t>
+          <t>1507.376</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-43.50</t>
+          <t>-40.67</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-7.39</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,17 +1886,17 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1336</t>
+          <t>823</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1906,57 +1906,57 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>113.9</t>
+          <t>111.2</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>119.18</t>
+          <t>118.72</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>119.4</t>
+          <t>119.21</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>121.95</t>
+          <t>121.84</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-168.80</t>
+          <t>-147.13</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-105.44</t>
+          <t>-108.61</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>406264871.9246773</t>
+          <t>405869227.0702006</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>112670218.0</t>
+          <t>162713049.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>220026836.0</t>
+          <t>197662013.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>389449404.3</t>
+          <t>333134571.9</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>458112049.14</t>
+          <t>455062786.1</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-169422568</t>
+          <t>-135472558</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-8833935.071817197</t>
+          <t>-12746324.66319245</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-28105711.51529783</t>
+          <t>-34264467.41575634</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>112670218</v>
+        <v>162713049</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>15.15</t>
+          <t>7.58</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>82.28</t>
+          <t>83.46</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>43.53</t>
+          <t>43.67</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>11210</t>
+          <t>11371</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>113.5</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1722.133</t>
+          <t>987.925</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-5.26</t>
+          <t>-7.55</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-22.70</t>
+          <t>-43.50</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1336</t>
+          <t>823</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-5.74</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>116.7</t>
+          <t>113.9</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>119.32</t>
+          <t>119.18</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>119.42</t>
+          <t>119.4</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>121.94</t>
+          <t>121.95</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-315.52</t>
+          <t>-168.80</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-103.15</t>
+          <t>-105.44</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>406264871.9246773</t>
+          <t>405869227.0702006</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>186253086.0</t>
+          <t>112670218.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>318062463.8</t>
+          <t>220026836.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>411469009.6</t>
+          <t>389449404.3</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>462766906.5</t>
+          <t>458112049.14</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-93406545</t>
+          <t>-169422568</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-5329975.718457082</t>
+          <t>-8833935.071817197</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-12941981.49623936</t>
+          <t>-28105711.51529783</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>186253086</v>
+        <v>112670218</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>15.15</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>82.28</t>
+          <t>83.46</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>43.53</t>
+          <t>43.67</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>11210</t>
+          <t>11371</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>113.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>112.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-5.63</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2649.921</t>
+          <t>1722.133</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-3.77</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>18.24</t>
+          <t>-22.70</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1336</t>
+          <t>823</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>17.28</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-8.90</t>
+          <t>-5.74</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>120.2</t>
+          <t>116.7</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>119.5</t>
+          <t>119.32</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>119.54</t>
+          <t>119.42</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>121.97</t>
+          <t>121.94</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-966.59</t>
+          <t>-315.52</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-100.66</t>
+          <t>-103.15</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>406264871.9246773</t>
+          <t>405869227.0702006</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>292137275.0</t>
+          <t>186253086.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>485899681.6</t>
+          <t>318062463.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>410942337.2</t>
+          <t>411469009.6</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>472868764.64</t>
+          <t>462766906.5</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>74957344</t>
+          <t>-93406545</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-3945974.667951212</t>
+          <t>-5329975.718457082</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>1298824.870138526</t>
+          <t>-12941981.49623936</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>292137275</v>
+        <v>186253086</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>82.28</t>
+          <t>83.46</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>43.53</t>
+          <t>43.67</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>11210</t>
+          <t>11371</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>115.5</t>
+          <t>108.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>117.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-5.63</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1998.479</t>
+          <t>2649.921</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,84 +3078,84 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>109.5</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-3.3</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-2.03</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>18.24</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-09-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>124.5</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>131.5</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
           <t>116.0</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-11.0</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>-0.26</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>9.33</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-09-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>124.5</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>115.0</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>131.5</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>116.0</t>
-        </is>
-      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>0</t>
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>6.10</t>
+          <t>8.09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1336</t>
+          <t>823</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>50.62</t>
+          <t>17.28</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>-8.90</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>120.2</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>119.62</t>
+          <t>119.5</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>119.79</t>
+          <t>119.54</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>121.95</t>
+          <t>121.97</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>20.33</t>
+          <t>-966.59</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-99.06</t>
+          <t>-100.66</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>406264871.9246773</t>
+          <t>405869227.0702006</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>234536441.0</t>
+          <t>292137275.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>453352594.4</t>
+          <t>485899681.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>414675114.7</t>
+          <t>410942337.2</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>478603045.96</t>
+          <t>472868764.64</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>38677479</t>
+          <t>74957344</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-4899574.583967528</t>
+          <t>-3945974.667951212</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>10251712.82674479</t>
+          <t>1298824.870138526</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>234536441</v>
+        <v>292137275</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>17.17</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>82.28</t>
+          <t>83.46</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>43.53</t>
+          <t>43.67</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>11210</t>
+          <t>11371</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>118.5</t>
+          <t>115.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>117.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>115.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>109.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-6.4</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2237.086</t>
+          <t>1998.479</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-14.83</t>
+          <t>-9.43</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>15.49</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>6.83</t>
+          <t>6.10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,72 +3630,72 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1336</t>
+          <t>823</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>40.74</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>80.25</t>
+          <t>50.62</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>121.3</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>119.4</t>
+          <t>119.62</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>119.79</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>121.73</t>
+          <t>121.95</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>506.78</t>
+          <t>20.33</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-99.11</t>
+          <t>-99.06</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>406264871.9246773</t>
+          <t>405869227.0702006</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>274537160.0</t>
+          <t>234536441.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>468607130.0</t>
+          <t>453352594.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>405744996.9</t>
+          <t>414675114.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>496122034.34</t>
+          <t>478603045.96</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>62862133</t>
+          <t>38677479</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-7654354.113187951</t>
+          <t>-4899574.583967528</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>28846938.09237003</t>
+          <t>10251712.82674479</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>274537160</v>
+        <v>234536441</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>21.21</t>
+          <t>17.17</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>82.28</t>
+          <t>83.46</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>43.53</t>
+          <t>43.67</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>11210</t>
+          <t>11371</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>118.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>115.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>-6.4</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4742.281</t>
+          <t>2237.086</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-22.49</t>
+          <t>-13.21</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>39.36</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>11.30</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14.48</t>
+          <t>6.83</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,77 +4066,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1336</t>
+          <t>823</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>40.74</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>70.67</t>
+          <t>80.25</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>6.49</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>120.2</t>
+          <t>121.3</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>119.4</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>120.2</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>121.48</t>
+          <t>121.73</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>3038.57</t>
+          <t>506.78</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-100.24</t>
+          <t>-99.11</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>406264871.9246773</t>
+          <t>405869227.0702006</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>602848357.0</t>
+          <t>274537160.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>558871972.6</t>
+          <t>468607130.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>401037331.1</t>
+          <t>405744996.9</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>530097463.36</t>
+          <t>496122034.34</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>157834641</t>
+          <t>62862133</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-14290952.69601668</t>
+          <t>-7654354.113187951</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>50095506.50425005</t>
+          <t>28846938.09237003</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>602848357</v>
+        <v>274537160</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>29.29</t>
+          <t>21.21</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>82.28</t>
+          <t>83.46</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>43.53</t>
+          <t>43.67</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>11210</t>
+          <t>11371</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8162.419</t>
+          <t>4742.281</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-22.01</t>
+          <t>-20.75</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>39.69</t>
+          <t>39.36</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>10.87</t>
+          <t>11.30</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>24.92</t>
+          <t>14.48</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,12 +4502,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1336</t>
+          <t>823</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4517,62 +4517,62 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>38.67</t>
+          <t>70.67</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>6.49</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>120.2</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>118.2</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>120.52</t>
+          <t>120.2</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>121.12</t>
+          <t>121.48</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>164.26</t>
+          <t>3038.57</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-102.05</t>
+          <t>-100.24</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>406264871.9246773</t>
+          <t>405869227.0702006</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1025439175.0</t>
+          <t>602848357.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>504875555.4</t>
+          <t>558871972.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>361436106.5</t>
+          <t>401037331.1</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>536684043.66</t>
+          <t>530097463.36</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>143439448</t>
+          <t>157834641</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-25997581.64151972</t>
+          <t>-14290952.69601668</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>43485279.32464111</t>
+          <t>50095506.50425005</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>1025439175</v>
+        <v>602848357</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>29.29</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>82.28</t>
+          <t>83.46</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>43.53</t>
+          <t>43.67</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>11210</t>
+          <t>11371</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>124.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1122.329</t>
+          <t>8162.419</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,84 +4822,84 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>127.5</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-20.28</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-2.03</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>39.69</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-09-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>124.5</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>131.5</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
           <t>116.0</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-11.0</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-0.26</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>22.56</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-09-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>124.5</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>115.0</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>131.5</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>116.0</t>
-        </is>
-      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>0</t>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>10.87</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>24.92</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1336</t>
+          <t>823</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>38.67</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>118.7</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>117.48</t>
+          <t>118.2</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>120.59</t>
+          <t>120.52</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>120.77</t>
+          <t>121.12</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-89.81</t>
+          <t>164.26</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-102.89</t>
+          <t>-102.05</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>406264871.9246773</t>
+          <t>405869227.0702006</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>129401839.0</t>
+          <t>1025439175.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>335984992.8</t>
+          <t>504875555.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>274141955.5</t>
+          <t>361436106.5</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>533459215.28</t>
+          <t>536684043.66</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>61843037</t>
+          <t>143439448</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-38630829.0899126</t>
+          <t>-25997581.64151972</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-12788535.69353741</t>
+          <t>43485279.32464111</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>129401839</v>
+        <v>1025439175</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>17.17</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>82.28</t>
+          <t>83.46</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>43.53</t>
+          <t>43.67</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>11210</t>
+          <t>11371</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>115.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2764.556</t>
+          <t>1122.329</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,72 +5258,72 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>116.0</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-9.43</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-2.03</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>22.56</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-09-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>124.5</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
           <t>115.0</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-10.05</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-0.26</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>33.12</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2025-10-31</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-09-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>124.5</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>115.0</t>
-        </is>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -5338,12 +5338,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>-7.63</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>8.44</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>6.61</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,47 +5374,47 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1336</t>
+          <t>823</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>34.67</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-4.17</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>118.7</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -5424,27 +5424,27 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>120.88</t>
+          <t>120.59</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>120.53</t>
+          <t>120.77</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-40.51</t>
+          <t>-89.81</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-102.24</t>
+          <t>-102.89</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,50 +5464,50 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>406264871.9246773</t>
+          <t>405869227.0702006</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>310809119.0</t>
+          <t>129401839.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>375997635.0</t>
+          <t>335984992.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>282457551.4</t>
+          <t>274141955.5</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>556111164.18</t>
+          <t>533459215.28</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>93540083</t>
+          <t>61843037</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-43329427.88925355</t>
+          <t>-38630829.0899126</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>3281033.69811964</t>
+          <t>-12788535.69353741</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>310809119</v>
+        <v>129401839</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>16.16</t>
+          <t>17.17</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>82.28</t>
+          <t>83.46</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>43.53</t>
+          <t>43.67</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>11210</t>
+          <t>11371</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>115.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
+          <t>116.5</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
+          <t>114.0</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
           <t>116.0</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>107.0</t>
-        </is>
-      </c>
-      <c r="CG12" t="inlineStr">
-        <is>
-          <t>115.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/玻_碳纖.xlsx
+++ b/Result/checksun_type/玻_碳纖.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>823.014</t>
+          <t>688.338</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>108.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-55.86</t>
+          <t>-46.80</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-7.83</t>
+          <t>-5.65</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>823</t>
+          <t>688</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>6.38</t>
+          <t>25.81</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>10.73</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-7.68</t>
+          <t>-7.54</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>108.2</t>
+          <t>107.9</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>117.2</t>
+          <t>116.7</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>118.83</t>
+          <t>118.76</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>121.47</t>
+          <t>121.31</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-93.34</t>
+          <t>-65.07</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.42</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-116.22</t>
+          <t>-119.37</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>405869227.0702006</t>
+          <t>405448591.3111588</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>86736509.0</t>
+          <t>74563221.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>137604256.0</t>
+          <t>115266283.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>311751968.8</t>
+          <t>216664373.4</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>442360683.54</t>
+          <t>435928377.96</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-174147712</t>
+          <t>-101398090</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-21347580.76687022</t>
+          <t>-25824785.94029485</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-46060059.89499024</t>
+          <t>-50449414.39413029</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>86736509</v>
+        <v>74563221</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,22 +1207,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>83.46</t>
+          <t>85.43</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>43.67</t>
+          <t>44.11</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>11371</t>
+          <t>11639</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>109.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>108.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1335.506</t>
+          <t>823.014</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-43.46</t>
+          <t>-55.86</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-9.13</t>
+          <t>-7.83</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>823</t>
+          <t>688</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.38</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>8.11</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-7.68</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>108.9</t>
+          <t>108.2</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>117.85</t>
+          <t>117.2</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>119.05</t>
+          <t>118.83</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>121.66</t>
+          <t>121.47</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-123.04</t>
+          <t>-93.34</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-112.43</t>
+          <t>-116.22</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>405869227.0702006</t>
+          <t>405448591.3111588</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>139648418.0</t>
+          <t>86736509.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>178684409.2</t>
+          <t>137604256.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>316018501.8</t>
+          <t>311751968.8</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>449139949.34</t>
+          <t>442360683.54</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-137334092</t>
+          <t>-174147712</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-16854402.74357567</t>
+          <t>-21347580.76687022</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-39448832.1856834</t>
+          <t>-46060059.89499024</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>139648418</v>
+        <v>86736509</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>83.46</t>
+          <t>85.43</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>43.67</t>
+          <t>44.11</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>11371</t>
+          <t>11639</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-6.88</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1507.376</t>
+          <t>1335.506</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>3.69</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-40.67</t>
+          <t>-43.46</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-7.39</t>
+          <t>-9.13</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,12 +1886,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>823</t>
+          <t>688</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1901,62 +1901,62 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>8.11</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>111.2</t>
+          <t>108.9</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>118.72</t>
+          <t>117.85</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>119.21</t>
+          <t>119.05</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>121.84</t>
+          <t>121.66</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-147.13</t>
+          <t>-123.04</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-108.61</t>
+          <t>-112.43</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>405869227.0702006</t>
+          <t>405448591.3111588</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>162713049.0</t>
+          <t>139648418.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>197662013.8</t>
+          <t>178684409.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>333134571.9</t>
+          <t>316018501.8</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>455062786.1</t>
+          <t>449139949.34</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-135472558</t>
+          <t>-137334092</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-12746324.66319245</t>
+          <t>-16854402.74357567</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-34264467.41575634</t>
+          <t>-39448832.1856834</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>162713049</v>
+        <v>139648418</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>7.58</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>83.46</t>
+          <t>85.43</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>43.67</t>
+          <t>44.11</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>11371</t>
+          <t>11639</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>-6.88</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>987.925</t>
+          <t>1507.376</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-7.55</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-43.50</t>
+          <t>-40.67</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-7.39</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,17 +2322,17 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>823</t>
+          <t>688</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -2342,57 +2342,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>113.9</t>
+          <t>111.2</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>119.18</t>
+          <t>118.72</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>119.4</t>
+          <t>119.21</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>121.95</t>
+          <t>121.84</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-168.80</t>
+          <t>-147.13</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-105.44</t>
+          <t>-108.61</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>405869227.0702006</t>
+          <t>405448591.3111588</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>112670218.0</t>
+          <t>162713049.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>220026836.0</t>
+          <t>197662013.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>389449404.3</t>
+          <t>333134571.9</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>458112049.14</t>
+          <t>455062786.1</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-169422568</t>
+          <t>-135472558</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-8833935.071817197</t>
+          <t>-12746324.66319245</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-28105711.51529783</t>
+          <t>-34264467.41575634</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>112670218</v>
+        <v>162713049</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>15.15</t>
+          <t>7.58</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>83.46</t>
+          <t>85.43</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>43.67</t>
+          <t>44.11</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>11371</t>
+          <t>11639</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>113.5</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1722.133</t>
+          <t>987.925</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-3.77</t>
+          <t>-5.07</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-22.70</t>
+          <t>-43.50</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>823</t>
+          <t>688</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-5.74</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>116.7</t>
+          <t>113.9</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>119.32</t>
+          <t>119.18</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>119.42</t>
+          <t>119.4</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>121.94</t>
+          <t>121.95</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-315.52</t>
+          <t>-168.80</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-103.15</t>
+          <t>-105.44</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>405869227.0702006</t>
+          <t>405448591.3111588</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>186253086.0</t>
+          <t>112670218.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>318062463.8</t>
+          <t>220026836.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>411469009.6</t>
+          <t>389449404.3</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>462766906.5</t>
+          <t>458112049.14</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-93406545</t>
+          <t>-169422568</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-5329975.718457082</t>
+          <t>-8833935.071817197</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-12941981.49623936</t>
+          <t>-28105711.51529783</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>186253086</v>
+        <v>112670218</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>15.15</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>83.46</t>
+          <t>85.43</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>43.67</t>
+          <t>44.11</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>11371</t>
+          <t>11639</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>113.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>112.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-5.63</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2649.921</t>
+          <t>1722.133</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-3.3</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>18.24</t>
+          <t>-22.70</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>823</t>
+          <t>688</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>17.28</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-8.90</t>
+          <t>-5.74</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>120.2</t>
+          <t>116.7</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>119.5</t>
+          <t>119.32</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>119.54</t>
+          <t>119.42</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>121.97</t>
+          <t>121.94</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-966.59</t>
+          <t>-315.52</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-100.66</t>
+          <t>-103.15</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>405869227.0702006</t>
+          <t>405448591.3111588</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>292137275.0</t>
+          <t>186253086.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>485899681.6</t>
+          <t>318062463.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>410942337.2</t>
+          <t>411469009.6</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>472868764.64</t>
+          <t>462766906.5</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>74957344</t>
+          <t>-93406545</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-3945974.667951212</t>
+          <t>-5329975.718457082</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>1298824.870138526</t>
+          <t>-12941981.49623936</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>292137275</v>
+        <v>186253086</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,12 +3387,12 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>83.46</t>
+          <t>85.43</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>43.67</t>
+          <t>44.11</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>11371</t>
+          <t>11639</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>115.5</t>
+          <t>108.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>117.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-5.63</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1998.479</t>
+          <t>2649.921</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,84 +3514,84 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>109.5</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-0.92</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-1.47</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>18.24</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-09-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>124.5</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>131.5</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
           <t>116.0</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-9.43</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>-2.03</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>9.33</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-09-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>124.5</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>115.0</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>131.5</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>116.0</t>
-        </is>
-      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>0</t>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>6.10</t>
+          <t>8.09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,77 +3630,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>823</t>
+          <t>688</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>50.62</t>
+          <t>17.28</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>-8.90</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>120.2</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>119.62</t>
+          <t>119.5</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>119.79</t>
+          <t>119.54</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>121.95</t>
+          <t>121.97</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>20.33</t>
+          <t>-966.59</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-99.06</t>
+          <t>-100.66</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>405869227.0702006</t>
+          <t>405448591.3111588</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>234536441.0</t>
+          <t>292137275.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>453352594.4</t>
+          <t>485899681.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>414675114.7</t>
+          <t>410942337.2</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>478603045.96</t>
+          <t>472868764.64</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>38677479</t>
+          <t>74957344</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-4899574.583967528</t>
+          <t>-3945974.667951212</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>10251712.82674479</t>
+          <t>1298824.870138526</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>234536441</v>
+        <v>292137275</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>17.17</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>83.46</t>
+          <t>85.43</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>43.67</t>
+          <t>44.11</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>11371</t>
+          <t>11639</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>118.5</t>
+          <t>115.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>117.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>115.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>109.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-6.4</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2237.086</t>
+          <t>1998.479</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-13.21</t>
+          <t>-6.91</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>15.49</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>6.83</t>
+          <t>6.10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,72 +4066,72 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>823</t>
+          <t>688</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>40.74</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>80.25</t>
+          <t>50.62</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>121.3</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>119.4</t>
+          <t>119.62</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>119.79</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>121.73</t>
+          <t>121.95</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>506.78</t>
+          <t>20.33</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-99.11</t>
+          <t>-99.06</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>405869227.0702006</t>
+          <t>405448591.3111588</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>274537160.0</t>
+          <t>234536441.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>468607130.0</t>
+          <t>453352594.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>405744996.9</t>
+          <t>414675114.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>496122034.34</t>
+          <t>478603045.96</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>62862133</t>
+          <t>38677479</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-7654354.113187951</t>
+          <t>-4899574.583967528</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>28846938.09237003</t>
+          <t>10251712.82674479</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>274537160</v>
+        <v>234536441</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>21.21</t>
+          <t>17.17</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>83.46</t>
+          <t>85.43</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>43.67</t>
+          <t>44.11</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>11371</t>
+          <t>11639</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>118.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>115.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>-6.4</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4742.281</t>
+          <t>2237.086</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-20.75</t>
+          <t>-10.6</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>39.36</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>11.30</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14.48</t>
+          <t>6.83</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,77 +4502,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>823</t>
+          <t>688</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>40.74</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>70.67</t>
+          <t>80.25</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>6.49</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>120.2</t>
+          <t>121.3</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>119.4</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>120.2</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>121.48</t>
+          <t>121.73</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>3038.57</t>
+          <t>506.78</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-100.24</t>
+          <t>-99.11</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>405869227.0702006</t>
+          <t>405448591.3111588</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>602848357.0</t>
+          <t>274537160.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>558871972.6</t>
+          <t>468607130.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>401037331.1</t>
+          <t>405744996.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>530097463.36</t>
+          <t>496122034.34</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>157834641</t>
+          <t>62862133</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-14290952.69601668</t>
+          <t>-7654354.113187951</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>50095506.50425005</t>
+          <t>28846938.09237003</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>602848357</v>
+        <v>274537160</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>29.29</t>
+          <t>21.21</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>83.46</t>
+          <t>85.43</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>43.67</t>
+          <t>44.11</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>11371</t>
+          <t>11639</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8162.419</t>
+          <t>4742.281</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-20.28</t>
+          <t>-17.97</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>39.69</t>
+          <t>39.36</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>10.87</t>
+          <t>11.30</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>24.92</t>
+          <t>14.48</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,12 +4938,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>823</t>
+          <t>688</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4953,62 +4953,62 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>38.67</t>
+          <t>70.67</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>6.49</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>120.2</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>118.2</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>120.52</t>
+          <t>120.2</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>121.12</t>
+          <t>121.48</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>164.26</t>
+          <t>3038.57</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-102.05</t>
+          <t>-100.24</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>405869227.0702006</t>
+          <t>405448591.3111588</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1025439175.0</t>
+          <t>602848357.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>504875555.4</t>
+          <t>558871972.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>361436106.5</t>
+          <t>401037331.1</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>536684043.66</t>
+          <t>530097463.36</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>143439448</t>
+          <t>157834641</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-25997581.64151972</t>
+          <t>-14290952.69601668</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>43485279.32464111</t>
+          <t>50095506.50425005</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>1025439175</v>
+        <v>602848357</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>29.29</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>83.46</t>
+          <t>85.43</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>43.67</t>
+          <t>44.11</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>11371</t>
+          <t>11639</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>124.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1122.329</t>
+          <t>8162.419</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,84 +5258,84 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>127.5</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-17.51</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-1.47</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>39.69</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-09-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>124.5</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>131.5</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
           <t>116.0</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-9.43</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-2.03</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>22.56</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-09-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>124.5</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>115.0</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>131.5</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>116.0</t>
-        </is>
-      </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>0</t>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>10.87</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>24.92</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>823</t>
+          <t>688</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>38.67</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>118.7</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>117.48</t>
+          <t>118.2</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>120.59</t>
+          <t>120.52</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>120.77</t>
+          <t>121.12</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-89.81</t>
+          <t>164.26</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-102.89</t>
+          <t>-102.05</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>405869227.0702006</t>
+          <t>405448591.3111588</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>129401839.0</t>
+          <t>1025439175.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>335984992.8</t>
+          <t>504875555.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>274141955.5</t>
+          <t>361436106.5</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>533459215.28</t>
+          <t>536684043.66</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>61843037</t>
+          <t>143439448</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-38630829.0899126</t>
+          <t>-25997581.64151972</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-12788535.69353741</t>
+          <t>43485279.32464111</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>129401839</v>
+        <v>1025439175</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>17.17</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>83.46</t>
+          <t>85.43</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>43.67</t>
+          <t>44.11</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>11371</t>
+          <t>11639</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>115.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/玻_碳纖.xlsx
+++ b/Result/checksun_type/玻_碳纖.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>107.9</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>116.7</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>118.76</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>116.7</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>118.76</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>74563221.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>115266283.0</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>115266283</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>216664373.4</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>435928377.96</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>435928377.96</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-50449414.39413029</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>74563221</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>74563221.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>108.2</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>117.2</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>118.83</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>117.2</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>118.83</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>86736509.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>137604256.0</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>137604256</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>311751968.8</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>442360683.54</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>442360683.54</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-46060059.89499024</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>86736509</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>86736509.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>108.9</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>117.85</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>119.05</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>117.85</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>119.05</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>139648418.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>178684409.2</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>178684409.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>316018501.8</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>449139949.34</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>449139949.34</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-39448832.1856834</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>139648418</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>139648418.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>111.2</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>118.72</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>119.21</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>118.72</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>119.21</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>162713049.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>197662013.8</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>197662013.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>333134571.9</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>455062786.1</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>455062786.1</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-34264467.41575634</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>162713049</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>162713049.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>113.9</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>119.18</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>119.4</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>119.18</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>119.4</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>112670218.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>220026836.0</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>220026836</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>389449404.3</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>458112049.14</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>458112049.14</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-28105711.51529783</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>112670218</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>112670218.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>116.7</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>119.32</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>119.42</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>119.32</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>119.42</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>186253086.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>318062463.8</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>318062463.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>411469009.6</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>462766906.5</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>462766906.5</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-12941981.49623936</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>186253086</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>186253086.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>120.2</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>119.5</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>119.54</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>119.5</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>119.54</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>292137275.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>485899681.6</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>485899681.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>410942337.2</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>472868764.64</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>472868764.64</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>1298824.870138526</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>292137275</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>292137275.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>121.5</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>119.62</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>119.79</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>119.62</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>119.79</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>234536441.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>453352594.4</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>453352594.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>414675114.7</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>478603045.96</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>478603045.96</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>10251712.82674479</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>234536441</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>234536441.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>121.3</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>119.4</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>120.0</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>119.4</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>120</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>274537160.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>468607130.0</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>468607130</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>405744996.9</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>496122034.34</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>496122034.34</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>28846938.09237003</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>274537160</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>274537160.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>120.2</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>119.0</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>120.2</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>119</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>120.2</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>602848357.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>558871972.6</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>558871972.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>401037331.1</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>530097463.36</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>530097463.36</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>50095506.50425005</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>602848357</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>602848357.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>120.0</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>118.2</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>120.52</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>120.52</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>1025439175.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>504875555.4</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>504875555.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>361436106.5</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>536684043.66</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>536684043.66</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>43485279.32464111</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>1025439175</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>1025439175.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>

--- a/Result/checksun_type/玻_碳纖.xlsx
+++ b/Result/checksun_type/玻_碳纖.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>688.338</t>
+          <t>497.76</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-2.7</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-46.80</t>
+          <t>-36.00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-5.65</t>
+          <t>-5.22</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,32 +1019,32 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>498</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>25.81</t>
+          <t>39.13</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>10.73</t>
+          <t>23.77</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-7.54</t>
+          <t>-7.90</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
@@ -1054,33 +1054,33 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>107.9</t>
+          <t>106.9</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>116.7</v>
+        <v>116.08</v>
       </c>
       <c r="AN2" t="n">
-        <v>118.76</v>
+        <v>118.57</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>121.31</t>
+          <t>121.12</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-65.07</t>
+          <t>-45.24</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-3.42</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-119.37</t>
+          <t>-121.84</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>405448591.3111588</t>
+          <t>404985181.6692858</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>74563221.0</t>
+          <t>54041228.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>115266283</v>
+        <v>103540485</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>216664373.4</t>
+          <t>161783660.5</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>435928377.96</v>
+        <v>428520261.8</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-101398090</t>
+          <t>-58243175</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-25824785.94029485</t>
+          <t>-30128646.05081488</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-50449414.39413029</t>
+          <t>-53799876.65867507</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>74563221.0</t>
+          <t>54041228.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>10.10</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>85.43</t>
+          <t>85.83</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>44.11</t>
+          <t>44.32</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>11639</t>
+          <t>11693</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1276,12 +1276,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>823.014</t>
+          <t>688.338</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>108.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-2.7</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-55.86</t>
+          <t>-46.80</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-7.83</t>
+          <t>-5.65</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1449,68 +1449,68 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>498</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>6.38</t>
+          <t>25.81</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>10.73</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-7.68</t>
+          <t>-7.54</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>108.2</t>
+          <t>107.9</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>117.2</v>
+        <v>116.7</v>
       </c>
       <c r="AN3" t="n">
-        <v>118.83</v>
+        <v>118.76</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>121.47</t>
+          <t>121.31</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-93.34</t>
+          <t>-65.07</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.42</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-116.22</t>
+          <t>-119.37</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>405448591.3111588</t>
+          <t>404985181.6692858</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>86736509.0</t>
+          <t>74563221.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>137604256</v>
+        <v>115266283</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>311751968.8</t>
+          <t>216664373.4</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>442360683.54</v>
+        <v>435928377.96</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-174147712</t>
+          <t>-101398090</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-21347580.76687022</t>
+          <t>-25824785.94029485</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-46060059.89499024</t>
+          <t>-50449414.39413029</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>86736509.0</t>
+          <t>74563221.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>85.43</t>
+          <t>85.83</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>44.11</t>
+          <t>44.32</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>11639</t>
+          <t>11693</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>109.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>108.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1335.506</t>
+          <t>823.014</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.69</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-2.7</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-43.46</t>
+          <t>-55.86</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-9.13</t>
+          <t>-7.83</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1879,68 +1879,68 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>498</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.38</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>8.11</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-7.68</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>108.9</t>
+          <t>108.2</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>117.85</v>
+        <v>117.2</v>
       </c>
       <c r="AN4" t="n">
-        <v>119.05</v>
+        <v>118.83</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>121.66</t>
+          <t>121.47</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-123.04</t>
+          <t>-93.34</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-112.43</t>
+          <t>-116.22</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>405448591.3111588</t>
+          <t>404985181.6692858</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>139648418.0</t>
+          <t>86736509.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>178684409.2</v>
+        <v>137604256</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>316018501.8</t>
+          <t>311751968.8</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>449139949.34</v>
+        <v>442360683.54</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-137334092</t>
+          <t>-174147712</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-16854402.74357567</t>
+          <t>-21347580.76687022</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-39448832.1856834</t>
+          <t>-46060059.89499024</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>139648418.0</t>
+          <t>86736509.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>85.43</t>
+          <t>85.83</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>44.11</t>
+          <t>44.32</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>11639</t>
+          <t>11693</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-6.88</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1507.376</t>
+          <t>1335.506</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-2.7</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-40.67</t>
+          <t>-43.46</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-7.39</t>
+          <t>-9.13</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>498</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2319,58 +2319,58 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>8.11</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>111.2</t>
+          <t>108.9</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>118.72</v>
+        <v>117.85</v>
       </c>
       <c r="AN5" t="n">
-        <v>119.21</v>
+        <v>119.05</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>121.84</t>
+          <t>121.66</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-147.13</t>
+          <t>-123.04</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-108.61</t>
+          <t>-112.43</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>405448591.3111588</t>
+          <t>404985181.6692858</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>162713049.0</t>
+          <t>139648418.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>197662013.8</v>
+        <v>178684409.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>333134571.9</t>
+          <t>316018501.8</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>455062786.1</v>
+        <v>449139949.34</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-135472558</t>
+          <t>-137334092</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-12746324.66319245</t>
+          <t>-16854402.74357567</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-34264467.41575634</t>
+          <t>-39448832.1856834</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>162713049.0</t>
+          <t>139648418.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>7.58</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>85.43</t>
+          <t>85.83</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>44.11</t>
+          <t>44.32</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>11639</t>
+          <t>11693</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>-6.88</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>987.925</t>
+          <t>1507.376</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-5.07</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-2.7</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-43.50</t>
+          <t>-40.67</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-7.39</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>498</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -2754,53 +2754,53 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>113.9</t>
+          <t>111.2</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>119.18</v>
+        <v>118.72</v>
       </c>
       <c r="AN6" t="n">
-        <v>119.4</v>
+        <v>119.21</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>121.95</t>
+          <t>121.84</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-168.80</t>
+          <t>-147.13</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-105.44</t>
+          <t>-108.61</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>405448591.3111588</t>
+          <t>404985181.6692858</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>112670218.0</t>
+          <t>162713049.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>220026836</v>
+        <v>197662013.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>389449404.3</t>
+          <t>333134571.9</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>458112049.14</v>
+        <v>455062786.1</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-169422568</t>
+          <t>-135472558</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-8833935.071817197</t>
+          <t>-12746324.66319245</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-28105711.51529783</t>
+          <t>-34264467.41575634</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>112670218.0</t>
+          <t>162713049.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>15.15</t>
+          <t>7.58</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>85.43</t>
+          <t>85.83</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>44.11</t>
+          <t>44.32</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>11639</t>
+          <t>11693</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>113.5</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1722.133</t>
+          <t>987.925</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-2.7</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-22.70</t>
+          <t>-43.50</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,68 +3169,68 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>498</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-5.74</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>116.7</t>
+          <t>113.9</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>119.32</v>
+        <v>119.18</v>
       </c>
       <c r="AN7" t="n">
-        <v>119.42</v>
+        <v>119.4</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>121.94</t>
+          <t>121.95</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-315.52</t>
+          <t>-168.80</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-103.15</t>
+          <t>-105.44</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>405448591.3111588</t>
+          <t>404985181.6692858</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>186253086.0</t>
+          <t>112670218.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>318062463.8</v>
+        <v>220026836</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>411469009.6</t>
+          <t>389449404.3</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>462766906.5</v>
+        <v>458112049.14</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-93406545</t>
+          <t>-169422568</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-5329975.718457082</t>
+          <t>-8833935.071817197</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-12941981.49623936</t>
+          <t>-28105711.51529783</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>186253086.0</t>
+          <t>112670218.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>15.15</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>85.43</t>
+          <t>85.83</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>44.11</t>
+          <t>44.32</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>11639</t>
+          <t>11693</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>113.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>112.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-5.63</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2649.921</t>
+          <t>1722.133</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-2.7</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>18.24</t>
+          <t>-22.70</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3599,68 +3599,68 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>498</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>17.28</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-8.90</t>
+          <t>-5.74</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>120.2</t>
+          <t>116.7</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>119.5</v>
+        <v>119.32</v>
       </c>
       <c r="AN8" t="n">
-        <v>119.54</v>
+        <v>119.42</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>121.97</t>
+          <t>121.94</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-966.59</t>
+          <t>-315.52</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-100.66</t>
+          <t>-103.15</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>405448591.3111588</t>
+          <t>404985181.6692858</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>292137275.0</t>
+          <t>186253086.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>485899681.6</v>
+        <v>318062463.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>410942337.2</t>
+          <t>411469009.6</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>472868764.64</v>
+        <v>462766906.5</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>74957344</t>
+          <t>-93406545</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-3945974.667951212</t>
+          <t>-5329975.718457082</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>1298824.870138526</t>
+          <t>-12941981.49623936</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>292137275.0</t>
+          <t>186253086.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>85.43</t>
+          <t>85.83</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>44.11</t>
+          <t>44.32</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>11639</t>
+          <t>11693</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>115.5</t>
+          <t>108.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>117.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3883,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-5.63</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1998.479</t>
+          <t>2649.921</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,84 +3908,84 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>109.5</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-0.46</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-2.7</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>18.24</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-09-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>124.5</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>131.5</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
           <t>116.0</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-6.91</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>-1.47</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>9.33</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-09-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>124.5</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>115.0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>131.5</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>116.0</t>
-        </is>
-      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>0</t>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>6.10</t>
+          <t>8.09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4029,68 +4029,68 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>498</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>50.62</t>
+          <t>17.28</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>-8.90</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>120.2</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>119.62</v>
+        <v>119.5</v>
       </c>
       <c r="AN9" t="n">
-        <v>119.79</v>
+        <v>119.54</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>121.95</t>
+          <t>121.97</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>20.33</t>
+          <t>-966.59</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-99.06</t>
+          <t>-100.66</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>405448591.3111588</t>
+          <t>404985181.6692858</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>234536441.0</t>
+          <t>292137275.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>453352594.4</v>
+        <v>485899681.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>414675114.7</t>
+          <t>410942337.2</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>478603045.96</v>
+        <v>472868764.64</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>38677479</t>
+          <t>74957344</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-4899574.583967528</t>
+          <t>-3945974.667951212</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>10251712.82674479</t>
+          <t>1298824.870138526</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>234536441.0</t>
+          <t>292137275.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>17.17</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>85.43</t>
+          <t>85.83</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>44.11</t>
+          <t>44.32</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>11639</t>
+          <t>11693</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>118.5</t>
+          <t>115.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>117.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>115.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>109.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-6.4</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2237.086</t>
+          <t>1998.479</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-10.6</t>
+          <t>-6.42</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-2.7</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>15.49</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>6.83</t>
+          <t>6.10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4459,63 +4459,63 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>498</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>40.74</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>80.25</t>
+          <t>50.62</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>121.3</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>119.4</v>
+        <v>119.62</v>
       </c>
       <c r="AN10" t="n">
-        <v>120</v>
+        <v>119.79</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>121.73</t>
+          <t>121.95</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>506.78</t>
+          <t>20.33</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-99.11</t>
+          <t>-99.06</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>405448591.3111588</t>
+          <t>404985181.6692858</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>274537160.0</t>
+          <t>234536441.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>468607130</v>
+        <v>453352594.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>405744996.9</t>
+          <t>414675114.7</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>496122034.34</v>
+        <v>478603045.96</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>62862133</t>
+          <t>38677479</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-7654354.113187951</t>
+          <t>-4899574.583967528</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>28846938.09237003</t>
+          <t>10251712.82674479</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>274537160.0</t>
+          <t>234536441.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>21.21</t>
+          <t>17.17</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>85.43</t>
+          <t>85.83</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>44.11</t>
+          <t>44.32</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>11639</t>
+          <t>11693</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>118.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>115.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>-6.4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4742.281</t>
+          <t>2237.086</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-17.97</t>
+          <t>-10.09</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-2.7</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>39.36</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>11.30</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14.48</t>
+          <t>6.83</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4889,68 +4889,68 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>498</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>40.74</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>70.67</t>
+          <t>80.25</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>6.49</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>120.2</t>
+          <t>121.3</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>119</v>
+        <v>119.4</v>
       </c>
       <c r="AN11" t="n">
-        <v>120.2</v>
+        <v>120</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>121.48</t>
+          <t>121.73</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>3038.57</t>
+          <t>506.78</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-100.24</t>
+          <t>-99.11</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>405448591.3111588</t>
+          <t>404985181.6692858</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>602848357.0</t>
+          <t>274537160.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>558871972.6</v>
+        <v>468607130</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>401037331.1</t>
+          <t>405744996.9</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>530097463.36</v>
+        <v>496122034.34</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>157834641</t>
+          <t>62862133</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-14290952.69601668</t>
+          <t>-7654354.113187951</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>50095506.50425005</t>
+          <t>28846938.09237003</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>602848357.0</t>
+          <t>274537160.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>29.29</t>
+          <t>21.21</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>85.43</t>
+          <t>85.83</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>44.11</t>
+          <t>44.32</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>11639</t>
+          <t>11693</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8162.419</t>
+          <t>4742.281</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-17.51</t>
+          <t>-17.43</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-2.7</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>39.69</t>
+          <t>39.36</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>10.87</t>
+          <t>11.30</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>24.92</t>
+          <t>14.48</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>498</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5329,58 +5329,58 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>38.67</t>
+          <t>70.67</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>6.49</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>120.2</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>118.2</v>
+        <v>119</v>
       </c>
       <c r="AN12" t="n">
-        <v>120.52</v>
+        <v>120.2</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>121.12</t>
+          <t>121.48</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>164.26</t>
+          <t>3038.57</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-102.05</t>
+          <t>-100.24</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>405448591.3111588</t>
+          <t>404985181.6692858</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>1025439175.0</t>
+          <t>602848357.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>504875555.4</v>
+        <v>558871972.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>361436106.5</t>
+          <t>401037331.1</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>536684043.66</v>
+        <v>530097463.36</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>143439448</t>
+          <t>157834641</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-25997581.64151972</t>
+          <t>-14290952.69601668</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>43485279.32464111</t>
+          <t>50095506.50425005</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>1025439175.0</t>
+          <t>602848357.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>29.29</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>85.43</t>
+          <t>85.83</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>44.11</t>
+          <t>44.32</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>11639</t>
+          <t>11693</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>124.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/玻_碳纖.xlsx
+++ b/Result/checksun_type/玻_碳纖.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>497.76</t>
+          <t>417.291</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-36.00</t>
+          <t>-42.34</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-5.22</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>417</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>39.13</t>
+          <t>36.84</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>23.77</t>
+          <t>33.93</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-7.90</t>
+          <t>-6.98</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>106.9</t>
+          <t>107.2</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>116.08</v>
+        <v>115.25</v>
       </c>
       <c r="AN2" t="n">
-        <v>118.57</v>
+        <v>118.34</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>121.12</t>
+          <t>120.96</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-45.24</t>
+          <t>-33.76</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>-3.41</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-121.84</t>
+          <t>-123.85</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>404985181.6692858</t>
+          <t>404504464.360913</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>54041228.0</t>
+          <t>45334899.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>103540485</v>
+        <v>80064855</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>161783660.5</t>
+          <t>138863434.4</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>428520261.8</v>
+        <v>419038513.76</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-58243175</t>
+          <t>-58798579</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-30128646.05081488</t>
+          <t>-34024727.88951867</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-53799876.65867507</t>
+          <t>-55453178.00238952</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>54041228.0</t>
+          <t>45334899.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>10.10</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>85.83</t>
+          <t>85.04</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>44.32</t>
+          <t>44.52</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>11693</t>
+          <t>11586</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>688.338</t>
+          <t>497.76</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-46.80</t>
+          <t>-36.00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-5.65</t>
+          <t>-5.22</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,37 +1444,37 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>417</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>25.81</t>
+          <t>39.13</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>10.73</t>
+          <t>23.77</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-7.54</t>
+          <t>-7.90</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1484,33 +1484,33 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>107.9</t>
+          <t>106.9</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>116.7</v>
+        <v>116.08</v>
       </c>
       <c r="AN3" t="n">
-        <v>118.76</v>
+        <v>118.57</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>121.31</t>
+          <t>121.12</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-65.07</t>
+          <t>-45.24</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-3.42</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-119.37</t>
+          <t>-121.84</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>404985181.6692858</t>
+          <t>404504464.360913</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>74563221.0</t>
+          <t>54041228.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>115266283</v>
+        <v>103540485</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>216664373.4</t>
+          <t>161783660.5</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>435928377.96</v>
+        <v>428520261.8</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-101398090</t>
+          <t>-58243175</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-25824785.94029485</t>
+          <t>-30128646.05081488</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-50449414.39413029</t>
+          <t>-53799876.65867507</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>74563221.0</t>
+          <t>54041228.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>10.10</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>85.83</t>
+          <t>85.04</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>44.32</t>
+          <t>44.52</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>11693</t>
+          <t>11586</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1706,12 +1706,12 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>823.014</t>
+          <t>688.338</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>108.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-55.86</t>
+          <t>-46.80</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-7.83</t>
+          <t>-5.65</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>417</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>6.38</t>
+          <t>25.81</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>10.73</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-7.68</t>
+          <t>-7.54</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>108.2</t>
+          <t>107.9</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>117.2</v>
+        <v>116.7</v>
       </c>
       <c r="AN4" t="n">
-        <v>118.83</v>
+        <v>118.76</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>121.47</t>
+          <t>121.31</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-93.34</t>
+          <t>-65.07</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.42</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-116.22</t>
+          <t>-119.37</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>404985181.6692858</t>
+          <t>404504464.360913</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>86736509.0</t>
+          <t>74563221.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>137604256</v>
+        <v>115266283</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>311751968.8</t>
+          <t>216664373.4</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>442360683.54</v>
+        <v>435928377.96</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-174147712</t>
+          <t>-101398090</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-21347580.76687022</t>
+          <t>-25824785.94029485</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-46060059.89499024</t>
+          <t>-50449414.39413029</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>86736509.0</t>
+          <t>74563221.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>85.83</t>
+          <t>85.04</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>44.32</t>
+          <t>44.52</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>11693</t>
+          <t>11586</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>109.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>108.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1335.506</t>
+          <t>823.014</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-43.46</t>
+          <t>-55.86</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-9.13</t>
+          <t>-7.83</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>417</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.38</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>8.11</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-7.68</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>108.9</t>
+          <t>108.2</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>117.85</v>
+        <v>117.2</v>
       </c>
       <c r="AN5" t="n">
-        <v>119.05</v>
+        <v>118.83</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>121.66</t>
+          <t>121.47</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-123.04</t>
+          <t>-93.34</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-112.43</t>
+          <t>-116.22</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>404985181.6692858</t>
+          <t>404504464.360913</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>139648418.0</t>
+          <t>86736509.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>178684409.2</v>
+        <v>137604256</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>316018501.8</t>
+          <t>311751968.8</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>449139949.34</v>
+        <v>442360683.54</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-137334092</t>
+          <t>-174147712</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-16854402.74357567</t>
+          <t>-21347580.76687022</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-39448832.1856834</t>
+          <t>-46060059.89499024</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>139648418.0</t>
+          <t>86736509.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>85.83</t>
+          <t>85.04</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>44.32</t>
+          <t>44.52</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>11693</t>
+          <t>11586</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-6.88</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1507.376</t>
+          <t>1335.506</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-40.67</t>
+          <t>-43.46</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-7.39</t>
+          <t>-9.13</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,12 +2734,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>417</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2749,58 +2749,58 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>8.11</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>111.2</t>
+          <t>108.9</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>118.72</v>
+        <v>117.85</v>
       </c>
       <c r="AN6" t="n">
-        <v>119.21</v>
+        <v>119.05</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>121.84</t>
+          <t>121.66</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-147.13</t>
+          <t>-123.04</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-108.61</t>
+          <t>-112.43</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>404985181.6692858</t>
+          <t>404504464.360913</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>162713049.0</t>
+          <t>139648418.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>197662013.8</v>
+        <v>178684409.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>333134571.9</t>
+          <t>316018501.8</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>455062786.1</v>
+        <v>449139949.34</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-135472558</t>
+          <t>-137334092</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-12746324.66319245</t>
+          <t>-16854402.74357567</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-34264467.41575634</t>
+          <t>-39448832.1856834</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>162713049.0</t>
+          <t>139648418.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>7.58</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>85.83</t>
+          <t>85.04</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>44.32</t>
+          <t>44.52</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>11693</t>
+          <t>11586</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>-6.88</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>987.925</t>
+          <t>1507.376</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-43.50</t>
+          <t>-40.67</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-7.39</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,17 +3164,17 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>417</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -3184,53 +3184,53 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>113.9</t>
+          <t>111.2</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>119.18</v>
+        <v>118.72</v>
       </c>
       <c r="AN7" t="n">
-        <v>119.4</v>
+        <v>119.21</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>121.95</t>
+          <t>121.84</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-168.80</t>
+          <t>-147.13</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-105.44</t>
+          <t>-108.61</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>404985181.6692858</t>
+          <t>404504464.360913</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>112670218.0</t>
+          <t>162713049.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>220026836</v>
+        <v>197662013.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>389449404.3</t>
+          <t>333134571.9</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>458112049.14</v>
+        <v>455062786.1</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-169422568</t>
+          <t>-135472558</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-8833935.071817197</t>
+          <t>-12746324.66319245</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-28105711.51529783</t>
+          <t>-34264467.41575634</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>112670218.0</t>
+          <t>162713049.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>15.15</t>
+          <t>7.58</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>85.83</t>
+          <t>85.04</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>44.32</t>
+          <t>44.52</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>11693</t>
+          <t>11586</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>113.5</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1722.133</t>
+          <t>987.925</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-5.56</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-22.70</t>
+          <t>-43.50</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>417</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-5.74</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>116.7</t>
+          <t>113.9</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>119.32</v>
+        <v>119.18</v>
       </c>
       <c r="AN8" t="n">
-        <v>119.42</v>
+        <v>119.4</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>121.94</t>
+          <t>121.95</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-315.52</t>
+          <t>-168.80</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-103.15</t>
+          <t>-105.44</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>404985181.6692858</t>
+          <t>404504464.360913</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>186253086.0</t>
+          <t>112670218.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>318062463.8</v>
+        <v>220026836</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>411469009.6</t>
+          <t>389449404.3</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>462766906.5</v>
+        <v>458112049.14</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-93406545</t>
+          <t>-169422568</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-5329975.718457082</t>
+          <t>-8833935.071817197</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-12941981.49623936</t>
+          <t>-28105711.51529783</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>186253086.0</t>
+          <t>112670218.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>15.15</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>85.83</t>
+          <t>85.04</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>44.32</t>
+          <t>44.52</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>11693</t>
+          <t>11586</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>113.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>112.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-5.63</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2649.921</t>
+          <t>1722.133</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>18.24</t>
+          <t>-22.70</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>417</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>17.28</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-8.90</t>
+          <t>-5.74</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>120.2</t>
+          <t>116.7</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>119.5</v>
+        <v>119.32</v>
       </c>
       <c r="AN9" t="n">
-        <v>119.54</v>
+        <v>119.42</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>121.97</t>
+          <t>121.94</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-966.59</t>
+          <t>-315.52</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-100.66</t>
+          <t>-103.15</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>404985181.6692858</t>
+          <t>404504464.360913</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>292137275.0</t>
+          <t>186253086.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>485899681.6</v>
+        <v>318062463.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>410942337.2</t>
+          <t>411469009.6</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>472868764.64</v>
+        <v>462766906.5</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>74957344</t>
+          <t>-93406545</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-3945974.667951212</t>
+          <t>-5329975.718457082</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>1298824.870138526</t>
+          <t>-12941981.49623936</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>292137275.0</t>
+          <t>186253086.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>85.83</t>
+          <t>85.04</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>44.32</t>
+          <t>44.52</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>11693</t>
+          <t>11586</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>115.5</t>
+          <t>108.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>117.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4313,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-5.63</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1998.479</t>
+          <t>2649.921</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,84 +4338,84 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>109.5</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-1.39</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-2.26</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>18.24</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-09-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>124.5</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>131.5</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
           <t>116.0</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-6.42</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>-2.7</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>9.33</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-09-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>124.5</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>115.0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>131.5</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>116.0</t>
-        </is>
-      </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>0</t>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>6.10</t>
+          <t>8.09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>417</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>50.62</t>
+          <t>17.28</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>-8.90</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>120.2</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>119.62</v>
+        <v>119.5</v>
       </c>
       <c r="AN10" t="n">
-        <v>119.79</v>
+        <v>119.54</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>121.95</t>
+          <t>121.97</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>20.33</t>
+          <t>-966.59</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-99.06</t>
+          <t>-100.66</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>404985181.6692858</t>
+          <t>404504464.360913</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>234536441.0</t>
+          <t>292137275.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>453352594.4</v>
+        <v>485899681.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>414675114.7</t>
+          <t>410942337.2</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>478603045.96</v>
+        <v>472868764.64</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>38677479</t>
+          <t>74957344</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-4899574.583967528</t>
+          <t>-3945974.667951212</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>10251712.82674479</t>
+          <t>1298824.870138526</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>234536441.0</t>
+          <t>292137275.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>17.17</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>85.83</t>
+          <t>85.04</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>44.32</t>
+          <t>44.52</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>11693</t>
+          <t>11586</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>118.5</t>
+          <t>115.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>117.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>115.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>109.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-6.4</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2237.086</t>
+          <t>1998.479</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-10.09</t>
+          <t>-7.41</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>15.49</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>6.83</t>
+          <t>6.10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,68 +4884,68 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>417</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>40.74</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>80.25</t>
+          <t>50.62</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>121.3</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>119.4</v>
+        <v>119.62</v>
       </c>
       <c r="AN11" t="n">
-        <v>120</v>
+        <v>119.79</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>121.73</t>
+          <t>121.95</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>506.78</t>
+          <t>20.33</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-99.11</t>
+          <t>-99.06</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>404985181.6692858</t>
+          <t>404504464.360913</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>274537160.0</t>
+          <t>234536441.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>468607130</v>
+        <v>453352594.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>405744996.9</t>
+          <t>414675114.7</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>496122034.34</v>
+        <v>478603045.96</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>62862133</t>
+          <t>38677479</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-7654354.113187951</t>
+          <t>-4899574.583967528</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>28846938.09237003</t>
+          <t>10251712.82674479</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>274537160.0</t>
+          <t>234536441.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>21.21</t>
+          <t>17.17</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>85.83</t>
+          <t>85.04</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>44.32</t>
+          <t>44.52</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>11693</t>
+          <t>11586</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>118.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>115.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>-6.4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4742.281</t>
+          <t>2237.086</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-17.43</t>
+          <t>-11.11</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>39.36</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>11.30</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14.48</t>
+          <t>6.83</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>417</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>40.74</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>70.67</t>
+          <t>80.25</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>6.49</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>120.2</t>
+          <t>121.3</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>119</v>
+        <v>119.4</v>
       </c>
       <c r="AN12" t="n">
-        <v>120.2</v>
+        <v>120</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>121.48</t>
+          <t>121.73</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>3038.57</t>
+          <t>506.78</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-100.24</t>
+          <t>-99.11</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>404985181.6692858</t>
+          <t>404504464.360913</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>602848357.0</t>
+          <t>274537160.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>558871972.6</v>
+        <v>468607130</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>401037331.1</t>
+          <t>405744996.9</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>530097463.36</v>
+        <v>496122034.34</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>157834641</t>
+          <t>62862133</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-14290952.69601668</t>
+          <t>-7654354.113187951</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>50095506.50425005</t>
+          <t>28846938.09237003</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>602848357.0</t>
+          <t>274537160.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>29.29</t>
+          <t>21.21</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>85.83</t>
+          <t>85.04</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>44.32</t>
+          <t>44.52</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>11693</t>
+          <t>11586</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/玻_碳纖.xlsx
+++ b/Result/checksun_type/玻_碳纖.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>417.291</t>
+          <t>694.884</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-42.34</t>
+          <t>-45.60</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>-9.13</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,37 +1014,37 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>417</t>
+          <t>695</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>36.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>33.93</t>
+          <t>25.32</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-6.98</t>
+          <t>-6.29</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
@@ -1058,29 +1058,29 @@
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>115.25</v>
+        <v>114.4</v>
       </c>
       <c r="AN2" t="n">
-        <v>118.34</v>
+        <v>118.09</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>120.96</t>
+          <t>120.69</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-33.76</t>
+          <t>-32.21</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-3.41</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-123.85</t>
+          <t>-125.94</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>404504464.360913</t>
+          <t>404084581.8974359</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>45334899.0</t>
+          <t>73164650.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>80064855</v>
+        <v>66768101.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>138863434.4</t>
+          <t>122726255.3</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>419038513.76</v>
+        <v>411205419.78</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-58798579</t>
+          <t>-55958153</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-34024727.88951867</t>
+          <t>-36965066.39388964</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-55453178.00238952</t>
+          <t>-53136928.16792992</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>45334899.0</t>
+          <t>73164650.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1206,17 +1206,17 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>85.04</t>
+          <t>82.28</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>44.52</t>
+          <t>44.11</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>11586</t>
+          <t>11210</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>497.76</t>
+          <t>417.291</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-36.00</t>
+          <t>-42.34</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-5.22</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>417</t>
+          <t>695</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>39.13</t>
+          <t>36.84</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>23.77</t>
+          <t>33.93</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-7.90</t>
+          <t>-6.98</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>106.9</t>
+          <t>107.2</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>116.08</v>
+        <v>115.25</v>
       </c>
       <c r="AN3" t="n">
-        <v>118.57</v>
+        <v>118.34</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>121.12</t>
+          <t>120.96</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-45.24</t>
+          <t>-33.76</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>-3.41</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-121.84</t>
+          <t>-123.85</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>404504464.360913</t>
+          <t>404084581.8974359</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>54041228.0</t>
+          <t>45334899.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>103540485</v>
+        <v>80064855</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>161783660.5</t>
+          <t>138863434.4</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>428520261.8</v>
+        <v>419038513.76</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-58243175</t>
+          <t>-58798579</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-30128646.05081488</t>
+          <t>-34024727.88951867</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-53799876.65867507</t>
+          <t>-55453178.00238952</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>54041228.0</t>
+          <t>45334899.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>10.10</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>85.04</t>
+          <t>82.28</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>44.52</t>
+          <t>44.11</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>11586</t>
+          <t>11210</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>688.338</t>
+          <t>497.76</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-46.80</t>
+          <t>-36.00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-5.65</t>
+          <t>-5.22</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,37 +1874,37 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>417</t>
+          <t>695</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>25.81</t>
+          <t>39.13</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>10.73</t>
+          <t>23.77</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-7.54</t>
+          <t>-7.90</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1914,33 +1914,33 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>107.9</t>
+          <t>106.9</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>116.7</v>
+        <v>116.08</v>
       </c>
       <c r="AN4" t="n">
-        <v>118.76</v>
+        <v>118.57</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>121.31</t>
+          <t>121.12</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-65.07</t>
+          <t>-45.24</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-3.42</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-119.37</t>
+          <t>-121.84</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>404504464.360913</t>
+          <t>404084581.8974359</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>74563221.0</t>
+          <t>54041228.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>115266283</v>
+        <v>103540485</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>216664373.4</t>
+          <t>161783660.5</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>435928377.96</v>
+        <v>428520261.8</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-101398090</t>
+          <t>-58243175</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-25824785.94029485</t>
+          <t>-30128646.05081488</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-50449414.39413029</t>
+          <t>-53799876.65867507</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>74563221.0</t>
+          <t>54041228.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>10.10</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>85.04</t>
+          <t>82.28</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>44.52</t>
+          <t>44.11</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>11586</t>
+          <t>11210</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>823.014</t>
+          <t>688.338</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>108.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>-3.83</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-55.86</t>
+          <t>-46.80</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-7.83</t>
+          <t>-5.65</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>417</t>
+          <t>695</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>6.38</t>
+          <t>25.81</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>10.73</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-7.68</t>
+          <t>-7.54</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>108.2</t>
+          <t>107.9</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>117.2</v>
+        <v>116.7</v>
       </c>
       <c r="AN5" t="n">
-        <v>118.83</v>
+        <v>118.76</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>121.47</t>
+          <t>121.31</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-93.34</t>
+          <t>-65.07</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.42</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-116.22</t>
+          <t>-119.37</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>404504464.360913</t>
+          <t>404084581.8974359</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>86736509.0</t>
+          <t>74563221.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>137604256</v>
+        <v>115266283</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>311751968.8</t>
+          <t>216664373.4</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>442360683.54</v>
+        <v>435928377.96</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-174147712</t>
+          <t>-101398090</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-21347580.76687022</t>
+          <t>-25824785.94029485</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-46060059.89499024</t>
+          <t>-50449414.39413029</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>86736509.0</t>
+          <t>74563221.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>85.04</t>
+          <t>82.28</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>44.52</t>
+          <t>44.11</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>11586</t>
+          <t>11210</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>109.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>108.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1335.506</t>
+          <t>823.014</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-43.46</t>
+          <t>-55.86</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-9.13</t>
+          <t>-7.83</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>417</t>
+          <t>695</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.38</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>8.11</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-7.68</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>108.9</t>
+          <t>108.2</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>117.85</v>
+        <v>117.2</v>
       </c>
       <c r="AN6" t="n">
-        <v>119.05</v>
+        <v>118.83</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>121.66</t>
+          <t>121.47</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-123.04</t>
+          <t>-93.34</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-112.43</t>
+          <t>-116.22</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>404504464.360913</t>
+          <t>404084581.8974359</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>139648418.0</t>
+          <t>86736509.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>178684409.2</v>
+        <v>137604256</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>316018501.8</t>
+          <t>311751968.8</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>449139949.34</v>
+        <v>442360683.54</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-137334092</t>
+          <t>-174147712</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-16854402.74357567</t>
+          <t>-21347580.76687022</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-39448832.1856834</t>
+          <t>-46060059.89499024</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>139648418.0</t>
+          <t>86736509.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>85.04</t>
+          <t>82.28</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>44.52</t>
+          <t>44.11</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>11586</t>
+          <t>11210</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-6.88</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1507.376</t>
+          <t>1335.506</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-40.67</t>
+          <t>-43.46</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-7.39</t>
+          <t>-9.13</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>417</t>
+          <t>695</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,58 +3179,58 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>8.11</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>111.2</t>
+          <t>108.9</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>118.72</v>
+        <v>117.85</v>
       </c>
       <c r="AN7" t="n">
-        <v>119.21</v>
+        <v>119.05</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>121.84</t>
+          <t>121.66</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-147.13</t>
+          <t>-123.04</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-108.61</t>
+          <t>-112.43</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>404504464.360913</t>
+          <t>404084581.8974359</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>162713049.0</t>
+          <t>139648418.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>197662013.8</v>
+        <v>178684409.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>333134571.9</t>
+          <t>316018501.8</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>455062786.1</v>
+        <v>449139949.34</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-135472558</t>
+          <t>-137334092</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-12746324.66319245</t>
+          <t>-16854402.74357567</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-34264467.41575634</t>
+          <t>-39448832.1856834</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>162713049.0</t>
+          <t>139648418.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>7.58</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>85.04</t>
+          <t>82.28</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>44.52</t>
+          <t>44.11</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>11586</t>
+          <t>11210</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>-6.88</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>987.925</t>
+          <t>1507.376</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-5.56</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-43.50</t>
+          <t>-40.67</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-7.39</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,17 +3594,17 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>417</t>
+          <t>695</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -3614,53 +3614,53 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>113.9</t>
+          <t>111.2</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>119.18</v>
+        <v>118.72</v>
       </c>
       <c r="AN8" t="n">
-        <v>119.4</v>
+        <v>119.21</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>121.95</t>
+          <t>121.84</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-168.80</t>
+          <t>-147.13</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-105.44</t>
+          <t>-108.61</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>404504464.360913</t>
+          <t>404084581.8974359</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>112670218.0</t>
+          <t>162713049.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>220026836</v>
+        <v>197662013.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>389449404.3</t>
+          <t>333134571.9</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>458112049.14</v>
+        <v>455062786.1</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-169422568</t>
+          <t>-135472558</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-8833935.071817197</t>
+          <t>-12746324.66319245</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-28105711.51529783</t>
+          <t>-34264467.41575634</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>112670218.0</t>
+          <t>162713049.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>15.15</t>
+          <t>7.58</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>85.04</t>
+          <t>82.28</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>44.52</t>
+          <t>44.11</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>11586</t>
+          <t>11210</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>113.5</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1722.133</t>
+          <t>987.925</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-22.70</t>
+          <t>-43.50</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>417</t>
+          <t>695</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-5.74</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>116.7</t>
+          <t>113.9</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>119.32</v>
+        <v>119.18</v>
       </c>
       <c r="AN9" t="n">
-        <v>119.42</v>
+        <v>119.4</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>121.94</t>
+          <t>121.95</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-315.52</t>
+          <t>-168.80</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-103.15</t>
+          <t>-105.44</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>404504464.360913</t>
+          <t>404084581.8974359</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>186253086.0</t>
+          <t>112670218.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>318062463.8</v>
+        <v>220026836</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>411469009.6</t>
+          <t>389449404.3</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>462766906.5</v>
+        <v>458112049.14</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-93406545</t>
+          <t>-169422568</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-5329975.718457082</t>
+          <t>-8833935.071817197</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-12941981.49623936</t>
+          <t>-28105711.51529783</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>186253086.0</t>
+          <t>112670218.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>15.15</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>85.04</t>
+          <t>82.28</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>44.52</t>
+          <t>44.11</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>11586</t>
+          <t>11210</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>113.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>112.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-5.63</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2649.921</t>
+          <t>1722.133</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-5.26</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>18.24</t>
+          <t>-22.70</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>417</t>
+          <t>695</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>17.28</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-8.90</t>
+          <t>-5.74</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>120.2</t>
+          <t>116.7</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>119.5</v>
+        <v>119.32</v>
       </c>
       <c r="AN10" t="n">
-        <v>119.54</v>
+        <v>119.42</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>121.97</t>
+          <t>121.94</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-966.59</t>
+          <t>-315.52</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-100.66</t>
+          <t>-103.15</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>404504464.360913</t>
+          <t>404084581.8974359</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>292137275.0</t>
+          <t>186253086.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>485899681.6</v>
+        <v>318062463.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>410942337.2</t>
+          <t>411469009.6</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>472868764.64</v>
+        <v>462766906.5</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>74957344</t>
+          <t>-93406545</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-3945974.667951212</t>
+          <t>-5329975.718457082</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>1298824.870138526</t>
+          <t>-12941981.49623936</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>292137275.0</t>
+          <t>186253086.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>85.04</t>
+          <t>82.28</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>44.52</t>
+          <t>44.11</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>11586</t>
+          <t>11210</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>115.5</t>
+          <t>108.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>117.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4743,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-5.63</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1998.479</t>
+          <t>2649.921</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,84 +4768,84 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>109.5</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-4.78</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-3.03</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>18.24</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-09-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>124.5</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>131.5</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
           <t>116.0</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-7.41</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-2.26</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>9.33</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-09-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>124.5</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>115.0</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>131.5</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>116.0</t>
-        </is>
-      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>0</t>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>6.10</t>
+          <t>8.09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>417</t>
+          <t>695</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>50.62</t>
+          <t>17.28</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>-8.90</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>120.2</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>119.62</v>
+        <v>119.5</v>
       </c>
       <c r="AN11" t="n">
-        <v>119.79</v>
+        <v>119.54</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>121.95</t>
+          <t>121.97</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>20.33</t>
+          <t>-966.59</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-99.06</t>
+          <t>-100.66</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>404504464.360913</t>
+          <t>404084581.8974359</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>234536441.0</t>
+          <t>292137275.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>453352594.4</v>
+        <v>485899681.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>414675114.7</t>
+          <t>410942337.2</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>478603045.96</v>
+        <v>472868764.64</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>38677479</t>
+          <t>74957344</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-4899574.583967528</t>
+          <t>-3945974.667951212</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>10251712.82674479</t>
+          <t>1298824.870138526</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>234536441.0</t>
+          <t>292137275.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>17.17</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>85.04</t>
+          <t>82.28</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>44.52</t>
+          <t>44.11</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>11586</t>
+          <t>11210</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>118.5</t>
+          <t>115.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>117.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>115.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>109.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-6.4</t>
+          <t>-3.38</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2237.086</t>
+          <t>1998.479</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-11.11</t>
+          <t>-11.0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>15.49</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>6.83</t>
+          <t>6.10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,68 +5314,68 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>417</t>
+          <t>695</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>40.74</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>80.25</t>
+          <t>50.62</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>121.3</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>119.4</v>
+        <v>119.62</v>
       </c>
       <c r="AN12" t="n">
-        <v>120</v>
+        <v>119.79</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>121.73</t>
+          <t>121.95</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>506.78</t>
+          <t>20.33</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-99.11</t>
+          <t>-99.06</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>404504464.360913</t>
+          <t>404084581.8974359</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>274537160.0</t>
+          <t>234536441.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>468607130</v>
+        <v>453352594.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>405744996.9</t>
+          <t>414675114.7</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>496122034.34</v>
+        <v>478603045.96</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>62862133</t>
+          <t>38677479</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-7654354.113187951</t>
+          <t>-4899574.583967528</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>28846938.09237003</t>
+          <t>10251712.82674479</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>274537160.0</t>
+          <t>234536441.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>21.21</t>
+          <t>17.17</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>85.04</t>
+          <t>82.28</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>44.52</t>
+          <t>44.11</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>11586</t>
+          <t>11210</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>118.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>115.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/玻_碳纖.xlsx
+++ b/Result/checksun_type/玻_碳纖.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>694.884</t>
+          <t>460.69</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-45.60</t>
+          <t>-39.87</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-9.13</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>461</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>25.32</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-6.29</t>
+          <t>-5.68</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>107.2</t>
+          <t>107.1</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>114.4</v>
+        <v>113.55</v>
       </c>
       <c r="AN2" t="n">
-        <v>118.09</v>
+        <v>117.93</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>120.69</t>
+          <t>120.44</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-32.21</t>
+          <t>-26.20</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-125.94</t>
+          <t>-127.76</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>404084581.8974359</t>
+          <t>403613693.0889047</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>73164650.0</t>
+          <t>48699833.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>66768101.4</v>
+        <v>59160766.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>122726255.3</t>
+          <t>98382511.1</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>411205419.78</v>
+        <v>408309837.48</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-55958153</t>
+          <t>-39221744</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-36965066.39388964</t>
+          <t>-39281516.38784661</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-53136928.16792992</t>
+          <t>-52021991.35460995</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>73164650.0</t>
+          <t>48699833.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>82.28</t>
+          <t>83.07</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>44.11</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>11210</t>
+          <t>11318</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>417.291</t>
+          <t>694.884</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-42.34</t>
+          <t>-45.60</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>-9.13</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,37 +1444,37 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>461</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>36.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>33.93</t>
+          <t>25.32</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-6.98</t>
+          <t>-6.29</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1488,29 +1488,29 @@
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>115.25</v>
+        <v>114.4</v>
       </c>
       <c r="AN3" t="n">
-        <v>118.34</v>
+        <v>118.09</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>120.96</t>
+          <t>120.69</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-33.76</t>
+          <t>-32.21</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-3.41</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-123.85</t>
+          <t>-125.94</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>404084581.8974359</t>
+          <t>403613693.0889047</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>45334899.0</t>
+          <t>73164650.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>80064855</v>
+        <v>66768101.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>138863434.4</t>
+          <t>122726255.3</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>419038513.76</v>
+        <v>411205419.78</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-58798579</t>
+          <t>-55958153</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-34024727.88951867</t>
+          <t>-36965066.39388964</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-55453178.00238952</t>
+          <t>-53136928.16792992</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>45334899.0</t>
+          <t>73164650.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1636,17 +1636,17 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>82.28</t>
+          <t>83.07</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>44.11</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>11210</t>
+          <t>11318</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>497.76</t>
+          <t>417.291</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-36.00</t>
+          <t>-42.34</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-5.22</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>461</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>39.13</t>
+          <t>36.84</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>23.77</t>
+          <t>33.93</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-7.90</t>
+          <t>-6.98</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>106.9</t>
+          <t>107.2</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>116.08</v>
+        <v>115.25</v>
       </c>
       <c r="AN4" t="n">
-        <v>118.57</v>
+        <v>118.34</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>121.12</t>
+          <t>120.96</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-45.24</t>
+          <t>-33.76</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>-3.41</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-121.84</t>
+          <t>-123.85</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>404084581.8974359</t>
+          <t>403613693.0889047</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>54041228.0</t>
+          <t>45334899.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>103540485</v>
+        <v>80064855</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>161783660.5</t>
+          <t>138863434.4</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>428520261.8</v>
+        <v>419038513.76</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-58243175</t>
+          <t>-58798579</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-30128646.05081488</t>
+          <t>-34024727.88951867</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-53799876.65867507</t>
+          <t>-55453178.00238952</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>54041228.0</t>
+          <t>45334899.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>10.10</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>82.28</t>
+          <t>83.07</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>44.11</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>11210</t>
+          <t>11318</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>688.338</t>
+          <t>497.76</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-3.83</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-46.80</t>
+          <t>-36.00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-5.65</t>
+          <t>-5.22</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,37 +2304,37 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>461</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>25.81</t>
+          <t>39.13</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>10.73</t>
+          <t>23.77</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-7.54</t>
+          <t>-7.90</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -2344,33 +2344,33 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>107.9</t>
+          <t>106.9</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>116.7</v>
+        <v>116.08</v>
       </c>
       <c r="AN5" t="n">
-        <v>118.76</v>
+        <v>118.57</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>121.31</t>
+          <t>121.12</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-65.07</t>
+          <t>-45.24</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-3.42</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-119.37</t>
+          <t>-121.84</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>404084581.8974359</t>
+          <t>403613693.0889047</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>74563221.0</t>
+          <t>54041228.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>115266283</v>
+        <v>103540485</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>216664373.4</t>
+          <t>161783660.5</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>435928377.96</v>
+        <v>428520261.8</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-101398090</t>
+          <t>-58243175</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-25824785.94029485</t>
+          <t>-30128646.05081488</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-50449414.39413029</t>
+          <t>-53799876.65867507</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>74563221.0</t>
+          <t>54041228.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>10.10</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>82.28</t>
+          <t>83.07</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>44.11</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>11210</t>
+          <t>11318</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2566,12 +2566,12 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>823.014</t>
+          <t>688.338</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>108.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-55.86</t>
+          <t>-46.80</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-7.83</t>
+          <t>-5.65</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>461</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>6.38</t>
+          <t>25.81</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>10.73</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-7.68</t>
+          <t>-7.54</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>108.2</t>
+          <t>107.9</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>117.2</v>
+        <v>116.7</v>
       </c>
       <c r="AN6" t="n">
-        <v>118.83</v>
+        <v>118.76</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>121.47</t>
+          <t>121.31</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-93.34</t>
+          <t>-65.07</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.42</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-116.22</t>
+          <t>-119.37</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>404084581.8974359</t>
+          <t>403613693.0889047</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>86736509.0</t>
+          <t>74563221.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>137604256</v>
+        <v>115266283</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>311751968.8</t>
+          <t>216664373.4</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>442360683.54</v>
+        <v>435928377.96</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-174147712</t>
+          <t>-101398090</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-21347580.76687022</t>
+          <t>-25824785.94029485</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-46060059.89499024</t>
+          <t>-50449414.39413029</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>86736509.0</t>
+          <t>74563221.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>82.28</t>
+          <t>83.07</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>44.11</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>11210</t>
+          <t>11318</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>109.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>108.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1335.506</t>
+          <t>823.014</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-43.46</t>
+          <t>-55.86</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-9.13</t>
+          <t>-7.83</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>461</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.38</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>8.11</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-7.68</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>108.9</t>
+          <t>108.2</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>117.85</v>
+        <v>117.2</v>
       </c>
       <c r="AN7" t="n">
-        <v>119.05</v>
+        <v>118.83</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>121.66</t>
+          <t>121.47</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-123.04</t>
+          <t>-93.34</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-112.43</t>
+          <t>-116.22</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>404084581.8974359</t>
+          <t>403613693.0889047</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>139648418.0</t>
+          <t>86736509.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>178684409.2</v>
+        <v>137604256</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>316018501.8</t>
+          <t>311751968.8</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>449139949.34</v>
+        <v>442360683.54</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-137334092</t>
+          <t>-174147712</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-16854402.74357567</t>
+          <t>-21347580.76687022</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-39448832.1856834</t>
+          <t>-46060059.89499024</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>139648418.0</t>
+          <t>86736509.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>82.28</t>
+          <t>83.07</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>44.11</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>11210</t>
+          <t>11318</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-6.88</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1507.376</t>
+          <t>1335.506</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-40.67</t>
+          <t>-43.46</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-7.39</t>
+          <t>-9.13</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>461</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3609,58 +3609,58 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>8.11</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>111.2</t>
+          <t>108.9</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>118.72</v>
+        <v>117.85</v>
       </c>
       <c r="AN8" t="n">
-        <v>119.21</v>
+        <v>119.05</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>121.84</t>
+          <t>121.66</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-147.13</t>
+          <t>-123.04</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-108.61</t>
+          <t>-112.43</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>404084581.8974359</t>
+          <t>403613693.0889047</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>162713049.0</t>
+          <t>139648418.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>197662013.8</v>
+        <v>178684409.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>333134571.9</t>
+          <t>316018501.8</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>455062786.1</v>
+        <v>449139949.34</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-135472558</t>
+          <t>-137334092</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-12746324.66319245</t>
+          <t>-16854402.74357567</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-34264467.41575634</t>
+          <t>-39448832.1856834</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>162713049.0</t>
+          <t>139648418.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>7.58</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>82.28</t>
+          <t>83.07</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>44.11</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>11210</t>
+          <t>11318</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>-6.88</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>987.925</t>
+          <t>1507.376</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-43.50</t>
+          <t>-40.67</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-7.39</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,17 +4024,17 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>461</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -4044,53 +4044,53 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>113.9</t>
+          <t>111.2</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>119.18</v>
+        <v>118.72</v>
       </c>
       <c r="AN9" t="n">
-        <v>119.4</v>
+        <v>119.21</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>121.95</t>
+          <t>121.84</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-168.80</t>
+          <t>-147.13</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-105.44</t>
+          <t>-108.61</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>404084581.8974359</t>
+          <t>403613693.0889047</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>112670218.0</t>
+          <t>162713049.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>220026836</v>
+        <v>197662013.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>389449404.3</t>
+          <t>333134571.9</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>458112049.14</v>
+        <v>455062786.1</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-169422568</t>
+          <t>-135472558</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-8833935.071817197</t>
+          <t>-12746324.66319245</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-28105711.51529783</t>
+          <t>-34264467.41575634</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>112670218.0</t>
+          <t>162713049.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>15.15</t>
+          <t>7.58</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>82.28</t>
+          <t>83.07</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>44.11</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>11210</t>
+          <t>11318</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>113.5</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1722.133</t>
+          <t>987.925</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-5.26</t>
+          <t>-8.06</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-22.70</t>
+          <t>-43.50</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>461</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-5.74</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>116.7</t>
+          <t>113.9</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>119.32</v>
+        <v>119.18</v>
       </c>
       <c r="AN10" t="n">
-        <v>119.42</v>
+        <v>119.4</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>121.94</t>
+          <t>121.95</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-315.52</t>
+          <t>-168.80</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-103.15</t>
+          <t>-105.44</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>404084581.8974359</t>
+          <t>403613693.0889047</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>186253086.0</t>
+          <t>112670218.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>318062463.8</v>
+        <v>220026836</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>411469009.6</t>
+          <t>389449404.3</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>462766906.5</v>
+        <v>458112049.14</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-93406545</t>
+          <t>-169422568</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-5329975.718457082</t>
+          <t>-8833935.071817197</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-12941981.49623936</t>
+          <t>-28105711.51529783</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>186253086.0</t>
+          <t>112670218.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>15.15</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>82.28</t>
+          <t>83.07</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>44.11</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>11210</t>
+          <t>11318</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>113.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>112.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-5.63</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2649.921</t>
+          <t>1722.133</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>18.24</t>
+          <t>-22.70</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>461</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>17.28</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-8.90</t>
+          <t>-5.74</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>120.2</t>
+          <t>116.7</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>119.5</v>
+        <v>119.32</v>
       </c>
       <c r="AN11" t="n">
-        <v>119.54</v>
+        <v>119.42</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>121.97</t>
+          <t>121.94</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-966.59</t>
+          <t>-315.52</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-100.66</t>
+          <t>-103.15</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>404084581.8974359</t>
+          <t>403613693.0889047</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>292137275.0</t>
+          <t>186253086.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>485899681.6</v>
+        <v>318062463.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>410942337.2</t>
+          <t>411469009.6</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>472868764.64</v>
+        <v>462766906.5</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>74957344</t>
+          <t>-93406545</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-3945974.667951212</t>
+          <t>-5329975.718457082</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>1298824.870138526</t>
+          <t>-12941981.49623936</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>292137275.0</t>
+          <t>186253086.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>82.28</t>
+          <t>83.07</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>44.11</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>11210</t>
+          <t>11318</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>115.5</t>
+          <t>108.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>117.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5173,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-3.38</t>
+          <t>-5.63</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1998.479</t>
+          <t>2649.921</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,84 +5198,84 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>109.5</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-3.79</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-1.63</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>18.24</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-09-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>124.5</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>131.5</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
           <t>116.0</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-11.0</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-3.03</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>9.33</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-09-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>124.5</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>115.0</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>131.5</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>116.0</t>
-        </is>
-      </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>0</t>
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>6.10</t>
+          <t>8.09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>461</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>50.62</t>
+          <t>17.28</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>-8.90</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>120.2</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>119.62</v>
+        <v>119.5</v>
       </c>
       <c r="AN12" t="n">
-        <v>119.79</v>
+        <v>119.54</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>121.95</t>
+          <t>121.97</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>20.33</t>
+          <t>-966.59</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-99.06</t>
+          <t>-100.66</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>404084581.8974359</t>
+          <t>403613693.0889047</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>234536441.0</t>
+          <t>292137275.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>453352594.4</v>
+        <v>485899681.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>414675114.7</t>
+          <t>410942337.2</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>478603045.96</v>
+        <v>472868764.64</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>38677479</t>
+          <t>74957344</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-4899574.583967528</t>
+          <t>-3945974.667951212</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>10251712.82674479</t>
+          <t>1298824.870138526</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>234536441.0</t>
+          <t>292137275.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>17.17</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>82.28</t>
+          <t>83.07</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>44.11</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>11210</t>
+          <t>11318</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>118.5</t>
+          <t>115.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>117.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>115.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>109.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/玻_碳纖.xlsx
+++ b/Result/checksun_type/玻_碳纖.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【e】;【x】看好</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>460.69</t>
+          <t>617.222</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-39.87</t>
+          <t>-33.70</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-9.57</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>617</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-5.68</t>
+          <t>-5.77</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>107.1</t>
+          <t>106.2</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>113.55</v>
+        <v>112.7</v>
       </c>
       <c r="AN2" t="n">
-        <v>117.93</v>
+        <v>117.72</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>120.44</t>
+          <t>120.13</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-26.20</t>
+          <t>-23.26</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-3.15</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-127.76</t>
+          <t>-129.47</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>403613693.0889047</t>
+          <t>403177926.7457386</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>48699833.0</t>
+          <t>64556125.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>59160766.2</v>
+        <v>57159347</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>98382511.1</t>
+          <t>86212815.0</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>408309837.48</v>
+        <v>406636712.2</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-39221744</t>
+          <t>-29053468</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-39281516.38784661</t>
+          <t>-40738477.54378109</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-52021991.35460995</t>
+          <t>-48751763.90142073</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>48699833.0</t>
+          <t>64556125.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>83.07</t>
+          <t>81.89</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.35</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>11318</t>
+          <t>11157</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1276,12 +1276,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>694.884</t>
+          <t>460.69</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-45.60</t>
+          <t>-39.87</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-9.13</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>617</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>25.32</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-6.29</t>
+          <t>-5.68</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>107.2</t>
+          <t>107.1</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>114.4</v>
+        <v>113.55</v>
       </c>
       <c r="AN3" t="n">
-        <v>118.09</v>
+        <v>117.93</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>120.69</t>
+          <t>120.44</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-32.21</t>
+          <t>-26.20</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-125.94</t>
+          <t>-127.76</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>403613693.0889047</t>
+          <t>403177926.7457386</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>73164650.0</t>
+          <t>48699833.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>66768101.4</v>
+        <v>59160766.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>122726255.3</t>
+          <t>98382511.1</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>411205419.78</v>
+        <v>408309837.48</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-55958153</t>
+          <t>-39221744</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-36965066.39388964</t>
+          <t>-39281516.38784661</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-53136928.16792992</t>
+          <t>-52021991.35460995</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>73164650.0</t>
+          <t>48699833.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>83.07</t>
+          <t>81.89</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.35</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>11318</t>
+          <t>11157</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>417.291</t>
+          <t>694.884</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-42.34</t>
+          <t>-45.60</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>-9.13</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,37 +1874,37 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>617</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>36.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>33.93</t>
+          <t>25.32</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-6.98</t>
+          <t>-6.29</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1918,29 +1918,29 @@
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>115.25</v>
+        <v>114.4</v>
       </c>
       <c r="AN4" t="n">
-        <v>118.34</v>
+        <v>118.09</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>120.96</t>
+          <t>120.69</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-33.76</t>
+          <t>-32.21</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-3.41</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-123.85</t>
+          <t>-125.94</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>403613693.0889047</t>
+          <t>403177926.7457386</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>45334899.0</t>
+          <t>73164650.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>80064855</v>
+        <v>66768101.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>138863434.4</t>
+          <t>122726255.3</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>419038513.76</v>
+        <v>411205419.78</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-58798579</t>
+          <t>-55958153</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-34024727.88951867</t>
+          <t>-36965066.39388964</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-55453178.00238952</t>
+          <t>-53136928.16792992</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>45334899.0</t>
+          <t>73164650.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2066,17 +2066,17 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>83.07</t>
+          <t>81.89</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.35</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>11318</t>
+          <t>11157</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>497.76</t>
+          <t>417.291</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-3.85</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-36.00</t>
+          <t>-42.34</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-5.22</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>617</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>39.13</t>
+          <t>36.84</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>23.77</t>
+          <t>33.93</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-7.90</t>
+          <t>-6.98</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>106.9</t>
+          <t>107.2</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>116.08</v>
+        <v>115.25</v>
       </c>
       <c r="AN5" t="n">
-        <v>118.57</v>
+        <v>118.34</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>121.12</t>
+          <t>120.96</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-45.24</t>
+          <t>-33.76</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>-3.41</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-121.84</t>
+          <t>-123.85</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>403613693.0889047</t>
+          <t>403177926.7457386</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>54041228.0</t>
+          <t>45334899.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>103540485</v>
+        <v>80064855</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>161783660.5</t>
+          <t>138863434.4</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>428520261.8</v>
+        <v>419038513.76</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-58243175</t>
+          <t>-58798579</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-30128646.05081488</t>
+          <t>-34024727.88951867</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-53799876.65867507</t>
+          <t>-55453178.00238952</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>54041228.0</t>
+          <t>45334899.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>10.10</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>83.07</t>
+          <t>81.89</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.35</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>11318</t>
+          <t>11157</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>688.338</t>
+          <t>497.76</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-4.81</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-46.80</t>
+          <t>-36.00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-5.65</t>
+          <t>-5.22</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,37 +2734,37 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>617</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>25.81</t>
+          <t>39.13</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>10.73</t>
+          <t>23.77</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-7.54</t>
+          <t>-7.90</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -2774,33 +2774,33 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>107.9</t>
+          <t>106.9</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>116.7</v>
+        <v>116.08</v>
       </c>
       <c r="AN6" t="n">
-        <v>118.76</v>
+        <v>118.57</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>121.31</t>
+          <t>121.12</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-65.07</t>
+          <t>-45.24</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-3.42</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-119.37</t>
+          <t>-121.84</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>403613693.0889047</t>
+          <t>403177926.7457386</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>74563221.0</t>
+          <t>54041228.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>115266283</v>
+        <v>103540485</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>216664373.4</t>
+          <t>161783660.5</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>435928377.96</v>
+        <v>428520261.8</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-101398090</t>
+          <t>-58243175</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-25824785.94029485</t>
+          <t>-30128646.05081488</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-50449414.39413029</t>
+          <t>-53799876.65867507</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>74563221.0</t>
+          <t>54041228.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>10.10</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>83.07</t>
+          <t>81.89</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.35</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>11318</t>
+          <t>11157</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -2996,12 +2996,12 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>823.014</t>
+          <t>688.338</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>108.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-4.33</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-55.86</t>
+          <t>-46.80</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-7.83</t>
+          <t>-5.65</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>617</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>6.38</t>
+          <t>25.81</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>10.73</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-7.68</t>
+          <t>-7.54</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>108.2</t>
+          <t>107.9</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>117.2</v>
+        <v>116.7</v>
       </c>
       <c r="AN7" t="n">
-        <v>118.83</v>
+        <v>118.76</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>121.47</t>
+          <t>121.31</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-93.34</t>
+          <t>-65.07</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.42</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-116.22</t>
+          <t>-119.37</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>403613693.0889047</t>
+          <t>403177926.7457386</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>86736509.0</t>
+          <t>74563221.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>137604256</v>
+        <v>115266283</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>311751968.8</t>
+          <t>216664373.4</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>442360683.54</v>
+        <v>435928377.96</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-174147712</t>
+          <t>-101398090</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-21347580.76687022</t>
+          <t>-25824785.94029485</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-46060059.89499024</t>
+          <t>-50449414.39413029</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>86736509.0</t>
+          <t>74563221.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>83.07</t>
+          <t>81.89</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.35</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>11318</t>
+          <t>11157</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>109.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>108.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1335.506</t>
+          <t>823.014</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-43.46</t>
+          <t>-55.86</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-9.13</t>
+          <t>-7.83</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>617</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.38</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>8.11</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-7.68</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>108.9</t>
+          <t>108.2</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>117.85</v>
+        <v>117.2</v>
       </c>
       <c r="AN8" t="n">
-        <v>119.05</v>
+        <v>118.83</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>121.66</t>
+          <t>121.47</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-123.04</t>
+          <t>-93.34</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-112.43</t>
+          <t>-116.22</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>403613693.0889047</t>
+          <t>403177926.7457386</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>139648418.0</t>
+          <t>86736509.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>178684409.2</v>
+        <v>137604256</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>316018501.8</t>
+          <t>311751968.8</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>449139949.34</v>
+        <v>442360683.54</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-137334092</t>
+          <t>-174147712</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-16854402.74357567</t>
+          <t>-21347580.76687022</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-39448832.1856834</t>
+          <t>-46060059.89499024</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>139648418.0</t>
+          <t>86736509.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>83.07</t>
+          <t>81.89</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.35</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>11318</t>
+          <t>11157</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-6.88</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1507.376</t>
+          <t>1335.506</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-40.67</t>
+          <t>-43.46</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-7.39</t>
+          <t>-9.13</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>617</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4039,58 +4039,58 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>8.11</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>111.2</t>
+          <t>108.9</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>118.72</v>
+        <v>117.85</v>
       </c>
       <c r="AN9" t="n">
-        <v>119.21</v>
+        <v>119.05</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>121.84</t>
+          <t>121.66</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-147.13</t>
+          <t>-123.04</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-108.61</t>
+          <t>-112.43</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>403613693.0889047</t>
+          <t>403177926.7457386</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>162713049.0</t>
+          <t>139648418.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>197662013.8</v>
+        <v>178684409.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>333134571.9</t>
+          <t>316018501.8</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>455062786.1</v>
+        <v>449139949.34</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-135472558</t>
+          <t>-137334092</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-12746324.66319245</t>
+          <t>-16854402.74357567</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-34264467.41575634</t>
+          <t>-39448832.1856834</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>162713049.0</t>
+          <t>139648418.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>7.58</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>83.07</t>
+          <t>81.89</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.35</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>11318</t>
+          <t>11157</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>-6.88</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>987.925</t>
+          <t>1507.376</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-8.06</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-43.50</t>
+          <t>-40.67</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-7.39</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,17 +4454,17 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>617</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -4474,53 +4474,53 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>113.9</t>
+          <t>111.2</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>119.18</v>
+        <v>118.72</v>
       </c>
       <c r="AN10" t="n">
-        <v>119.4</v>
+        <v>119.21</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>121.95</t>
+          <t>121.84</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-168.80</t>
+          <t>-147.13</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-105.44</t>
+          <t>-108.61</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>403613693.0889047</t>
+          <t>403177926.7457386</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>112670218.0</t>
+          <t>162713049.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>220026836</v>
+        <v>197662013.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>389449404.3</t>
+          <t>333134571.9</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>458112049.14</v>
+        <v>455062786.1</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-169422568</t>
+          <t>-135472558</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-8833935.071817197</t>
+          <t>-12746324.66319245</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-28105711.51529783</t>
+          <t>-34264467.41575634</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>112670218.0</t>
+          <t>162713049.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>15.15</t>
+          <t>7.58</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>83.07</t>
+          <t>81.89</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.35</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>11318</t>
+          <t>11157</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>113.5</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1722.133</t>
+          <t>987.925</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-9.62</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-22.70</t>
+          <t>-43.50</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>617</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-5.74</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>116.7</t>
+          <t>113.9</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>119.32</v>
+        <v>119.18</v>
       </c>
       <c r="AN11" t="n">
-        <v>119.42</v>
+        <v>119.4</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>121.94</t>
+          <t>121.95</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-315.52</t>
+          <t>-168.80</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-103.15</t>
+          <t>-105.44</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>403613693.0889047</t>
+          <t>403177926.7457386</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>186253086.0</t>
+          <t>112670218.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>318062463.8</v>
+        <v>220026836</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>411469009.6</t>
+          <t>389449404.3</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>462766906.5</v>
+        <v>458112049.14</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-93406545</t>
+          <t>-169422568</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-5329975.718457082</t>
+          <t>-8833935.071817197</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-12941981.49623936</t>
+          <t>-28105711.51529783</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>186253086.0</t>
+          <t>112670218.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>15.15</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>83.07</t>
+          <t>81.89</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.35</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>11318</t>
+          <t>11157</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>113.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>112.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-5.63</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2649.921</t>
+          <t>1722.133</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-5.77</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>18.24</t>
+          <t>-22.70</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-3.55</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>617</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>17.28</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-8.90</t>
+          <t>-5.74</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>120.2</t>
+          <t>116.7</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>119.5</v>
+        <v>119.32</v>
       </c>
       <c r="AN12" t="n">
-        <v>119.54</v>
+        <v>119.42</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>121.97</t>
+          <t>121.94</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-966.59</t>
+          <t>-315.52</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-100.66</t>
+          <t>-103.15</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>403613693.0889047</t>
+          <t>403177926.7457386</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>292137275.0</t>
+          <t>186253086.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>485899681.6</v>
+        <v>318062463.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>410942337.2</t>
+          <t>411469009.6</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>472868764.64</v>
+        <v>462766906.5</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>74957344</t>
+          <t>-93406545</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-3945974.667951212</t>
+          <t>-5329975.718457082</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>1298824.870138526</t>
+          <t>-12941981.49623936</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>292137275.0</t>
+          <t>186253086.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>83.07</t>
+          <t>81.89</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.35</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>11318</t>
+          <t>11157</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>115.5</t>
+          <t>108.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>117.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/玻_碳纖.xlsx
+++ b/Result/checksun_type/玻_碳纖.xlsx
@@ -888,7 +888,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>617.222</t>
+          <t>1943.113</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-33.70</t>
+          <t>-8.63</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-9.57</t>
+          <t>-10.87</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-6.83</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1034,53 +1034,53 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-5.77</t>
+          <t>-5.90</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>106.2</t>
+          <t>104.9</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>112.7</v>
+        <v>111.48</v>
       </c>
       <c r="AN2" t="n">
-        <v>117.72</v>
+        <v>117.45</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>120.13</t>
+          <t>119.82</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-23.26</t>
+          <t>-22.00</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-3.15</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-129.47</t>
+          <t>-131.19</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>403177926.7457386</t>
+          <t>403039460.5255319</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>64556125.0</t>
+          <t>203706161.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>57159347</v>
+        <v>87092333.59999999</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>86212815.0</t>
+          <t>95316409.3</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>406636712.2</v>
+        <v>406267066.38</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-29053468</t>
+          <t>-8224075</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-40738477.54378109</t>
+          <t>-39826028.36576135</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-48751763.90142073</t>
+          <t>-34807557.88665277</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>64556125.0</t>
+          <t>203706161.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>81.89</t>
+          <t>80.71</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>44.35</t>
+          <t>44.51</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>11157</t>
+          <t>10996</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1271,17 +1271,17 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>109.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>460.69</t>
+          <t>617.222</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-39.87</t>
+          <t>-33.70</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-9.57</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-5.68</t>
+          <t>-5.77</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>107.1</t>
+          <t>106.2</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>113.55</v>
+        <v>112.7</v>
       </c>
       <c r="AN3" t="n">
-        <v>117.93</v>
+        <v>117.72</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>120.44</t>
+          <t>120.13</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-26.20</t>
+          <t>-23.26</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-3.15</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-127.76</t>
+          <t>-129.47</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>403177926.7457386</t>
+          <t>403039460.5255319</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>48699833.0</t>
+          <t>64556125.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>59160766.2</v>
+        <v>57159347</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>98382511.1</t>
+          <t>86212815.0</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>408309837.48</v>
+        <v>406636712.2</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-39221744</t>
+          <t>-29053468</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-39281516.38784661</t>
+          <t>-40738477.54378109</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-52021991.35460995</t>
+          <t>-48751763.90142073</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>48699833.0</t>
+          <t>64556125.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>81.89</t>
+          <t>80.71</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>44.35</t>
+          <t>44.51</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>11157</t>
+          <t>10996</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1706,12 +1706,12 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>694.884</t>
+          <t>460.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-45.60</t>
+          <t>-39.87</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-9.13</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>25.32</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-6.29</t>
+          <t>-5.68</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>107.2</t>
+          <t>107.1</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>114.4</v>
+        <v>113.55</v>
       </c>
       <c r="AN4" t="n">
-        <v>118.09</v>
+        <v>117.93</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>120.69</t>
+          <t>120.44</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-32.21</t>
+          <t>-26.20</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-125.94</t>
+          <t>-127.76</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>403177926.7457386</t>
+          <t>403039460.5255319</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>73164650.0</t>
+          <t>48699833.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>66768101.4</v>
+        <v>59160766.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>122726255.3</t>
+          <t>98382511.1</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>411205419.78</v>
+        <v>408309837.48</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-55958153</t>
+          <t>-39221744</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-36965066.39388964</t>
+          <t>-39281516.38784661</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-53136928.16792992</t>
+          <t>-52021991.35460995</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>73164650.0</t>
+          <t>48699833.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>81.89</t>
+          <t>80.71</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>44.35</t>
+          <t>44.51</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>11157</t>
+          <t>10996</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>417.291</t>
+          <t>694.884</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-3.85</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-42.34</t>
+          <t>-45.60</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>-9.13</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,37 +2304,37 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>36.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>33.93</t>
+          <t>25.32</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-6.98</t>
+          <t>-6.29</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -2348,29 +2348,29 @@
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>115.25</v>
+        <v>114.4</v>
       </c>
       <c r="AN5" t="n">
-        <v>118.34</v>
+        <v>118.09</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>120.96</t>
+          <t>120.69</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-33.76</t>
+          <t>-32.21</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-3.41</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-123.85</t>
+          <t>-125.94</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>403177926.7457386</t>
+          <t>403039460.5255319</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>45334899.0</t>
+          <t>73164650.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>80064855</v>
+        <v>66768101.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>138863434.4</t>
+          <t>122726255.3</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>419038513.76</v>
+        <v>411205419.78</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-58798579</t>
+          <t>-55958153</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-34024727.88951867</t>
+          <t>-36965066.39388964</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-55453178.00238952</t>
+          <t>-53136928.16792992</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>45334899.0</t>
+          <t>73164650.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2496,17 +2496,17 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>81.89</t>
+          <t>80.71</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>44.35</t>
+          <t>44.51</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>11157</t>
+          <t>10996</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>497.76</t>
+          <t>417.291</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-4.81</t>
+          <t>-5.37</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-36.00</t>
+          <t>-42.34</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-5.22</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>39.13</t>
+          <t>36.84</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>23.77</t>
+          <t>33.93</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-7.90</t>
+          <t>-6.98</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>106.9</t>
+          <t>107.2</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>116.08</v>
+        <v>115.25</v>
       </c>
       <c r="AN6" t="n">
-        <v>118.57</v>
+        <v>118.34</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>121.12</t>
+          <t>120.96</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-45.24</t>
+          <t>-33.76</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>-3.41</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-121.84</t>
+          <t>-123.85</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>403177926.7457386</t>
+          <t>403039460.5255319</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>54041228.0</t>
+          <t>45334899.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>103540485</v>
+        <v>80064855</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>161783660.5</t>
+          <t>138863434.4</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>428520261.8</v>
+        <v>419038513.76</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-58243175</t>
+          <t>-58798579</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-30128646.05081488</t>
+          <t>-34024727.88951867</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-53799876.65867507</t>
+          <t>-55453178.00238952</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>54041228.0</t>
+          <t>45334899.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>10.10</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>81.89</t>
+          <t>80.71</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>44.35</t>
+          <t>44.51</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>11157</t>
+          <t>10996</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>688.338</t>
+          <t>497.76</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-46.80</t>
+          <t>-36.00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-5.65</t>
+          <t>-5.22</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,37 +3164,37 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>25.81</t>
+          <t>39.13</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>10.73</t>
+          <t>23.77</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-7.54</t>
+          <t>-7.90</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -3204,33 +3204,33 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>107.9</t>
+          <t>106.9</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>116.7</v>
+        <v>116.08</v>
       </c>
       <c r="AN7" t="n">
-        <v>118.76</v>
+        <v>118.57</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>121.31</t>
+          <t>121.12</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-65.07</t>
+          <t>-45.24</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-3.42</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-119.37</t>
+          <t>-121.84</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>403177926.7457386</t>
+          <t>403039460.5255319</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>74563221.0</t>
+          <t>54041228.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>115266283</v>
+        <v>103540485</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>216664373.4</t>
+          <t>161783660.5</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>435928377.96</v>
+        <v>428520261.8</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-101398090</t>
+          <t>-58243175</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-25824785.94029485</t>
+          <t>-30128646.05081488</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-50449414.39413029</t>
+          <t>-53799876.65867507</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>74563221.0</t>
+          <t>54041228.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>10.10</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>81.89</t>
+          <t>80.71</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>44.35</t>
+          <t>44.51</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>11157</t>
+          <t>10996</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>823.014</t>
+          <t>688.338</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>108.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-5.85</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-55.86</t>
+          <t>-46.80</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-7.83</t>
+          <t>-5.65</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>6.38</t>
+          <t>25.81</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>10.73</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-7.68</t>
+          <t>-7.54</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>108.2</t>
+          <t>107.9</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>117.2</v>
+        <v>116.7</v>
       </c>
       <c r="AN8" t="n">
-        <v>118.83</v>
+        <v>118.76</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>121.47</t>
+          <t>121.31</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-93.34</t>
+          <t>-65.07</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-3.35</t>
+          <t>-3.42</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-116.22</t>
+          <t>-119.37</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>403177926.7457386</t>
+          <t>403039460.5255319</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>86736509.0</t>
+          <t>74563221.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>137604256</v>
+        <v>115266283</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>311751968.8</t>
+          <t>216664373.4</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>442360683.54</v>
+        <v>435928377.96</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-174147712</t>
+          <t>-101398090</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-21347580.76687022</t>
+          <t>-25824785.94029485</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-46060059.89499024</t>
+          <t>-50449414.39413029</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>86736509.0</t>
+          <t>74563221.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>81.89</t>
+          <t>80.71</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>44.35</t>
+          <t>44.51</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>11157</t>
+          <t>10996</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>109.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>108.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1335.506</t>
+          <t>823.014</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-3.41</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-43.46</t>
+          <t>-55.86</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-9.13</t>
+          <t>-7.83</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.38</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>8.11</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-7.68</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>108.9</t>
+          <t>108.2</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>117.85</v>
+        <v>117.2</v>
       </c>
       <c r="AN9" t="n">
-        <v>119.05</v>
+        <v>118.83</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>121.66</t>
+          <t>121.47</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-123.04</t>
+          <t>-93.34</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-3.35</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-112.43</t>
+          <t>-116.22</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>403177926.7457386</t>
+          <t>403039460.5255319</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>139648418.0</t>
+          <t>86736509.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>178684409.2</v>
+        <v>137604256</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>316018501.8</t>
+          <t>311751968.8</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>449139949.34</v>
+        <v>442360683.54</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-137334092</t>
+          <t>-174147712</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-16854402.74357567</t>
+          <t>-21347580.76687022</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-39448832.1856834</t>
+          <t>-46060059.89499024</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>139648418.0</t>
+          <t>86736509.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>81.89</t>
+          <t>80.71</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>44.35</t>
+          <t>44.51</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>11157</t>
+          <t>10996</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-6.88</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1507.376</t>
+          <t>1335.506</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.4</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-40.67</t>
+          <t>-43.46</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-7.39</t>
+          <t>-9.13</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4469,58 +4469,58 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>8.11</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>111.2</t>
+          <t>108.9</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>118.72</v>
+        <v>117.85</v>
       </c>
       <c r="AN10" t="n">
-        <v>119.21</v>
+        <v>119.05</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>121.84</t>
+          <t>121.66</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-147.13</t>
+          <t>-123.04</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-108.61</t>
+          <t>-112.43</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>403177926.7457386</t>
+          <t>403039460.5255319</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>162713049.0</t>
+          <t>139648418.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>197662013.8</v>
+        <v>178684409.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>333134571.9</t>
+          <t>316018501.8</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>455062786.1</v>
+        <v>449139949.34</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-135472558</t>
+          <t>-137334092</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-12746324.66319245</t>
+          <t>-16854402.74357567</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-34264467.41575634</t>
+          <t>-39448832.1856834</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>162713049.0</t>
+          <t>139648418.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>7.58</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4646,17 +4646,17 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>81.89</t>
+          <t>80.71</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>44.35</t>
+          <t>44.51</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>11157</t>
+          <t>10996</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>-6.88</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>987.925</t>
+          <t>1507.376</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-9.62</t>
+          <t>-3.9</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-43.50</t>
+          <t>-40.67</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-7.39</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,17 +4884,17 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -4904,53 +4904,53 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.43</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>113.9</t>
+          <t>111.2</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>119.18</v>
+        <v>118.72</v>
       </c>
       <c r="AN11" t="n">
-        <v>119.4</v>
+        <v>119.21</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>121.95</t>
+          <t>121.84</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-168.80</t>
+          <t>-147.13</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-105.44</t>
+          <t>-108.61</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>403177926.7457386</t>
+          <t>403039460.5255319</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>112670218.0</t>
+          <t>162713049.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>220026836</v>
+        <v>197662013.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>389449404.3</t>
+          <t>333134571.9</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>458112049.14</v>
+        <v>455062786.1</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-169422568</t>
+          <t>-135472558</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-8833935.071817197</t>
+          <t>-12746324.66319245</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-28105711.51529783</t>
+          <t>-34264467.41575634</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>112670218.0</t>
+          <t>162713049.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>15.15</t>
+          <t>7.58</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>81.89</t>
+          <t>80.71</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>44.35</t>
+          <t>44.51</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>11157</t>
+          <t>10996</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>113.5</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1722.133</t>
+          <t>987.925</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-5.77</t>
+          <t>-11.22</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-22.70</t>
+          <t>-43.50</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>24.32</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-5.74</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-4.43</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-2.06</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>116.7</t>
+          <t>113.9</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>119.32</v>
+        <v>119.18</v>
       </c>
       <c r="AN12" t="n">
-        <v>119.42</v>
+        <v>119.4</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>121.94</t>
+          <t>121.95</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-315.52</t>
+          <t>-168.80</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-103.15</t>
+          <t>-105.44</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>403177926.7457386</t>
+          <t>403039460.5255319</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>186253086.0</t>
+          <t>112670218.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>318062463.8</v>
+        <v>220026836</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>411469009.6</t>
+          <t>389449404.3</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>462766906.5</v>
+        <v>458112049.14</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-93406545</t>
+          <t>-169422568</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-5329975.718457082</t>
+          <t>-8833935.071817197</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-12941981.49623936</t>
+          <t>-28105711.51529783</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>186253086.0</t>
+          <t>112670218.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>15.15</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>81.89</t>
+          <t>80.71</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>44.35</t>
+          <t>44.51</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>11157</t>
+          <t>10996</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>113.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>112.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/玻_碳纖.xlsx
+++ b/Result/checksun_type/玻_碳纖.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1943.113</t>
+          <t>593.888</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-8.63</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-10.87</t>
+          <t>-10.43</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-6.83</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,74 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>594</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>3.51</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>-2.29</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>-5.90</t>
-        </is>
+          <t>2.56</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>-6.31</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-5.34</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>104.9</t>
+          <t>103.9</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>111.48</v>
+        <v>110.9</v>
       </c>
       <c r="AN2" t="n">
-        <v>117.45</v>
+        <v>117.15</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>119.82</t>
+          <t>119.56</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-22.00</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>-4.07</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-3.34</t>
-        </is>
+          <t>-18.13</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>-4.13</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>-3.5</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1090,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-131.19</t>
+          <t>-132.67</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>403039460.5255319</t>
+          <t>402598001.2117564</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>203706161.0</t>
+          <t>60912790.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>87092333.59999999</v>
+        <v>90207911.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>95316409.3</t>
+          <t>85136383.4</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>406267066.38</v>
+        <v>403373073.88</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-8224075</t>
+          <t>5071528</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-39826028.36576135</t>
+          <t>-39066012.8562825</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-34807557.88665277</t>
+          <t>-34885927.55414887</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>203706161.0</t>
+          <t>60912790.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,12 +1193,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1216,7 +1208,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>80.71</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>44.51</t>
+          <t>44.61</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>10996</t>
+          <t>11049</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1318,7 +1310,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>617.222</t>
+          <t>1943.113</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-33.70</t>
+          <t>-8.63</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-9.57</t>
+          <t>-10.87</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-6.83</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,12 +1436,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>594</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1462,56 +1454,48 @@
           <t>3.51</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>-2.07</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>-5.77</t>
-        </is>
+      <c r="AH3" t="n">
+        <v>-2.29</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>-5.9</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>106.2</t>
+          <t>104.9</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>112.7</v>
+        <v>111.48</v>
       </c>
       <c r="AN3" t="n">
-        <v>117.72</v>
+        <v>117.45</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>120.13</t>
+          <t>119.82</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-23.26</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>-3.89</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-3.15</t>
-        </is>
+          <t>-22.00</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>-4.07</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>-3.34</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1520,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-129.47</t>
+          <t>-131.19</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>403039460.5255319</t>
+          <t>402598001.2117564</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>64556125.0</t>
+          <t>203706161.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>57159347</v>
+        <v>87092333.59999999</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>86212815.0</t>
+          <t>95316409.3</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>406636712.2</v>
+        <v>406267066.38</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-29053468</t>
+          <t>-8224075</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-40738477.54378109</t>
+          <t>-39826028.36576135</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-48751763.90142073</t>
+          <t>-34807557.88665277</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>64556125.0</t>
+          <t>203706161.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1615,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>80.71</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>44.51</t>
+          <t>44.61</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>10996</t>
+          <t>11049</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1701,17 +1685,17 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>109.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>460.69</t>
+          <t>617.222</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-39.87</t>
+          <t>-33.70</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-9.57</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,74 +1858,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>594</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>15.79</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>-1.49</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>-5.68</t>
-        </is>
+          <t>3.51</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>-2.07</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-5.77</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>107.1</t>
+          <t>106.2</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>113.55</v>
+        <v>112.7</v>
       </c>
       <c r="AN4" t="n">
-        <v>117.93</v>
+        <v>117.72</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>120.44</t>
+          <t>120.13</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-26.20</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>-3.75</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-2.97</t>
-        </is>
+          <t>-23.26</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>-3.89</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-3.15</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1950,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-127.76</t>
+          <t>-129.47</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>403039460.5255319</t>
+          <t>402598001.2117564</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>48699833.0</t>
+          <t>64556125.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>59160766.2</v>
+        <v>57159347</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>98382511.1</t>
+          <t>86212815.0</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>408309837.48</v>
+        <v>406636712.2</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-39221744</t>
+          <t>-29053468</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-39281516.38784661</t>
+          <t>-40738477.54378109</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-52021991.35460995</t>
+          <t>-48751763.90142073</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>48699833.0</t>
+          <t>64556125.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2047,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>80.71</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>44.51</t>
+          <t>44.61</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>10996</t>
+          <t>11049</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,7 +2102,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2136,12 +2112,12 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>694.884</t>
+          <t>460.69</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-45.60</t>
+          <t>-39.87</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-9.13</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,74 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>594</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>25.32</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>-2.52</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>-6.29</t>
-        </is>
+          <t>15.79</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-5.68</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>107.2</t>
+          <t>107.1</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>114.4</v>
+        <v>113.55</v>
       </c>
       <c r="AN5" t="n">
-        <v>118.09</v>
+        <v>117.93</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>120.69</t>
+          <t>120.44</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-32.21</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>-3.67</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-2.78</t>
-        </is>
+          <t>-26.20</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-3.75</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>-2.97</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2380,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-125.94</t>
+          <t>-127.76</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>403039460.5255319</t>
+          <t>402598001.2117564</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>73164650.0</t>
+          <t>48699833.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>66768101.4</v>
+        <v>59160766.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>122726255.3</t>
+          <t>98382511.1</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>411205419.78</v>
+        <v>408309837.48</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-55958153</t>
+          <t>-39221744</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-36965066.39388964</t>
+          <t>-39281516.38784661</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-53136928.16792992</t>
+          <t>-52021991.35460995</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>73164650.0</t>
+          <t>48699833.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2459,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>80.71</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>44.51</t>
+          <t>44.61</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>10996</t>
+          <t>11049</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>417.291</t>
+          <t>694.884</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-42.34</t>
+          <t>-45.60</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>-9.13</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,37 +2702,33 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>594</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>36.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>33.93</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>-6.98</t>
-        </is>
+          <t>25.32</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>-2.52</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-6.29</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -2778,30 +2742,26 @@
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>115.25</v>
+        <v>114.4</v>
       </c>
       <c r="AN6" t="n">
-        <v>118.34</v>
+        <v>118.09</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>120.96</t>
+          <t>120.69</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-33.76</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>-3.41</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>-2.55</t>
-        </is>
+          <t>-32.21</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-3.67</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-2.78</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2810,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-123.85</t>
+          <t>-125.94</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>403039460.5255319</t>
+          <t>402598001.2117564</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>45334899.0</t>
+          <t>73164650.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>80064855</v>
+        <v>66768101.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>138863434.4</t>
+          <t>122726255.3</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>419038513.76</v>
+        <v>411205419.78</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-58798579</t>
+          <t>-55958153</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-34024727.88951867</t>
+          <t>-36965066.39388964</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-55453178.00238952</t>
+          <t>-53136928.16792992</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>45334899.0</t>
+          <t>73164650.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2926,17 +2886,17 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>80.71</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>44.51</t>
+          <t>44.61</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>10996</t>
+          <t>11049</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>497.76</t>
+          <t>417.291</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-36.00</t>
+          <t>-42.34</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-5.22</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,74 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>594</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>39.13</t>
+          <t>36.84</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>23.77</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>1.96</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>-7.90</t>
-        </is>
+          <t>33.93</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>-6.98</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>106.9</t>
+          <t>107.2</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>116.08</v>
+        <v>115.25</v>
       </c>
       <c r="AN7" t="n">
-        <v>118.57</v>
+        <v>118.34</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>121.12</t>
+          <t>120.96</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-45.24</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>-3.39</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-2.34</t>
-        </is>
+          <t>-33.76</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>-3.41</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>-2.55</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3240,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-121.84</t>
+          <t>-123.85</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>403039460.5255319</t>
+          <t>402598001.2117564</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>54041228.0</t>
+          <t>45334899.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>103540485</v>
+        <v>80064855</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>161783660.5</t>
+          <t>138863434.4</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>428520261.8</v>
+        <v>419038513.76</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-58243175</t>
+          <t>-58798579</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-30128646.05081488</t>
+          <t>-34024727.88951867</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-53799876.65867507</t>
+          <t>-55453178.00238952</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>54041228.0</t>
+          <t>45334899.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>10.10</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3303,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>80.71</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>44.51</t>
+          <t>44.61</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>10996</t>
+          <t>11049</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>688.338</t>
+          <t>497.76</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-5.85</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-46.80</t>
+          <t>-36.00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-5.65</t>
+          <t>-5.22</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,37 +3546,33 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>594</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>25.81</t>
+          <t>39.13</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>10.73</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>0.56</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>-7.54</t>
-        </is>
+          <t>23.77</t>
+        </is>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>-7.9</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -3634,34 +3582,30 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>107.9</t>
+          <t>106.9</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>116.7</v>
+        <v>116.08</v>
       </c>
       <c r="AN8" t="n">
-        <v>118.76</v>
+        <v>118.57</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>121.31</t>
+          <t>121.12</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-65.07</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>-3.42</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-2.07</t>
-        </is>
+          <t>-45.24</t>
+        </is>
+      </c>
+      <c r="AQ8" t="n">
+        <v>-3.39</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>-2.34</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3670,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-119.37</t>
+          <t>-121.84</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>403039460.5255319</t>
+          <t>402598001.2117564</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>74563221.0</t>
+          <t>54041228.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>115266283</v>
+        <v>103540485</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>216664373.4</t>
+          <t>161783660.5</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>435928377.96</v>
+        <v>428520261.8</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-101398090</t>
+          <t>-58243175</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-25824785.94029485</t>
+          <t>-30128646.05081488</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-50449414.39413029</t>
+          <t>-53799876.65867507</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>74563221.0</t>
+          <t>54041228.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>10.10</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3725,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3796,7 +3740,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>80.71</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>44.51</t>
+          <t>44.61</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>10996</t>
+          <t>11049</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,7 +3790,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -3856,12 +3800,12 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>823.014</t>
+          <t>688.338</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>108.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-3.41</t>
+          <t>-5.34</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-55.86</t>
+          <t>-46.80</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-7.83</t>
+          <t>-5.65</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,74 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>594</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>6.38</t>
+          <t>25.81</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2.13</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>-2.03</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>-7.68</t>
-        </is>
+          <t>10.73</t>
+        </is>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-7.54</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>108.2</t>
+          <t>107.9</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>117.2</v>
+        <v>116.7</v>
       </c>
       <c r="AN9" t="n">
-        <v>118.83</v>
+        <v>118.76</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>121.47</t>
+          <t>121.31</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-93.34</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>-3.35</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-1.74</t>
-        </is>
+          <t>-65.07</t>
+        </is>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-3.42</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>-2.07</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4100,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-116.22</t>
+          <t>-119.37</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>403039460.5255319</t>
+          <t>402598001.2117564</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>86736509.0</t>
+          <t>74563221.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>137604256</v>
+        <v>115266283</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>311751968.8</t>
+          <t>216664373.4</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>442360683.54</v>
+        <v>435928377.96</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-174147712</t>
+          <t>-101398090</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-21347580.76687022</t>
+          <t>-25824785.94029485</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-46060059.89499024</t>
+          <t>-50449414.39413029</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>86736509.0</t>
+          <t>74563221.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4147,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>80.71</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>44.51</t>
+          <t>44.61</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>10996</t>
+          <t>11049</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>109.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>108.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1335.506</t>
+          <t>823.014</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-43.46</t>
+          <t>-55.86</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-9.13</t>
+          <t>-7.83</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,74 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>594</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.38</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>8.11</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>-4.04</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>-7.59</t>
-        </is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="AH10" t="n">
+        <v>-2.03</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-7.68</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>108.9</t>
+          <t>108.2</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>117.85</v>
+        <v>117.2</v>
       </c>
       <c r="AN10" t="n">
-        <v>119.05</v>
+        <v>118.83</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>121.66</t>
+          <t>121.47</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-123.04</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>-2.97</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-1.33</t>
-        </is>
+          <t>-93.34</t>
+        </is>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-3.35</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>-1.74</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4530,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-112.43</t>
+          <t>-116.22</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>403039460.5255319</t>
+          <t>402598001.2117564</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>139648418.0</t>
+          <t>86736509.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>178684409.2</v>
+        <v>137604256</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>316018501.8</t>
+          <t>311751968.8</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>449139949.34</v>
+        <v>442360683.54</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-137334092</t>
+          <t>-174147712</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-16854402.74357567</t>
+          <t>-21347580.76687022</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-39448832.1856834</t>
+          <t>-46060059.89499024</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>139648418.0</t>
+          <t>86736509.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4579,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>80.71</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>44.51</t>
+          <t>44.61</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>10996</t>
+          <t>11049</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-6.88</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1507.376</t>
+          <t>1335.506</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-3.9</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-40.67</t>
+          <t>-43.46</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-7.39</t>
+          <t>-9.13</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4812,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>594</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4899,59 +4827,51 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>9.01</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>-4.23</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>-6.34</t>
-        </is>
+          <t>8.11</t>
+        </is>
+      </c>
+      <c r="AH11" t="n">
+        <v>-4.04</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-7.59</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>111.2</t>
+          <t>108.9</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>118.72</v>
+        <v>117.85</v>
       </c>
       <c r="AN11" t="n">
-        <v>119.21</v>
+        <v>119.05</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>121.84</t>
+          <t>121.66</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-147.13</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>-2.28</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-0.92</t>
-        </is>
+          <t>-123.04</t>
+        </is>
+      </c>
+      <c r="AQ11" t="n">
+        <v>-2.97</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>-1.33</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4960,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-108.61</t>
+          <t>-112.43</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>403039460.5255319</t>
+          <t>402598001.2117564</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>162713049.0</t>
+          <t>139648418.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>197662013.8</v>
+        <v>178684409.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>333134571.9</t>
+          <t>316018501.8</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>455062786.1</v>
+        <v>449139949.34</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-135472558</t>
+          <t>-137334092</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-12746324.66319245</t>
+          <t>-16854402.74357567</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-34264467.41575634</t>
+          <t>-39448832.1856834</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>162713049.0</t>
+          <t>139648418.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>7.58</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5081,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>80.71</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>44.51</t>
+          <t>44.61</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>10996</t>
+          <t>11049</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>-6.88</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>987.925</t>
+          <t>1507.376</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-11.22</t>
+          <t>-3.4</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-43.50</t>
+          <t>-40.67</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-7.39</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,17 +5234,17 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>594</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -5332,56 +5252,48 @@
           <t>9.01</t>
         </is>
       </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>0.09</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>-4.43</t>
-        </is>
+      <c r="AH12" t="n">
+        <v>-4.23</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-6.34</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>113.9</t>
+          <t>111.2</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>119.18</v>
+        <v>118.72</v>
       </c>
       <c r="AN12" t="n">
-        <v>119.4</v>
+        <v>119.21</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>121.95</t>
+          <t>121.84</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-168.80</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>-1.57</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>-0.58</t>
-        </is>
+          <t>-147.13</t>
+        </is>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-2.28</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-0.92</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5390,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-105.44</t>
+          <t>-108.61</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>403039460.5255319</t>
+          <t>402598001.2117564</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>112670218.0</t>
+          <t>162713049.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>220026836</v>
+        <v>197662013.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>389449404.3</t>
+          <t>333134571.9</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>458112049.14</v>
+        <v>455062786.1</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-169422568</t>
+          <t>-135472558</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-8833935.071817197</t>
+          <t>-12746324.66319245</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-28105711.51529783</t>
+          <t>-34264467.41575634</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>112670218.0</t>
+          <t>162713049.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>15.15</t>
+          <t>7.58</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>80.71</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>44.51</t>
+          <t>44.61</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>10996</t>
+          <t>11049</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>113.5</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/玻_碳纖.xlsx
+++ b/Result/checksun_type/玻_碳纖.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>593.888</t>
+          <t>775.327</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>15.71</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-10.43</t>
+          <t>-9.57</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,66 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>775</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>10.26</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>-0.87</v>
+        <v>0.19</v>
       </c>
       <c r="AI2" t="n">
-        <v>-6.31</v>
+        <v>-5.94</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-5.34</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>103.9</t>
+          <t>103.8</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>110.9</v>
+        <v>110.35</v>
       </c>
       <c r="AN2" t="n">
-        <v>117.15</v>
+        <v>116.94</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>119.56</t>
+          <t>119.31</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-18.13</t>
+          <t>-12.25</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-4.13</v>
+        <v>-4.05</v>
       </c>
       <c r="AR2" t="n">
-        <v>-3.5</v>
+        <v>-3.61</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-132.67</t>
+          <t>-133.70</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>402598001.2117564</t>
+          <t>402199070.8896747</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>60912790.0</t>
+          <t>80369509.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>90207911.8</v>
+        <v>91648883.59999999</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>85136383.4</t>
+          <t>79208492.5</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>403373073.88</v>
+        <v>400946194.74</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>5071528</t>
+          <t>12440391</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-39066012.8562825</t>
+          <t>-38072685.37186095</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-34885927.55414887</t>
+          <t>-32609384.20754242</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>60912790.0</t>
+          <t>80369509.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>81.89</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>44.61</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>11049</t>
+          <t>11157</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
+          <t>105.5</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>102.5</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
           <t>104.0</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>101.0</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>103.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1943.113</t>
+          <t>593.888</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-8.63</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-10.87</t>
+          <t>-10.43</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-6.83</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,66 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>775</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>-2.29</v>
+        <v>-0.87</v>
       </c>
       <c r="AI3" t="n">
-        <v>-5.9</v>
+        <v>-6.31</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-5.34</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>104.9</t>
+          <t>103.9</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>111.48</v>
+        <v>110.9</v>
       </c>
       <c r="AN3" t="n">
-        <v>117.45</v>
+        <v>117.15</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>119.82</t>
+          <t>119.56</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-22.00</t>
+          <t>-18.13</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-4.07</v>
+        <v>-4.13</v>
       </c>
       <c r="AR3" t="n">
-        <v>-3.34</v>
+        <v>-3.5</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-131.19</t>
+          <t>-132.67</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>402598001.2117564</t>
+          <t>402199070.8896747</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>203706161.0</t>
+          <t>60912790.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>87092333.59999999</v>
+        <v>90207911.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>95316409.3</t>
+          <t>85136383.4</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>406267066.38</v>
+        <v>403373073.88</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-8224075</t>
+          <t>5071528</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-39826028.36576135</t>
+          <t>-39066012.8562825</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-34807557.88665277</t>
+          <t>-34885927.55414887</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>203706161.0</t>
+          <t>60912790.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>81.89</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>44.61</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>11049</t>
+          <t>11157</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>617.222</t>
+          <t>1943.113</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-33.70</t>
+          <t>-8.63</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-9.57</t>
+          <t>-10.87</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-6.83</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,12 +1858,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>775</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1877,47 +1877,47 @@
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>-2.07</v>
+        <v>-2.29</v>
       </c>
       <c r="AI4" t="n">
-        <v>-5.77</v>
+        <v>-5.9</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>106.2</t>
+          <t>104.9</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>112.7</v>
+        <v>111.48</v>
       </c>
       <c r="AN4" t="n">
-        <v>117.72</v>
+        <v>117.45</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>120.13</t>
+          <t>119.82</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-23.26</t>
+          <t>-22.00</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-3.89</v>
+        <v>-4.07</v>
       </c>
       <c r="AR4" t="n">
-        <v>-3.15</v>
+        <v>-3.34</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-129.47</t>
+          <t>-131.19</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>402598001.2117564</t>
+          <t>402199070.8896747</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>64556125.0</t>
+          <t>203706161.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>57159347</v>
+        <v>87092333.59999999</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>86212815.0</t>
+          <t>95316409.3</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>406636712.2</v>
+        <v>406267066.38</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-29053468</t>
+          <t>-8224075</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-40738477.54378109</t>
+          <t>-39826028.36576135</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-48751763.90142073</t>
+          <t>-34807557.88665277</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>64556125.0</t>
+          <t>203706161.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,22 +2037,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>81.89</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>44.61</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>11049</t>
+          <t>11157</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2107,17 +2107,17 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>109.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>460.69</t>
+          <t>617.222</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-39.87</t>
+          <t>-33.70</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-9.57</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,66 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>775</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>-1.49</v>
+        <v>-2.07</v>
       </c>
       <c r="AI5" t="n">
-        <v>-5.68</v>
+        <v>-5.77</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>107.1</t>
+          <t>106.2</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>113.55</v>
+        <v>112.7</v>
       </c>
       <c r="AN5" t="n">
-        <v>117.93</v>
+        <v>117.72</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>120.44</t>
+          <t>120.13</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-26.20</t>
+          <t>-23.26</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-3.75</v>
+        <v>-3.89</v>
       </c>
       <c r="AR5" t="n">
-        <v>-2.97</v>
+        <v>-3.15</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-127.76</t>
+          <t>-129.47</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>402598001.2117564</t>
+          <t>402199070.8896747</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>48699833.0</t>
+          <t>64556125.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>59160766.2</v>
+        <v>57159347</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>98382511.1</t>
+          <t>86212815.0</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>408309837.48</v>
+        <v>406636712.2</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-39221744</t>
+          <t>-29053468</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-39281516.38784661</t>
+          <t>-40738477.54378109</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-52021991.35460995</t>
+          <t>-48751763.90142073</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>48699833.0</t>
+          <t>64556125.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>81.89</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>44.61</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>11049</t>
+          <t>11157</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>694.884</t>
+          <t>460.69</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-45.60</t>
+          <t>-39.87</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-9.13</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,66 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>775</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>25.32</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>-2.52</v>
+        <v>-1.49</v>
       </c>
       <c r="AI6" t="n">
-        <v>-6.29</v>
+        <v>-5.68</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>107.2</t>
+          <t>107.1</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>114.4</v>
+        <v>113.55</v>
       </c>
       <c r="AN6" t="n">
-        <v>118.09</v>
+        <v>117.93</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>120.69</t>
+          <t>120.44</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-32.21</t>
+          <t>-26.20</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-3.67</v>
+        <v>-3.75</v>
       </c>
       <c r="AR6" t="n">
-        <v>-2.78</v>
+        <v>-2.97</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-125.94</t>
+          <t>-127.76</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>402598001.2117564</t>
+          <t>402199070.8896747</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>73164650.0</t>
+          <t>48699833.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>66768101.4</v>
+        <v>59160766.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>122726255.3</t>
+          <t>98382511.1</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>411205419.78</v>
+        <v>408309837.48</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-55958153</t>
+          <t>-39221744</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-36965066.39388964</t>
+          <t>-39281516.38784661</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-53136928.16792992</t>
+          <t>-52021991.35460995</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>73164650.0</t>
+          <t>48699833.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,22 +2881,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>81.89</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>44.61</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>11049</t>
+          <t>11157</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>417.291</t>
+          <t>694.884</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-42.34</t>
+          <t>-45.60</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>-9.13</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,33 +3124,33 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>775</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>36.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>33.93</t>
+          <t>25.32</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>0.75</v>
+        <v>-2.52</v>
       </c>
       <c r="AI7" t="n">
-        <v>-6.98</v>
+        <v>-6.29</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -3164,26 +3164,26 @@
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>115.25</v>
+        <v>114.4</v>
       </c>
       <c r="AN7" t="n">
-        <v>118.34</v>
+        <v>118.09</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>120.96</t>
+          <t>120.69</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-33.76</t>
+          <t>-32.21</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-3.41</v>
+        <v>-3.67</v>
       </c>
       <c r="AR7" t="n">
-        <v>-2.55</v>
+        <v>-2.78</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-123.85</t>
+          <t>-125.94</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>402598001.2117564</t>
+          <t>402199070.8896747</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>45334899.0</t>
+          <t>73164650.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>80064855</v>
+        <v>66768101.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>138863434.4</t>
+          <t>122726255.3</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>419038513.76</v>
+        <v>411205419.78</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-58798579</t>
+          <t>-55958153</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-34024727.88951867</t>
+          <t>-36965066.39388964</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-55453178.00238952</t>
+          <t>-53136928.16792992</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>45334899.0</t>
+          <t>73164650.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3308,17 +3308,17 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>81.89</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>44.61</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>11049</t>
+          <t>11157</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>497.76</t>
+          <t>417.291</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-3.85</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-36.00</t>
+          <t>-42.34</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-5.22</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,66 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>775</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>39.13</t>
+          <t>36.84</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>23.77</t>
+          <t>33.93</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>1.96</v>
+        <v>0.75</v>
       </c>
       <c r="AI8" t="n">
-        <v>-7.9</v>
+        <v>-6.98</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>106.9</t>
+          <t>107.2</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>116.08</v>
+        <v>115.25</v>
       </c>
       <c r="AN8" t="n">
-        <v>118.57</v>
+        <v>118.34</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>121.12</t>
+          <t>120.96</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-45.24</t>
+          <t>-33.76</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-3.39</v>
+        <v>-3.41</v>
       </c>
       <c r="AR8" t="n">
-        <v>-2.34</v>
+        <v>-2.55</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-121.84</t>
+          <t>-123.85</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>402598001.2117564</t>
+          <t>402199070.8896747</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>54041228.0</t>
+          <t>45334899.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>103540485</v>
+        <v>80064855</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>161783660.5</t>
+          <t>138863434.4</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>428520261.8</v>
+        <v>419038513.76</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-58243175</t>
+          <t>-58798579</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-30128646.05081488</t>
+          <t>-34024727.88951867</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-53799876.65867507</t>
+          <t>-55453178.00238952</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>54041228.0</t>
+          <t>45334899.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>10.10</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3725,22 +3725,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>81.89</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>44.61</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>11049</t>
+          <t>11157</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>688.338</t>
+          <t>497.76</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-5.34</t>
+          <t>-4.81</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-46.80</t>
+          <t>-36.00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-5.65</t>
+          <t>-5.22</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,33 +3968,33 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>775</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>25.81</t>
+          <t>39.13</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>10.73</t>
+          <t>23.77</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.96</v>
       </c>
       <c r="AI9" t="n">
-        <v>-7.54</v>
+        <v>-7.9</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -4004,30 +4004,30 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>107.9</t>
+          <t>106.9</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>116.7</v>
+        <v>116.08</v>
       </c>
       <c r="AN9" t="n">
-        <v>118.76</v>
+        <v>118.57</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>121.31</t>
+          <t>121.12</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-65.07</t>
+          <t>-45.24</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-3.42</v>
+        <v>-3.39</v>
       </c>
       <c r="AR9" t="n">
-        <v>-2.07</v>
+        <v>-2.34</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-119.37</t>
+          <t>-121.84</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>402598001.2117564</t>
+          <t>402199070.8896747</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>74563221.0</t>
+          <t>54041228.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>115266283</v>
+        <v>103540485</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>216664373.4</t>
+          <t>161783660.5</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>435928377.96</v>
+        <v>428520261.8</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-101398090</t>
+          <t>-58243175</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-25824785.94029485</t>
+          <t>-30128646.05081488</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-50449414.39413029</t>
+          <t>-53799876.65867507</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>74563221.0</t>
+          <t>54041228.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>10.10</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>81.89</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>44.61</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>11049</t>
+          <t>11157</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4222,12 +4222,12 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>823.014</t>
+          <t>688.338</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>108.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-4.33</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-55.86</t>
+          <t>-46.80</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-7.83</t>
+          <t>-5.65</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>775</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>6.38</t>
+          <t>25.81</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>10.73</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>-2.03</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AI10" t="n">
-        <v>-7.68</v>
+        <v>-7.54</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>108.2</t>
+          <t>107.9</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>117.2</v>
+        <v>116.7</v>
       </c>
       <c r="AN10" t="n">
-        <v>118.83</v>
+        <v>118.76</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>121.47</t>
+          <t>121.31</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-93.34</t>
+          <t>-65.07</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-3.35</v>
+        <v>-3.42</v>
       </c>
       <c r="AR10" t="n">
-        <v>-1.74</v>
+        <v>-2.07</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-116.22</t>
+          <t>-119.37</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>402598001.2117564</t>
+          <t>402199070.8896747</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>86736509.0</t>
+          <t>74563221.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>137604256</v>
+        <v>115266283</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>311751968.8</t>
+          <t>216664373.4</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>442360683.54</v>
+        <v>435928377.96</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-174147712</t>
+          <t>-101398090</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-21347580.76687022</t>
+          <t>-25824785.94029485</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-46060059.89499024</t>
+          <t>-50449414.39413029</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>86736509.0</t>
+          <t>74563221.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,22 +4569,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>81.89</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>44.61</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>11049</t>
+          <t>11157</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>109.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>108.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1335.506</t>
+          <t>823.014</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-43.46</t>
+          <t>-55.86</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-9.13</t>
+          <t>-7.83</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>775</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.38</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>8.11</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>-4.04</v>
+        <v>-2.03</v>
       </c>
       <c r="AI11" t="n">
-        <v>-7.59</v>
+        <v>-7.68</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>108.9</t>
+          <t>108.2</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>117.85</v>
+        <v>117.2</v>
       </c>
       <c r="AN11" t="n">
-        <v>119.05</v>
+        <v>118.83</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>121.66</t>
+          <t>121.47</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-123.04</t>
+          <t>-93.34</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-2.97</v>
+        <v>-3.35</v>
       </c>
       <c r="AR11" t="n">
-        <v>-1.33</v>
+        <v>-1.74</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-112.43</t>
+          <t>-116.22</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>402598001.2117564</t>
+          <t>402199070.8896747</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>139648418.0</t>
+          <t>86736509.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>178684409.2</v>
+        <v>137604256</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>316018501.8</t>
+          <t>311751968.8</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>449139949.34</v>
+        <v>442360683.54</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-137334092</t>
+          <t>-174147712</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-16854402.74357567</t>
+          <t>-21347580.76687022</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-39448832.1856834</t>
+          <t>-46060059.89499024</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>139648418.0</t>
+          <t>86736509.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>81.89</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>44.61</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>11049</t>
+          <t>11157</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-6.88</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1507.376</t>
+          <t>1335.506</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-3.4</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-40.67</t>
+          <t>-43.46</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-7.39</t>
+          <t>-9.13</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,12 +5234,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>775</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5249,51 +5249,51 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>8.11</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>-4.23</v>
+        <v>-4.04</v>
       </c>
       <c r="AI12" t="n">
-        <v>-6.34</v>
+        <v>-7.59</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>111.2</t>
+          <t>108.9</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>118.72</v>
+        <v>117.85</v>
       </c>
       <c r="AN12" t="n">
-        <v>119.21</v>
+        <v>119.05</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>121.84</t>
+          <t>121.66</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-147.13</t>
+          <t>-123.04</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-2.28</v>
+        <v>-2.97</v>
       </c>
       <c r="AR12" t="n">
-        <v>-0.92</v>
+        <v>-1.33</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-108.61</t>
+          <t>-112.43</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>402598001.2117564</t>
+          <t>402199070.8896747</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>162713049.0</t>
+          <t>139648418.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>197662013.8</v>
+        <v>178684409.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>333134571.9</t>
+          <t>316018501.8</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>455062786.1</v>
+        <v>449139949.34</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-135472558</t>
+          <t>-137334092</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-12746324.66319245</t>
+          <t>-16854402.74357567</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-34264467.41575634</t>
+          <t>-39448832.1856834</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>162713049.0</t>
+          <t>139648418.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>7.58</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>81.89</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>44.61</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>11049</t>
+          <t>11157</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/玻_碳纖.xlsx
+++ b/Result/checksun_type/玻_碳纖.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>775.327</t>
+          <t>843.89</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>15.71</t>
+          <t>25.42</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>844</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,51 +1029,51 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>10.26</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>0.19</v>
+        <v>0.48</v>
       </c>
       <c r="AI2" t="n">
-        <v>-5.94</v>
+        <v>-5.69</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.8</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>103.8</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>110.35</v>
+        <v>109.75</v>
       </c>
       <c r="AN2" t="n">
-        <v>116.94</v>
+        <v>116.51</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>119.31</t>
+          <t>119.11</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-12.25</t>
+          <t>-7.23</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-4.05</v>
+        <v>-3.94</v>
       </c>
       <c r="AR2" t="n">
-        <v>-3.61</v>
+        <v>-3.67</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-133.70</t>
+          <t>-134.32</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>402199070.8896747</t>
+          <t>401817128.4766949</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>80369509.0</t>
+          <t>87855895.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>91648883.59999999</v>
+        <v>99480096</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>79208492.5</t>
+          <t>79320431.1</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>400946194.74</v>
+        <v>376415022.36</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>12440391</t>
+          <t>20159664</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-38072685.37186095</t>
+          <t>-36775209.20845608</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-32609384.20754242</t>
+          <t>-29639090.30972932</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>80369509.0</t>
+          <t>87855895.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.34</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>593.888</t>
+          <t>775.327</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>15.71</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-10.43</t>
+          <t>-9.57</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,66 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>844</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>10.26</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>-0.87</v>
+        <v>0.19</v>
       </c>
       <c r="AI3" t="n">
-        <v>-6.31</v>
+        <v>-5.94</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-5.34</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>103.9</t>
+          <t>103.8</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>110.9</v>
+        <v>110.35</v>
       </c>
       <c r="AN3" t="n">
-        <v>117.15</v>
+        <v>116.94</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>119.56</t>
+          <t>119.31</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-18.13</t>
+          <t>-12.25</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-4.13</v>
+        <v>-4.05</v>
       </c>
       <c r="AR3" t="n">
-        <v>-3.5</v>
+        <v>-3.61</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-132.67</t>
+          <t>-133.70</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>402199070.8896747</t>
+          <t>401817128.4766949</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>60912790.0</t>
+          <t>80369509.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>90207911.8</v>
+        <v>91648883.59999999</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>85136383.4</t>
+          <t>79208492.5</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>403373073.88</v>
+        <v>400946194.74</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>5071528</t>
+          <t>12440391</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-39066012.8562825</t>
+          <t>-38072685.37186095</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-34885927.55414887</t>
+          <t>-32609384.20754242</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>60912790.0</t>
+          <t>80369509.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.34</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
+          <t>105.5</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>102.5</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
           <t>104.0</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>101.0</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>103.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1943.113</t>
+          <t>593.888</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-8.63</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-10.87</t>
+          <t>-10.43</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-6.83</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,66 +1858,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>844</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>-2.29</v>
+        <v>-0.87</v>
       </c>
       <c r="AI4" t="n">
-        <v>-5.9</v>
+        <v>-6.31</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-5.34</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>104.9</t>
+          <t>103.9</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>111.48</v>
+        <v>110.9</v>
       </c>
       <c r="AN4" t="n">
-        <v>117.45</v>
+        <v>117.15</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>119.82</t>
+          <t>119.56</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-22.00</t>
+          <t>-18.13</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-4.07</v>
+        <v>-4.13</v>
       </c>
       <c r="AR4" t="n">
-        <v>-3.34</v>
+        <v>-3.5</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-131.19</t>
+          <t>-132.67</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>402199070.8896747</t>
+          <t>401817128.4766949</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>203706161.0</t>
+          <t>60912790.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>87092333.59999999</v>
+        <v>90207911.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>95316409.3</t>
+          <t>85136383.4</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>406267066.38</v>
+        <v>403373073.88</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-8224075</t>
+          <t>5071528</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-39826028.36576135</t>
+          <t>-39066012.8562825</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-34807557.88665277</t>
+          <t>-34885927.55414887</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>203706161.0</t>
+          <t>60912790.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,12 +2037,12 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.34</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>617.222</t>
+          <t>1943.113</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-33.70</t>
+          <t>-8.63</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-9.57</t>
+          <t>-10.87</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-6.83</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,12 +2280,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>844</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2299,47 +2299,47 @@
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>-2.07</v>
+        <v>-2.29</v>
       </c>
       <c r="AI5" t="n">
-        <v>-5.77</v>
+        <v>-5.9</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>106.2</t>
+          <t>104.9</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>112.7</v>
+        <v>111.48</v>
       </c>
       <c r="AN5" t="n">
-        <v>117.72</v>
+        <v>117.45</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>120.13</t>
+          <t>119.82</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-23.26</t>
+          <t>-22.00</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-3.89</v>
+        <v>-4.07</v>
       </c>
       <c r="AR5" t="n">
-        <v>-3.15</v>
+        <v>-3.34</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-129.47</t>
+          <t>-131.19</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>402199070.8896747</t>
+          <t>401817128.4766949</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>64556125.0</t>
+          <t>203706161.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>57159347</v>
+        <v>87092333.59999999</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>86212815.0</t>
+          <t>95316409.3</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>406636712.2</v>
+        <v>406267066.38</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-29053468</t>
+          <t>-8224075</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-40738477.54378109</t>
+          <t>-39826028.36576135</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-48751763.90142073</t>
+          <t>-34807557.88665277</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>64556125.0</t>
+          <t>203706161.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,17 +2459,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.34</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2529,17 +2529,17 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>109.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>460.69</t>
+          <t>617.222</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-39.87</t>
+          <t>-33.70</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-9.57</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,66 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>844</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>-1.49</v>
+        <v>-2.07</v>
       </c>
       <c r="AI6" t="n">
-        <v>-5.68</v>
+        <v>-5.77</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>107.1</t>
+          <t>106.2</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>113.55</v>
+        <v>112.7</v>
       </c>
       <c r="AN6" t="n">
-        <v>117.93</v>
+        <v>117.72</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>120.44</t>
+          <t>120.13</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-26.20</t>
+          <t>-23.26</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-3.75</v>
+        <v>-3.89</v>
       </c>
       <c r="AR6" t="n">
-        <v>-2.97</v>
+        <v>-3.15</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-127.76</t>
+          <t>-129.47</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>402199070.8896747</t>
+          <t>401817128.4766949</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>48699833.0</t>
+          <t>64556125.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>59160766.2</v>
+        <v>57159347</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>98382511.1</t>
+          <t>86212815.0</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>408309837.48</v>
+        <v>406636712.2</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-39221744</t>
+          <t>-29053468</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-39281516.38784661</t>
+          <t>-40738477.54378109</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-52021991.35460995</t>
+          <t>-48751763.90142073</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>48699833.0</t>
+          <t>64556125.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.34</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -2956,12 +2956,12 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>694.884</t>
+          <t>460.69</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-45.60</t>
+          <t>-39.87</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-9.13</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,66 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>844</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>25.32</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>-2.52</v>
+        <v>-1.49</v>
       </c>
       <c r="AI7" t="n">
-        <v>-6.29</v>
+        <v>-5.68</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>107.2</t>
+          <t>107.1</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>114.4</v>
+        <v>113.55</v>
       </c>
       <c r="AN7" t="n">
-        <v>118.09</v>
+        <v>117.93</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>120.69</t>
+          <t>120.44</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-32.21</t>
+          <t>-26.20</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-3.67</v>
+        <v>-3.75</v>
       </c>
       <c r="AR7" t="n">
-        <v>-2.78</v>
+        <v>-2.97</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-125.94</t>
+          <t>-127.76</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>402199070.8896747</t>
+          <t>401817128.4766949</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>73164650.0</t>
+          <t>48699833.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>66768101.4</v>
+        <v>59160766.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>122726255.3</t>
+          <t>98382511.1</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>411205419.78</v>
+        <v>408309837.48</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-55958153</t>
+          <t>-39221744</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-36965066.39388964</t>
+          <t>-39281516.38784661</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-53136928.16792992</t>
+          <t>-52021991.35460995</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>73164650.0</t>
+          <t>48699833.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3303,17 +3303,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.34</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>417.291</t>
+          <t>694.884</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-3.85</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-42.34</t>
+          <t>-45.60</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>-9.13</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,33 +3546,33 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>844</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>36.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>33.93</t>
+          <t>25.32</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>0.75</v>
+        <v>-2.52</v>
       </c>
       <c r="AI8" t="n">
-        <v>-6.98</v>
+        <v>-6.29</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -3586,26 +3586,26 @@
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>115.25</v>
+        <v>114.4</v>
       </c>
       <c r="AN8" t="n">
-        <v>118.34</v>
+        <v>118.09</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>120.96</t>
+          <t>120.69</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-33.76</t>
+          <t>-32.21</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-3.41</v>
+        <v>-3.67</v>
       </c>
       <c r="AR8" t="n">
-        <v>-2.55</v>
+        <v>-2.78</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-123.85</t>
+          <t>-125.94</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>402199070.8896747</t>
+          <t>401817128.4766949</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>45334899.0</t>
+          <t>73164650.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>80064855</v>
+        <v>66768101.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>138863434.4</t>
+          <t>122726255.3</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>419038513.76</v>
+        <v>411205419.78</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-58798579</t>
+          <t>-55958153</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-34024727.88951867</t>
+          <t>-36965066.39388964</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-55453178.00238952</t>
+          <t>-53136928.16792992</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>45334899.0</t>
+          <t>73164650.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.34</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>497.76</t>
+          <t>417.291</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-4.81</t>
+          <t>-3.85</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-36.00</t>
+          <t>-42.34</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-5.22</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>844</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>39.13</t>
+          <t>36.84</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>23.77</t>
+          <t>33.93</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>1.96</v>
+        <v>0.75</v>
       </c>
       <c r="AI9" t="n">
-        <v>-7.9</v>
+        <v>-6.98</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>106.9</t>
+          <t>107.2</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>116.08</v>
+        <v>115.25</v>
       </c>
       <c r="AN9" t="n">
-        <v>118.57</v>
+        <v>118.34</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>121.12</t>
+          <t>120.96</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-45.24</t>
+          <t>-33.76</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-3.39</v>
+        <v>-3.41</v>
       </c>
       <c r="AR9" t="n">
-        <v>-2.34</v>
+        <v>-2.55</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-121.84</t>
+          <t>-123.85</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>402199070.8896747</t>
+          <t>401817128.4766949</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>54041228.0</t>
+          <t>45334899.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>103540485</v>
+        <v>80064855</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>161783660.5</t>
+          <t>138863434.4</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>428520261.8</v>
+        <v>419038513.76</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-58243175</t>
+          <t>-58798579</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-30128646.05081488</t>
+          <t>-34024727.88951867</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-53799876.65867507</t>
+          <t>-55453178.00238952</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>54041228.0</t>
+          <t>45334899.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>10.10</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,17 +4147,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.34</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>688.338</t>
+          <t>497.76</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>-4.81</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-46.80</t>
+          <t>-36.00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-5.65</t>
+          <t>-5.22</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,33 +4390,33 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>844</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>25.81</t>
+          <t>39.13</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>10.73</t>
+          <t>23.77</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.96</v>
       </c>
       <c r="AI10" t="n">
-        <v>-7.54</v>
+        <v>-7.9</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -4426,30 +4426,30 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>107.9</t>
+          <t>106.9</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>116.7</v>
+        <v>116.08</v>
       </c>
       <c r="AN10" t="n">
-        <v>118.76</v>
+        <v>118.57</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>121.31</t>
+          <t>121.12</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-65.07</t>
+          <t>-45.24</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-3.42</v>
+        <v>-3.39</v>
       </c>
       <c r="AR10" t="n">
-        <v>-2.07</v>
+        <v>-2.34</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-119.37</t>
+          <t>-121.84</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>402199070.8896747</t>
+          <t>401817128.4766949</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>74563221.0</t>
+          <t>54041228.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>115266283</v>
+        <v>103540485</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>216664373.4</t>
+          <t>161783660.5</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>435928377.96</v>
+        <v>428520261.8</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-101398090</t>
+          <t>-58243175</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-25824785.94029485</t>
+          <t>-30128646.05081488</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-50449414.39413029</t>
+          <t>-53799876.65867507</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>74563221.0</t>
+          <t>54041228.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>10.10</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,12 +4569,12 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4609,7 +4609,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.34</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>823.014</t>
+          <t>688.338</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>108.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-4.33</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-55.86</t>
+          <t>-46.80</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-7.83</t>
+          <t>-5.65</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>844</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>6.38</t>
+          <t>25.81</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>10.73</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>-2.03</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AI11" t="n">
-        <v>-7.68</v>
+        <v>-7.54</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>108.2</t>
+          <t>107.9</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>117.2</v>
+        <v>116.7</v>
       </c>
       <c r="AN11" t="n">
-        <v>118.83</v>
+        <v>118.76</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>121.47</t>
+          <t>121.31</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-93.34</t>
+          <t>-65.07</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-3.35</v>
+        <v>-3.42</v>
       </c>
       <c r="AR11" t="n">
-        <v>-1.74</v>
+        <v>-2.07</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-116.22</t>
+          <t>-119.37</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>402199070.8896747</t>
+          <t>401817128.4766949</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>86736509.0</t>
+          <t>74563221.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>137604256</v>
+        <v>115266283</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>311751968.8</t>
+          <t>216664373.4</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>442360683.54</v>
+        <v>435928377.96</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-174147712</t>
+          <t>-101398090</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-21347580.76687022</t>
+          <t>-25824785.94029485</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-46060059.89499024</t>
+          <t>-50449414.39413029</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>86736509.0</t>
+          <t>74563221.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.34</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>109.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>108.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1335.506</t>
+          <t>823.014</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-43.46</t>
+          <t>-55.86</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-9.13</t>
+          <t>-7.83</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>844</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.38</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>8.11</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>-4.04</v>
+        <v>-2.03</v>
       </c>
       <c r="AI12" t="n">
-        <v>-7.59</v>
+        <v>-7.68</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>108.9</t>
+          <t>108.2</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>117.85</v>
+        <v>117.2</v>
       </c>
       <c r="AN12" t="n">
-        <v>119.05</v>
+        <v>118.83</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>121.66</t>
+          <t>121.47</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-123.04</t>
+          <t>-93.34</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-2.97</v>
+        <v>-3.35</v>
       </c>
       <c r="AR12" t="n">
-        <v>-1.33</v>
+        <v>-1.74</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-112.43</t>
+          <t>-116.22</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>402199070.8896747</t>
+          <t>401817128.4766949</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>139648418.0</t>
+          <t>86736509.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>178684409.2</v>
+        <v>137604256</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>316018501.8</t>
+          <t>311751968.8</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>449139949.34</v>
+        <v>442360683.54</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-137334092</t>
+          <t>-174147712</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-16854402.74357567</t>
+          <t>-21347580.76687022</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-39448832.1856834</t>
+          <t>-46060059.89499024</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>139648418.0</t>
+          <t>86736509.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.34</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/玻_碳纖.xlsx
+++ b/Result/checksun_type/玻_碳纖.xlsx
@@ -883,42 +883,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>672.31</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>105.5</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>843.89</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>25.42</t>
+          <t>27.60</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-9.57</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,66 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>844</t>
+          <t>672</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>54.55</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>33.57</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>0.48</v>
+        <v>1.64</v>
       </c>
       <c r="AI2" t="n">
-        <v>-5.69</v>
+        <v>-4.46</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-5.8</t>
+          <t>-6.33</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>103.8</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>109.75</v>
+        <v>108.65</v>
       </c>
       <c r="AN2" t="n">
-        <v>116.51</v>
+        <v>115.99</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>119.11</t>
+          <t>118.94</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-7.23</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-3.94</v>
+        <v>-3.69</v>
       </c>
       <c r="AR2" t="n">
-        <v>-3.67</v>
+        <v>-3.68</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-134.32</t>
+          <t>-134.35</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>401817128.4766949</t>
+          <t>401400381.8060648</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>87855895.0</t>
+          <t>70895826.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>99480096</v>
+        <v>100748036.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>79320431.1</t>
+          <t>78953691.6</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>376415022.36</v>
+        <v>316450597.8</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>20159664</t>
+          <t>21794344</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-36775209.20845608</t>
+          <t>-35439163.56077314</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-29639090.30972932</t>
+          <t>-28090912.49851693</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>87855895.0</t>
+          <t>70895826.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>81.89</t>
+          <t>83.07</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>45.34</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>11157</t>
+          <t>11318</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>775.327</t>
+          <t>843.89</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>15.71</t>
+          <t>25.42</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,12 +1436,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>844</t>
+          <t>672</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1451,51 +1451,51 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>10.26</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>0.19</v>
+        <v>0.48</v>
       </c>
       <c r="AI3" t="n">
-        <v>-5.94</v>
+        <v>-5.69</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.8</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>103.8</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>110.35</v>
+        <v>109.75</v>
       </c>
       <c r="AN3" t="n">
-        <v>116.94</v>
+        <v>116.51</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>119.31</t>
+          <t>119.11</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-12.25</t>
+          <t>-7.23</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-4.05</v>
+        <v>-3.94</v>
       </c>
       <c r="AR3" t="n">
-        <v>-3.61</v>
+        <v>-3.67</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-133.70</t>
+          <t>-134.32</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>401817128.4766949</t>
+          <t>401400381.8060648</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>80369509.0</t>
+          <t>87855895.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>91648883.59999999</v>
+        <v>99480096</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>79208492.5</t>
+          <t>79320431.1</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>400946194.74</v>
+        <v>376415022.36</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>12440391</t>
+          <t>20159664</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-38072685.37186095</t>
+          <t>-36775209.20845608</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-32609384.20754242</t>
+          <t>-29639090.30972932</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>80369509.0</t>
+          <t>87855895.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>81.89</t>
+          <t>83.07</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>45.34</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>11157</t>
+          <t>11318</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>593.888</t>
+          <t>775.327</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>15.71</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-10.43</t>
+          <t>-9.57</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,66 +1858,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>844</t>
+          <t>672</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>10.26</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>-0.87</v>
+        <v>0.19</v>
       </c>
       <c r="AI4" t="n">
-        <v>-6.31</v>
+        <v>-5.94</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-5.34</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>103.9</t>
+          <t>103.8</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>110.9</v>
+        <v>110.35</v>
       </c>
       <c r="AN4" t="n">
-        <v>117.15</v>
+        <v>116.94</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>119.56</t>
+          <t>119.31</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-18.13</t>
+          <t>-12.25</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-4.13</v>
+        <v>-4.05</v>
       </c>
       <c r="AR4" t="n">
-        <v>-3.5</v>
+        <v>-3.61</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-132.67</t>
+          <t>-133.70</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>401817128.4766949</t>
+          <t>401400381.8060648</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>60912790.0</t>
+          <t>80369509.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>90207911.8</v>
+        <v>91648883.59999999</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>85136383.4</t>
+          <t>79208492.5</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>403373073.88</v>
+        <v>400946194.74</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>5071528</t>
+          <t>12440391</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-39066012.8562825</t>
+          <t>-38072685.37186095</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-34885927.55414887</t>
+          <t>-32609384.20754242</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>60912790.0</t>
+          <t>80369509.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>81.89</t>
+          <t>83.07</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>45.34</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>11157</t>
+          <t>11318</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
+          <t>105.5</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>102.5</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
           <t>104.0</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>101.0</t>
-        </is>
-      </c>
-      <c r="CG4" t="inlineStr">
-        <is>
-          <t>103.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1943.113</t>
+          <t>593.888</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-8.63</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-10.87</t>
+          <t>-10.43</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-6.83</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,66 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>844</t>
+          <t>672</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>-2.29</v>
+        <v>-0.87</v>
       </c>
       <c r="AI5" t="n">
-        <v>-5.9</v>
+        <v>-6.31</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-5.34</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>104.9</t>
+          <t>103.9</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>111.48</v>
+        <v>110.9</v>
       </c>
       <c r="AN5" t="n">
-        <v>117.45</v>
+        <v>117.15</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>119.82</t>
+          <t>119.56</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-22.00</t>
+          <t>-18.13</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-4.07</v>
+        <v>-4.13</v>
       </c>
       <c r="AR5" t="n">
-        <v>-3.34</v>
+        <v>-3.5</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-131.19</t>
+          <t>-132.67</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>401817128.4766949</t>
+          <t>401400381.8060648</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>203706161.0</t>
+          <t>60912790.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>87092333.59999999</v>
+        <v>90207911.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>95316409.3</t>
+          <t>85136383.4</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>406267066.38</v>
+        <v>403373073.88</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-8224075</t>
+          <t>5071528</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-39826028.36576135</t>
+          <t>-39066012.8562825</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-34807557.88665277</t>
+          <t>-34885927.55414887</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>203706161.0</t>
+          <t>60912790.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,12 +2459,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>81.89</t>
+          <t>83.07</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>45.34</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>11157</t>
+          <t>11318</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>617.222</t>
+          <t>1943.113</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-33.70</t>
+          <t>-8.63</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-9.57</t>
+          <t>-10.87</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-6.83</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,12 +2702,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>844</t>
+          <t>672</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2721,47 +2721,47 @@
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>-2.07</v>
+        <v>-2.29</v>
       </c>
       <c r="AI6" t="n">
-        <v>-5.77</v>
+        <v>-5.9</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>106.2</t>
+          <t>104.9</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>112.7</v>
+        <v>111.48</v>
       </c>
       <c r="AN6" t="n">
-        <v>117.72</v>
+        <v>117.45</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>120.13</t>
+          <t>119.82</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-23.26</t>
+          <t>-22.00</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-3.89</v>
+        <v>-4.07</v>
       </c>
       <c r="AR6" t="n">
-        <v>-3.15</v>
+        <v>-3.34</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-129.47</t>
+          <t>-131.19</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>401817128.4766949</t>
+          <t>401400381.8060648</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>64556125.0</t>
+          <t>203706161.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>57159347</v>
+        <v>87092333.59999999</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>86212815.0</t>
+          <t>95316409.3</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>406636712.2</v>
+        <v>406267066.38</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-29053468</t>
+          <t>-8224075</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-40738477.54378109</t>
+          <t>-39826028.36576135</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-48751763.90142073</t>
+          <t>-34807557.88665277</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>64556125.0</t>
+          <t>203706161.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,22 +2881,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>81.89</t>
+          <t>83.07</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>45.34</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>11157</t>
+          <t>11318</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2951,17 +2951,17 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>109.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>460.69</t>
+          <t>617.222</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-39.87</t>
+          <t>-33.70</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-9.57</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,66 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>844</t>
+          <t>672</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>-1.49</v>
+        <v>-2.07</v>
       </c>
       <c r="AI7" t="n">
-        <v>-5.68</v>
+        <v>-5.77</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>107.1</t>
+          <t>106.2</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>113.55</v>
+        <v>112.7</v>
       </c>
       <c r="AN7" t="n">
-        <v>117.93</v>
+        <v>117.72</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>120.44</t>
+          <t>120.13</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-26.20</t>
+          <t>-23.26</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-3.75</v>
+        <v>-3.89</v>
       </c>
       <c r="AR7" t="n">
-        <v>-2.97</v>
+        <v>-3.15</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-127.76</t>
+          <t>-129.47</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>401817128.4766949</t>
+          <t>401400381.8060648</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>48699833.0</t>
+          <t>64556125.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>59160766.2</v>
+        <v>57159347</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>98382511.1</t>
+          <t>86212815.0</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>408309837.48</v>
+        <v>406636712.2</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-39221744</t>
+          <t>-29053468</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-39281516.38784661</t>
+          <t>-40738477.54378109</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-52021991.35460995</t>
+          <t>-48751763.90142073</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>48699833.0</t>
+          <t>64556125.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>81.89</t>
+          <t>83.07</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>45.34</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>11157</t>
+          <t>11318</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>694.884</t>
+          <t>460.69</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-45.60</t>
+          <t>-39.87</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-9.13</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,66 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>844</t>
+          <t>672</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>25.32</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>-2.52</v>
+        <v>-1.49</v>
       </c>
       <c r="AI8" t="n">
-        <v>-6.29</v>
+        <v>-5.68</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>107.2</t>
+          <t>107.1</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>114.4</v>
+        <v>113.55</v>
       </c>
       <c r="AN8" t="n">
-        <v>118.09</v>
+        <v>117.93</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>120.69</t>
+          <t>120.44</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-32.21</t>
+          <t>-26.20</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-3.67</v>
+        <v>-3.75</v>
       </c>
       <c r="AR8" t="n">
-        <v>-2.78</v>
+        <v>-2.97</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-125.94</t>
+          <t>-127.76</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>401817128.4766949</t>
+          <t>401400381.8060648</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>73164650.0</t>
+          <t>48699833.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>66768101.4</v>
+        <v>59160766.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>122726255.3</t>
+          <t>98382511.1</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>411205419.78</v>
+        <v>408309837.48</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-55958153</t>
+          <t>-39221744</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-36965066.39388964</t>
+          <t>-39281516.38784661</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-53136928.16792992</t>
+          <t>-52021991.35460995</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>73164650.0</t>
+          <t>48699833.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3725,22 +3725,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>81.89</t>
+          <t>83.07</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>45.34</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>11157</t>
+          <t>11318</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>417.291</t>
+          <t>694.884</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-3.85</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-42.34</t>
+          <t>-45.60</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>-9.13</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,33 +3968,33 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>844</t>
+          <t>672</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>36.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>33.93</t>
+          <t>25.32</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>0.75</v>
+        <v>-2.52</v>
       </c>
       <c r="AI9" t="n">
-        <v>-6.98</v>
+        <v>-6.29</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -4008,26 +4008,26 @@
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>115.25</v>
+        <v>114.4</v>
       </c>
       <c r="AN9" t="n">
-        <v>118.34</v>
+        <v>118.09</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>120.96</t>
+          <t>120.69</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-33.76</t>
+          <t>-32.21</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-3.41</v>
+        <v>-3.67</v>
       </c>
       <c r="AR9" t="n">
-        <v>-2.55</v>
+        <v>-2.78</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-123.85</t>
+          <t>-125.94</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>401817128.4766949</t>
+          <t>401400381.8060648</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>45334899.0</t>
+          <t>73164650.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>80064855</v>
+        <v>66768101.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>138863434.4</t>
+          <t>122726255.3</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>419038513.76</v>
+        <v>411205419.78</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-58798579</t>
+          <t>-55958153</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-34024727.88951867</t>
+          <t>-36965066.39388964</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-55453178.00238952</t>
+          <t>-53136928.16792992</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>45334899.0</t>
+          <t>73164650.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4152,17 +4152,17 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>81.89</t>
+          <t>83.07</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>45.34</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>11157</t>
+          <t>11318</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>497.76</t>
+          <t>417.291</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-4.81</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-36.00</t>
+          <t>-42.34</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-5.22</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>844</t>
+          <t>672</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>39.13</t>
+          <t>36.84</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>23.77</t>
+          <t>33.93</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>1.96</v>
+        <v>0.75</v>
       </c>
       <c r="AI10" t="n">
-        <v>-7.9</v>
+        <v>-6.98</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>106.9</t>
+          <t>107.2</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>116.08</v>
+        <v>115.25</v>
       </c>
       <c r="AN10" t="n">
-        <v>118.57</v>
+        <v>118.34</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>121.12</t>
+          <t>120.96</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-45.24</t>
+          <t>-33.76</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-3.39</v>
+        <v>-3.41</v>
       </c>
       <c r="AR10" t="n">
-        <v>-2.34</v>
+        <v>-2.55</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-121.84</t>
+          <t>-123.85</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>401817128.4766949</t>
+          <t>401400381.8060648</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>54041228.0</t>
+          <t>45334899.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>103540485</v>
+        <v>80064855</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>161783660.5</t>
+          <t>138863434.4</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>428520261.8</v>
+        <v>419038513.76</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-58243175</t>
+          <t>-58798579</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-30128646.05081488</t>
+          <t>-34024727.88951867</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-53799876.65867507</t>
+          <t>-55453178.00238952</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>54041228.0</t>
+          <t>45334899.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>10.10</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,22 +4569,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>81.89</t>
+          <t>83.07</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>45.34</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>11157</t>
+          <t>11318</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>688.338</t>
+          <t>497.76</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-4.33</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-46.80</t>
+          <t>-36.00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-5.65</t>
+          <t>-5.22</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,33 +4812,33 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>844</t>
+          <t>672</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>25.81</t>
+          <t>39.13</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>10.73</t>
+          <t>23.77</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.96</v>
       </c>
       <c r="AI11" t="n">
-        <v>-7.54</v>
+        <v>-7.9</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -4848,30 +4848,30 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>107.9</t>
+          <t>106.9</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>116.7</v>
+        <v>116.08</v>
       </c>
       <c r="AN11" t="n">
-        <v>118.76</v>
+        <v>118.57</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>121.31</t>
+          <t>121.12</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-65.07</t>
+          <t>-45.24</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-3.42</v>
+        <v>-3.39</v>
       </c>
       <c r="AR11" t="n">
-        <v>-2.07</v>
+        <v>-2.34</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-119.37</t>
+          <t>-121.84</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>401817128.4766949</t>
+          <t>401400381.8060648</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>74563221.0</t>
+          <t>54041228.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>115266283</v>
+        <v>103540485</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>216664373.4</t>
+          <t>161783660.5</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>435928377.96</v>
+        <v>428520261.8</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-101398090</t>
+          <t>-58243175</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-25824785.94029485</t>
+          <t>-30128646.05081488</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-50449414.39413029</t>
+          <t>-53799876.65867507</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>74563221.0</t>
+          <t>54041228.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>10.10</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>81.89</t>
+          <t>83.07</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>45.34</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>11157</t>
+          <t>11318</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5066,12 +5066,12 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>823.014</t>
+          <t>688.338</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>108.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-55.86</t>
+          <t>-46.80</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-7.83</t>
+          <t>-5.65</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>844</t>
+          <t>672</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>6.38</t>
+          <t>25.81</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>10.73</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>-2.03</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AI12" t="n">
-        <v>-7.68</v>
+        <v>-7.54</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>108.2</t>
+          <t>107.9</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>117.2</v>
+        <v>116.7</v>
       </c>
       <c r="AN12" t="n">
-        <v>118.83</v>
+        <v>118.76</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>121.47</t>
+          <t>121.31</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-93.34</t>
+          <t>-65.07</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-3.35</v>
+        <v>-3.42</v>
       </c>
       <c r="AR12" t="n">
-        <v>-1.74</v>
+        <v>-2.07</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-116.22</t>
+          <t>-119.37</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>401817128.4766949</t>
+          <t>401400381.8060648</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>86736509.0</t>
+          <t>74563221.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>137604256</v>
+        <v>115266283</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>311751968.8</t>
+          <t>216664373.4</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>442360683.54</v>
+        <v>435928377.96</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-174147712</t>
+          <t>-101398090</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-21347580.76687022</t>
+          <t>-25824785.94029485</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-46060059.89499024</t>
+          <t>-50449414.39413029</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>86736509.0</t>
+          <t>74563221.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>9.60</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>81.89</t>
+          <t>83.07</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>45.34</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>11157</t>
+          <t>11318</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>109.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>108.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/玻_碳纖.xlsx
+++ b/Result/checksun_type/玻_碳纖.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【e】;【x】看好</t>
+          <t>【d2】;【x】看好</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>672.31</t>
+          <t>1572.193</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>27.60</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>4.80</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,66 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>1572</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>54.55</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>33.57</t>
+          <t>59.21</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>1.64</v>
+        <v>2.96</v>
       </c>
       <c r="AI2" t="n">
-        <v>-4.46</v>
+        <v>-2.55</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-6.33</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>103.8</t>
+          <t>104.9</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>108.65</v>
+        <v>107.65</v>
       </c>
       <c r="AN2" t="n">
-        <v>115.99</v>
+        <v>115.48</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>118.94</t>
+          <t>118.76</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>9.49</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-3.69</v>
+        <v>-3.25</v>
       </c>
       <c r="AR2" t="n">
-        <v>-3.68</v>
+        <v>-3.59</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,53 +1082,53 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-134.35</t>
+          <t>-133.55</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/12/11</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>401400381.8060648</t>
+          <t>401190858.6950704</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>70895826.0</t>
+          <t>168425982.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>100748036.2</v>
+        <v>93692000.40000001</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>78953691.6</t>
+          <t>90392167.0</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>316450597.8</v>
+        <v>282867348.74</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>21794344</t>
+          <t>3299833</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-35439163.56077314</t>
+          <t>-32908546.63114733</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-28090912.49851693</t>
+          <t>-18990153.51820534</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>70895826.0</t>
+          <t>168425982.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>83.07</t>
+          <t>85.04</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>11318</t>
+          <t>11586</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>843.89</t>
+          <t>672.31</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>25.42</t>
+          <t>27.60</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-9.57</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,66 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>1572</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>54.55</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>33.57</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>0.48</v>
+        <v>1.64</v>
       </c>
       <c r="AI3" t="n">
-        <v>-5.69</v>
+        <v>-4.46</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-5.8</t>
+          <t>-6.33</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>103.8</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>109.75</v>
+        <v>108.65</v>
       </c>
       <c r="AN3" t="n">
-        <v>116.51</v>
+        <v>115.99</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>119.11</t>
+          <t>118.94</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-7.23</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-3.94</v>
+        <v>-3.69</v>
       </c>
       <c r="AR3" t="n">
-        <v>-3.67</v>
+        <v>-3.68</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,53 +1504,53 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-134.32</t>
+          <t>-134.35</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/12/11</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>401400381.8060648</t>
+          <t>401190858.6950704</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>87855895.0</t>
+          <t>70895826.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>99480096</v>
+        <v>100748036.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>79320431.1</t>
+          <t>78953691.6</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>376415022.36</v>
+        <v>316450597.8</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>20159664</t>
+          <t>21794344</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-36775209.20845608</t>
+          <t>-35439163.56077314</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-29639090.30972932</t>
+          <t>-28090912.49851693</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>87855895.0</t>
+          <t>70895826.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1625,12 +1625,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>83.07</t>
+          <t>85.04</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>11318</t>
+          <t>11586</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>775.327</t>
+          <t>843.89</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>15.71</t>
+          <t>25.42</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,12 +1858,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>1572</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1873,51 +1873,51 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>10.26</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>0.19</v>
+        <v>0.48</v>
       </c>
       <c r="AI4" t="n">
-        <v>-5.94</v>
+        <v>-5.69</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.8</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>103.8</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>110.35</v>
+        <v>109.75</v>
       </c>
       <c r="AN4" t="n">
-        <v>116.94</v>
+        <v>116.51</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>119.31</t>
+          <t>119.11</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-12.25</t>
+          <t>-7.23</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-4.05</v>
+        <v>-3.94</v>
       </c>
       <c r="AR4" t="n">
-        <v>-3.61</v>
+        <v>-3.67</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,53 +1926,53 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-133.70</t>
+          <t>-134.32</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/12/11</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>401400381.8060648</t>
+          <t>401190858.6950704</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>80369509.0</t>
+          <t>87855895.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>91648883.59999999</v>
+        <v>99480096</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>79208492.5</t>
+          <t>79320431.1</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>400946194.74</v>
+        <v>376415022.36</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>12440391</t>
+          <t>20159664</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-38072685.37186095</t>
+          <t>-36775209.20845608</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-32609384.20754242</t>
+          <t>-29639090.30972932</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>80369509.0</t>
+          <t>87855895.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>83.07</t>
+          <t>85.04</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>11318</t>
+          <t>11586</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,12 +2102,12 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>593.888</t>
+          <t>775.327</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,102 +2174,102 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-1.14</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>15.71</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-09-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>124.5</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>131.5</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>116.0</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>-9.57</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>7.33</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>2.37</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>-0.56</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>5.96</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-09-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>124.5</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>115.0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>131.5</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>116.0</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>-10.43</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>7.33</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,66 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>1572</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>10.26</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>-0.87</v>
+        <v>0.19</v>
       </c>
       <c r="AI5" t="n">
-        <v>-6.31</v>
+        <v>-5.94</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-5.34</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>103.9</t>
+          <t>103.8</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>110.9</v>
+        <v>110.35</v>
       </c>
       <c r="AN5" t="n">
-        <v>117.15</v>
+        <v>116.94</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>119.56</t>
+          <t>119.31</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-18.13</t>
+          <t>-12.25</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-4.13</v>
+        <v>-4.05</v>
       </c>
       <c r="AR5" t="n">
-        <v>-3.5</v>
+        <v>-3.61</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,53 +2348,53 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-132.67</t>
+          <t>-133.70</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/12/11</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>401400381.8060648</t>
+          <t>401190858.6950704</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>60912790.0</t>
+          <t>80369509.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>90207911.8</v>
+        <v>91648883.59999999</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>85136383.4</t>
+          <t>79208492.5</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>403373073.88</v>
+        <v>400946194.74</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>5071528</t>
+          <t>12440391</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-39066012.8562825</t>
+          <t>-38072685.37186095</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-34885927.55414887</t>
+          <t>-32609384.20754242</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>60912790.0</t>
+          <t>80369509.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>83.07</t>
+          <t>85.04</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>11318</t>
+          <t>11586</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
+          <t>105.5</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>102.5</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
           <t>104.0</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>101.0</t>
-        </is>
-      </c>
-      <c r="CG5" t="inlineStr">
-        <is>
-          <t>103.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1943.113</t>
+          <t>593.888</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-8.63</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-10.87</t>
+          <t>-10.43</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-6.83</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,66 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>1572</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>-2.29</v>
+        <v>-0.87</v>
       </c>
       <c r="AI6" t="n">
-        <v>-5.9</v>
+        <v>-6.31</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-5.34</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>104.9</t>
+          <t>103.9</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>111.48</v>
+        <v>110.9</v>
       </c>
       <c r="AN6" t="n">
-        <v>117.45</v>
+        <v>117.15</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>119.82</t>
+          <t>119.56</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-22.00</t>
+          <t>-18.13</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-4.07</v>
+        <v>-4.13</v>
       </c>
       <c r="AR6" t="n">
-        <v>-3.34</v>
+        <v>-3.5</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,53 +2770,53 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-131.19</t>
+          <t>-132.67</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/12/11</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>401400381.8060648</t>
+          <t>401190858.6950704</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>203706161.0</t>
+          <t>60912790.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>87092333.59999999</v>
+        <v>90207911.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>95316409.3</t>
+          <t>85136383.4</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>406267066.38</v>
+        <v>403373073.88</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-8224075</t>
+          <t>5071528</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-39826028.36576135</t>
+          <t>-39066012.8562825</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-34807557.88665277</t>
+          <t>-34885927.55414887</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>203706161.0</t>
+          <t>60912790.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2881,12 +2881,12 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>83.07</t>
+          <t>85.04</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>11318</t>
+          <t>11586</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>617.222</t>
+          <t>1943.113</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>5.09</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-33.70</t>
+          <t>-8.63</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-9.57</t>
+          <t>-10.87</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-6.83</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,12 +3124,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>1572</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3143,47 +3143,47 @@
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>-2.07</v>
+        <v>-2.29</v>
       </c>
       <c r="AI7" t="n">
-        <v>-5.77</v>
+        <v>-5.9</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>106.2</t>
+          <t>104.9</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>112.7</v>
+        <v>111.48</v>
       </c>
       <c r="AN7" t="n">
-        <v>117.72</v>
+        <v>117.45</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>120.13</t>
+          <t>119.82</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-23.26</t>
+          <t>-22.00</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-3.89</v>
+        <v>-4.07</v>
       </c>
       <c r="AR7" t="n">
-        <v>-3.15</v>
+        <v>-3.34</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,53 +3192,53 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-129.47</t>
+          <t>-131.19</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/12/11</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>401400381.8060648</t>
+          <t>401190858.6950704</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>64556125.0</t>
+          <t>203706161.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>57159347</v>
+        <v>87092333.59999999</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>86212815.0</t>
+          <t>95316409.3</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>406636712.2</v>
+        <v>406267066.38</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-29053468</t>
+          <t>-8224075</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-40738477.54378109</t>
+          <t>-39826028.36576135</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-48751763.90142073</t>
+          <t>-34807557.88665277</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>64556125.0</t>
+          <t>203706161.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3303,22 +3303,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>83.07</t>
+          <t>85.04</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>11318</t>
+          <t>11586</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3373,17 +3373,17 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>109.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>460.69</t>
+          <t>617.222</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-39.87</t>
+          <t>-33.70</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-9.57</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,66 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>1572</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>-1.49</v>
+        <v>-2.07</v>
       </c>
       <c r="AI8" t="n">
-        <v>-5.68</v>
+        <v>-5.77</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>107.1</t>
+          <t>106.2</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>113.55</v>
+        <v>112.7</v>
       </c>
       <c r="AN8" t="n">
-        <v>117.93</v>
+        <v>117.72</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>120.44</t>
+          <t>120.13</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-26.20</t>
+          <t>-23.26</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-3.75</v>
+        <v>-3.89</v>
       </c>
       <c r="AR8" t="n">
-        <v>-2.97</v>
+        <v>-3.15</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,53 +3614,53 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-127.76</t>
+          <t>-129.47</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/12/11</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>401400381.8060648</t>
+          <t>401190858.6950704</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>48699833.0</t>
+          <t>64556125.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>59160766.2</v>
+        <v>57159347</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>98382511.1</t>
+          <t>86212815.0</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>408309837.48</v>
+        <v>406636712.2</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-39221744</t>
+          <t>-29053468</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-39281516.38784661</t>
+          <t>-40738477.54378109</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-52021991.35460995</t>
+          <t>-48751763.90142073</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>48699833.0</t>
+          <t>64556125.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>83.07</t>
+          <t>85.04</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>11318</t>
+          <t>11586</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -3800,12 +3800,12 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>694.884</t>
+          <t>460.69</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-45.60</t>
+          <t>-39.87</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-9.13</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,66 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>1572</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>25.32</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>-2.52</v>
+        <v>-1.49</v>
       </c>
       <c r="AI9" t="n">
-        <v>-6.29</v>
+        <v>-5.68</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>107.2</t>
+          <t>107.1</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>114.4</v>
+        <v>113.55</v>
       </c>
       <c r="AN9" t="n">
-        <v>118.09</v>
+        <v>117.93</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>120.69</t>
+          <t>120.44</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-32.21</t>
+          <t>-26.20</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-3.67</v>
+        <v>-3.75</v>
       </c>
       <c r="AR9" t="n">
-        <v>-2.78</v>
+        <v>-2.97</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,53 +4036,53 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-125.94</t>
+          <t>-127.76</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/12/11</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>401400381.8060648</t>
+          <t>401190858.6950704</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>73164650.0</t>
+          <t>48699833.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>66768101.4</v>
+        <v>59160766.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>122726255.3</t>
+          <t>98382511.1</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>411205419.78</v>
+        <v>408309837.48</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-55958153</t>
+          <t>-39221744</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-36965066.39388964</t>
+          <t>-39281516.38784661</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-53136928.16792992</t>
+          <t>-52021991.35460995</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>73164650.0</t>
+          <t>48699833.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4147,22 +4147,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>83.07</t>
+          <t>85.04</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>11318</t>
+          <t>11586</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>417.291</t>
+          <t>694.884</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-42.34</t>
+          <t>-45.60</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>-9.13</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,33 +4390,33 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>1572</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>36.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>33.93</t>
+          <t>25.32</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>0.75</v>
+        <v>-2.52</v>
       </c>
       <c r="AI10" t="n">
-        <v>-6.98</v>
+        <v>-6.29</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -4430,26 +4430,26 @@
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>115.25</v>
+        <v>114.4</v>
       </c>
       <c r="AN10" t="n">
-        <v>118.34</v>
+        <v>118.09</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>120.96</t>
+          <t>120.69</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-33.76</t>
+          <t>-32.21</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-3.41</v>
+        <v>-3.67</v>
       </c>
       <c r="AR10" t="n">
-        <v>-2.55</v>
+        <v>-2.78</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,53 +4458,53 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-123.85</t>
+          <t>-125.94</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/12/11</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>401400381.8060648</t>
+          <t>401190858.6950704</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>45334899.0</t>
+          <t>73164650.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>80064855</v>
+        <v>66768101.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>138863434.4</t>
+          <t>122726255.3</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>419038513.76</v>
+        <v>411205419.78</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-58798579</t>
+          <t>-55958153</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-34024727.88951867</t>
+          <t>-36965066.39388964</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-55453178.00238952</t>
+          <t>-53136928.16792992</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>45334899.0</t>
+          <t>73164650.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>83.07</t>
+          <t>85.04</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>11318</t>
+          <t>11586</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>497.76</t>
+          <t>417.291</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-36.00</t>
+          <t>-42.34</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-5.22</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>1572</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>39.13</t>
+          <t>36.84</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>23.77</t>
+          <t>33.93</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>1.96</v>
+        <v>0.75</v>
       </c>
       <c r="AI11" t="n">
-        <v>-7.9</v>
+        <v>-6.98</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.1</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-2.10</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>106.9</t>
+          <t>107.2</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>116.08</v>
+        <v>115.25</v>
       </c>
       <c r="AN11" t="n">
-        <v>118.57</v>
+        <v>118.34</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>121.12</t>
+          <t>120.96</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-45.24</t>
+          <t>-33.76</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-3.39</v>
+        <v>-3.41</v>
       </c>
       <c r="AR11" t="n">
-        <v>-2.34</v>
+        <v>-2.55</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,53 +4880,53 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-121.84</t>
+          <t>-123.85</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/12/11</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>401400381.8060648</t>
+          <t>401190858.6950704</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>54041228.0</t>
+          <t>45334899.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>103540485</v>
+        <v>80064855</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>161783660.5</t>
+          <t>138863434.4</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>428520261.8</v>
+        <v>419038513.76</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-58243175</t>
+          <t>-58798579</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-30128646.05081488</t>
+          <t>-34024727.88951867</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-53799876.65867507</t>
+          <t>-55453178.00238952</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>54041228.0</t>
+          <t>45334899.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>10.10</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>83.07</t>
+          <t>85.04</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>11318</t>
+          <t>11586</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>688.338</t>
+          <t>497.76</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-46.80</t>
+          <t>-36.00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-5.65</t>
+          <t>-5.22</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,33 +5234,33 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>1572</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>25.81</t>
+          <t>39.13</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>10.73</t>
+          <t>23.77</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.96</v>
       </c>
       <c r="AI12" t="n">
-        <v>-7.54</v>
+        <v>-7.9</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-2.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -5270,30 +5270,30 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>107.9</t>
+          <t>106.9</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>116.7</v>
+        <v>116.08</v>
       </c>
       <c r="AN12" t="n">
-        <v>118.76</v>
+        <v>118.57</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>121.31</t>
+          <t>121.12</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-65.07</t>
+          <t>-45.24</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-3.42</v>
+        <v>-3.39</v>
       </c>
       <c r="AR12" t="n">
-        <v>-2.07</v>
+        <v>-2.34</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,53 +5302,53 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-119.37</t>
+          <t>-121.84</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/12/11</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>401400381.8060648</t>
+          <t>401190858.6950704</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>74563221.0</t>
+          <t>54041228.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>115266283</v>
+        <v>103540485</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>216664373.4</t>
+          <t>161783660.5</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>435928377.96</v>
+        <v>428520261.8</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-101398090</t>
+          <t>-58243175</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-25824785.94029485</t>
+          <t>-30128646.05081488</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-50449414.39413029</t>
+          <t>-53799876.65867507</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>74563221.0</t>
+          <t>54041228.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>9.60</t>
+          <t>10.10</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>83.07</t>
+          <t>85.04</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>11318</t>
+          <t>11586</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,7 +5478,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -5488,12 +5488,12 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/玻_碳纖.xlsx
+++ b/Result/checksun_type/玻_碳纖.xlsx
@@ -923,12 +923,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1403.157</t>
+          <t>769.691</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -953,12 +953,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10.32</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-9.57</t>
+          <t>-7.83</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,22 +1068,22 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -1094,66 +1094,66 @@
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>1403</t>
+          <t>770</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>63.64</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>60.61</t>
+          <t>63.64</t>
         </is>
       </c>
       <c r="AP2" t="n">
-        <v>-1.05</v>
+        <v>0.47</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-1.64</v>
+        <v>-0.8</v>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-7.01</t>
+          <t>-7.09</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>105.1</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>106.85</v>
+        <v>106.35</v>
       </c>
       <c r="AV2" t="n">
-        <v>114.91</v>
+        <v>114.47</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>118.54</t>
+          <t>118.3</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>13.31</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>-3.19</v>
+        <v>-2.94</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-3.51</v>
+        <v>-3.4</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-132.80</t>
+          <t>-131.74</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
@@ -1172,43 +1172,43 @@
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>400937359.8607595</t>
+          <t>400544610.7247191</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>147302125.0</t>
+          <t>80866650.0</t>
         </is>
       </c>
       <c r="BF2" t="n">
-        <v>110969867.4</v>
+        <v>111069295.6</v>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>100588889.6</t>
+          <t>101359089.6</t>
         </is>
       </c>
       <c r="BH2" t="n">
-        <v>254957469.96</v>
+        <v>244947022.76</v>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>10380977</t>
+          <t>9710206</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>-29957871.40620652</t>
+          <t>-27608336.15261859</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>-13729157.66903208</t>
+          <t>-14685892.25788501</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>147302125.0</t>
+          <t>80866650.0</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1283,12 +1283,12 @@
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>81.89</t>
+          <t>83.46</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>45.26</t>
+          <t>45.32</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>11157</t>
+          <t>11371</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1338,22 +1338,22 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>-3.74</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1572.193</t>
+          <t>1403.157</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1410,17 +1410,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-3.85</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>10.32</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>-9.57</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1530,22 +1530,22 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>4.80</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1556,66 +1556,66 @@
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>1403</t>
+          <t>770</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>59.21</t>
+          <t>60.61</t>
         </is>
       </c>
       <c r="AP3" t="n">
-        <v>2.96</v>
+        <v>-1.05</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-2.55</v>
+        <v>-1.64</v>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>-7.01</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>104.9</t>
+          <t>105.1</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>107.65</v>
+        <v>106.85</v>
       </c>
       <c r="AV3" t="n">
-        <v>115.48</v>
+        <v>114.91</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>118.76</t>
+          <t>118.54</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>9.49</t>
+          <t>9.16</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>-3.25</v>
+        <v>-3.19</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-3.59</v>
+        <v>-3.51</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-133.55</t>
+          <t>-132.80</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -1634,43 +1634,43 @@
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>400937359.8607595</t>
+          <t>400544610.7247191</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>168425982.0</t>
+          <t>147302125.0</t>
         </is>
       </c>
       <c r="BF3" t="n">
-        <v>93692000.40000001</v>
+        <v>110969867.4</v>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>90392167.0</t>
+          <t>100588889.6</t>
         </is>
       </c>
       <c r="BH3" t="n">
-        <v>282867348.74</v>
+        <v>254957469.96</v>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>3299833</t>
+          <t>10380977</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>-32908546.63114733</t>
+          <t>-29957871.40620652</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>-18990153.51820534</t>
+          <t>-13729157.66903208</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>168425982.0</t>
+          <t>147302125.0</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>81.89</t>
+          <t>83.46</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>45.26</t>
+          <t>45.32</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>11157</t>
+          <t>11371</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1800,22 +1800,22 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CO3" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CP3" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>672.31</t>
+          <t>1572.193</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1872,17 +1872,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>27.60</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1992,22 +1992,22 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>4.80</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -2018,66 +2018,66 @@
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>1403</t>
+          <t>770</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>54.55</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>33.57</t>
+          <t>59.21</t>
         </is>
       </c>
       <c r="AP4" t="n">
-        <v>1.64</v>
+        <v>2.96</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-4.46</v>
+        <v>-2.55</v>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-6.33</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>103.8</t>
+          <t>104.9</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>108.65</v>
+        <v>107.65</v>
       </c>
       <c r="AV4" t="n">
-        <v>115.99</v>
+        <v>115.48</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>118.94</t>
+          <t>118.76</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>9.49</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>-3.69</v>
+        <v>-3.25</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-3.68</v>
+        <v>-3.59</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-134.35</t>
+          <t>-133.55</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -2096,43 +2096,43 @@
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>400937359.8607595</t>
+          <t>400544610.7247191</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>70895826.0</t>
+          <t>168425982.0</t>
         </is>
       </c>
       <c r="BF4" t="n">
-        <v>100748036.2</v>
+        <v>93692000.40000001</v>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>78953691.6</t>
+          <t>90392167.0</t>
         </is>
       </c>
       <c r="BH4" t="n">
-        <v>316450597.8</v>
+        <v>282867348.74</v>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>21794344</t>
+          <t>3299833</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>-35439163.56077314</t>
+          <t>-32908546.63114733</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>-28090912.49851693</t>
+          <t>-18990153.51820534</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>70895826.0</t>
+          <t>168425982.0</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2207,12 +2207,12 @@
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>81.89</t>
+          <t>83.46</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2237,12 +2237,12 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>45.26</t>
+          <t>45.32</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>11157</t>
+          <t>11371</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2262,22 +2262,22 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CO4" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CP4" t="inlineStr">
@@ -2309,12 +2309,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>843.89</t>
+          <t>672.31</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2334,17 +2334,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>25.42</t>
+          <t>27.60</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-9.57</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2454,22 +2454,22 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -2480,66 +2480,66 @@
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>1403</t>
+          <t>770</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>54.55</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>33.57</t>
         </is>
       </c>
       <c r="AP5" t="n">
-        <v>0.48</v>
+        <v>1.64</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-5.69</v>
+        <v>-4.46</v>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-5.8</t>
+          <t>-6.33</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>103.8</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>109.75</v>
+        <v>108.65</v>
       </c>
       <c r="AV5" t="n">
-        <v>116.51</v>
+        <v>115.99</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>119.11</t>
+          <t>118.94</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>-7.23</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>-3.94</v>
+        <v>-3.69</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-3.67</v>
+        <v>-3.68</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-134.32</t>
+          <t>-134.35</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -2558,43 +2558,43 @@
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>400937359.8607595</t>
+          <t>400544610.7247191</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>87855895.0</t>
+          <t>70895826.0</t>
         </is>
       </c>
       <c r="BF5" t="n">
-        <v>99480096</v>
+        <v>100748036.2</v>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>79320431.1</t>
+          <t>78953691.6</t>
         </is>
       </c>
       <c r="BH5" t="n">
-        <v>376415022.36</v>
+        <v>316450597.8</v>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>20159664</t>
+          <t>21794344</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>-36775209.20845608</t>
+          <t>-35439163.56077314</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>-29639090.30972932</t>
+          <t>-28090912.49851693</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>87855895.0</t>
+          <t>70895826.0</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2669,12 +2669,12 @@
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>81.89</t>
+          <t>83.46</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2699,12 +2699,12 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>45.26</t>
+          <t>45.32</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>11157</t>
+          <t>11371</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2724,22 +2724,22 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CO5" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CP5" t="inlineStr">
@@ -2771,12 +2771,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>775.327</t>
+          <t>843.89</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2796,17 +2796,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>15.71</t>
+          <t>25.42</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2916,22 +2916,22 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -2942,12 +2942,12 @@
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>1403</t>
+          <t>770</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -2957,51 +2957,51 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>10.26</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="AP6" t="n">
-        <v>0.19</v>
+        <v>0.48</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-5.94</v>
+        <v>-5.69</v>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.8</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>103.8</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>110.35</v>
+        <v>109.75</v>
       </c>
       <c r="AV6" t="n">
-        <v>116.94</v>
+        <v>116.51</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>119.31</t>
+          <t>119.11</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>-12.25</t>
+          <t>-7.23</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>-4.05</v>
+        <v>-3.94</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-3.61</v>
+        <v>-3.67</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-133.70</t>
+          <t>-134.32</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -3020,43 +3020,43 @@
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>400937359.8607595</t>
+          <t>400544610.7247191</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>80369509.0</t>
+          <t>87855895.0</t>
         </is>
       </c>
       <c r="BF6" t="n">
-        <v>91648883.59999999</v>
+        <v>99480096</v>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>79208492.5</t>
+          <t>79320431.1</t>
         </is>
       </c>
       <c r="BH6" t="n">
-        <v>400946194.74</v>
+        <v>376415022.36</v>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>12440391</t>
+          <t>20159664</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>-38072685.37186095</t>
+          <t>-36775209.20845608</t>
         </is>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>-32609384.20754242</t>
+          <t>-29639090.30972932</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>80369509.0</t>
+          <t>87855895.0</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>81.89</t>
+          <t>83.46</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>45.26</t>
+          <t>45.32</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>11157</t>
+          <t>11371</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3233,12 +3233,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>593.888</t>
+          <t>775.327</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3258,17 +3258,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>15.71</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-10.43</t>
+          <t>-9.57</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3378,22 +3378,22 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -3404,66 +3404,66 @@
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>1403</t>
+          <t>770</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>10.26</t>
         </is>
       </c>
       <c r="AP7" t="n">
-        <v>-0.87</v>
+        <v>0.19</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-6.31</v>
+        <v>-5.94</v>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-5.34</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>103.9</t>
+          <t>103.8</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>110.9</v>
+        <v>110.35</v>
       </c>
       <c r="AV7" t="n">
-        <v>117.15</v>
+        <v>116.94</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>119.56</t>
+          <t>119.31</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>-18.13</t>
+          <t>-12.25</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>-4.13</v>
+        <v>-4.05</v>
       </c>
       <c r="AZ7" t="n">
-        <v>-3.5</v>
+        <v>-3.61</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-132.67</t>
+          <t>-133.70</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -3482,43 +3482,43 @@
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>400937359.8607595</t>
+          <t>400544610.7247191</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>60912790.0</t>
+          <t>80369509.0</t>
         </is>
       </c>
       <c r="BF7" t="n">
-        <v>90207911.8</v>
+        <v>91648883.59999999</v>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>85136383.4</t>
+          <t>79208492.5</t>
         </is>
       </c>
       <c r="BH7" t="n">
-        <v>403373073.88</v>
+        <v>400946194.74</v>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>5071528</t>
+          <t>12440391</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>-39066012.8562825</t>
+          <t>-38072685.37186095</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>-34885927.55414887</t>
+          <t>-32609384.20754242</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>60912790.0</t>
+          <t>80369509.0</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="CA7" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>81.89</t>
+          <t>83.46</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>45.26</t>
+          <t>45.32</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>11157</t>
+          <t>11371</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3648,22 +3648,22 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
+          <t>105.5</t>
+        </is>
+      </c>
+      <c r="CN7" t="inlineStr">
+        <is>
+          <t>102.5</t>
+        </is>
+      </c>
+      <c r="CO7" t="inlineStr">
+        <is>
           <t>104.0</t>
-        </is>
-      </c>
-      <c r="CN7" t="inlineStr">
-        <is>
-          <t>101.0</t>
-        </is>
-      </c>
-      <c r="CO7" t="inlineStr">
-        <is>
-          <t>103.0</t>
         </is>
       </c>
       <c r="CP7" t="inlineStr">
@@ -3695,42 +3695,42 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>593.888</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>103.0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2.83</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>-1.42</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>1943.113</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>102.5</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>-2.53</t>
-        </is>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-8.63</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-10.87</t>
+          <t>-10.43</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3840,22 +3840,22 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-6.83</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -3866,66 +3866,66 @@
       <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>1403</t>
+          <t>770</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AP8" t="n">
-        <v>-2.29</v>
+        <v>-0.87</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-5.9</v>
+        <v>-6.31</v>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-5.34</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>104.9</t>
+          <t>103.9</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>111.48</v>
+        <v>110.9</v>
       </c>
       <c r="AV8" t="n">
-        <v>117.45</v>
+        <v>117.15</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>119.82</t>
+          <t>119.56</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>-22.00</t>
+          <t>-18.13</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>-4.07</v>
+        <v>-4.13</v>
       </c>
       <c r="AZ8" t="n">
-        <v>-3.34</v>
+        <v>-3.5</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-131.19</t>
+          <t>-132.67</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -3944,43 +3944,43 @@
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>400937359.8607595</t>
+          <t>400544610.7247191</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>203706161.0</t>
+          <t>60912790.0</t>
         </is>
       </c>
       <c r="BF8" t="n">
-        <v>87092333.59999999</v>
+        <v>90207911.8</v>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>95316409.3</t>
+          <t>85136383.4</t>
         </is>
       </c>
       <c r="BH8" t="n">
-        <v>406267066.38</v>
+        <v>403373073.88</v>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>-8224075</t>
+          <t>5071528</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>-39826028.36576135</t>
+          <t>-39066012.8562825</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>-34807557.88665277</t>
+          <t>-34885927.55414887</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>203706161.0</t>
+          <t>60912790.0</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>81.89</t>
+          <t>83.46</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>45.26</t>
+          <t>45.32</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>11157</t>
+          <t>11371</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4110,22 +4110,22 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CO8" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CP8" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>617.222</t>
+          <t>1943.113</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4182,17 +4182,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-33.70</t>
+          <t>-8.63</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-9.57</t>
+          <t>-10.87</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4302,22 +4302,22 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-6.83</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -4328,12 +4328,12 @@
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>1403</t>
+          <t>770</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4347,47 +4347,47 @@
         </is>
       </c>
       <c r="AP9" t="n">
-        <v>-2.07</v>
+        <v>-2.29</v>
       </c>
       <c r="AQ9" t="n">
-        <v>-5.77</v>
+        <v>-5.9</v>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>106.2</t>
+          <t>104.9</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>112.7</v>
+        <v>111.48</v>
       </c>
       <c r="AV9" t="n">
-        <v>117.72</v>
+        <v>117.45</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>120.13</t>
+          <t>119.82</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>-23.26</t>
+          <t>-22.00</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>-3.89</v>
+        <v>-4.07</v>
       </c>
       <c r="AZ9" t="n">
-        <v>-3.15</v>
+        <v>-3.34</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-129.47</t>
+          <t>-131.19</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -4406,43 +4406,43 @@
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>400937359.8607595</t>
+          <t>400544610.7247191</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>64556125.0</t>
+          <t>203706161.0</t>
         </is>
       </c>
       <c r="BF9" t="n">
-        <v>57159347</v>
+        <v>87092333.59999999</v>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>86212815.0</t>
+          <t>95316409.3</t>
         </is>
       </c>
       <c r="BH9" t="n">
-        <v>406636712.2</v>
+        <v>406267066.38</v>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>-29053468</t>
+          <t>-8224075</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>-40738477.54378109</t>
+          <t>-39826028.36576135</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>-48751763.90142073</t>
+          <t>-34807557.88665277</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>64556125.0</t>
+          <t>203706161.0</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4507,22 +4507,22 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>81.89</t>
+          <t>83.46</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>45.26</t>
+          <t>45.32</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>11157</t>
+          <t>11371</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4577,17 +4577,17 @@
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>109.5</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CO9" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CP9" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>460.69</t>
+          <t>617.222</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4644,17 +4644,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-39.87</t>
+          <t>-33.70</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-9.57</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4764,22 +4764,22 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -4790,66 +4790,66 @@
       <c r="AK10" t="inlineStr"/>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>1403</t>
+          <t>770</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="AP10" t="n">
-        <v>-1.49</v>
+        <v>-2.07</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-5.68</v>
+        <v>-5.77</v>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>107.1</t>
+          <t>106.2</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>113.55</v>
+        <v>112.7</v>
       </c>
       <c r="AV10" t="n">
-        <v>117.93</v>
+        <v>117.72</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>120.44</t>
+          <t>120.13</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>-26.20</t>
+          <t>-23.26</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>-3.75</v>
+        <v>-3.89</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-2.97</v>
+        <v>-3.15</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-127.76</t>
+          <t>-129.47</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -4868,43 +4868,43 @@
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>400937359.8607595</t>
+          <t>400544610.7247191</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>48699833.0</t>
+          <t>64556125.0</t>
         </is>
       </c>
       <c r="BF10" t="n">
-        <v>59160766.2</v>
+        <v>57159347</v>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>98382511.1</t>
+          <t>86212815.0</t>
         </is>
       </c>
       <c r="BH10" t="n">
-        <v>408309837.48</v>
+        <v>406636712.2</v>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>-39221744</t>
+          <t>-29053468</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>-39281516.38784661</t>
+          <t>-40738477.54378109</t>
         </is>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>-52021991.35460995</t>
+          <t>-48751763.90142073</t>
         </is>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>48699833.0</t>
+          <t>64556125.0</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4979,12 +4979,12 @@
       </c>
       <c r="CA10" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>81.89</t>
+          <t>83.46</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>45.26</t>
+          <t>45.32</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>11157</t>
+          <t>11371</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5044,12 +5044,12 @@
       </c>
       <c r="CN10" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CO10" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CP10" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>694.884</t>
+          <t>460.69</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5106,17 +5106,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-45.60</t>
+          <t>-39.87</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-9.13</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5226,22 +5226,22 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -5252,66 +5252,66 @@
       <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>1403</t>
+          <t>770</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>25.32</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="AP11" t="n">
-        <v>-2.52</v>
+        <v>-1.49</v>
       </c>
       <c r="AQ11" t="n">
-        <v>-6.29</v>
+        <v>-5.68</v>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>107.2</t>
+          <t>107.1</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>114.4</v>
+        <v>113.55</v>
       </c>
       <c r="AV11" t="n">
-        <v>118.09</v>
+        <v>117.93</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>120.69</t>
+          <t>120.44</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>-32.21</t>
+          <t>-26.20</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>-3.67</v>
+        <v>-3.75</v>
       </c>
       <c r="AZ11" t="n">
-        <v>-2.78</v>
+        <v>-2.97</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-125.94</t>
+          <t>-127.76</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -5330,43 +5330,43 @@
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>400937359.8607595</t>
+          <t>400544610.7247191</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>73164650.0</t>
+          <t>48699833.0</t>
         </is>
       </c>
       <c r="BF11" t="n">
-        <v>66768101.4</v>
+        <v>59160766.2</v>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>122726255.3</t>
+          <t>98382511.1</t>
         </is>
       </c>
       <c r="BH11" t="n">
-        <v>411205419.78</v>
+        <v>408309837.48</v>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>-55958153</t>
+          <t>-39221744</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>-36965066.39388964</t>
+          <t>-39281516.38784661</t>
         </is>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>-53136928.16792992</t>
+          <t>-52021991.35460995</t>
         </is>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>73164650.0</t>
+          <t>48699833.0</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="CA11" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>81.89</t>
+          <t>83.46</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5471,12 +5471,12 @@
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>45.26</t>
+          <t>45.32</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>11157</t>
+          <t>11371</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5496,22 +5496,22 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CO11" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CP11" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>417.291</t>
+          <t>694.884</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5568,17 +5568,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-3.85</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-42.34</t>
+          <t>-45.60</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>-9.13</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5688,22 +5688,22 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -5714,33 +5714,33 @@
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>1403</t>
+          <t>770</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>36.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>33.93</t>
+          <t>25.32</t>
         </is>
       </c>
       <c r="AP12" t="n">
-        <v>0.75</v>
+        <v>-2.52</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-6.98</v>
+        <v>-6.29</v>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5754,26 +5754,26 @@
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>115.25</v>
+        <v>114.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>118.34</v>
+        <v>118.09</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>120.96</t>
+          <t>120.69</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>-33.76</t>
+          <t>-32.21</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>-3.41</v>
+        <v>-3.67</v>
       </c>
       <c r="AZ12" t="n">
-        <v>-2.55</v>
+        <v>-2.78</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-123.85</t>
+          <t>-125.94</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -5792,43 +5792,43 @@
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>400937359.8607595</t>
+          <t>400544610.7247191</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>45334899.0</t>
+          <t>73164650.0</t>
         </is>
       </c>
       <c r="BF12" t="n">
-        <v>80064855</v>
+        <v>66768101.4</v>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>138863434.4</t>
+          <t>122726255.3</t>
         </is>
       </c>
       <c r="BH12" t="n">
-        <v>419038513.76</v>
+        <v>411205419.78</v>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>-58798579</t>
+          <t>-55958153</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>-34024727.88951867</t>
+          <t>-36965066.39388964</t>
         </is>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>-55453178.00238952</t>
+          <t>-53136928.16792992</t>
         </is>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>45334899.0</t>
+          <t>73164650.0</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="CA12" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="CC12" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>81.89</t>
+          <t>83.46</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>45.26</t>
+          <t>45.32</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>11157</t>
+          <t>11371</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -5958,22 +5958,22 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CO12" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CP12" t="inlineStr">

--- a/Result/checksun_type/玻_碳纖.xlsx
+++ b/Result/checksun_type/玻_碳纖.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CR12"/>
+  <dimension ref="A1:CV12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,345 +566,365 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
+          <t>MACD_hist_diff</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
           <t>MA_death_cross_d</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d收盤價</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d2</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d2收盤價</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>MACD_hist_diff</t>
-        </is>
-      </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
+          <t>MACD_death_cross_d</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d收盤價</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d2</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d2收盤價</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>量能</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>價能</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>cond_entry</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>text_desc</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>盤後量</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>成交量</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>%K</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>%D</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>MA5_%</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>均價_%</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>均價long_%</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>均價longlong_%</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>MA_short</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>MA_long</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>MA_longlong</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>MA_longlonglong</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>MACD_%</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>MACD</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL_max</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MACDSL_%</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MACD_last_cross_date</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>成交金額平均</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>成交金額</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_short</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long50</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>Volume_Oscillator</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>volume_threshold</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>VPC_MACD</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>Volume_Price_Change</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -1048,325 +1068,345 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
           <t>2025/09/24</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>125.5</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>2025/06/30</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>70.1</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0.13</t>
-        </is>
-      </c>
       <c r="AG2" t="inlineStr">
         <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>109.5</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>2025/11/10</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
           <t>2025-12-15</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>2.35</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>3.92</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr">
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>770</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t>63.64</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AS2" t="inlineStr">
         <is>
           <t>63.64</t>
         </is>
       </c>
-      <c r="AP2" t="n">
+      <c r="AT2" t="n">
         <v>0.47</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AU2" t="n">
         <v>-0.8</v>
       </c>
-      <c r="AR2" t="inlineStr">
+      <c r="AV2" t="inlineStr">
         <is>
           <t>-7.09</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>-3.24</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>105.5</t>
         </is>
       </c>
-      <c r="AU2" t="n">
+      <c r="AY2" t="n">
         <v>106.35</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="AZ2" t="n">
         <v>114.47</v>
       </c>
-      <c r="AW2" t="inlineStr">
+      <c r="BA2" t="inlineStr">
         <is>
           <t>118.3</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
         <is>
           <t>13.31</t>
         </is>
       </c>
-      <c r="AY2" t="n">
+      <c r="BC2" t="n">
         <v>-2.94</v>
       </c>
-      <c r="AZ2" t="n">
+      <c r="BD2" t="n">
         <v>-3.4</v>
       </c>
-      <c r="BA2" t="inlineStr">
+      <c r="BE2" t="inlineStr">
         <is>
           <t>10.7</t>
         </is>
       </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BF2" t="inlineStr">
         <is>
           <t>-131.74</t>
         </is>
       </c>
-      <c r="BC2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>2025/12/11</t>
         </is>
       </c>
-      <c r="BD2" t="inlineStr">
+      <c r="BH2" t="inlineStr">
         <is>
           <t>400544610.7247191</t>
         </is>
       </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BI2" t="inlineStr">
         <is>
           <t>80866650.0</t>
         </is>
       </c>
-      <c r="BF2" t="n">
+      <c r="BJ2" t="n">
         <v>111069295.6</v>
       </c>
-      <c r="BG2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>101359089.6</t>
         </is>
       </c>
-      <c r="BH2" t="n">
+      <c r="BL2" t="n">
         <v>244947022.76</v>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BM2" t="inlineStr">
         <is>
           <t>9710206</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BN2" t="inlineStr">
         <is>
           <t>-27608336.15261859</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>-14685892.25788501</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>80866650.0</t>
         </is>
       </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
         <is>
           <t>99.0</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BS2" t="inlineStr">
         <is>
           <t>2025/07/18</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>7.07</t>
         </is>
       </c>
-      <c r="BQ2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>上緯投控</t>
         </is>
       </c>
-      <c r="BR2" t="inlineStr">
+      <c r="BV2" t="inlineStr">
         <is>
           <t>上緯投控</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
+      <c r="BW2" t="inlineStr">
         <is>
           <t>綠能環保</t>
         </is>
       </c>
-      <c r="BT2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
+      <c r="BY2" t="inlineStr">
         <is>
           <t>1.06</t>
         </is>
       </c>
-      <c r="BV2" t="inlineStr">
+      <c r="BZ2" t="inlineStr">
         <is>
           <t>-4.012262137013166</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="CA2" t="inlineStr">
         <is>
           <t>-1.72716244973935</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>4.777195903551031</t>
         </is>
       </c>
-      <c r="BY2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ2" t="inlineStr">
+      <c r="CD2" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CE2" t="inlineStr">
         <is>
           <t>1.19</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CF2" t="inlineStr">
         <is>
           <t>2.21</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
+      <c r="CG2" t="inlineStr">
         <is>
           <t>-29.60</t>
         </is>
       </c>
-      <c r="CD2" t="inlineStr">
+      <c r="CH2" t="inlineStr">
         <is>
           <t>83.46</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CJ2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CK2" t="inlineStr">
         <is>
           <t>45.32</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CL2" t="inlineStr">
         <is>
           <t>11371</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CM2" t="inlineStr">
         <is>
           <t>環保耐蝕材料39.58%、環保綠能材料33.76%、其他25.01%、循環經濟材料1.65% (2024年)</t>
         </is>
       </c>
-      <c r="CJ2" t="inlineStr">
+      <c r="CN2" t="inlineStr">
         <is>
           <t>上緯投控-綠能環保-上市</t>
         </is>
       </c>
-      <c r="CK2" t="inlineStr">
+      <c r="CO2" t="inlineStr">
         <is>
           <t>綠能環保平上市</t>
         </is>
       </c>
-      <c r="CL2" t="inlineStr">
+      <c r="CP2" t="inlineStr">
         <is>
           <t>103.0</t>
         </is>
       </c>
-      <c r="CM2" t="inlineStr">
+      <c r="CQ2" t="inlineStr">
         <is>
           <t>106.0</t>
         </is>
       </c>
-      <c r="CN2" t="inlineStr">
+      <c r="CR2" t="inlineStr">
         <is>
           <t>102.0</t>
         </is>
       </c>
-      <c r="CO2" t="inlineStr">
+      <c r="CS2" t="inlineStr">
         <is>
           <t>106.0</t>
         </is>
       </c>
-      <c r="CP2" t="inlineStr">
+      <c r="CT2" t="inlineStr">
         <is>
           <t>89.23</t>
         </is>
       </c>
-      <c r="CQ2" t="inlineStr">
+      <c r="CU2" t="inlineStr">
         <is>
           <t>** 風力發電 - 玻/碳纖、樹酯</t>
         </is>
       </c>
-      <c r="CR2" t="inlineStr">
+      <c r="CV2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1510,325 +1550,345 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
           <t>2025/09/24</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>125.5</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>2025/06/30</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>70.1</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
       <c r="AG3" t="inlineStr">
         <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>109.5</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>2025/11/10</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
           <t>2025-12-12</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>4.28</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>-2.88</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr">
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AQ3" t="inlineStr">
         <is>
           <t>770</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AR3" t="inlineStr">
         <is>
           <t>27.27</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AS3" t="inlineStr">
         <is>
           <t>60.61</t>
         </is>
       </c>
-      <c r="AP3" t="n">
+      <c r="AT3" t="n">
         <v>-1.05</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AU3" t="n">
         <v>-1.64</v>
       </c>
-      <c r="AR3" t="inlineStr">
+      <c r="AV3" t="inlineStr">
         <is>
           <t>-7.01</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr">
+      <c r="AW3" t="inlineStr">
         <is>
           <t>-3.06</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>105.1</t>
         </is>
       </c>
-      <c r="AU3" t="n">
+      <c r="AY3" t="n">
         <v>106.85</v>
       </c>
-      <c r="AV3" t="n">
+      <c r="AZ3" t="n">
         <v>114.91</v>
       </c>
-      <c r="AW3" t="inlineStr">
+      <c r="BA3" t="inlineStr">
         <is>
           <t>118.54</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="BB3" t="inlineStr">
         <is>
           <t>9.16</t>
         </is>
       </c>
-      <c r="AY3" t="n">
+      <c r="BC3" t="n">
         <v>-3.19</v>
       </c>
-      <c r="AZ3" t="n">
+      <c r="BD3" t="n">
         <v>-3.51</v>
       </c>
-      <c r="BA3" t="inlineStr">
+      <c r="BE3" t="inlineStr">
         <is>
           <t>10.7</t>
         </is>
       </c>
-      <c r="BB3" t="inlineStr">
+      <c r="BF3" t="inlineStr">
         <is>
           <t>-132.80</t>
         </is>
       </c>
-      <c r="BC3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2025/12/11</t>
         </is>
       </c>
-      <c r="BD3" t="inlineStr">
+      <c r="BH3" t="inlineStr">
         <is>
           <t>400544610.7247191</t>
         </is>
       </c>
-      <c r="BE3" t="inlineStr">
+      <c r="BI3" t="inlineStr">
         <is>
           <t>147302125.0</t>
         </is>
       </c>
-      <c r="BF3" t="n">
+      <c r="BJ3" t="n">
         <v>110969867.4</v>
       </c>
-      <c r="BG3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>100588889.6</t>
         </is>
       </c>
-      <c r="BH3" t="n">
+      <c r="BL3" t="n">
         <v>254957469.96</v>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BM3" t="inlineStr">
         <is>
           <t>10380977</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BN3" t="inlineStr">
         <is>
           <t>-29957871.40620652</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>-13729157.66903208</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>147302125.0</t>
         </is>
       </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
         <is>
           <t>99.0</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>2025/07/18</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>5.05</t>
         </is>
       </c>
-      <c r="BQ3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>上緯投控</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
+      <c r="BV3" t="inlineStr">
         <is>
           <t>上緯投控</t>
         </is>
       </c>
-      <c r="BS3" t="inlineStr">
+      <c r="BW3" t="inlineStr">
         <is>
           <t>綠能環保</t>
         </is>
       </c>
-      <c r="BT3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
+      <c r="BY3" t="inlineStr">
         <is>
           <t>1.06</t>
         </is>
       </c>
-      <c r="BV3" t="inlineStr">
+      <c r="BZ3" t="inlineStr">
         <is>
           <t>-4.012262137013166</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="CA3" t="inlineStr">
         <is>
           <t>-1.72716244973935</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>4.777195903551031</t>
         </is>
       </c>
-      <c r="BY3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ3" t="inlineStr">
+      <c r="CD3" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CE3" t="inlineStr">
         <is>
           <t>1.17</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CF3" t="inlineStr">
         <is>
           <t>2.21</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
+      <c r="CG3" t="inlineStr">
         <is>
           <t>-29.60</t>
         </is>
       </c>
-      <c r="CD3" t="inlineStr">
+      <c r="CH3" t="inlineStr">
         <is>
           <t>83.46</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CJ3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CK3" t="inlineStr">
         <is>
           <t>45.32</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CL3" t="inlineStr">
         <is>
           <t>11371</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CM3" t="inlineStr">
         <is>
           <t>環保耐蝕材料39.58%、環保綠能材料33.76%、其他25.01%、循環經濟材料1.65% (2024年)</t>
         </is>
       </c>
-      <c r="CJ3" t="inlineStr">
+      <c r="CN3" t="inlineStr">
         <is>
           <t>上緯投控-綠能環保-上市</t>
         </is>
       </c>
-      <c r="CK3" t="inlineStr">
+      <c r="CO3" t="inlineStr">
         <is>
           <t>綠能環保平上市</t>
         </is>
       </c>
-      <c r="CL3" t="inlineStr">
+      <c r="CP3" t="inlineStr">
         <is>
           <t>107.0</t>
         </is>
       </c>
-      <c r="CM3" t="inlineStr">
+      <c r="CQ3" t="inlineStr">
         <is>
           <t>107.5</t>
         </is>
       </c>
-      <c r="CN3" t="inlineStr">
+      <c r="CR3" t="inlineStr">
         <is>
           <t>103.5</t>
         </is>
       </c>
-      <c r="CO3" t="inlineStr">
+      <c r="CS3" t="inlineStr">
         <is>
           <t>104.0</t>
         </is>
       </c>
-      <c r="CP3" t="inlineStr">
+      <c r="CT3" t="inlineStr">
         <is>
           <t>89.23</t>
         </is>
       </c>
-      <c r="CQ3" t="inlineStr">
+      <c r="CU3" t="inlineStr">
         <is>
           <t>** 風力發電 - 玻/碳纖、樹酯</t>
         </is>
       </c>
-      <c r="CR3" t="inlineStr">
+      <c r="CV3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1972,325 +2032,345 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
           <t>2025/09/24</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>125.5</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>2025/06/30</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>70.1</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0.35</t>
-        </is>
-      </c>
       <c r="AG4" t="inlineStr">
         <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>109.5</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>2025/11/10</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>4.80</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>1.93</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr">
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
+      <c r="AQ4" t="inlineStr">
         <is>
           <t>770</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
+      <c r="AR4" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
+      <c r="AS4" t="inlineStr">
         <is>
           <t>59.21</t>
         </is>
       </c>
-      <c r="AP4" t="n">
+      <c r="AT4" t="n">
         <v>2.96</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AU4" t="n">
         <v>-2.55</v>
       </c>
-      <c r="AR4" t="inlineStr">
+      <c r="AV4" t="inlineStr">
         <is>
           <t>-6.78</t>
         </is>
       </c>
-      <c r="AS4" t="inlineStr">
+      <c r="AW4" t="inlineStr">
         <is>
           <t>-2.76</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>104.9</t>
         </is>
       </c>
-      <c r="AU4" t="n">
+      <c r="AY4" t="n">
         <v>107.65</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="AZ4" t="n">
         <v>115.48</v>
       </c>
-      <c r="AW4" t="inlineStr">
+      <c r="BA4" t="inlineStr">
         <is>
           <t>118.76</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="BB4" t="inlineStr">
         <is>
           <t>9.49</t>
         </is>
       </c>
-      <c r="AY4" t="n">
+      <c r="BC4" t="n">
         <v>-3.25</v>
       </c>
-      <c r="AZ4" t="n">
+      <c r="BD4" t="n">
         <v>-3.59</v>
       </c>
-      <c r="BA4" t="inlineStr">
+      <c r="BE4" t="inlineStr">
         <is>
           <t>10.7</t>
         </is>
       </c>
-      <c r="BB4" t="inlineStr">
+      <c r="BF4" t="inlineStr">
         <is>
           <t>-133.55</t>
         </is>
       </c>
-      <c r="BC4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>2025/12/11</t>
         </is>
       </c>
-      <c r="BD4" t="inlineStr">
+      <c r="BH4" t="inlineStr">
         <is>
           <t>400544610.7247191</t>
         </is>
       </c>
-      <c r="BE4" t="inlineStr">
+      <c r="BI4" t="inlineStr">
         <is>
           <t>168425982.0</t>
         </is>
       </c>
-      <c r="BF4" t="n">
+      <c r="BJ4" t="n">
         <v>93692000.40000001</v>
       </c>
-      <c r="BG4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>90392167.0</t>
         </is>
       </c>
-      <c r="BH4" t="n">
+      <c r="BL4" t="n">
         <v>282867348.74</v>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BM4" t="inlineStr">
         <is>
           <t>3299833</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BN4" t="inlineStr">
         <is>
           <t>-32908546.63114733</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>-18990153.51820534</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>168425982.0</t>
         </is>
       </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
         <is>
           <t>99.0</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BS4" t="inlineStr">
         <is>
           <t>2025/07/18</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
+      <c r="BT4" t="inlineStr">
         <is>
           <t>9.09</t>
         </is>
       </c>
-      <c r="BQ4" t="inlineStr">
+      <c r="BU4" t="inlineStr">
         <is>
           <t>上緯投控</t>
         </is>
       </c>
-      <c r="BR4" t="inlineStr">
+      <c r="BV4" t="inlineStr">
         <is>
           <t>上緯投控</t>
         </is>
       </c>
-      <c r="BS4" t="inlineStr">
+      <c r="BW4" t="inlineStr">
         <is>
           <t>綠能環保</t>
         </is>
       </c>
-      <c r="BT4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
+      <c r="BY4" t="inlineStr">
         <is>
           <t>1.06</t>
         </is>
       </c>
-      <c r="BV4" t="inlineStr">
+      <c r="BZ4" t="inlineStr">
         <is>
           <t>-4.012262137013166</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="CA4" t="inlineStr">
         <is>
           <t>-1.72716244973935</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>4.777195903551031</t>
         </is>
       </c>
-      <c r="BY4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
-      <c r="BZ4" t="inlineStr">
+      <c r="CD4" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CE4" t="inlineStr">
         <is>
           <t>1.21</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CF4" t="inlineStr">
         <is>
           <t>2.21</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
+      <c r="CG4" t="inlineStr">
         <is>
           <t>-29.60</t>
         </is>
       </c>
-      <c r="CD4" t="inlineStr">
+      <c r="CH4" t="inlineStr">
         <is>
           <t>83.46</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CG4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CJ4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CK4" t="inlineStr">
         <is>
           <t>45.32</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CL4" t="inlineStr">
         <is>
           <t>11371</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CM4" t="inlineStr">
         <is>
           <t>環保耐蝕材料39.58%、環保綠能材料33.76%、其他25.01%、循環經濟材料1.65% (2024年)</t>
         </is>
       </c>
-      <c r="CJ4" t="inlineStr">
+      <c r="CN4" t="inlineStr">
         <is>
           <t>上緯投控-綠能環保-上市</t>
         </is>
       </c>
-      <c r="CK4" t="inlineStr">
+      <c r="CO4" t="inlineStr">
         <is>
           <t>綠能環保平上市</t>
         </is>
       </c>
-      <c r="CL4" t="inlineStr">
+      <c r="CP4" t="inlineStr">
         <is>
           <t>105.5</t>
         </is>
       </c>
-      <c r="CM4" t="inlineStr">
+      <c r="CQ4" t="inlineStr">
         <is>
           <t>109.0</t>
         </is>
       </c>
-      <c r="CN4" t="inlineStr">
+      <c r="CR4" t="inlineStr">
         <is>
           <t>105.0</t>
         </is>
       </c>
-      <c r="CO4" t="inlineStr">
+      <c r="CS4" t="inlineStr">
         <is>
           <t>108.0</t>
         </is>
       </c>
-      <c r="CP4" t="inlineStr">
+      <c r="CT4" t="inlineStr">
         <is>
           <t>89.23</t>
         </is>
       </c>
-      <c r="CQ4" t="inlineStr">
+      <c r="CU4" t="inlineStr">
         <is>
           <t>** 風力發電 - 玻/碳纖、樹酯</t>
         </is>
       </c>
-      <c r="CR4" t="inlineStr">
+      <c r="CV4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2434,325 +2514,345 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
           <t>2025/09/24</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>125.5</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>2025/06/30</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>70.1</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
       <c r="AG5" t="inlineStr">
         <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>109.5</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>2025/11/10</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
           <t>2025-12-10</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>2.05</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr">
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>770</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>54.55</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
+      <c r="AS5" t="inlineStr">
         <is>
           <t>33.57</t>
         </is>
       </c>
-      <c r="AP5" t="n">
+      <c r="AT5" t="n">
         <v>1.64</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AU5" t="n">
         <v>-4.46</v>
       </c>
-      <c r="AR5" t="inlineStr">
+      <c r="AV5" t="inlineStr">
         <is>
           <t>-6.33</t>
         </is>
       </c>
-      <c r="AS5" t="inlineStr">
+      <c r="AW5" t="inlineStr">
         <is>
           <t>-2.48</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>103.8</t>
         </is>
       </c>
-      <c r="AU5" t="n">
+      <c r="AY5" t="n">
         <v>108.65</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="AZ5" t="n">
         <v>115.99</v>
       </c>
-      <c r="AW5" t="inlineStr">
+      <c r="BA5" t="inlineStr">
         <is>
           <t>118.94</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="BB5" t="inlineStr">
         <is>
           <t>-0.32</t>
         </is>
       </c>
-      <c r="AY5" t="n">
+      <c r="BC5" t="n">
         <v>-3.69</v>
       </c>
-      <c r="AZ5" t="n">
+      <c r="BD5" t="n">
         <v>-3.68</v>
       </c>
-      <c r="BA5" t="inlineStr">
+      <c r="BE5" t="inlineStr">
         <is>
           <t>10.7</t>
         </is>
       </c>
-      <c r="BB5" t="inlineStr">
+      <c r="BF5" t="inlineStr">
         <is>
           <t>-134.35</t>
         </is>
       </c>
-      <c r="BC5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>2025/12/11</t>
         </is>
       </c>
-      <c r="BD5" t="inlineStr">
+      <c r="BH5" t="inlineStr">
         <is>
           <t>400544610.7247191</t>
         </is>
       </c>
-      <c r="BE5" t="inlineStr">
+      <c r="BI5" t="inlineStr">
         <is>
           <t>70895826.0</t>
         </is>
       </c>
-      <c r="BF5" t="n">
+      <c r="BJ5" t="n">
         <v>100748036.2</v>
       </c>
-      <c r="BG5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>78953691.6</t>
         </is>
       </c>
-      <c r="BH5" t="n">
+      <c r="BL5" t="n">
         <v>316450597.8</v>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BM5" t="inlineStr">
         <is>
           <t>21794344</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BN5" t="inlineStr">
         <is>
           <t>-35439163.56077314</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>-28090912.49851693</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>70895826.0</t>
         </is>
       </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
         <is>
           <t>99.0</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BS5" t="inlineStr">
         <is>
           <t>2025/07/18</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
+      <c r="BT5" t="inlineStr">
         <is>
           <t>6.57</t>
         </is>
       </c>
-      <c r="BQ5" t="inlineStr">
+      <c r="BU5" t="inlineStr">
         <is>
           <t>上緯投控</t>
         </is>
       </c>
-      <c r="BR5" t="inlineStr">
+      <c r="BV5" t="inlineStr">
         <is>
           <t>上緯投控</t>
         </is>
       </c>
-      <c r="BS5" t="inlineStr">
+      <c r="BW5" t="inlineStr">
         <is>
           <t>綠能環保</t>
         </is>
       </c>
-      <c r="BT5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
+      <c r="BY5" t="inlineStr">
         <is>
           <t>1.06</t>
         </is>
       </c>
-      <c r="BV5" t="inlineStr">
+      <c r="BZ5" t="inlineStr">
         <is>
           <t>-4.012262137013166</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="CA5" t="inlineStr">
         <is>
           <t>-1.72716244973935</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>4.777195903551031</t>
         </is>
       </c>
-      <c r="BY5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ5" t="inlineStr">
+      <c r="CD5" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CE5" t="inlineStr">
         <is>
           <t>1.18</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CF5" t="inlineStr">
         <is>
           <t>2.21</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
+      <c r="CG5" t="inlineStr">
         <is>
           <t>-29.60</t>
         </is>
       </c>
-      <c r="CD5" t="inlineStr">
+      <c r="CH5" t="inlineStr">
         <is>
           <t>83.46</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CG5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CJ5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CK5" t="inlineStr">
         <is>
           <t>45.32</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CL5" t="inlineStr">
         <is>
           <t>11371</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CM5" t="inlineStr">
         <is>
           <t>環保耐蝕材料39.58%、環保綠能材料33.76%、其他25.01%、循環經濟材料1.65% (2024年)</t>
         </is>
       </c>
-      <c r="CJ5" t="inlineStr">
+      <c r="CN5" t="inlineStr">
         <is>
           <t>上緯投控-綠能環保-上市</t>
         </is>
       </c>
-      <c r="CK5" t="inlineStr">
+      <c r="CO5" t="inlineStr">
         <is>
           <t>綠能環保平上市</t>
         </is>
       </c>
-      <c r="CL5" t="inlineStr">
+      <c r="CP5" t="inlineStr">
         <is>
           <t>104.0</t>
         </is>
       </c>
-      <c r="CM5" t="inlineStr">
+      <c r="CQ5" t="inlineStr">
         <is>
           <t>107.0</t>
         </is>
       </c>
-      <c r="CN5" t="inlineStr">
+      <c r="CR5" t="inlineStr">
         <is>
           <t>104.0</t>
         </is>
       </c>
-      <c r="CO5" t="inlineStr">
+      <c r="CS5" t="inlineStr">
         <is>
           <t>105.5</t>
         </is>
       </c>
-      <c r="CP5" t="inlineStr">
+      <c r="CT5" t="inlineStr">
         <is>
           <t>89.23</t>
         </is>
       </c>
-      <c r="CQ5" t="inlineStr">
+      <c r="CU5" t="inlineStr">
         <is>
           <t>** 風力發電 - 玻/碳纖、樹酯</t>
         </is>
       </c>
-      <c r="CR5" t="inlineStr">
+      <c r="CV5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2896,325 +2996,345 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
           <t>2025/09/24</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>125.5</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>2025/06/30</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>70.1</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0.18</t>
-        </is>
-      </c>
       <c r="AG6" t="inlineStr">
         <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>109.5</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>2025/11/10</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
           <t>2025-12-09</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>2.58</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>-0.46</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr">
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
+      <c r="AQ6" t="inlineStr">
         <is>
           <t>770</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr">
+      <c r="AR6" t="inlineStr">
         <is>
           <t>23.08</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr">
+      <c r="AS6" t="inlineStr">
         <is>
           <t>17.95</t>
         </is>
       </c>
-      <c r="AP6" t="n">
+      <c r="AT6" t="n">
         <v>0.48</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="AU6" t="n">
         <v>-5.69</v>
       </c>
-      <c r="AR6" t="inlineStr">
+      <c r="AV6" t="inlineStr">
         <is>
           <t>-5.8</t>
         </is>
       </c>
-      <c r="AS6" t="inlineStr">
+      <c r="AW6" t="inlineStr">
         <is>
           <t>-2.18</t>
         </is>
       </c>
-      <c r="AT6" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>103.5</t>
         </is>
       </c>
-      <c r="AU6" t="n">
+      <c r="AY6" t="n">
         <v>109.75</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="AZ6" t="n">
         <v>116.51</v>
       </c>
-      <c r="AW6" t="inlineStr">
+      <c r="BA6" t="inlineStr">
         <is>
           <t>119.11</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="BB6" t="inlineStr">
         <is>
           <t>-7.23</t>
         </is>
       </c>
-      <c r="AY6" t="n">
+      <c r="BC6" t="n">
         <v>-3.94</v>
       </c>
-      <c r="AZ6" t="n">
+      <c r="BD6" t="n">
         <v>-3.67</v>
       </c>
-      <c r="BA6" t="inlineStr">
+      <c r="BE6" t="inlineStr">
         <is>
           <t>10.7</t>
         </is>
       </c>
-      <c r="BB6" t="inlineStr">
+      <c r="BF6" t="inlineStr">
         <is>
           <t>-134.32</t>
         </is>
       </c>
-      <c r="BC6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>2025/12/11</t>
         </is>
       </c>
-      <c r="BD6" t="inlineStr">
+      <c r="BH6" t="inlineStr">
         <is>
           <t>400544610.7247191</t>
         </is>
       </c>
-      <c r="BE6" t="inlineStr">
+      <c r="BI6" t="inlineStr">
         <is>
           <t>87855895.0</t>
         </is>
       </c>
-      <c r="BF6" t="n">
+      <c r="BJ6" t="n">
         <v>99480096</v>
       </c>
-      <c r="BG6" t="inlineStr">
+      <c r="BK6" t="inlineStr">
         <is>
           <t>79320431.1</t>
         </is>
       </c>
-      <c r="BH6" t="n">
+      <c r="BL6" t="n">
         <v>376415022.36</v>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BM6" t="inlineStr">
         <is>
           <t>20159664</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BN6" t="inlineStr">
         <is>
           <t>-36775209.20845608</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>-29639090.30972932</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>87855895.0</t>
         </is>
       </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
         <is>
           <t>99.0</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BS6" t="inlineStr">
         <is>
           <t>2025/07/18</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
+      <c r="BT6" t="inlineStr">
         <is>
           <t>5.05</t>
         </is>
       </c>
-      <c r="BQ6" t="inlineStr">
+      <c r="BU6" t="inlineStr">
         <is>
           <t>上緯投控</t>
         </is>
       </c>
-      <c r="BR6" t="inlineStr">
+      <c r="BV6" t="inlineStr">
         <is>
           <t>上緯投控</t>
         </is>
       </c>
-      <c r="BS6" t="inlineStr">
+      <c r="BW6" t="inlineStr">
         <is>
           <t>綠能環保</t>
         </is>
       </c>
-      <c r="BT6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU6" t="inlineStr">
+      <c r="BY6" t="inlineStr">
         <is>
           <t>1.06</t>
         </is>
       </c>
-      <c r="BV6" t="inlineStr">
+      <c r="BZ6" t="inlineStr">
         <is>
           <t>-4.012262137013166</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="CA6" t="inlineStr">
         <is>
           <t>-1.72716244973935</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>4.777195903551031</t>
         </is>
       </c>
-      <c r="BY6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ6" t="inlineStr">
+      <c r="CD6" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CE6" t="inlineStr">
         <is>
           <t>1.17</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CF6" t="inlineStr">
         <is>
           <t>2.21</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
+      <c r="CG6" t="inlineStr">
         <is>
           <t>-29.60</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
+      <c r="CH6" t="inlineStr">
         <is>
           <t>83.46</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CG6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CJ6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CK6" t="inlineStr">
         <is>
           <t>45.32</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CL6" t="inlineStr">
         <is>
           <t>11371</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CM6" t="inlineStr">
         <is>
           <t>環保耐蝕材料39.58%、環保綠能材料33.76%、其他25.01%、循環經濟材料1.65% (2024年)</t>
         </is>
       </c>
-      <c r="CJ6" t="inlineStr">
+      <c r="CN6" t="inlineStr">
         <is>
           <t>上緯投控-綠能環保-上市</t>
         </is>
       </c>
-      <c r="CK6" t="inlineStr">
+      <c r="CO6" t="inlineStr">
         <is>
           <t>綠能環保平上市</t>
         </is>
       </c>
-      <c r="CL6" t="inlineStr">
+      <c r="CP6" t="inlineStr">
         <is>
           <t>103.0</t>
         </is>
       </c>
-      <c r="CM6" t="inlineStr">
+      <c r="CQ6" t="inlineStr">
         <is>
           <t>106.0</t>
         </is>
       </c>
-      <c r="CN6" t="inlineStr">
+      <c r="CR6" t="inlineStr">
         <is>
           <t>102.5</t>
         </is>
       </c>
-      <c r="CO6" t="inlineStr">
+      <c r="CS6" t="inlineStr">
         <is>
           <t>104.0</t>
         </is>
       </c>
-      <c r="CP6" t="inlineStr">
+      <c r="CT6" t="inlineStr">
         <is>
           <t>89.23</t>
         </is>
       </c>
-      <c r="CQ6" t="inlineStr">
+      <c r="CU6" t="inlineStr">
         <is>
           <t>** 風力發電 - 玻/碳纖、樹酯</t>
         </is>
       </c>
-      <c r="CR6" t="inlineStr">
+      <c r="CV6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3358,325 +3478,345 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
+          <t>0.19</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
           <t>2025/09/24</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>125.5</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>2025/06/30</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>70.1</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>0.19</t>
-        </is>
-      </c>
       <c r="AG7" t="inlineStr">
         <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>109.5</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>2025/11/10</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>2.37</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr">
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
+      <c r="AQ7" t="inlineStr">
         <is>
           <t>770</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
+      <c r="AR7" t="inlineStr">
         <is>
           <t>23.08</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr">
+      <c r="AS7" t="inlineStr">
         <is>
           <t>10.26</t>
         </is>
       </c>
-      <c r="AP7" t="n">
+      <c r="AT7" t="n">
         <v>0.19</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AU7" t="n">
         <v>-5.94</v>
       </c>
-      <c r="AR7" t="inlineStr">
+      <c r="AV7" t="inlineStr">
         <is>
           <t>-5.64</t>
         </is>
       </c>
-      <c r="AS7" t="inlineStr">
+      <c r="AW7" t="inlineStr">
         <is>
           <t>-1.99</t>
         </is>
       </c>
-      <c r="AT7" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>103.8</t>
         </is>
       </c>
-      <c r="AU7" t="n">
+      <c r="AY7" t="n">
         <v>110.35</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="AZ7" t="n">
         <v>116.94</v>
       </c>
-      <c r="AW7" t="inlineStr">
+      <c r="BA7" t="inlineStr">
         <is>
           <t>119.31</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="BB7" t="inlineStr">
         <is>
           <t>-12.25</t>
         </is>
       </c>
-      <c r="AY7" t="n">
+      <c r="BC7" t="n">
         <v>-4.05</v>
       </c>
-      <c r="AZ7" t="n">
+      <c r="BD7" t="n">
         <v>-3.61</v>
       </c>
-      <c r="BA7" t="inlineStr">
+      <c r="BE7" t="inlineStr">
         <is>
           <t>10.7</t>
         </is>
       </c>
-      <c r="BB7" t="inlineStr">
+      <c r="BF7" t="inlineStr">
         <is>
           <t>-133.70</t>
         </is>
       </c>
-      <c r="BC7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>2025/12/11</t>
         </is>
       </c>
-      <c r="BD7" t="inlineStr">
+      <c r="BH7" t="inlineStr">
         <is>
           <t>400544610.7247191</t>
         </is>
       </c>
-      <c r="BE7" t="inlineStr">
+      <c r="BI7" t="inlineStr">
         <is>
           <t>80369509.0</t>
         </is>
       </c>
-      <c r="BF7" t="n">
+      <c r="BJ7" t="n">
         <v>91648883.59999999</v>
       </c>
-      <c r="BG7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>79208492.5</t>
         </is>
       </c>
-      <c r="BH7" t="n">
+      <c r="BL7" t="n">
         <v>400946194.74</v>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BM7" t="inlineStr">
         <is>
           <t>12440391</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BN7" t="inlineStr">
         <is>
           <t>-38072685.37186095</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>-32609384.20754242</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>80369509.0</t>
         </is>
       </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
         <is>
           <t>99.0</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BS7" t="inlineStr">
         <is>
           <t>2025/07/18</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
+      <c r="BT7" t="inlineStr">
         <is>
           <t>5.05</t>
         </is>
       </c>
-      <c r="BQ7" t="inlineStr">
+      <c r="BU7" t="inlineStr">
         <is>
           <t>上緯投控</t>
         </is>
       </c>
-      <c r="BR7" t="inlineStr">
+      <c r="BV7" t="inlineStr">
         <is>
           <t>上緯投控</t>
         </is>
       </c>
-      <c r="BS7" t="inlineStr">
+      <c r="BW7" t="inlineStr">
         <is>
           <t>綠能環保</t>
         </is>
       </c>
-      <c r="BT7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
+      <c r="BY7" t="inlineStr">
         <is>
           <t>1.06</t>
         </is>
       </c>
-      <c r="BV7" t="inlineStr">
+      <c r="BZ7" t="inlineStr">
         <is>
           <t>-4.012262137013166</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="CA7" t="inlineStr">
         <is>
           <t>-1.72716244973935</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>4.777195903551031</t>
         </is>
       </c>
-      <c r="BY7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ7" t="inlineStr">
+      <c r="CD7" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CE7" t="inlineStr">
         <is>
           <t>1.17</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CF7" t="inlineStr">
         <is>
           <t>2.21</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
+      <c r="CG7" t="inlineStr">
         <is>
           <t>-29.60</t>
         </is>
       </c>
-      <c r="CD7" t="inlineStr">
+      <c r="CH7" t="inlineStr">
         <is>
           <t>83.46</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CG7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CJ7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CK7" t="inlineStr">
         <is>
           <t>45.32</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CL7" t="inlineStr">
         <is>
           <t>11371</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CM7" t="inlineStr">
         <is>
           <t>環保耐蝕材料39.58%、環保綠能材料33.76%、其他25.01%、循環經濟材料1.65% (2024年)</t>
         </is>
       </c>
-      <c r="CJ7" t="inlineStr">
+      <c r="CN7" t="inlineStr">
         <is>
           <t>上緯投控-綠能環保-上市</t>
         </is>
       </c>
-      <c r="CK7" t="inlineStr">
+      <c r="CO7" t="inlineStr">
         <is>
           <t>綠能環保平上市</t>
         </is>
       </c>
-      <c r="CL7" t="inlineStr">
+      <c r="CP7" t="inlineStr">
         <is>
           <t>105.5</t>
         </is>
       </c>
-      <c r="CM7" t="inlineStr">
+      <c r="CQ7" t="inlineStr">
         <is>
           <t>105.5</t>
         </is>
       </c>
-      <c r="CN7" t="inlineStr">
+      <c r="CR7" t="inlineStr">
         <is>
           <t>102.5</t>
         </is>
       </c>
-      <c r="CO7" t="inlineStr">
+      <c r="CS7" t="inlineStr">
         <is>
           <t>104.0</t>
         </is>
       </c>
-      <c r="CP7" t="inlineStr">
+      <c r="CT7" t="inlineStr">
         <is>
           <t>89.23</t>
         </is>
       </c>
-      <c r="CQ7" t="inlineStr">
+      <c r="CU7" t="inlineStr">
         <is>
           <t>** 風力發電 - 玻/碳纖、樹酯</t>
         </is>
       </c>
-      <c r="CR7" t="inlineStr">
+      <c r="CV7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3820,325 +3960,345 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
           <t>2025/09/24</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>125.5</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>2025/06/30</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>70.1</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
       <c r="AG8" t="inlineStr">
         <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>109.5</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>2025/11/10</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>1.81</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>1.01</t>
         </is>
       </c>
-      <c r="AJ8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr">
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
+      <c r="AQ8" t="inlineStr">
         <is>
           <t>770</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr">
+      <c r="AR8" t="inlineStr">
         <is>
           <t>7.69</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr">
+      <c r="AS8" t="inlineStr">
         <is>
           <t>2.56</t>
         </is>
       </c>
-      <c r="AP8" t="n">
+      <c r="AT8" t="n">
         <v>-0.87</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AU8" t="n">
         <v>-6.31</v>
       </c>
-      <c r="AR8" t="inlineStr">
+      <c r="AV8" t="inlineStr">
         <is>
           <t>-5.34</t>
         </is>
       </c>
-      <c r="AS8" t="inlineStr">
+      <c r="AW8" t="inlineStr">
         <is>
           <t>-2.02</t>
         </is>
       </c>
-      <c r="AT8" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>103.9</t>
         </is>
       </c>
-      <c r="AU8" t="n">
+      <c r="AY8" t="n">
         <v>110.9</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="AZ8" t="n">
         <v>117.15</v>
       </c>
-      <c r="AW8" t="inlineStr">
+      <c r="BA8" t="inlineStr">
         <is>
           <t>119.56</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="BB8" t="inlineStr">
         <is>
           <t>-18.13</t>
         </is>
       </c>
-      <c r="AY8" t="n">
+      <c r="BC8" t="n">
         <v>-4.13</v>
       </c>
-      <c r="AZ8" t="n">
+      <c r="BD8" t="n">
         <v>-3.5</v>
       </c>
-      <c r="BA8" t="inlineStr">
+      <c r="BE8" t="inlineStr">
         <is>
           <t>10.7</t>
         </is>
       </c>
-      <c r="BB8" t="inlineStr">
+      <c r="BF8" t="inlineStr">
         <is>
           <t>-132.67</t>
         </is>
       </c>
-      <c r="BC8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>2025/12/11</t>
         </is>
       </c>
-      <c r="BD8" t="inlineStr">
+      <c r="BH8" t="inlineStr">
         <is>
           <t>400544610.7247191</t>
         </is>
       </c>
-      <c r="BE8" t="inlineStr">
+      <c r="BI8" t="inlineStr">
         <is>
           <t>60912790.0</t>
         </is>
       </c>
-      <c r="BF8" t="n">
+      <c r="BJ8" t="n">
         <v>90207911.8</v>
       </c>
-      <c r="BG8" t="inlineStr">
+      <c r="BK8" t="inlineStr">
         <is>
           <t>85136383.4</t>
         </is>
       </c>
-      <c r="BH8" t="n">
+      <c r="BL8" t="n">
         <v>403373073.88</v>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BM8" t="inlineStr">
         <is>
           <t>5071528</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BN8" t="inlineStr">
         <is>
           <t>-39066012.8562825</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>-34885927.55414887</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>60912790.0</t>
         </is>
       </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
         <is>
           <t>99.0</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BS8" t="inlineStr">
         <is>
           <t>2025/07/18</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
+      <c r="BT8" t="inlineStr">
         <is>
           <t>4.04</t>
         </is>
       </c>
-      <c r="BQ8" t="inlineStr">
+      <c r="BU8" t="inlineStr">
         <is>
           <t>上緯投控</t>
         </is>
       </c>
-      <c r="BR8" t="inlineStr">
+      <c r="BV8" t="inlineStr">
         <is>
           <t>上緯投控</t>
         </is>
       </c>
-      <c r="BS8" t="inlineStr">
+      <c r="BW8" t="inlineStr">
         <is>
           <t>綠能環保</t>
         </is>
       </c>
-      <c r="BT8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
+      <c r="BY8" t="inlineStr">
         <is>
           <t>1.06</t>
         </is>
       </c>
-      <c r="BV8" t="inlineStr">
+      <c r="BZ8" t="inlineStr">
         <is>
           <t>-4.012262137013166</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="CA8" t="inlineStr">
         <is>
           <t>-1.72716244973935</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>4.777195903551031</t>
         </is>
       </c>
-      <c r="BY8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ8" t="inlineStr">
+      <c r="CD8" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CE8" t="inlineStr">
         <is>
           <t>1.15</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CF8" t="inlineStr">
         <is>
           <t>2.21</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
+      <c r="CG8" t="inlineStr">
         <is>
           <t>-29.60</t>
         </is>
       </c>
-      <c r="CD8" t="inlineStr">
+      <c r="CH8" t="inlineStr">
         <is>
           <t>83.46</t>
         </is>
       </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CG8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CJ8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CK8" t="inlineStr">
         <is>
           <t>45.32</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CL8" t="inlineStr">
         <is>
           <t>11371</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CM8" t="inlineStr">
         <is>
           <t>環保耐蝕材料39.58%、環保綠能材料33.76%、其他25.01%、循環經濟材料1.65% (2024年)</t>
         </is>
       </c>
-      <c r="CJ8" t="inlineStr">
+      <c r="CN8" t="inlineStr">
         <is>
           <t>上緯投控-綠能環保-上市</t>
         </is>
       </c>
-      <c r="CK8" t="inlineStr">
+      <c r="CO8" t="inlineStr">
         <is>
           <t>綠能環保平上市</t>
         </is>
       </c>
-      <c r="CL8" t="inlineStr">
+      <c r="CP8" t="inlineStr">
         <is>
           <t>103.0</t>
         </is>
       </c>
-      <c r="CM8" t="inlineStr">
+      <c r="CQ8" t="inlineStr">
         <is>
           <t>104.0</t>
         </is>
       </c>
-      <c r="CN8" t="inlineStr">
+      <c r="CR8" t="inlineStr">
         <is>
           <t>101.0</t>
         </is>
       </c>
-      <c r="CO8" t="inlineStr">
+      <c r="CS8" t="inlineStr">
         <is>
           <t>103.0</t>
         </is>
       </c>
-      <c r="CP8" t="inlineStr">
+      <c r="CT8" t="inlineStr">
         <is>
           <t>89.23</t>
         </is>
       </c>
-      <c r="CQ8" t="inlineStr">
+      <c r="CU8" t="inlineStr">
         <is>
           <t>** 風力發電 - 玻/碳纖、樹酯</t>
         </is>
       </c>
-      <c r="CR8" t="inlineStr">
+      <c r="CV8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4282,325 +4442,345 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
+          <t>-0.0</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
           <t>2025/09/24</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>125.5</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>2025/06/30</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>70.1</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
       <c r="AG9" t="inlineStr">
         <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>109.5</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>2025/11/10</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AH9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>5.93</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>-6.83</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr">
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
+      <c r="AQ9" t="inlineStr">
         <is>
           <t>770</t>
         </is>
       </c>
-      <c r="AN9" t="inlineStr">
+      <c r="AR9" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
+      <c r="AS9" t="inlineStr">
         <is>
           <t>3.51</t>
         </is>
       </c>
-      <c r="AP9" t="n">
+      <c r="AT9" t="n">
         <v>-2.29</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AU9" t="n">
         <v>-5.9</v>
       </c>
-      <c r="AR9" t="inlineStr">
+      <c r="AV9" t="inlineStr">
         <is>
           <t>-5.09</t>
         </is>
       </c>
-      <c r="AS9" t="inlineStr">
+      <c r="AW9" t="inlineStr">
         <is>
           <t>-1.98</t>
         </is>
       </c>
-      <c r="AT9" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>104.9</t>
         </is>
       </c>
-      <c r="AU9" t="n">
+      <c r="AY9" t="n">
         <v>111.48</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="AZ9" t="n">
         <v>117.45</v>
       </c>
-      <c r="AW9" t="inlineStr">
+      <c r="BA9" t="inlineStr">
         <is>
           <t>119.82</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="BB9" t="inlineStr">
         <is>
           <t>-22.00</t>
         </is>
       </c>
-      <c r="AY9" t="n">
+      <c r="BC9" t="n">
         <v>-4.07</v>
       </c>
-      <c r="AZ9" t="n">
+      <c r="BD9" t="n">
         <v>-3.34</v>
       </c>
-      <c r="BA9" t="inlineStr">
+      <c r="BE9" t="inlineStr">
         <is>
           <t>10.7</t>
         </is>
       </c>
-      <c r="BB9" t="inlineStr">
+      <c r="BF9" t="inlineStr">
         <is>
           <t>-131.19</t>
         </is>
       </c>
-      <c r="BC9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>2025/12/11</t>
         </is>
       </c>
-      <c r="BD9" t="inlineStr">
+      <c r="BH9" t="inlineStr">
         <is>
           <t>400544610.7247191</t>
         </is>
       </c>
-      <c r="BE9" t="inlineStr">
+      <c r="BI9" t="inlineStr">
         <is>
           <t>203706161.0</t>
         </is>
       </c>
-      <c r="BF9" t="n">
+      <c r="BJ9" t="n">
         <v>87092333.59999999</v>
       </c>
-      <c r="BG9" t="inlineStr">
+      <c r="BK9" t="inlineStr">
         <is>
           <t>95316409.3</t>
         </is>
       </c>
-      <c r="BH9" t="n">
+      <c r="BL9" t="n">
         <v>406267066.38</v>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BM9" t="inlineStr">
         <is>
           <t>-8224075</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BN9" t="inlineStr">
         <is>
           <t>-39826028.36576135</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>-34807557.88665277</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>203706161.0</t>
         </is>
       </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
         <is>
           <t>99.0</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BS9" t="inlineStr">
         <is>
           <t>2025/07/18</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
+      <c r="BT9" t="inlineStr">
         <is>
           <t>3.54</t>
         </is>
       </c>
-      <c r="BQ9" t="inlineStr">
+      <c r="BU9" t="inlineStr">
         <is>
           <t>上緯投控</t>
         </is>
       </c>
-      <c r="BR9" t="inlineStr">
+      <c r="BV9" t="inlineStr">
         <is>
           <t>上緯投控</t>
         </is>
       </c>
-      <c r="BS9" t="inlineStr">
+      <c r="BW9" t="inlineStr">
         <is>
           <t>綠能環保</t>
         </is>
       </c>
-      <c r="BT9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
+      <c r="BY9" t="inlineStr">
         <is>
           <t>1.06</t>
         </is>
       </c>
-      <c r="BV9" t="inlineStr">
+      <c r="BZ9" t="inlineStr">
         <is>
           <t>-4.012262137013166</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="CA9" t="inlineStr">
         <is>
           <t>-1.72716244973935</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>4.777195903551031</t>
         </is>
       </c>
-      <c r="BY9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ9" t="inlineStr">
+      <c r="CD9" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CE9" t="inlineStr">
         <is>
           <t>1.15</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CF9" t="inlineStr">
         <is>
           <t>2.21</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
+      <c r="CG9" t="inlineStr">
         <is>
           <t>-29.60</t>
         </is>
       </c>
-      <c r="CD9" t="inlineStr">
+      <c r="CH9" t="inlineStr">
         <is>
           <t>83.46</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CG9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CJ9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CK9" t="inlineStr">
         <is>
           <t>45.32</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CL9" t="inlineStr">
         <is>
           <t>11371</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CM9" t="inlineStr">
         <is>
           <t>環保耐蝕材料39.58%、環保綠能材料33.76%、其他25.01%、循環經濟材料1.65% (2024年)</t>
         </is>
       </c>
-      <c r="CJ9" t="inlineStr">
+      <c r="CN9" t="inlineStr">
         <is>
           <t>上緯投控-綠能環保-上市</t>
         </is>
       </c>
-      <c r="CK9" t="inlineStr">
+      <c r="CO9" t="inlineStr">
         <is>
           <t>綠能環保平上市</t>
         </is>
       </c>
-      <c r="CL9" t="inlineStr">
+      <c r="CP9" t="inlineStr">
         <is>
           <t>106.0</t>
         </is>
       </c>
-      <c r="CM9" t="inlineStr">
+      <c r="CQ9" t="inlineStr">
         <is>
           <t>109.5</t>
         </is>
       </c>
-      <c r="CN9" t="inlineStr">
+      <c r="CR9" t="inlineStr">
         <is>
           <t>102.5</t>
         </is>
       </c>
-      <c r="CO9" t="inlineStr">
+      <c r="CS9" t="inlineStr">
         <is>
           <t>102.5</t>
         </is>
       </c>
-      <c r="CP9" t="inlineStr">
+      <c r="CT9" t="inlineStr">
         <is>
           <t>89.23</t>
         </is>
       </c>
-      <c r="CQ9" t="inlineStr">
+      <c r="CU9" t="inlineStr">
         <is>
           <t>** 風力發電 - 玻/碳纖、樹酯</t>
         </is>
       </c>
-      <c r="CR9" t="inlineStr">
+      <c r="CV9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4744,325 +4924,345 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
           <t>2025/09/24</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>125.5</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>2025/06/30</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
         <is>
           <t>70.1</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
-      </c>
       <c r="AG10" t="inlineStr">
         <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>109.5</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>2025/11/10</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="AH10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>1.88</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>-2.88</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr">
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
+      <c r="AQ10" t="inlineStr">
         <is>
           <t>770</t>
         </is>
       </c>
-      <c r="AN10" t="inlineStr">
+      <c r="AR10" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr">
+      <c r="AS10" t="inlineStr">
         <is>
           <t>3.51</t>
         </is>
       </c>
-      <c r="AP10" t="n">
+      <c r="AT10" t="n">
         <v>-2.07</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AU10" t="n">
         <v>-5.77</v>
       </c>
-      <c r="AR10" t="inlineStr">
+      <c r="AV10" t="inlineStr">
         <is>
           <t>-4.26</t>
         </is>
       </c>
-      <c r="AS10" t="inlineStr">
+      <c r="AW10" t="inlineStr">
         <is>
           <t>-2.01</t>
         </is>
       </c>
-      <c r="AT10" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>106.2</t>
         </is>
       </c>
-      <c r="AU10" t="n">
+      <c r="AY10" t="n">
         <v>112.7</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="AZ10" t="n">
         <v>117.72</v>
       </c>
-      <c r="AW10" t="inlineStr">
+      <c r="BA10" t="inlineStr">
         <is>
           <t>120.13</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="BB10" t="inlineStr">
         <is>
           <t>-23.26</t>
         </is>
       </c>
-      <c r="AY10" t="n">
+      <c r="BC10" t="n">
         <v>-3.89</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="BD10" t="n">
         <v>-3.15</v>
       </c>
-      <c r="BA10" t="inlineStr">
+      <c r="BE10" t="inlineStr">
         <is>
           <t>10.7</t>
         </is>
       </c>
-      <c r="BB10" t="inlineStr">
+      <c r="BF10" t="inlineStr">
         <is>
           <t>-129.47</t>
         </is>
       </c>
-      <c r="BC10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>2025/12/11</t>
         </is>
       </c>
-      <c r="BD10" t="inlineStr">
+      <c r="BH10" t="inlineStr">
         <is>
           <t>400544610.7247191</t>
         </is>
       </c>
-      <c r="BE10" t="inlineStr">
+      <c r="BI10" t="inlineStr">
         <is>
           <t>64556125.0</t>
         </is>
       </c>
-      <c r="BF10" t="n">
+      <c r="BJ10" t="n">
         <v>57159347</v>
       </c>
-      <c r="BG10" t="inlineStr">
+      <c r="BK10" t="inlineStr">
         <is>
           <t>86212815.0</t>
         </is>
       </c>
-      <c r="BH10" t="n">
+      <c r="BL10" t="n">
         <v>406636712.2</v>
       </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BM10" t="inlineStr">
         <is>
           <t>-29053468</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BN10" t="inlineStr">
         <is>
           <t>-40738477.54378109</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>-48751763.90142073</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
         <is>
           <t>64556125.0</t>
         </is>
       </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
         <is>
           <t>99.0</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BS10" t="inlineStr">
         <is>
           <t>2025/07/18</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
+      <c r="BT10" t="inlineStr">
         <is>
           <t>5.05</t>
         </is>
       </c>
-      <c r="BQ10" t="inlineStr">
+      <c r="BU10" t="inlineStr">
         <is>
           <t>上緯投控</t>
         </is>
       </c>
-      <c r="BR10" t="inlineStr">
+      <c r="BV10" t="inlineStr">
         <is>
           <t>上緯投控</t>
         </is>
       </c>
-      <c r="BS10" t="inlineStr">
+      <c r="BW10" t="inlineStr">
         <is>
           <t>綠能環保</t>
         </is>
       </c>
-      <c r="BT10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU10" t="inlineStr">
+      <c r="BY10" t="inlineStr">
         <is>
           <t>1.06</t>
         </is>
       </c>
-      <c r="BV10" t="inlineStr">
+      <c r="BZ10" t="inlineStr">
         <is>
           <t>-4.012262137013166</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="CA10" t="inlineStr">
         <is>
           <t>-1.72716244973935</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>4.777195903551031</t>
         </is>
       </c>
-      <c r="BY10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ10" t="inlineStr">
+      <c r="CD10" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CE10" t="inlineStr">
         <is>
           <t>1.17</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CF10" t="inlineStr">
         <is>
           <t>2.21</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
+      <c r="CG10" t="inlineStr">
         <is>
           <t>-29.60</t>
         </is>
       </c>
-      <c r="CD10" t="inlineStr">
+      <c r="CH10" t="inlineStr">
         <is>
           <t>83.46</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CG10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CJ10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CK10" t="inlineStr">
         <is>
           <t>45.32</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CL10" t="inlineStr">
         <is>
           <t>11371</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CM10" t="inlineStr">
         <is>
           <t>環保耐蝕材料39.58%、環保綠能材料33.76%、其他25.01%、循環經濟材料1.65% (2024年)</t>
         </is>
       </c>
-      <c r="CJ10" t="inlineStr">
+      <c r="CN10" t="inlineStr">
         <is>
           <t>上緯投控-綠能環保-上市</t>
         </is>
       </c>
-      <c r="CK10" t="inlineStr">
+      <c r="CO10" t="inlineStr">
         <is>
           <t>綠能環保平上市</t>
         </is>
       </c>
-      <c r="CL10" t="inlineStr">
+      <c r="CP10" t="inlineStr">
         <is>
           <t>106.0</t>
         </is>
       </c>
-      <c r="CM10" t="inlineStr">
+      <c r="CQ10" t="inlineStr">
         <is>
           <t>107.0</t>
         </is>
       </c>
-      <c r="CN10" t="inlineStr">
+      <c r="CR10" t="inlineStr">
         <is>
           <t>104.0</t>
         </is>
       </c>
-      <c r="CO10" t="inlineStr">
+      <c r="CS10" t="inlineStr">
         <is>
           <t>104.0</t>
         </is>
       </c>
-      <c r="CP10" t="inlineStr">
+      <c r="CT10" t="inlineStr">
         <is>
           <t>89.23</t>
         </is>
       </c>
-      <c r="CQ10" t="inlineStr">
+      <c r="CU10" t="inlineStr">
         <is>
           <t>** 風力發電 - 玻/碳纖、樹酯</t>
         </is>
       </c>
-      <c r="CR10" t="inlineStr">
+      <c r="CV10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5206,325 +5406,345 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
           <t>2025/09/24</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>125.5</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AE11" t="inlineStr">
         <is>
           <t>2025/06/30</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AF11" t="inlineStr">
         <is>
           <t>70.1</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>0.12</t>
-        </is>
-      </c>
       <c r="AG11" t="inlineStr">
         <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>109.5</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>2025/11/10</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
           <t>2025-12-02</t>
         </is>
       </c>
-      <c r="AH11" t="inlineStr">
+      <c r="AL11" t="inlineStr">
         <is>
           <t>1.41</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
+      <c r="AM11" t="inlineStr">
         <is>
           <t>-0.95</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr">
+      <c r="AN11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr">
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
+      <c r="AQ11" t="inlineStr">
         <is>
           <t>770</t>
         </is>
       </c>
-      <c r="AN11" t="inlineStr">
+      <c r="AR11" t="inlineStr">
         <is>
           <t>10.53</t>
         </is>
       </c>
-      <c r="AO11" t="inlineStr">
+      <c r="AS11" t="inlineStr">
         <is>
           <t>15.79</t>
         </is>
       </c>
-      <c r="AP11" t="n">
+      <c r="AT11" t="n">
         <v>-1.49</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AU11" t="n">
         <v>-5.68</v>
       </c>
-      <c r="AR11" t="inlineStr">
+      <c r="AV11" t="inlineStr">
         <is>
           <t>-3.71</t>
         </is>
       </c>
-      <c r="AS11" t="inlineStr">
+      <c r="AW11" t="inlineStr">
         <is>
           <t>-2.09</t>
         </is>
       </c>
-      <c r="AT11" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>107.1</t>
         </is>
       </c>
-      <c r="AU11" t="n">
+      <c r="AY11" t="n">
         <v>113.55</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="AZ11" t="n">
         <v>117.93</v>
       </c>
-      <c r="AW11" t="inlineStr">
+      <c r="BA11" t="inlineStr">
         <is>
           <t>120.44</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="BB11" t="inlineStr">
         <is>
           <t>-26.20</t>
         </is>
       </c>
-      <c r="AY11" t="n">
+      <c r="BC11" t="n">
         <v>-3.75</v>
       </c>
-      <c r="AZ11" t="n">
+      <c r="BD11" t="n">
         <v>-2.97</v>
       </c>
-      <c r="BA11" t="inlineStr">
+      <c r="BE11" t="inlineStr">
         <is>
           <t>10.7</t>
         </is>
       </c>
-      <c r="BB11" t="inlineStr">
+      <c r="BF11" t="inlineStr">
         <is>
           <t>-127.76</t>
         </is>
       </c>
-      <c r="BC11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>2025/12/11</t>
         </is>
       </c>
-      <c r="BD11" t="inlineStr">
+      <c r="BH11" t="inlineStr">
         <is>
           <t>400544610.7247191</t>
         </is>
       </c>
-      <c r="BE11" t="inlineStr">
+      <c r="BI11" t="inlineStr">
         <is>
           <t>48699833.0</t>
         </is>
       </c>
-      <c r="BF11" t="n">
+      <c r="BJ11" t="n">
         <v>59160766.2</v>
       </c>
-      <c r="BG11" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>98382511.1</t>
         </is>
       </c>
-      <c r="BH11" t="n">
+      <c r="BL11" t="n">
         <v>408309837.48</v>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BM11" t="inlineStr">
         <is>
           <t>-39221744</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BN11" t="inlineStr">
         <is>
           <t>-39281516.38784661</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>-52021991.35460995</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>48699833.0</t>
         </is>
       </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
         <is>
           <t>99.0</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BS11" t="inlineStr">
         <is>
           <t>2025/07/18</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
+      <c r="BT11" t="inlineStr">
         <is>
           <t>6.57</t>
         </is>
       </c>
-      <c r="BQ11" t="inlineStr">
+      <c r="BU11" t="inlineStr">
         <is>
           <t>上緯投控</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
+      <c r="BV11" t="inlineStr">
         <is>
           <t>上緯投控</t>
         </is>
       </c>
-      <c r="BS11" t="inlineStr">
+      <c r="BW11" t="inlineStr">
         <is>
           <t>綠能環保</t>
         </is>
       </c>
-      <c r="BT11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
+      <c r="BY11" t="inlineStr">
         <is>
           <t>1.06</t>
         </is>
       </c>
-      <c r="BV11" t="inlineStr">
+      <c r="BZ11" t="inlineStr">
         <is>
           <t>-4.012262137013166</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="CA11" t="inlineStr">
         <is>
           <t>-1.72716244973935</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>4.777195903551031</t>
         </is>
       </c>
-      <c r="BY11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ11" t="inlineStr">
+      <c r="CD11" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CE11" t="inlineStr">
         <is>
           <t>1.18</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CF11" t="inlineStr">
         <is>
           <t>2.21</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
+      <c r="CG11" t="inlineStr">
         <is>
           <t>-29.60</t>
         </is>
       </c>
-      <c r="CD11" t="inlineStr">
+      <c r="CH11" t="inlineStr">
         <is>
           <t>83.46</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CG11" t="inlineStr">
+      <c r="CI11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CJ11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CK11" t="inlineStr">
         <is>
           <t>45.32</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CL11" t="inlineStr">
         <is>
           <t>11371</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CM11" t="inlineStr">
         <is>
           <t>環保耐蝕材料39.58%、環保綠能材料33.76%、其他25.01%、循環經濟材料1.65% (2024年)</t>
         </is>
       </c>
-      <c r="CJ11" t="inlineStr">
+      <c r="CN11" t="inlineStr">
         <is>
           <t>上緯投控-綠能環保-上市</t>
         </is>
       </c>
-      <c r="CK11" t="inlineStr">
+      <c r="CO11" t="inlineStr">
         <is>
           <t>綠能環保平上市</t>
         </is>
       </c>
-      <c r="CL11" t="inlineStr">
+      <c r="CP11" t="inlineStr">
         <is>
           <t>105.5</t>
         </is>
       </c>
-      <c r="CM11" t="inlineStr">
+      <c r="CQ11" t="inlineStr">
         <is>
           <t>107.0</t>
         </is>
       </c>
-      <c r="CN11" t="inlineStr">
+      <c r="CR11" t="inlineStr">
         <is>
           <t>105.0</t>
         </is>
       </c>
-      <c r="CO11" t="inlineStr">
+      <c r="CS11" t="inlineStr">
         <is>
           <t>105.5</t>
         </is>
       </c>
-      <c r="CP11" t="inlineStr">
+      <c r="CT11" t="inlineStr">
         <is>
           <t>89.23</t>
         </is>
       </c>
-      <c r="CQ11" t="inlineStr">
+      <c r="CU11" t="inlineStr">
         <is>
           <t>** 風力發電 - 玻/碳纖、樹酯</t>
         </is>
       </c>
-      <c r="CR11" t="inlineStr">
+      <c r="CV11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5668,325 +5888,345 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
           <t>2025/09/24</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>125.5</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AE12" t="inlineStr">
         <is>
           <t>2025/06/30</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
+      <c r="AF12" t="inlineStr">
         <is>
           <t>70.1</t>
         </is>
       </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
       <c r="AG12" t="inlineStr">
         <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>109.5</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>2025/11/10</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
           <t>2025-12-01</t>
         </is>
       </c>
-      <c r="AH12" t="inlineStr">
+      <c r="AL12" t="inlineStr">
         <is>
           <t>2.12</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
+      <c r="AM12" t="inlineStr">
         <is>
           <t>-2.87</t>
         </is>
       </c>
-      <c r="AJ12" t="inlineStr">
+      <c r="AN12" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="inlineStr">
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
+      <c r="AQ12" t="inlineStr">
         <is>
           <t>770</t>
         </is>
       </c>
-      <c r="AN12" t="inlineStr">
+      <c r="AR12" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO12" t="inlineStr">
+      <c r="AS12" t="inlineStr">
         <is>
           <t>25.32</t>
         </is>
       </c>
-      <c r="AP12" t="n">
+      <c r="AT12" t="n">
         <v>-2.52</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AU12" t="n">
         <v>-6.29</v>
       </c>
-      <c r="AR12" t="inlineStr">
+      <c r="AV12" t="inlineStr">
         <is>
           <t>-3.12</t>
         </is>
       </c>
-      <c r="AS12" t="inlineStr">
+      <c r="AW12" t="inlineStr">
         <is>
           <t>-2.16</t>
         </is>
       </c>
-      <c r="AT12" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>107.2</t>
         </is>
       </c>
-      <c r="AU12" t="n">
+      <c r="AY12" t="n">
         <v>114.4</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="AZ12" t="n">
         <v>118.09</v>
       </c>
-      <c r="AW12" t="inlineStr">
+      <c r="BA12" t="inlineStr">
         <is>
           <t>120.69</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
+      <c r="BB12" t="inlineStr">
         <is>
           <t>-32.21</t>
         </is>
       </c>
-      <c r="AY12" t="n">
+      <c r="BC12" t="n">
         <v>-3.67</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="BD12" t="n">
         <v>-2.78</v>
       </c>
-      <c r="BA12" t="inlineStr">
+      <c r="BE12" t="inlineStr">
         <is>
           <t>10.7</t>
         </is>
       </c>
-      <c r="BB12" t="inlineStr">
+      <c r="BF12" t="inlineStr">
         <is>
           <t>-125.94</t>
         </is>
       </c>
-      <c r="BC12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>2025/12/11</t>
         </is>
       </c>
-      <c r="BD12" t="inlineStr">
+      <c r="BH12" t="inlineStr">
         <is>
           <t>400544610.7247191</t>
         </is>
       </c>
-      <c r="BE12" t="inlineStr">
+      <c r="BI12" t="inlineStr">
         <is>
           <t>73164650.0</t>
         </is>
       </c>
-      <c r="BF12" t="n">
+      <c r="BJ12" t="n">
         <v>66768101.4</v>
       </c>
-      <c r="BG12" t="inlineStr">
+      <c r="BK12" t="inlineStr">
         <is>
           <t>122726255.3</t>
         </is>
       </c>
-      <c r="BH12" t="n">
+      <c r="BL12" t="n">
         <v>411205419.78</v>
       </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BM12" t="inlineStr">
         <is>
           <t>-55958153</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
+      <c r="BN12" t="inlineStr">
         <is>
           <t>-36965066.39388964</t>
         </is>
       </c>
-      <c r="BK12" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>-53136928.16792992</t>
         </is>
       </c>
-      <c r="BL12" t="inlineStr">
+      <c r="BP12" t="inlineStr">
         <is>
           <t>73164650.0</t>
         </is>
       </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
         <is>
           <t>99.0</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
+      <c r="BS12" t="inlineStr">
         <is>
           <t>2025/07/18</t>
         </is>
       </c>
-      <c r="BP12" t="inlineStr">
+      <c r="BT12" t="inlineStr">
         <is>
           <t>5.56</t>
         </is>
       </c>
-      <c r="BQ12" t="inlineStr">
+      <c r="BU12" t="inlineStr">
         <is>
           <t>上緯投控</t>
         </is>
       </c>
-      <c r="BR12" t="inlineStr">
+      <c r="BV12" t="inlineStr">
         <is>
           <t>上緯投控</t>
         </is>
       </c>
-      <c r="BS12" t="inlineStr">
+      <c r="BW12" t="inlineStr">
         <is>
           <t>綠能環保</t>
         </is>
       </c>
-      <c r="BT12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU12" t="inlineStr">
+      <c r="BY12" t="inlineStr">
         <is>
           <t>1.06</t>
         </is>
       </c>
-      <c r="BV12" t="inlineStr">
+      <c r="BZ12" t="inlineStr">
         <is>
           <t>-4.012262137013166</t>
         </is>
       </c>
-      <c r="BW12" t="inlineStr">
+      <c r="CA12" t="inlineStr">
         <is>
           <t>-1.72716244973935</t>
         </is>
       </c>
-      <c r="BX12" t="inlineStr">
+      <c r="CB12" t="inlineStr">
         <is>
           <t>4.777195903551031</t>
         </is>
       </c>
-      <c r="BY12" t="inlineStr">
+      <c r="CC12" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ12" t="inlineStr">
+      <c r="CD12" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CE12" t="inlineStr">
         <is>
           <t>1.17</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
+      <c r="CF12" t="inlineStr">
         <is>
           <t>2.21</t>
         </is>
       </c>
-      <c r="CC12" t="inlineStr">
+      <c r="CG12" t="inlineStr">
         <is>
           <t>-29.60</t>
         </is>
       </c>
-      <c r="CD12" t="inlineStr">
+      <c r="CH12" t="inlineStr">
         <is>
           <t>83.46</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CG12" t="inlineStr">
+      <c r="CI12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CJ12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CK12" t="inlineStr">
         <is>
           <t>45.32</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CL12" t="inlineStr">
         <is>
           <t>11371</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CM12" t="inlineStr">
         <is>
           <t>環保耐蝕材料39.58%、環保綠能材料33.76%、其他25.01%、循環經濟材料1.65% (2024年)</t>
         </is>
       </c>
-      <c r="CJ12" t="inlineStr">
+      <c r="CN12" t="inlineStr">
         <is>
           <t>上緯投控-綠能環保-上市</t>
         </is>
       </c>
-      <c r="CK12" t="inlineStr">
+      <c r="CO12" t="inlineStr">
         <is>
           <t>綠能環保平上市</t>
         </is>
       </c>
-      <c r="CL12" t="inlineStr">
+      <c r="CP12" t="inlineStr">
         <is>
           <t>107.5</t>
         </is>
       </c>
-      <c r="CM12" t="inlineStr">
+      <c r="CQ12" t="inlineStr">
         <is>
           <t>108.0</t>
         </is>
       </c>
-      <c r="CN12" t="inlineStr">
+      <c r="CR12" t="inlineStr">
         <is>
           <t>104.0</t>
         </is>
       </c>
-      <c r="CO12" t="inlineStr">
+      <c r="CS12" t="inlineStr">
         <is>
           <t>104.5</t>
         </is>
       </c>
-      <c r="CP12" t="inlineStr">
+      <c r="CT12" t="inlineStr">
         <is>
           <t>89.23</t>
         </is>
       </c>
-      <c r="CQ12" t="inlineStr">
+      <c r="CU12" t="inlineStr">
         <is>
           <t>** 風力發電 - 玻/碳纖、樹酯</t>
         </is>
       </c>
-      <c r="CR12" t="inlineStr">
+      <c r="CV12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/玻_碳纖.xlsx
+++ b/Result/checksun_type/玻_碳纖.xlsx
@@ -943,12 +943,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>769.691</t>
+          <t>746.762</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-7.83</t>
+          <t>-7.39</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1134,266 +1134,266 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>747</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>63.64</t>
+          <t>72.73</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>63.64</t>
+          <t>54.55</t>
         </is>
       </c>
       <c r="AT2" t="n">
         <v>0.47</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0.8</v>
+        <v>-0.19</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>-7.09</t>
+          <t>-6.92</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
+          <t>106.0</t>
+        </is>
+      </c>
+      <c r="AY2" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>114.09</v>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>118.09</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>17.62</t>
+        </is>
+      </c>
+      <c r="BC2" t="n">
+        <v>-2.68</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>-3.25</v>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>10.7</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>-130.41</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>2025/12/11</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>400150306.371669</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>79603738.0</t>
+        </is>
+      </c>
+      <c r="BJ2" t="n">
+        <v>109418864.2</v>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>104449480.1</t>
+        </is>
+      </c>
+      <c r="BL2" t="n">
+        <v>235214284.48</v>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>4969384</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>-25681388.67739034</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>-15083177.56363492</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>79603738.0</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>2025/07/18</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>7.58</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>上緯投控</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>上緯投控</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>綠能環保</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>1.06</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>-4.012262137013166</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>-1.72716244973935</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>4.777195903551031</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
+          <t>-29.60</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
+          <t>83.86</t>
+        </is>
+      </c>
+      <c r="CI2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CJ2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CK2" t="inlineStr">
+        <is>
+          <t>45.64</t>
+        </is>
+      </c>
+      <c r="CL2" t="inlineStr">
+        <is>
+          <t>11425</t>
+        </is>
+      </c>
+      <c r="CM2" t="inlineStr">
+        <is>
+          <t>環保耐蝕材料39.58%、環保綠能材料33.76%、其他25.01%、循環經濟材料1.65% (2024年)</t>
+        </is>
+      </c>
+      <c r="CN2" t="inlineStr">
+        <is>
+          <t>上緯投控-綠能環保-上市</t>
+        </is>
+      </c>
+      <c r="CO2" t="inlineStr">
+        <is>
+          <t>綠能環保平上市</t>
+        </is>
+      </c>
+      <c r="CP2" t="inlineStr">
+        <is>
           <t>105.5</t>
         </is>
       </c>
-      <c r="AY2" t="n">
-        <v>106.35</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>114.47</v>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>118.3</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>13.31</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>-2.94</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>-3.4</v>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>10.7</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>-131.74</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>2025/12/11</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>400544610.7247191</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>80866650.0</t>
-        </is>
-      </c>
-      <c r="BJ2" t="n">
-        <v>111069295.6</v>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>101359089.6</t>
-        </is>
-      </c>
-      <c r="BL2" t="n">
-        <v>244947022.76</v>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>9710206</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>-27608336.15261859</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>-14685892.25788501</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>80866650.0</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>99.0</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>2025/07/18</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>7.07</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>上緯投控</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>上緯投控</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>綠能環保</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>1.06</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>-4.012262137013166</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
-        <is>
-          <t>-1.72716244973935</t>
-        </is>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>4.777195903551031</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>1.19</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>2.21</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>-29.60</t>
-        </is>
-      </c>
-      <c r="CH2" t="inlineStr">
-        <is>
-          <t>83.46</t>
-        </is>
-      </c>
-      <c r="CI2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CJ2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CK2" t="inlineStr">
-        <is>
-          <t>45.32</t>
-        </is>
-      </c>
-      <c r="CL2" t="inlineStr">
-        <is>
-          <t>11371</t>
-        </is>
-      </c>
-      <c r="CM2" t="inlineStr">
-        <is>
-          <t>環保耐蝕材料39.58%、環保綠能材料33.76%、其他25.01%、循環經濟材料1.65% (2024年)</t>
-        </is>
-      </c>
-      <c r="CN2" t="inlineStr">
-        <is>
-          <t>上緯投控-綠能環保-上市</t>
-        </is>
-      </c>
-      <c r="CO2" t="inlineStr">
-        <is>
-          <t>綠能環保平上市</t>
-        </is>
-      </c>
-      <c r="CP2" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1403.157</t>
+          <t>769.691</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1450,17 +1450,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>10.32</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-9.57</t>
+          <t>-7.83</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,17 +1595,17 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1616,66 +1616,66 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>747</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>63.64</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>60.61</t>
+          <t>63.64</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>-1.05</v>
+        <v>0.47</v>
       </c>
       <c r="AU3" t="n">
-        <v>-1.64</v>
+        <v>-0.8</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>-7.01</t>
+          <t>-7.09</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>105.1</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>106.85</v>
+        <v>106.35</v>
       </c>
       <c r="AZ3" t="n">
-        <v>114.91</v>
+        <v>114.47</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>118.54</t>
+          <t>118.3</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>13.31</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-3.19</v>
+        <v>-2.94</v>
       </c>
       <c r="BD3" t="n">
-        <v>-3.51</v>
+        <v>-3.4</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-132.80</t>
+          <t>-131.74</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,43 +1694,43 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>400544610.7247191</t>
+          <t>400150306.371669</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>147302125.0</t>
+          <t>80866650.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>110969867.4</v>
+        <v>111069295.6</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>100588889.6</t>
+          <t>101359089.6</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>254957469.96</v>
+        <v>244947022.76</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>10380977</t>
+          <t>9710206</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-29957871.40620652</t>
+          <t>-27608336.15261859</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-13729157.66903208</t>
+          <t>-14685892.25788501</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>147302125.0</t>
+          <t>80866650.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>83.46</t>
+          <t>83.86</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>45.32</t>
+          <t>45.64</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>11371</t>
+          <t>11425</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1860,22 +1860,22 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>-3.74</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1572.193</t>
+          <t>1403.157</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1932,17 +1932,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>10.32</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>-9.57</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2077,17 +2077,17 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>4.80</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2098,66 +2098,66 @@
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>747</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>59.21</t>
+          <t>60.61</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>2.96</v>
+        <v>-1.05</v>
       </c>
       <c r="AU4" t="n">
-        <v>-2.55</v>
+        <v>-1.64</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>-7.01</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>104.9</t>
+          <t>105.1</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>107.65</v>
+        <v>106.85</v>
       </c>
       <c r="AZ4" t="n">
-        <v>115.48</v>
+        <v>114.91</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>118.76</t>
+          <t>118.54</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>9.49</t>
+          <t>9.16</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-3.25</v>
+        <v>-3.19</v>
       </c>
       <c r="BD4" t="n">
-        <v>-3.59</v>
+        <v>-3.51</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-133.55</t>
+          <t>-132.80</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -2176,43 +2176,43 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>400544610.7247191</t>
+          <t>400150306.371669</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>168425982.0</t>
+          <t>147302125.0</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>93692000.40000001</v>
+        <v>110969867.4</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>90392167.0</t>
+          <t>100588889.6</t>
         </is>
       </c>
       <c r="BL4" t="n">
-        <v>282867348.74</v>
+        <v>254957469.96</v>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>3299833</t>
+          <t>10380977</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-32908546.63114733</t>
+          <t>-29957871.40620652</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-18990153.51820534</t>
+          <t>-13729157.66903208</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>168425982.0</t>
+          <t>147302125.0</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>83.46</t>
+          <t>83.86</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>45.32</t>
+          <t>45.64</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>11371</t>
+          <t>11425</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2342,22 +2342,22 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2379,7 +2379,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>672.31</t>
+          <t>1572.193</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2414,17 +2414,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>27.60</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2559,17 +2559,17 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>4.80</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2580,66 +2580,66 @@
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>747</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>54.55</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>33.57</t>
+          <t>59.21</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>1.64</v>
+        <v>2.96</v>
       </c>
       <c r="AU5" t="n">
-        <v>-4.46</v>
+        <v>-2.55</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>-6.33</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>103.8</t>
+          <t>104.9</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>108.65</v>
+        <v>107.65</v>
       </c>
       <c r="AZ5" t="n">
-        <v>115.99</v>
+        <v>115.48</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>118.94</t>
+          <t>118.76</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>9.49</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-3.69</v>
+        <v>-3.25</v>
       </c>
       <c r="BD5" t="n">
-        <v>-3.68</v>
+        <v>-3.59</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-134.35</t>
+          <t>-133.55</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -2658,43 +2658,43 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>400544610.7247191</t>
+          <t>400150306.371669</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>70895826.0</t>
+          <t>168425982.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>100748036.2</v>
+        <v>93692000.40000001</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>78953691.6</t>
+          <t>90392167.0</t>
         </is>
       </c>
       <c r="BL5" t="n">
-        <v>316450597.8</v>
+        <v>282867348.74</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>21794344</t>
+          <t>3299833</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-35439163.56077314</t>
+          <t>-32908546.63114733</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-28090912.49851693</t>
+          <t>-18990153.51820534</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>70895826.0</t>
+          <t>168425982.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
@@ -2769,12 +2769,12 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>83.46</t>
+          <t>83.86</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>45.32</t>
+          <t>45.64</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>11371</t>
+          <t>11425</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2824,22 +2824,22 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>843.89</t>
+          <t>672.31</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2896,17 +2896,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>25.42</t>
+          <t>27.60</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-9.57</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3062,66 +3062,66 @@
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>747</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>54.55</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>33.57</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>0.48</v>
+        <v>1.64</v>
       </c>
       <c r="AU6" t="n">
-        <v>-5.69</v>
+        <v>-4.46</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>-5.8</t>
+          <t>-6.33</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>103.8</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>109.75</v>
+        <v>108.65</v>
       </c>
       <c r="AZ6" t="n">
-        <v>116.51</v>
+        <v>115.99</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>119.11</t>
+          <t>118.94</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-7.23</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-3.94</v>
+        <v>-3.69</v>
       </c>
       <c r="BD6" t="n">
-        <v>-3.67</v>
+        <v>-3.68</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-134.32</t>
+          <t>-134.35</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -3140,43 +3140,43 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>400544610.7247191</t>
+          <t>400150306.371669</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>87855895.0</t>
+          <t>70895826.0</t>
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>99480096</v>
+        <v>100748036.2</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>79320431.1</t>
+          <t>78953691.6</t>
         </is>
       </c>
       <c r="BL6" t="n">
-        <v>376415022.36</v>
+        <v>316450597.8</v>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>20159664</t>
+          <t>21794344</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-36775209.20845608</t>
+          <t>-35439163.56077314</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-29639090.30972932</t>
+          <t>-28090912.49851693</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>87855895.0</t>
+          <t>70895826.0</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>83.46</t>
+          <t>83.86</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>45.32</t>
+          <t>45.64</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>11371</t>
+          <t>11425</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>775.327</t>
+          <t>843.89</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3378,17 +3378,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>15.71</t>
+          <t>25.42</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3544,12 +3544,12 @@
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>747</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -3559,51 +3559,51 @@
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>10.26</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>0.19</v>
+        <v>0.48</v>
       </c>
       <c r="AU7" t="n">
-        <v>-5.94</v>
+        <v>-5.69</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.8</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>103.8</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>110.35</v>
+        <v>109.75</v>
       </c>
       <c r="AZ7" t="n">
-        <v>116.94</v>
+        <v>116.51</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>119.31</t>
+          <t>119.11</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-12.25</t>
+          <t>-7.23</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-4.05</v>
+        <v>-3.94</v>
       </c>
       <c r="BD7" t="n">
-        <v>-3.61</v>
+        <v>-3.67</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-133.70</t>
+          <t>-134.32</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -3622,43 +3622,43 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>400544610.7247191</t>
+          <t>400150306.371669</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>80369509.0</t>
+          <t>87855895.0</t>
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>91648883.59999999</v>
+        <v>99480096</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>79208492.5</t>
+          <t>79320431.1</t>
         </is>
       </c>
       <c r="BL7" t="n">
-        <v>400946194.74</v>
+        <v>376415022.36</v>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>12440391</t>
+          <t>20159664</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-38072685.37186095</t>
+          <t>-36775209.20845608</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-32609384.20754242</t>
+          <t>-29639090.30972932</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>80369509.0</t>
+          <t>87855895.0</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>83.46</t>
+          <t>83.86</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>45.32</t>
+          <t>45.64</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>11371</t>
+          <t>11425</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3788,12 +3788,12 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>593.888</t>
+          <t>775.327</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3860,17 +3860,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>15.71</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-10.43</t>
+          <t>-9.57</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -4026,66 +4026,66 @@
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>747</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>10.26</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>-0.87</v>
+        <v>0.19</v>
       </c>
       <c r="AU8" t="n">
-        <v>-6.31</v>
+        <v>-5.94</v>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>-5.34</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>103.9</t>
+          <t>103.8</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>110.9</v>
+        <v>110.35</v>
       </c>
       <c r="AZ8" t="n">
-        <v>117.15</v>
+        <v>116.94</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>119.56</t>
+          <t>119.31</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-18.13</t>
+          <t>-12.25</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-4.13</v>
+        <v>-4.05</v>
       </c>
       <c r="BD8" t="n">
-        <v>-3.5</v>
+        <v>-3.61</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-132.67</t>
+          <t>-133.70</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -4104,43 +4104,43 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>400544610.7247191</t>
+          <t>400150306.371669</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>60912790.0</t>
+          <t>80369509.0</t>
         </is>
       </c>
       <c r="BJ8" t="n">
-        <v>90207911.8</v>
+        <v>91648883.59999999</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>85136383.4</t>
+          <t>79208492.5</t>
         </is>
       </c>
       <c r="BL8" t="n">
-        <v>403373073.88</v>
+        <v>400946194.74</v>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>5071528</t>
+          <t>12440391</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-39066012.8562825</t>
+          <t>-38072685.37186095</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-34885927.55414887</t>
+          <t>-32609384.20754242</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>60912790.0</t>
+          <t>80369509.0</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>83.46</t>
+          <t>83.86</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>45.32</t>
+          <t>45.64</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>11371</t>
+          <t>11425</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
@@ -4270,22 +4270,22 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
+          <t>105.5</t>
+        </is>
+      </c>
+      <c r="CR8" t="inlineStr">
+        <is>
+          <t>102.5</t>
+        </is>
+      </c>
+      <c r="CS8" t="inlineStr">
+        <is>
           <t>104.0</t>
-        </is>
-      </c>
-      <c r="CR8" t="inlineStr">
-        <is>
-          <t>101.0</t>
-        </is>
-      </c>
-      <c r="CS8" t="inlineStr">
-        <is>
-          <t>103.0</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1943.113</t>
+          <t>593.888</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4342,17 +4342,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-8.63</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-10.87</t>
+          <t>-10.43</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4487,17 +4487,17 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>-6.83</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4508,66 +4508,66 @@
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>747</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>-2.29</v>
+        <v>-0.87</v>
       </c>
       <c r="AU9" t="n">
-        <v>-5.9</v>
+        <v>-6.31</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-5.34</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>104.9</t>
+          <t>103.9</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>111.48</v>
+        <v>110.9</v>
       </c>
       <c r="AZ9" t="n">
-        <v>117.45</v>
+        <v>117.15</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>119.82</t>
+          <t>119.56</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-22.00</t>
+          <t>-18.13</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-4.07</v>
+        <v>-4.13</v>
       </c>
       <c r="BD9" t="n">
-        <v>-3.34</v>
+        <v>-3.5</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-131.19</t>
+          <t>-132.67</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -4586,43 +4586,43 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>400544610.7247191</t>
+          <t>400150306.371669</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>203706161.0</t>
+          <t>60912790.0</t>
         </is>
       </c>
       <c r="BJ9" t="n">
-        <v>87092333.59999999</v>
+        <v>90207911.8</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>95316409.3</t>
+          <t>85136383.4</t>
         </is>
       </c>
       <c r="BL9" t="n">
-        <v>406267066.38</v>
+        <v>403373073.88</v>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-8224075</t>
+          <t>5071528</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-39826028.36576135</t>
+          <t>-39066012.8562825</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-34807557.88665277</t>
+          <t>-34885927.55414887</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>203706161.0</t>
+          <t>60912790.0</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4687,12 +4687,12 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>83.46</t>
+          <t>83.86</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>45.32</t>
+          <t>45.64</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>11371</t>
+          <t>11425</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
@@ -4752,22 +4752,22 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>617.222</t>
+          <t>1943.113</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4824,17 +4824,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-33.70</t>
+          <t>-8.63</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-9.57</t>
+          <t>-10.87</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -4969,17 +4969,17 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-6.83</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4990,12 +4990,12 @@
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>747</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -5009,47 +5009,47 @@
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>-2.07</v>
+        <v>-2.29</v>
       </c>
       <c r="AU10" t="n">
-        <v>-5.77</v>
+        <v>-5.9</v>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>106.2</t>
+          <t>104.9</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>112.7</v>
+        <v>111.48</v>
       </c>
       <c r="AZ10" t="n">
-        <v>117.72</v>
+        <v>117.45</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>120.13</t>
+          <t>119.82</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-23.26</t>
+          <t>-22.00</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-3.89</v>
+        <v>-4.07</v>
       </c>
       <c r="BD10" t="n">
-        <v>-3.15</v>
+        <v>-3.34</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-129.47</t>
+          <t>-131.19</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -5068,43 +5068,43 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>400544610.7247191</t>
+          <t>400150306.371669</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>64556125.0</t>
+          <t>203706161.0</t>
         </is>
       </c>
       <c r="BJ10" t="n">
-        <v>57159347</v>
+        <v>87092333.59999999</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>86212815.0</t>
+          <t>95316409.3</t>
         </is>
       </c>
       <c r="BL10" t="n">
-        <v>406636712.2</v>
+        <v>406267066.38</v>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-29053468</t>
+          <t>-8224075</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-40738477.54378109</t>
+          <t>-39826028.36576135</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-48751763.90142073</t>
+          <t>-34807557.88665277</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>64556125.0</t>
+          <t>203706161.0</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
@@ -5179,12 +5179,12 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>83.46</t>
+          <t>83.86</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>45.32</t>
+          <t>45.64</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>11371</t>
+          <t>11425</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5239,17 +5239,17 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>109.5</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>460.69</t>
+          <t>617.222</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5306,17 +5306,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-39.87</t>
+          <t>-33.70</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-9.57</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5451,17 +5451,17 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -5472,66 +5472,66 @@
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>747</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>-1.49</v>
+        <v>-2.07</v>
       </c>
       <c r="AU11" t="n">
-        <v>-5.68</v>
+        <v>-5.77</v>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>107.1</t>
+          <t>106.2</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>113.55</v>
+        <v>112.7</v>
       </c>
       <c r="AZ11" t="n">
-        <v>117.93</v>
+        <v>117.72</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>120.44</t>
+          <t>120.13</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-26.20</t>
+          <t>-23.26</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-3.75</v>
+        <v>-3.89</v>
       </c>
       <c r="BD11" t="n">
-        <v>-2.97</v>
+        <v>-3.15</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-127.76</t>
+          <t>-129.47</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -5550,43 +5550,43 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>400544610.7247191</t>
+          <t>400150306.371669</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>48699833.0</t>
+          <t>64556125.0</t>
         </is>
       </c>
       <c r="BJ11" t="n">
-        <v>59160766.2</v>
+        <v>57159347</v>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>98382511.1</t>
+          <t>86212815.0</t>
         </is>
       </c>
       <c r="BL11" t="n">
-        <v>408309837.48</v>
+        <v>406636712.2</v>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-39221744</t>
+          <t>-29053468</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-39281516.38784661</t>
+          <t>-40738477.54378109</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-52021991.35460995</t>
+          <t>-48751763.90142073</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>48699833.0</t>
+          <t>64556125.0</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5661,12 +5661,12 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>83.46</t>
+          <t>83.86</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>45.32</t>
+          <t>45.64</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>11371</t>
+          <t>11425</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="CP11" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CQ11" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
@@ -5763,12 +5763,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>694.884</t>
+          <t>460.69</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5788,17 +5788,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-45.60</t>
+          <t>-39.87</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-9.13</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5933,17 +5933,17 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5954,66 +5954,66 @@
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>747</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>25.32</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>-2.52</v>
+        <v>-1.49</v>
       </c>
       <c r="AU12" t="n">
-        <v>-6.29</v>
+        <v>-5.68</v>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>107.2</t>
+          <t>107.1</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>114.4</v>
+        <v>113.55</v>
       </c>
       <c r="AZ12" t="n">
-        <v>118.09</v>
+        <v>117.93</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>120.69</t>
+          <t>120.44</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-32.21</t>
+          <t>-26.20</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-3.67</v>
+        <v>-3.75</v>
       </c>
       <c r="BD12" t="n">
-        <v>-2.78</v>
+        <v>-2.97</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>-125.94</t>
+          <t>-127.76</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -6032,43 +6032,43 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>400544610.7247191</t>
+          <t>400150306.371669</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>73164650.0</t>
+          <t>48699833.0</t>
         </is>
       </c>
       <c r="BJ12" t="n">
-        <v>66768101.4</v>
+        <v>59160766.2</v>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>122726255.3</t>
+          <t>98382511.1</t>
         </is>
       </c>
       <c r="BL12" t="n">
-        <v>411205419.78</v>
+        <v>408309837.48</v>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>-55958153</t>
+          <t>-39221744</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-36965066.39388964</t>
+          <t>-39281516.38784661</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-53136928.16792992</t>
+          <t>-52021991.35460995</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>73164650.0</t>
+          <t>48699833.0</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
@@ -6143,12 +6143,12 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>83.46</t>
+          <t>83.86</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>45.32</t>
+          <t>45.64</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>11371</t>
+          <t>11425</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
@@ -6198,22 +6198,22 @@
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">

--- a/Result/checksun_type/玻_碳纖.xlsx
+++ b/Result/checksun_type/玻_碳纖.xlsx
@@ -933,7 +933,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【d2】;【x】看好</t>
+          <t>【d1】;【x】看好</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -943,12 +943,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>746.762</t>
+          <t>1291.85</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>10.06</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-7.39</t>
+          <t>-6.52</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1139,61 +1139,61 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>72.73</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>54.55</t>
+          <t>75.45</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>0.47</v>
+        <v>1.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0.19</v>
+        <v>0.31</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>-6.92</t>
+          <t>-6.7</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>106.4</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>106.2</v>
+        <v>106.08</v>
       </c>
       <c r="AZ2" t="n">
-        <v>114.09</v>
+        <v>113.69</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>118.09</t>
+          <t>117.75</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>17.62</t>
+          <t>23.17</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-2.68</v>
+        <v>-2.36</v>
       </c>
       <c r="BD2" t="n">
-        <v>-3.25</v>
+        <v>-3.08</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-130.41</t>
+          <t>-128.74</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,43 +1212,43 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>400150306.371669</t>
+          <t>399884426.5546218</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>79603738.0</t>
+          <t>140208078.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>109418864.2</v>
+        <v>123281314.6</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>104449480.1</t>
+          <t>112014675.4</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>235214284.48</v>
+        <v>232090955.84</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>4969384</t>
+          <t>11266639</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-25681388.67739034</t>
+          <t>-23336386.16372551</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-15083177.56363492</t>
+          <t>-10438872.33856899</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>79603738.0</t>
+          <t>140208078.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>7.58</t>
+          <t>8.59</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1313,22 +1313,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>83.86</t>
+          <t>84.65</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>45.64</t>
+          <t>45.54</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>11425</t>
+          <t>11532</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1378,22 +1378,22 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>111.0</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>769.691</t>
+          <t>746.762</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1450,17 +1450,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-7.83</t>
+          <t>-7.39</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,17 +1595,17 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1621,261 +1621,261 @@
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>63.64</t>
+          <t>72.73</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>63.64</t>
+          <t>54.55</t>
         </is>
       </c>
       <c r="AT3" t="n">
         <v>0.47</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.8</v>
+        <v>-0.19</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>-7.09</t>
+          <t>-6.92</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
+          <t>106.0</t>
+        </is>
+      </c>
+      <c r="AY3" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>114.09</v>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>118.09</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>17.62</t>
+        </is>
+      </c>
+      <c r="BC3" t="n">
+        <v>-2.68</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>-3.25</v>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>10.7</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>-130.41</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>2025/12/11</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>399884426.5546218</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>79603738.0</t>
+        </is>
+      </c>
+      <c r="BJ3" t="n">
+        <v>109418864.2</v>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>104449480.1</t>
+        </is>
+      </c>
+      <c r="BL3" t="n">
+        <v>235214284.48</v>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>4969384</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>-25681388.67739034</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>-15083177.56363492</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>79603738.0</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>2025/07/18</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>7.58</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>上緯投控</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>上緯投控</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>綠能環保</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>1.06</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>-4.012262137013166</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>-1.72716244973935</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>4.777195903551031</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
+          <t>-29.60</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
+          <t>84.65</t>
+        </is>
+      </c>
+      <c r="CI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CJ3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CK3" t="inlineStr">
+        <is>
+          <t>45.54</t>
+        </is>
+      </c>
+      <c r="CL3" t="inlineStr">
+        <is>
+          <t>11532</t>
+        </is>
+      </c>
+      <c r="CM3" t="inlineStr">
+        <is>
+          <t>環保耐蝕材料39.58%、環保綠能材料33.76%、其他25.01%、循環經濟材料1.65% (2024年)</t>
+        </is>
+      </c>
+      <c r="CN3" t="inlineStr">
+        <is>
+          <t>上緯投控-綠能環保-上市</t>
+        </is>
+      </c>
+      <c r="CO3" t="inlineStr">
+        <is>
+          <t>綠能環保平上市</t>
+        </is>
+      </c>
+      <c r="CP3" t="inlineStr">
+        <is>
           <t>105.5</t>
         </is>
       </c>
-      <c r="AY3" t="n">
-        <v>106.35</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>114.47</v>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>118.3</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>13.31</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
-        <v>-2.94</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>-3.4</v>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>10.7</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>-131.74</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>2025/12/11</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>400150306.371669</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>80866650.0</t>
-        </is>
-      </c>
-      <c r="BJ3" t="n">
-        <v>111069295.6</v>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>101359089.6</t>
-        </is>
-      </c>
-      <c r="BL3" t="n">
-        <v>244947022.76</v>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>9710206</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>-27608336.15261859</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>-14685892.25788501</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>80866650.0</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>99.0</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>2025/07/18</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>7.07</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>上緯投控</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>上緯投控</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>綠能環保</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>1.06</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>-4.012262137013166</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr">
-        <is>
-          <t>-1.72716244973935</t>
-        </is>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>4.777195903551031</t>
-        </is>
-      </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>1.19</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>2.2</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>-29.60</t>
-        </is>
-      </c>
-      <c r="CH3" t="inlineStr">
-        <is>
-          <t>83.86</t>
-        </is>
-      </c>
-      <c r="CI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CJ3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CK3" t="inlineStr">
-        <is>
-          <t>45.64</t>
-        </is>
-      </c>
-      <c r="CL3" t="inlineStr">
-        <is>
-          <t>11425</t>
-        </is>
-      </c>
-      <c r="CM3" t="inlineStr">
-        <is>
-          <t>環保耐蝕材料39.58%、環保綠能材料33.76%、其他25.01%、循環經濟材料1.65% (2024年)</t>
-        </is>
-      </c>
-      <c r="CN3" t="inlineStr">
-        <is>
-          <t>上緯投控-綠能環保-上市</t>
-        </is>
-      </c>
-      <c r="CO3" t="inlineStr">
-        <is>
-          <t>綠能環保平上市</t>
-        </is>
-      </c>
-      <c r="CP3" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1403.157</t>
+          <t>769.691</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1932,162 +1932,162 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-0.7</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>9.58</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-10-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-11-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-09-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>124.5</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>131.5</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>116.0</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>-7.83</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>7.33</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025/05/22</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2025/09/24</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>125.5</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>2025/06/30</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>70.1</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>2025/11/18</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>109.5</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>2025/11/10</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>115.0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
           <t>2.35</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-1.93</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>10.32</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-10-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-11-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-09-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>124.5</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>115.0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>131.5</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>116.0</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>-9.57</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>7.33</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2025/05/22</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>82.0</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2025/09/24</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>125.5</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>2025/06/30</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>70.1</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>2025/11/18</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>109.5</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>2025/11/10</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>115.0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>4.28</t>
-        </is>
-      </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2103,61 +2103,61 @@
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>63.64</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>60.61</t>
+          <t>63.64</t>
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>-1.05</v>
+        <v>0.47</v>
       </c>
       <c r="AU4" t="n">
-        <v>-1.64</v>
+        <v>-0.8</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>-7.01</t>
+          <t>-7.09</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>105.1</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="AY4" t="n">
-        <v>106.85</v>
+        <v>106.35</v>
       </c>
       <c r="AZ4" t="n">
-        <v>114.91</v>
+        <v>114.47</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>118.54</t>
+          <t>118.3</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>13.31</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-3.19</v>
+        <v>-2.94</v>
       </c>
       <c r="BD4" t="n">
-        <v>-3.51</v>
+        <v>-3.4</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-132.80</t>
+          <t>-131.74</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -2176,43 +2176,43 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>400150306.371669</t>
+          <t>399884426.5546218</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>147302125.0</t>
+          <t>80866650.0</t>
         </is>
       </c>
       <c r="BJ4" t="n">
-        <v>110969867.4</v>
+        <v>111069295.6</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>100588889.6</t>
+          <t>101359089.6</t>
         </is>
       </c>
       <c r="BL4" t="n">
-        <v>254957469.96</v>
+        <v>244947022.76</v>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>10380977</t>
+          <t>9710206</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-29957871.40620652</t>
+          <t>-27608336.15261859</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-13729157.66903208</t>
+          <t>-14685892.25788501</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>147302125.0</t>
+          <t>80866650.0</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>83.86</t>
+          <t>84.65</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>45.64</t>
+          <t>45.54</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>11425</t>
+          <t>11532</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2342,22 +2342,22 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>-3.74</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1572.193</t>
+          <t>1403.157</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2414,17 +2414,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>10.32</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>-9.57</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2559,17 +2559,17 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>4.80</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2585,61 +2585,61 @@
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>59.21</t>
+          <t>60.61</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>2.96</v>
+        <v>-1.05</v>
       </c>
       <c r="AU5" t="n">
-        <v>-2.55</v>
+        <v>-1.64</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>-7.01</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>104.9</t>
+          <t>105.1</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>107.65</v>
+        <v>106.85</v>
       </c>
       <c r="AZ5" t="n">
-        <v>115.48</v>
+        <v>114.91</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>118.76</t>
+          <t>118.54</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>9.49</t>
+          <t>9.16</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-3.25</v>
+        <v>-3.19</v>
       </c>
       <c r="BD5" t="n">
-        <v>-3.59</v>
+        <v>-3.51</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-133.55</t>
+          <t>-132.80</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -2658,43 +2658,43 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>400150306.371669</t>
+          <t>399884426.5546218</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>168425982.0</t>
+          <t>147302125.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>93692000.40000001</v>
+        <v>110969867.4</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>90392167.0</t>
+          <t>100588889.6</t>
         </is>
       </c>
       <c r="BL5" t="n">
-        <v>282867348.74</v>
+        <v>254957469.96</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>3299833</t>
+          <t>10380977</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-32908546.63114733</t>
+          <t>-29957871.40620652</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-18990153.51820534</t>
+          <t>-13729157.66903208</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>168425982.0</t>
+          <t>147302125.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
@@ -2769,12 +2769,12 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>83.86</t>
+          <t>84.65</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>45.64</t>
+          <t>45.54</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>11425</t>
+          <t>11532</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2824,22 +2824,22 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2861,7 +2861,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>672.31</t>
+          <t>1572.193</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2896,17 +2896,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>27.60</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>4.80</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3067,61 +3067,61 @@
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>54.55</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>33.57</t>
+          <t>59.21</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>1.64</v>
+        <v>2.96</v>
       </c>
       <c r="AU6" t="n">
-        <v>-4.46</v>
+        <v>-2.55</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>-6.33</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>103.8</t>
+          <t>104.9</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>108.65</v>
+        <v>107.65</v>
       </c>
       <c r="AZ6" t="n">
-        <v>115.99</v>
+        <v>115.48</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>118.94</t>
+          <t>118.76</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>9.49</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-3.69</v>
+        <v>-3.25</v>
       </c>
       <c r="BD6" t="n">
-        <v>-3.68</v>
+        <v>-3.59</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-134.35</t>
+          <t>-133.55</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -3140,43 +3140,43 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>400150306.371669</t>
+          <t>399884426.5546218</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>70895826.0</t>
+          <t>168425982.0</t>
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>100748036.2</v>
+        <v>93692000.40000001</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>78953691.6</t>
+          <t>90392167.0</t>
         </is>
       </c>
       <c r="BL6" t="n">
-        <v>316450597.8</v>
+        <v>282867348.74</v>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>21794344</t>
+          <t>3299833</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-35439163.56077314</t>
+          <t>-32908546.63114733</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-28090912.49851693</t>
+          <t>-18990153.51820534</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>70895826.0</t>
+          <t>168425982.0</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>83.86</t>
+          <t>84.65</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>45.64</t>
+          <t>45.54</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>11425</t>
+          <t>11532</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>843.89</t>
+          <t>672.31</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3378,17 +3378,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>25.42</t>
+          <t>27.60</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-9.57</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3549,61 +3549,61 @@
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>54.55</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>33.57</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>0.48</v>
+        <v>1.64</v>
       </c>
       <c r="AU7" t="n">
-        <v>-5.69</v>
+        <v>-4.46</v>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>-5.8</t>
+          <t>-6.33</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>103.8</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>109.75</v>
+        <v>108.65</v>
       </c>
       <c r="AZ7" t="n">
-        <v>116.51</v>
+        <v>115.99</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>119.11</t>
+          <t>118.94</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-7.23</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-3.94</v>
+        <v>-3.69</v>
       </c>
       <c r="BD7" t="n">
-        <v>-3.67</v>
+        <v>-3.68</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-134.32</t>
+          <t>-134.35</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -3622,43 +3622,43 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>400150306.371669</t>
+          <t>399884426.5546218</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>87855895.0</t>
+          <t>70895826.0</t>
         </is>
       </c>
       <c r="BJ7" t="n">
-        <v>99480096</v>
+        <v>100748036.2</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>79320431.1</t>
+          <t>78953691.6</t>
         </is>
       </c>
       <c r="BL7" t="n">
-        <v>376415022.36</v>
+        <v>316450597.8</v>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>20159664</t>
+          <t>21794344</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-36775209.20845608</t>
+          <t>-35439163.56077314</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-29639090.30972932</t>
+          <t>-28090912.49851693</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>87855895.0</t>
+          <t>70895826.0</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
@@ -3733,12 +3733,12 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>83.86</t>
+          <t>84.65</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>45.64</t>
+          <t>45.54</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>11425</t>
+          <t>11532</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
@@ -3788,22 +3788,22 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>775.327</t>
+          <t>843.89</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3860,17 +3860,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>15.71</t>
+          <t>25.42</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -4041,51 +4041,51 @@
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>10.26</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>0.19</v>
+        <v>0.48</v>
       </c>
       <c r="AU8" t="n">
-        <v>-5.94</v>
+        <v>-5.69</v>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.8</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>103.8</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>110.35</v>
+        <v>109.75</v>
       </c>
       <c r="AZ8" t="n">
-        <v>116.94</v>
+        <v>116.51</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>119.31</t>
+          <t>119.11</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-12.25</t>
+          <t>-7.23</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-4.05</v>
+        <v>-3.94</v>
       </c>
       <c r="BD8" t="n">
-        <v>-3.61</v>
+        <v>-3.67</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-133.70</t>
+          <t>-134.32</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -4104,43 +4104,43 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>400150306.371669</t>
+          <t>399884426.5546218</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>80369509.0</t>
+          <t>87855895.0</t>
         </is>
       </c>
       <c r="BJ8" t="n">
-        <v>91648883.59999999</v>
+        <v>99480096</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>79208492.5</t>
+          <t>79320431.1</t>
         </is>
       </c>
       <c r="BL8" t="n">
-        <v>400946194.74</v>
+        <v>376415022.36</v>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>12440391</t>
+          <t>20159664</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-38072685.37186095</t>
+          <t>-36775209.20845608</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-32609384.20754242</t>
+          <t>-29639090.30972932</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>80369509.0</t>
+          <t>87855895.0</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
@@ -4220,7 +4220,7 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>83.86</t>
+          <t>84.65</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>45.64</t>
+          <t>45.54</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>11425</t>
+          <t>11532</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>593.888</t>
+          <t>775.327</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4342,17 +4342,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>15.71</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-10.43</t>
+          <t>-9.57</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4487,17 +4487,17 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -4513,61 +4513,61 @@
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>10.26</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>-0.87</v>
+        <v>0.19</v>
       </c>
       <c r="AU9" t="n">
-        <v>-6.31</v>
+        <v>-5.94</v>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>-5.34</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>103.9</t>
+          <t>103.8</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>110.9</v>
+        <v>110.35</v>
       </c>
       <c r="AZ9" t="n">
-        <v>117.15</v>
+        <v>116.94</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>119.56</t>
+          <t>119.31</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-18.13</t>
+          <t>-12.25</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-4.13</v>
+        <v>-4.05</v>
       </c>
       <c r="BD9" t="n">
-        <v>-3.5</v>
+        <v>-3.61</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-132.67</t>
+          <t>-133.70</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -4586,43 +4586,43 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>400150306.371669</t>
+          <t>399884426.5546218</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>60912790.0</t>
+          <t>80369509.0</t>
         </is>
       </c>
       <c r="BJ9" t="n">
-        <v>90207911.8</v>
+        <v>91648883.59999999</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>85136383.4</t>
+          <t>79208492.5</t>
         </is>
       </c>
       <c r="BL9" t="n">
-        <v>403373073.88</v>
+        <v>400946194.74</v>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>5071528</t>
+          <t>12440391</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-39066012.8562825</t>
+          <t>-38072685.37186095</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-34885927.55414887</t>
+          <t>-32609384.20754242</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>60912790.0</t>
+          <t>80369509.0</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>83.86</t>
+          <t>84.65</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>45.64</t>
+          <t>45.54</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>11425</t>
+          <t>11532</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
@@ -4752,22 +4752,22 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
+          <t>105.5</t>
+        </is>
+      </c>
+      <c r="CR9" t="inlineStr">
+        <is>
+          <t>102.5</t>
+        </is>
+      </c>
+      <c r="CS9" t="inlineStr">
+        <is>
           <t>104.0</t>
-        </is>
-      </c>
-      <c r="CR9" t="inlineStr">
-        <is>
-          <t>101.0</t>
-        </is>
-      </c>
-      <c r="CS9" t="inlineStr">
-        <is>
-          <t>103.0</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1943.113</t>
+          <t>593.888</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4824,17 +4824,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-8.63</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-10.87</t>
+          <t>-10.43</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -4969,17 +4969,17 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>-6.83</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -4995,61 +4995,61 @@
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>-2.29</v>
+        <v>-0.87</v>
       </c>
       <c r="AU10" t="n">
-        <v>-5.9</v>
+        <v>-6.31</v>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>-5.09</t>
+          <t>-5.34</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>104.9</t>
+          <t>103.9</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>111.48</v>
+        <v>110.9</v>
       </c>
       <c r="AZ10" t="n">
-        <v>117.45</v>
+        <v>117.15</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>119.82</t>
+          <t>119.56</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-22.00</t>
+          <t>-18.13</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-4.07</v>
+        <v>-4.13</v>
       </c>
       <c r="BD10" t="n">
-        <v>-3.34</v>
+        <v>-3.5</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-131.19</t>
+          <t>-132.67</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
@@ -5068,43 +5068,43 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>400150306.371669</t>
+          <t>399884426.5546218</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>203706161.0</t>
+          <t>60912790.0</t>
         </is>
       </c>
       <c r="BJ10" t="n">
-        <v>87092333.59999999</v>
+        <v>90207911.8</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>95316409.3</t>
+          <t>85136383.4</t>
         </is>
       </c>
       <c r="BL10" t="n">
-        <v>406267066.38</v>
+        <v>403373073.88</v>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-8224075</t>
+          <t>5071528</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-39826028.36576135</t>
+          <t>-39066012.8562825</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-34807557.88665277</t>
+          <t>-34885927.55414887</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>203706161.0</t>
+          <t>60912790.0</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
@@ -5184,7 +5184,7 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>83.86</t>
+          <t>84.65</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>45.64</t>
+          <t>45.54</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>11425</t>
+          <t>11532</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5234,22 +5234,22 @@
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>109.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>617.222</t>
+          <t>1943.113</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5306,17 +5306,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-33.70</t>
+          <t>-8.63</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-9.57</t>
+          <t>-10.87</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5451,17 +5451,17 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-6.83</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -5491,47 +5491,47 @@
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>-2.07</v>
+        <v>-2.29</v>
       </c>
       <c r="AU11" t="n">
-        <v>-5.77</v>
+        <v>-5.9</v>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-5.09</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>106.2</t>
+          <t>104.9</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>112.7</v>
+        <v>111.48</v>
       </c>
       <c r="AZ11" t="n">
-        <v>117.72</v>
+        <v>117.45</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>120.13</t>
+          <t>119.82</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-23.26</t>
+          <t>-22.00</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-3.89</v>
+        <v>-4.07</v>
       </c>
       <c r="BD11" t="n">
-        <v>-3.15</v>
+        <v>-3.34</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-129.47</t>
+          <t>-131.19</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -5550,43 +5550,43 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>400150306.371669</t>
+          <t>399884426.5546218</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>64556125.0</t>
+          <t>203706161.0</t>
         </is>
       </c>
       <c r="BJ11" t="n">
-        <v>57159347</v>
+        <v>87092333.59999999</v>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>86212815.0</t>
+          <t>95316409.3</t>
         </is>
       </c>
       <c r="BL11" t="n">
-        <v>406636712.2</v>
+        <v>406267066.38</v>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-29053468</t>
+          <t>-8224075</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-40738477.54378109</t>
+          <t>-39826028.36576135</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-48751763.90142073</t>
+          <t>-34807557.88665277</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>64556125.0</t>
+          <t>203706161.0</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
@@ -5661,12 +5661,12 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>83.86</t>
+          <t>84.65</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>45.64</t>
+          <t>45.54</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>11425</t>
+          <t>11532</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
@@ -5721,17 +5721,17 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>109.5</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>102.5</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
@@ -5763,12 +5763,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>460.69</t>
+          <t>617.222</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5788,17 +5788,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-39.87</t>
+          <t>-33.70</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-9.57</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5933,17 +5933,17 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -5959,61 +5959,61 @@
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>-1.49</v>
+        <v>-2.07</v>
       </c>
       <c r="AU12" t="n">
-        <v>-5.68</v>
+        <v>-5.77</v>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>107.1</t>
+          <t>106.2</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>113.55</v>
+        <v>112.7</v>
       </c>
       <c r="AZ12" t="n">
-        <v>117.93</v>
+        <v>117.72</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>120.44</t>
+          <t>120.13</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-26.20</t>
+          <t>-23.26</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-3.75</v>
+        <v>-3.89</v>
       </c>
       <c r="BD12" t="n">
-        <v>-2.97</v>
+        <v>-3.15</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>-127.76</t>
+          <t>-129.47</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -6032,43 +6032,43 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>400150306.371669</t>
+          <t>399884426.5546218</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>48699833.0</t>
+          <t>64556125.0</t>
         </is>
       </c>
       <c r="BJ12" t="n">
-        <v>59160766.2</v>
+        <v>57159347</v>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>98382511.1</t>
+          <t>86212815.0</t>
         </is>
       </c>
       <c r="BL12" t="n">
-        <v>408309837.48</v>
+        <v>406636712.2</v>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>-39221744</t>
+          <t>-29053468</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-39281516.38784661</t>
+          <t>-40738477.54378109</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-52021991.35460995</t>
+          <t>-48751763.90142073</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>48699833.0</t>
+          <t>64556125.0</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>6.57</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
@@ -6143,12 +6143,12 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>83.86</t>
+          <t>84.65</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>45.64</t>
+          <t>45.54</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>11425</t>
+          <t>11532</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
@@ -6208,12 +6208,12 @@
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">

--- a/Result/checksun_type/玻_碳纖.xlsx
+++ b/Result/checksun_type/玻_碳纖.xlsx
@@ -943,12 +943,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1291.85</t>
+          <t>641.051</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10.06</t>
+          <t>4.80</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-6.52</t>
+          <t>-8.26</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1134,66 +1134,66 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>641</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>75.45</t>
+          <t>66.74</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>-0.38</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.31</v>
+        <v>0.24</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>-6.7</t>
+          <t>-6.66</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>106.4</t>
+          <t>105.9</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>106.08</v>
+        <v>105.65</v>
       </c>
       <c r="AZ2" t="n">
-        <v>113.69</v>
+        <v>113.19</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>117.75</t>
+          <t>117.21</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>23.17</t>
+          <t>22.78</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-2.36</v>
+        <v>-2.25</v>
       </c>
       <c r="BD2" t="n">
-        <v>-3.08</v>
+        <v>-2.91</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-128.74</t>
+          <t>-127.19</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,43 +1212,43 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>399884426.5546218</t>
+          <t>399467116.693007</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>140208078.0</t>
+          <t>67671917.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>123281314.6</v>
+        <v>103130501.6</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>112014675.4</t>
+          <t>98411251.0</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>232090955.84</v>
+        <v>227121320.92</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>11266639</t>
+          <t>4719250</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-23336386.16372551</t>
+          <t>-21648803.51508445</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-10438872.33856899</t>
+          <t>-12367098.9475586</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>140208078.0</t>
+          <t>67671917.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>8.59</t>
+          <t>6.57</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1313,22 +1313,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>84.65</t>
+          <t>83.07</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>45.54</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>11532</t>
+          <t>11318</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1378,22 +1378,22 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1415,7 +1415,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>746.762</t>
+          <t>1291.85</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1450,17 +1450,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>10.06</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-7.39</t>
+          <t>-6.52</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1595,17 +1595,17 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -1616,66 +1616,66 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>641</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>72.73</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>54.55</t>
+          <t>75.45</t>
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>0.47</v>
+        <v>1.03</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.19</v>
+        <v>0.31</v>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>-6.92</t>
+          <t>-6.7</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-3.39</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>106.4</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>106.2</v>
+        <v>106.08</v>
       </c>
       <c r="AZ3" t="n">
-        <v>114.09</v>
+        <v>113.69</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>118.09</t>
+          <t>117.75</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>17.62</t>
+          <t>23.17</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-2.68</v>
+        <v>-2.36</v>
       </c>
       <c r="BD3" t="n">
-        <v>-3.25</v>
+        <v>-3.08</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-130.41</t>
+          <t>-128.74</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
@@ -1694,43 +1694,43 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>399884426.5546218</t>
+          <t>399467116.693007</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>79603738.0</t>
+          <t>140208078.0</t>
         </is>
       </c>
       <c r="BJ3" t="n">
-        <v>109418864.2</v>
+        <v>123281314.6</v>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>104449480.1</t>
+          <t>112014675.4</t>
         </is>
       </c>
       <c r="BL3" t="n">
-        <v>235214284.48</v>
+        <v>232090955.84</v>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>4969384</t>
+          <t>11266639</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-25681388.67739034</t>
+          <t>-23336386.16372551</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-15083177.56363492</t>
+          <t>-10438872.33856899</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>79603738.0</t>
+          <t>140208078.0</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>7.58</t>
+          <t>8.59</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1795,22 +1795,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>84.65</t>
+          <t>83.07</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>45.54</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>11532</t>
+          <t>11318</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
@@ -1860,22 +1860,22 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>111.0</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>769.691</t>
+          <t>746.762</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1932,17 +1932,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-7.83</t>
+          <t>-7.39</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2077,17 +2077,17 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -2098,266 +2098,266 @@
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>641</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>63.64</t>
+          <t>72.73</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>63.64</t>
+          <t>54.55</t>
         </is>
       </c>
       <c r="AT4" t="n">
         <v>0.47</v>
       </c>
       <c r="AU4" t="n">
-        <v>-0.8</v>
+        <v>-0.19</v>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>-7.09</t>
+          <t>-6.92</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
+          <t>106.0</t>
+        </is>
+      </c>
+      <c r="AY4" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>114.09</v>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>118.09</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>17.62</t>
+        </is>
+      </c>
+      <c r="BC4" t="n">
+        <v>-2.68</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>-3.25</v>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>10.7</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>-130.41</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>2025/12/11</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>399467116.693007</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>79603738.0</t>
+        </is>
+      </c>
+      <c r="BJ4" t="n">
+        <v>109418864.2</v>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>104449480.1</t>
+        </is>
+      </c>
+      <c r="BL4" t="n">
+        <v>235214284.48</v>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>4969384</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>-25681388.67739034</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>-15083177.56363492</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>79603738.0</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>2025/07/18</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>7.58</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>上緯投控</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>上緯投控</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>綠能環保</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>1.06</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>-4.012262137013166</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>-1.72716244973935</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>4.777195903551031</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
+          <t>-29.60</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
+          <t>83.07</t>
+        </is>
+      </c>
+      <c r="CI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CJ4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CK4" t="inlineStr">
+        <is>
+          <t>45.05</t>
+        </is>
+      </c>
+      <c r="CL4" t="inlineStr">
+        <is>
+          <t>11318</t>
+        </is>
+      </c>
+      <c r="CM4" t="inlineStr">
+        <is>
+          <t>環保耐蝕材料39.58%、環保綠能材料33.76%、其他25.01%、循環經濟材料1.65% (2024年)</t>
+        </is>
+      </c>
+      <c r="CN4" t="inlineStr">
+        <is>
+          <t>上緯投控-綠能環保-上市</t>
+        </is>
+      </c>
+      <c r="CO4" t="inlineStr">
+        <is>
+          <t>綠能環保平上市</t>
+        </is>
+      </c>
+      <c r="CP4" t="inlineStr">
+        <is>
           <t>105.5</t>
         </is>
       </c>
-      <c r="AY4" t="n">
-        <v>106.35</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>114.47</v>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>118.3</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>13.31</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
-        <v>-2.94</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>-3.4</v>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>10.7</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>-131.74</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>2025/12/11</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>399884426.5546218</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>80866650.0</t>
-        </is>
-      </c>
-      <c r="BJ4" t="n">
-        <v>111069295.6</v>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>101359089.6</t>
-        </is>
-      </c>
-      <c r="BL4" t="n">
-        <v>244947022.76</v>
-      </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>9710206</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
-        <is>
-          <t>-27608336.15261859</t>
-        </is>
-      </c>
-      <c r="BO4" t="inlineStr">
-        <is>
-          <t>-14685892.25788501</t>
-        </is>
-      </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>80866650.0</t>
-        </is>
-      </c>
-      <c r="BQ4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>99.0</t>
-        </is>
-      </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>2025/07/18</t>
-        </is>
-      </c>
-      <c r="BT4" t="inlineStr">
-        <is>
-          <t>7.07</t>
-        </is>
-      </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>上緯投控</t>
-        </is>
-      </c>
-      <c r="BV4" t="inlineStr">
-        <is>
-          <t>上緯投控</t>
-        </is>
-      </c>
-      <c r="BW4" t="inlineStr">
-        <is>
-          <t>綠能環保</t>
-        </is>
-      </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BY4" t="inlineStr">
-        <is>
-          <t>1.06</t>
-        </is>
-      </c>
-      <c r="BZ4" t="inlineStr">
-        <is>
-          <t>-4.012262137013166</t>
-        </is>
-      </c>
-      <c r="CA4" t="inlineStr">
-        <is>
-          <t>-1.72716244973935</t>
-        </is>
-      </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>4.777195903551031</t>
-        </is>
-      </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CD4" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>1.19</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>2.18</t>
-        </is>
-      </c>
-      <c r="CG4" t="inlineStr">
-        <is>
-          <t>-29.60</t>
-        </is>
-      </c>
-      <c r="CH4" t="inlineStr">
-        <is>
-          <t>84.65</t>
-        </is>
-      </c>
-      <c r="CI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CJ4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CK4" t="inlineStr">
-        <is>
-          <t>45.54</t>
-        </is>
-      </c>
-      <c r="CL4" t="inlineStr">
-        <is>
-          <t>11532</t>
-        </is>
-      </c>
-      <c r="CM4" t="inlineStr">
-        <is>
-          <t>環保耐蝕材料39.58%、環保綠能材料33.76%、其他25.01%、循環經濟材料1.65% (2024年)</t>
-        </is>
-      </c>
-      <c r="CN4" t="inlineStr">
-        <is>
-          <t>上緯投控-綠能環保-上市</t>
-        </is>
-      </c>
-      <c r="CO4" t="inlineStr">
-        <is>
-          <t>綠能環保平上市</t>
-        </is>
-      </c>
-      <c r="CP4" t="inlineStr">
-        <is>
-          <t>103.0</t>
-        </is>
-      </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1403.157</t>
+          <t>769.691</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2414,17 +2414,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>10.32</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-9.57</t>
+          <t>-7.83</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2559,17 +2559,17 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -2580,66 +2580,66 @@
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>641</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>63.64</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>60.61</t>
+          <t>63.64</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>-1.05</v>
+        <v>0.47</v>
       </c>
       <c r="AU5" t="n">
-        <v>-1.64</v>
+        <v>-0.8</v>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>-7.01</t>
+          <t>-7.09</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>105.1</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>106.85</v>
+        <v>106.35</v>
       </c>
       <c r="AZ5" t="n">
-        <v>114.91</v>
+        <v>114.47</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>118.54</t>
+          <t>118.3</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>13.31</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-3.19</v>
+        <v>-2.94</v>
       </c>
       <c r="BD5" t="n">
-        <v>-3.51</v>
+        <v>-3.4</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-132.80</t>
+          <t>-131.74</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -2658,43 +2658,43 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>399884426.5546218</t>
+          <t>399467116.693007</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>147302125.0</t>
+          <t>80866650.0</t>
         </is>
       </c>
       <c r="BJ5" t="n">
-        <v>110969867.4</v>
+        <v>111069295.6</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>100588889.6</t>
+          <t>101359089.6</t>
         </is>
       </c>
       <c r="BL5" t="n">
-        <v>254957469.96</v>
+        <v>244947022.76</v>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>10380977</t>
+          <t>9710206</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-29957871.40620652</t>
+          <t>-27608336.15261859</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-13729157.66903208</t>
+          <t>-14685892.25788501</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>147302125.0</t>
+          <t>80866650.0</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
@@ -2769,12 +2769,12 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>84.65</t>
+          <t>83.07</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2799,12 +2799,12 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>45.54</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>11532</t>
+          <t>11318</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
@@ -2824,22 +2824,22 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2871,12 +2871,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>-3.74</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1572.193</t>
+          <t>1403.157</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2896,17 +2896,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>10.32</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>-9.57</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>4.80</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -3062,66 +3062,66 @@
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>641</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>59.21</t>
+          <t>60.61</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>2.96</v>
+        <v>-1.05</v>
       </c>
       <c r="AU6" t="n">
-        <v>-2.55</v>
+        <v>-1.64</v>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>-7.01</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>104.9</t>
+          <t>105.1</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>107.65</v>
+        <v>106.85</v>
       </c>
       <c r="AZ6" t="n">
-        <v>115.48</v>
+        <v>114.91</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>118.76</t>
+          <t>118.54</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>9.49</t>
+          <t>9.16</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-3.25</v>
+        <v>-3.19</v>
       </c>
       <c r="BD6" t="n">
-        <v>-3.59</v>
+        <v>-3.51</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-133.55</t>
+          <t>-132.80</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -3140,43 +3140,43 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>399884426.5546218</t>
+          <t>399467116.693007</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>168425982.0</t>
+          <t>147302125.0</t>
         </is>
       </c>
       <c r="BJ6" t="n">
-        <v>93692000.40000001</v>
+        <v>110969867.4</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>90392167.0</t>
+          <t>100588889.6</t>
         </is>
       </c>
       <c r="BL6" t="n">
-        <v>282867348.74</v>
+        <v>254957469.96</v>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>3299833</t>
+          <t>10380977</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-32908546.63114733</t>
+          <t>-29957871.40620652</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-18990153.51820534</t>
+          <t>-13729157.66903208</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>168425982.0</t>
+          <t>147302125.0</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>84.65</t>
+          <t>83.07</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>45.54</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>11532</t>
+          <t>11318</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
@@ -3306,22 +3306,22 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
@@ -3343,7 +3343,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>672.31</t>
+          <t>1572.193</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3378,17 +3378,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>27.60</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-6.09</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>4.80</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -3544,66 +3544,66 @@
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>641</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>54.55</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>33.57</t>
+          <t>59.21</t>
         </is>
